--- a/articles_presse.xlsx
+++ b/articles_presse.xlsx
@@ -14,7 +14,7 @@
     <sheet name="_donnees_graphiques" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ARTICLES'!$A$1:$G$837</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ARTICLES'!$A$1:$G$1052</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -408,12 +408,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$58</f>
+              <f>'_donnees_graphiques'!$A$3:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$B$3:$B$58</f>
+              <f>'_donnees_graphiques'!$B$3:$B$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -444,12 +444,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$58</f>
+              <f>'_donnees_graphiques'!$A$3:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$C$3:$C$58</f>
+              <f>'_donnees_graphiques'!$C$3:$C$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -480,12 +480,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$58</f>
+              <f>'_donnees_graphiques'!$A$3:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$D$3:$D$58</f>
+              <f>'_donnees_graphiques'!$D$3:$D$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -516,12 +516,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$58</f>
+              <f>'_donnees_graphiques'!$A$3:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$E$3:$E$58</f>
+              <f>'_donnees_graphiques'!$E$3:$E$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$58</f>
+              <f>'_donnees_graphiques'!$A$3:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$F$3:$F$58</f>
+              <f>'_donnees_graphiques'!$F$3:$F$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -675,12 +675,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$5</f>
+              <f>'_donnees_graphiques'!$H$3:$H$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$I$3:$I$5</f>
+              <f>'_donnees_graphiques'!$I$3:$I$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -711,12 +711,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$5</f>
+              <f>'_donnees_graphiques'!$H$3:$H$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$J$3:$J$5</f>
+              <f>'_donnees_graphiques'!$J$3:$J$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -747,12 +747,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$5</f>
+              <f>'_donnees_graphiques'!$H$3:$H$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$K$3:$K$5</f>
+              <f>'_donnees_graphiques'!$K$3:$K$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -783,12 +783,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$5</f>
+              <f>'_donnees_graphiques'!$H$3:$H$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$L$3:$L$5</f>
+              <f>'_donnees_graphiques'!$L$3:$L$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -819,12 +819,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$5</f>
+              <f>'_donnees_graphiques'!$H$3:$H$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$5</f>
+              <f>'_donnees_graphiques'!$M$3:$M$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G837"/>
+  <dimension ref="A1:G1052"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -32214,8 +32214,7963 @@
         </is>
       </c>
     </row>
+    <row r="838">
+      <c r="A838" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B838" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Le Point</t>
+        </is>
+      </c>
+      <c r="D838" s="10" t="inlineStr">
+        <is>
+          <t>« Mon problème, c’est que je ne suis pas assez connu » : David Lisnard ne veut plus jouer les figurants</t>
+        </is>
+      </c>
+      <c r="E838" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxONFFvVTdJdmhZTWV0MTV4VVpLRGhvYnktX0RnTFhfYkttSURQUF9UdGt6MmJDLTEwWTUySEl6SFhmQ2czakxURVYwMnN4QWJUMTB5b3FCNndnWWxaUzJJQldnUzJXQVpPMzJ2T2owWkZET1JKQmVhSTdIYnpKeDZoejhYUHBsbi1HcTFVcFdJRGg4TnZsTnBzMTRhRkZPM3EtcFJlcmh2MTdwckdFTG1INDJZNktJVGVxdk9jVVdpMnBsNHFxQjBKdzhVTTB5Uzc0MFpLQkJWS2FNTFlVLV9QNTBrRmNSd200QkJNMg?oc=5</t>
+        </is>
+      </c>
+      <c r="F838" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G838" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B839" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C839" s="14" t="inlineStr">
+        <is>
+          <t>20 Minutes</t>
+        </is>
+      </c>
+      <c r="D839" s="15" t="inlineStr">
+        <is>
+          <t>David Lisnard assure avoir déjà recueilli 500 promesses de parrainages</t>
+        </is>
+      </c>
+      <c r="E839" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQQmRJM1VaU2phV2J1UW5sTFp0U3ZFSUFINkVSc1NlaW5lRHluaXppUzMycWh5NXVmbG9IRUUzSU1US2NzTHRpMWQ1TDhNcTZsWjVRdlA2MExhU2xTOVRtN1BOZE0xQ3NFRlhUVGdOOGt4cGxENG04Q29IUnBQbTRyRVJZRnhQckFRQWtXNXJwRlJNQVlxcHBhQ09BNldjc1MxMG1LLTdmZHlIY0FYeGQ3SXVwUzVQMGJBaE00NzJkazFFaDFheWdGYms3dy1VU00?oc=5</t>
+        </is>
+      </c>
+      <c r="F839" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G839" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B840" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Le Parisien</t>
+        </is>
+      </c>
+      <c r="D840" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : le maire de Cannes David Lisnard assure avoir déjà recueilli les 500 promesses de parrainages</t>
+        </is>
+      </c>
+      <c r="E840" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxOR0xQTXcxUGF0WGJvRU1xdWgxNm9LN210NlhiXzhGamZHcHpnNnVWdnhnMHk0NlRYdFFkeFU5RzVTTVVjNVFxa2cyRFBXQnM0VGc5ZjlVMTlBQi16MWNsSXNqdFlZLVBSdWNpazVINHpqNUJsSmgxR3dBMFd1VnItSjk5a1pYOFVlNTJyV1hGT0tEcE9Tank5SXIyMXBIanF5eTQtclM1YlpvWWdCOUhBa1lFVldMSmV6UnAwTUxadDRjdDZZVTV1MnRJTlZHSHBhcGNsUERzWGdBMXNKbm53M01jVlZ4NDNLZjc1WDUybEhKZ2pWVklmSlhTMzJQU0gwYnBNLTBUbkpWWFd4SEZaU3EwZVB4TXRoRV9yUG9zQkFfNXZFcXc3UFo1NzVSLXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F840" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G840" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B841" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C841" s="14" t="inlineStr">
+        <is>
+          <t>RCF Radio</t>
+        </is>
+      </c>
+      <c r="D841" s="15" t="inlineStr">
+        <is>
+          <t>David Lisnard assure avoir déjà recueilli 500 promesses de parrainages en vue de la présidentielle de 2027</t>
+        </is>
+      </c>
+      <c r="E841" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQeU9ORXJNWUdlZEoyYlB1enpEQkkyY3pBZGRpTnU4bzBjWDRyNHpvUWpVcWloaVBqaFdHSE5WOHZnZXpiWnVYUWg2VFFkVzcxODhMZExkZnEwczF5N1M4d3k5UnQ1cnR2RnRjb1JIRnd5cFVONkFEUkNPeWwzcU9wQjBIQ2hid0NRSEM1bXRMZkowZlpHanBLcHZxaTVpWExRZmJ3b3ZnaUlRLUhZR3BldWJtSUtaODBB?oc=5</t>
+        </is>
+      </c>
+      <c r="F841" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G841" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B842" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Valeurs actuelles</t>
+        </is>
+      </c>
+      <c r="D842" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle : David Lisnard affirme avoir déjà réuni ses 500 parrainages</t>
+        </is>
+      </c>
+      <c r="E842" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQYWl5RGtaNDVJTUtYZHdoM1E1SWc3NXRaMzRlem1zcUhCLXRNYjJqQ0JwdE9vRzhGRnFBcFRKQW9xYll5TkVDdVRmaEVLeWRwSzNUZ0N6clpGajRpbmZpVXRpUldZRDlDTG9MVFdKd2FHX1Z1QVl6cUZIemNCX2pfUHUzUHpLWUt4Ql9hcFFFckJjUlhzWkJXY1lkSkkzVnhJZHVVT0hQYURDUElJZVo3aHNmTTllU3JkNUZ3S01WdDdNQl9aeVZWdTFrSHVIcnlJTnFLSFhvMy16RlFrMWJvLU1vNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F842" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G842" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B843" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C843" s="14" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D843" s="15" t="inlineStr">
+        <is>
+          <t>«De ce point de vue là, on est tranquille» : David Lisnard assure avoir déjà recueilli 500 promesses de parrainages pour la présidentielle 2027</t>
+        </is>
+      </c>
+      <c r="E843" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNeTI1Wk5wb1Q2NlhUSFNNa3FkVXZNVjVEWFplWGhZLXVBckoxX3Bsdm9wMHdfa3JkSkdRdWR3b2ZWcHF2NkJySWRsbXdKVU5XYUJFNGdfV2VkZWprVGJrcS1SSXVlczhRRFVKYzdOUUVneHhKVFJENHhIeVdMdW1BOVZoTXQ5VUROUVR6bC1aNzdSVjNmVk9hN1lLQ0dadHE5djlDQTlWQnp6TnY1TFlZM3ZaTjZEdWplOE5lOWNiM0wwSEhGYXpCU1pCb0lxS2tuWDRlVmtrcTVTdEhiWmtFOU1GNDBORkhLUUNPSEZiWWRpeEhveDdaYnFCUGZNU0w2Zm1JN0dlaXZHVWVQZkh5bkxGdXA4LXpRbXp5aDd4WlJwS3dsRVBmV0pPWl83TldC?oc=5</t>
+        </is>
+      </c>
+      <c r="F843" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G843" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B844" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Nice Premium</t>
+        </is>
+      </c>
+      <c r="D844" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : David Lisnard annonce avoir 500 promesses de parrainage</t>
+        </is>
+      </c>
+      <c r="E844" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQdFJ2RlVySGYtUXBiZkhpZUVTTFYyN2lpX2V3d1FxQks4RWVOTTZyaExsY1djdmVNTm1XRFIxNlpzRi1kZ1hpTG5UN1g2alJXMXlrMjNVU0l1dDFWdW1FZkowZ0lhc084NDlOMlNiNm04elg2QjQzcTM1RUpUMlFvSWo0dzNNWGVUeHNzYXZrUU84R29xMkJBZ2ZBU0lib3pmN3dZOFVlSkJLS2xrZUZ1bG5tVGY?oc=5</t>
+        </is>
+      </c>
+      <c r="F844" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G844" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B845" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C845" s="14" t="inlineStr">
+        <is>
+          <t>Nice-Matin</t>
+        </is>
+      </c>
+      <c r="D845" s="15" t="inlineStr">
+        <is>
+          <t>« Je suis un pied de nez à tous les candidats du système » : le maire de Cannes David Lisnard réagit après avoir déjà obtenu 500 promesses de parrainages pour l’élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E845" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AJBVV95cUxQOUk1bkd6V2pIVWRSei0wajJpY05pLVJtVUdMbU5uOG14MVBKTFNRQ2RjZEdFeDRXZjgwa2hGeWdnTl9RNkJ5MEJ1QkhBeUctSlZaaF8yNFYtbjl2Z0MxSWctc2xiZUZvd0JqX1Q5UGtqT0JwMWpGV3hGTTYyRGVLN2lsM0F5MDBwSDNZaFd2U1lSOVdxRDNsdld5S1JtajhWQkVfaGZqMWV3OXRYOE45bjczYk5oUHhLekRYZm8zTWxoZE9HVzFOVHZ5UEIyZzN0azZPOFpUNE0wcTh1ZWtQend5d0Z3bDBNal82a0I3MzBucTJDVF9Tc2RsLWVxZ3JkVFBPdVMtMjFwY2ZUWkduM3A2cVdYYnFsc3ktbllDa194ZlpnY0Yyd1ZUR1pRS2x0eTl5RDJJNE51R0JkZ08zOWZTS2FKbldNekxlSEtMUnM?oc=5</t>
+        </is>
+      </c>
+      <c r="F845" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G845" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B846" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D846" s="10" t="inlineStr">
+        <is>
+          <t>Immigration : «Il faut rétablir le délit de séjour illégal en France», plaide David Lisnard</t>
+        </is>
+      </c>
+      <c r="E846" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNMVVPQmEyVEZOMjNzQWNEUXdjUnU3djhGWk1VVkdOc2tSZURBbFU5MFZzVlN2dDR1RENHd053UENTVTUtY2lBVTdmN0IxUDlSS3YwZXFuMkJFNXNDNGI4aVFkRF9zcU5ySlNNSVlxU0ZrdTU3aGdySzZnYlJvTTlTb0dYS1RseHAyQmE3RXFuRzBtZGJHU184dTdNbXRaUjFpdUFoQmdwNVU4MHRkcVJZTDgtOEpSSFRl0gG-AUFVX3lxTE9ZYllZaEhiZVRieW1KazZCWkdUMEFuWFlXSEEyOC1acUdKMk9EVGlkQmt4dDJuczJabkFURjRGX2tkenc3NjhHekFtNm5uRkZOeDdxM1dERGI5VXZQZXRkX2cybDBRN2JaZmpGZFBxSmRIUU5LczVqdm1IcUNraFNzRXhRaHVfOUQwekNhLXc5WkF3NVNDX2p0NlJ2Ukw5OVo2WXFjTUtpZ1oyWHhJZWd3MVVHb1Bnd01ELUNqOWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F846" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G846" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B847" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C847" s="14" t="inlineStr">
+        <is>
+          <t>Valeurs actuelles</t>
+        </is>
+      </c>
+      <c r="D847" s="15" t="inlineStr">
+        <is>
+          <t>Lisnard, combien de divisions ? Ses plans pour 2027</t>
+        </is>
+      </c>
+      <c r="E847" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPLU84Nmdad2FxcFEtVE1jYmtCNGN1eG9WMFpqQ2JuU1NpN0xZTzk5ZXRyejQ2NHpyV3pwUnoyN0g0cFlEeUFtcmdWVDRSRWZ3b0NkcmhhU2RDUnd4VWVkMEk1OXdmRE5CMjBEa0VUQVFvQW1RRWxrUHhHN1l5TWZPXzU3eFBQLW9VaDlCMzI4eEl5c3JpdUhYOERCTXRWNWdYdmpyMkRR?oc=5</t>
+        </is>
+      </c>
+      <c r="F847" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G847" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B848" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D848" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : David Lisnard sécurise ses parrainages, mais doit encore convaincre les électeurs de droite</t>
+        </is>
+      </c>
+      <c r="E848" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxONVR1N1o1elVXOENxV2lGaDFSMkFvZFduRHVUbDkzZ3RZRDhGUlBlMWgtTzJuZDZWY09aY1dSRU9vY3V4TlFUUVZPTHhiSmpqNjFTUGtkWGJTWm5fY2lxVXdoUWFKU2NkTWJzUUFNN1dOQjg1WWdQcmRGdkxyVzY4aVI4VUkybi1QMkhNY2NWWDdzQ3A0dUs4aGFiZ2p1Nkkwc0RtMWhaZjViYlRfSGxYWDhPWlE4NmFBMGxfazExR29Nd1pfZEVrVWVNU2p0WDFCUk9LZ1F1U05FNC1BQ29sUGxRd1lQREIycWczY1d5RzM5UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F848" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G848" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B849" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C849" s="14" t="inlineStr">
+        <is>
+          <t>epochtimes.fr</t>
+        </is>
+      </c>
+      <c r="D849" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle : David Lisnard affiche 500 promesses de parrainages et vise plus de notoriété</t>
+        </is>
+      </c>
+      <c r="E849" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMmgyTkZ3MlB2UC0tV0k4aXZKcTVmNE5YcHNoZW1XMmo5RVR5SEVxeXBoX1NSR2lxc2lLZzVHSW9zYnYyZHI5cjhPOFlpRkxBSTBHUm1WMGhIZ2NwRWZjRTBBY1RQMWlJem1NTzl0QzJHLWgwLXdIRDQ3ejRBOGVXSzZYaHVUOEZvQ1VqTGJWQWUzejZ1TG12U212bG1PN0VrdmlQNGV5eFJ6a05zblZ4aGlVRnB0M2xGVG9mMGd4VEZKZHlZTlFFc0p3?oc=5</t>
+        </is>
+      </c>
+      <c r="F849" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G849" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B850" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D850" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : le RN dispose de plus de 400 promesses de parrainages, indique Louis Aliot</t>
+        </is>
+      </c>
+      <c r="E850" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNOGt3cllHUlhSRzJqSnljYmIxT1BKbGh0dVhDcVZDajlEcmN1ejZtZkNLTUwxeHQ4MFBPZTh1SllNUTRldDdoSlF1eklmY2ZySXNJdl9tVDBXcHZyWDZ0RnJVTVAzT1Y5RS1QNkdHdUU4R2JxRlBZSThXY1RBYzlfRlMzYW5WVlJrWWZPdjh2d3JQdzRxWGE5ckJKdFNzVU12ZmRMd2FjZHl2Zk1NaV9PY2paT2EwNTAyMzIwRtIBwgFBVV95cUxOd0l0UU5tZExVYmFYcDBYNDVVMVRPdEt4OElBeWg5QnVnazlUMVQ5NUhJZmpDV0tBU3dXNzZZWDU4SXdzUU5haFBLd2tycDBkZy1zUnRZSlh4STlFSlRnTXh4VThZVjltSllBSjdxeGZBUGFTNWwwNXhqQkZPN25TV0R4X1NwakUtcFhwZnhPSVFLU2h4QXg3dGE2LW9IWWh3aEgwR2haMThpajRDYnBQY2dwNUVfN3N6Q0RyYmo3cm1sZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F850" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G850" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B851" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C851" s="14" t="inlineStr">
+        <is>
+          <t>Presse Agence</t>
+        </is>
+      </c>
+      <c r="D851" s="15" t="inlineStr">
+        <is>
+          <t>Cannes : David Lisnard agit contre le risque d'inondations</t>
+        </is>
+      </c>
+      <c r="E851" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQQmpwdzVRTEFPNnlhazB6ZDZGaDhSeGZKNnY0M0cwd0JfT2RrcjNiS3h5cTMxbkZfTEE5TUtQQWF3NWZya2U3X055VDh1MndjU3I5dm9mTU9uYXFmUVV3VWFqb2dzTG9UZzd6M0xNUmdxb0l0MEE0d1FCSEYzb29WUnBObERrc2FFSUd3RFpnNUVuNnRIajE4UVpJeFpveXJEMTBzQ1Fma2hLQ1dHaUUzVGFkWnM?oc=5</t>
+        </is>
+      </c>
+      <c r="F851" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G851" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B852" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>MaVille.com</t>
+        </is>
+      </c>
+      <c r="D852" s="10" t="inlineStr">
+        <is>
+          <t>Tous les avis</t>
+        </is>
+      </c>
+      <c r="E852" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPSUF5N2RNVkw1MXJ2dkJadjRjS016OThaZTBMVF9jY2JSek5JTGVBaktsZ3ZxVkt2M1N3aEtlUGs2MjAtc2JkTDVFbGJ4cHZuWmd1WGpJZjdQYTAzdXZUbktTTVFRTjREZ21Db0Jaa2ZHNkhaSnZvTkRKUGd2amhGd1ZLd2tBSDBkTHhJekMwZDNaWXFGOW5MTjFXVFVDVUVCVHdodWVjOWxPLXFLSlhsQXd4a2hRMVNLQ0ZHZHRBamROQUlGbWZPNEVnSHZjNDAyYm9aR0hTN0lqRHR6blNhM2VyZ2FnclZy?oc=5</t>
+        </is>
+      </c>
+      <c r="F852" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G852" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B853" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C853" s="14" t="inlineStr">
+        <is>
+          <t>L'Express</t>
+        </is>
+      </c>
+      <c r="D853" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Retailleau, Bertrand, Lisnard… La droite face au casse-tête de la primaire</t>
+        </is>
+      </c>
+      <c r="E853" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQcFBlQmkyckdCUEVvdXdWWHBNMmwtWDFQX25iOFNodV9NZ1NtUDgxSTdHanV1d283UHBfY3ROOUtVRmxIMkhYVnFPNUhWeTdQM3dOVm1KTUpMZUZqdE03NnNDQUdUXzduWnBZUUQxZGxnNTFxbjRYNmVwVTc5QVE4YU45OEh5V0dvMVpNdVRxa1J1MXc2NWZpUk1uUE8xM25wV3FRTGoyOTljQkxvOW9iMzJEWndmT1d6a0MwdnVKeFJvQkVIYjJ5eFB4M3ZEVllKNWRycWJzeVpQX2ctNWFCWEFhR2M0d18zbVg5M0RBZ2dvLUMxNkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F853" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G853" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B854" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>TV-Programme.com</t>
+        </is>
+      </c>
+      <c r="D854" s="10" t="inlineStr">
+        <is>
+          <t>Pascal Praud sur David Lisnard : "J’ai le droit de l’applaudir ? C’est formidable, ce qu’il dit !"</t>
+        </is>
+      </c>
+      <c r="E854" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxPSWFfU1NidE1SMXBPSUkxT0Y1ZWJQcFZLY3JTWERjZjNyQXVfNkgyajdScEZpZDZDWmZkVkhTMG1iYWZTZmFKMUMzQmxpVld3MVV5aXRDUWF2NVNydUVCcTI1VDFubFhlNktUTmhjcWdfSk1fZUVvb05DSzVDLXpPVFFnQVVsMDVWYkNFVzh3MWJuS29iX2VCR1VLUkx6REFCUlJsUWtJT1dLb1VwaEI0aDczRGVCY0paMzZXQm1nSkRsWTFOZ19JWFE4blhWM0RPbGRlMXBKN0lrZ1ZSM2V5S1dGS1JqdGVxejRiNXN5aUhZVTdTNEZz?oc=5</t>
+        </is>
+      </c>
+      <c r="F854" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G854" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B855" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C855" s="14" t="inlineStr">
+        <is>
+          <t>L'Express</t>
+        </is>
+      </c>
+      <c r="D855" s="15" t="inlineStr">
+        <is>
+          <t>"J'irai jusqu'au bout" : Bruno Retailleau, la présidentielle 2027 et l'impossible art du verbe</t>
+        </is>
+      </c>
+      <c r="E855" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPY0kzWHV2bmQ0dG9YMWRVcU5wUkpydkNaMGxzVk9Wc2IxUFZPWmR1UHhnd0xOVWl5bnBsM2VtQUM5cnN2WWpIeDhKeWQzb1FzQzVTNkFxNjRFRFJOUW1rWWNJMWo2WHJyYkZKWnJ1LXlTM0dsdnVMTWFId2J3RW56QkRrYTFDbFJiV25UT3JMREdlV2tzXzFVZDR1ajhTQjMxczJIWC05Tms2WHJCc1ZhcUdzTmFQWFAtX1pnX1M0VHhqYmJOdGlFVU11MUNKUUZnbllzcEFzUUl0TFU3T1VwY3Fn?oc=5</t>
+        </is>
+      </c>
+      <c r="F855" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G855" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B856" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Le Monde.fr</t>
+        </is>
+      </c>
+      <c r="D856" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Bruno Retailleau, une approche très libérale du dérèglement climatique</t>
+        </is>
+      </c>
+      <c r="E856" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgJBVV95cUxPazI2S0M3bXpRRUdtazRRbFduNERscUdmQlRrbWFoRVZwb0lXWlJISnRvaFNYWUlBZW1oN0tnTEI2eVNfLXlSTWx5WVpjYjVDcTRUblZvajZ5RUNyTlpQZmxITWxsb2hQUVlaMS1nUnUxQkt2cml5UEhXalcyV0tUczJNSUlaN2w5Yk5TNllNZDgtd2lLcGtsQ0lkUFk4dW5RMjRzMk51b3dWd0ZFWFZNUVYwWU9qbVFtWUdyUkptNkRvaGJkaDFGM0xndE40czE1VEU5VV95dDJBN3NEMVdhZXdyd1M3YjFyRzhQZVlNdWFKTDg2bS1XRjBaZ1FXTGFRTFZUdkFlSURvc1pDYS0ydmZNS1Q2WE05YV9hZVpJVW5nd3ppRDFucjNENC03cmxqQ3lOblZn?oc=5</t>
+        </is>
+      </c>
+      <c r="F856" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G856" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B857" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C857" s="14" t="inlineStr">
+        <is>
+          <t>Figaro Immobilier</t>
+        </is>
+      </c>
+      <c r="D857" s="15" t="inlineStr">
+        <is>
+          <t>«Devenir propriétaire, c’est un patrimoine à transmettre» : Bruno Retailleau propose des prêts immobiliers attractifs pour relancer la natalité</t>
+        </is>
+      </c>
+      <c r="E857" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxQelZ5V2NzWHhsS05HU2wtSlVyTGJFY3RlSElsYzk5bW9USFdQYVZaYzhVUUFVYmFNV3VlWlMzRk90QkEyVHM1Umt6YVJESWpIeDFTNEg1dzd5eE1saERZbEtlNzBpUnFrM29XYXNkb1ZndkFYX2FKWEFsa3VtWnBuQzFuUC1hSGtlcDZ1dHJNMXVNNDZ5ZW9NWEdyNmU5X19JLXI0enA2VUlpVGItWTRzY1Bqa2pxWXh5ZG4yR2RGWnhrRHIyVFdFLUtESFV2dDE2TWxVYXMxLXlqeDFmY2J2dFM0TEpGS2dpQXJBMGNpMjNWVE1wVHJheGs3b0NXODZGV0llSGlrVGVFV2JU?oc=5</t>
+        </is>
+      </c>
+      <c r="F857" s="12" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G857" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B858" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D858" s="10" t="inlineStr">
+        <is>
+          <t>« Ma candidature est essentielle » : à la Foire de Châlons, Bruno Retailleau veut incarner la « rupture »</t>
+        </is>
+      </c>
+      <c r="E858" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPLTRXRmlIQVdMVWtTTkZEdFZzYUVNemVub2c2THZWbDdwQW1kQzdRYjQ0RW1hSTg5RzR2c0xNNFpTZmZHQ3hKNF92ZFBENURTazgtdWU3c2JUaUF2U01sTlZOMjlpXzRzdVpEZG5UVHhRc3FsTElFcGZlaUJuU3cybk5XQTBSQzk4Si1pLW1XUm5mZGZaZWl5b0p2SG5GWUk2bDVEZDVCSXJZem1UUzVvVWg4UENrdnpRSkcwNUNJMy1KWmpZNGJzS1NhNUtVZVBQVzlKWkwxci1WVVB3WVRGS3hiOHJURFZ4?oc=5</t>
+        </is>
+      </c>
+      <c r="F858" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G858" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B859" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C859" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D859" s="15" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau et Gabriel Attal y sont déjà passés: les patrons de la grande distribution recoivent les candidats à l'élection présidentielle de 2027</t>
+        </is>
+      </c>
+      <c r="E859" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxQNERzLWRnNzFVeXJnZEZYYVItdmlNNkNEdXVPR1p1cTNRdFBwZ0p3ckp1V3RKWEp4OW1KdV93TmVkZVM0SUJhYTVOSlMySDRrZkREWWlkRVFCVU0zN3owT09oQ2h3dE1qRnRaUU83SnNBaThaUWZUNmxlYmZQN3JoZjdFSDZ2VmFHXzNCS0xsRDJUODQtUUwyeUNfb3FfcEFyNC1zX2RYaTl0NlFOQ2JLOFBIQndmTG1CRDlpWXZOcnhDanhSaHh5YWxzSXMweTVvMEtEU0ExSE1BTFJzWUlwWFRxOEZPYkY4dGJWNFR1SkZYRUpBSDJCdk81NEdobHk4bjNJU3FfLVJQZkYwWkFnZXB5eDJkc1lzQnhNSHdhX2UtM3g1ci1qTWtjOHlWSmlGNVgwVFJVRXZ2dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F859" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G859" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B860" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>midilibre.fr</t>
+        </is>
+      </c>
+      <c r="D860" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : "C’est un parti de collabos", Bruno Retailleau charge une nouvelle fois LFI… et maintient sa candidature à l’Elysée</t>
+        </is>
+      </c>
+      <c r="E860" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNM1RYaDVic3A5OUxLcllUT3BWQk9XRHRKTGdYWWVwT0kwZHFvVzNrTG42Vzd4VC04X3l3R2VfUWFXRjRmNmNIclpKYk5YYmV4ZWhKcVRwX0F4NnlNYzBkY3F0NXNnbndfejV4RWxzVGdoMGZ2WXI5eEVsSTdRZHJuRGZ6V3hialhDOTFjRksySTRFdFBFb1ByUV83TzR6a2tKcElrRzNrNGlGNWk1NFZnNzRxQXNOWkdLQ0Z1bUJodVdmdXp4SmhPem5fWThYWE41RzJhOGlKcDNzLVZQU2tGcWxxLW1Id2lYbHBTWEo1RW9CenZWWlZuY1pLMG1zbHA2M1Zva0FzcTVvQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F860" s="8" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="G860" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B861" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C861" s="14" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D861" s="15" t="inlineStr">
+        <is>
+          <t>Guillaume Tabard : « Les projets de Bruno Retailleau, un big bang institutionnel et populaire »</t>
+        </is>
+      </c>
+      <c r="E861" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOV0E3Q09jU29NRDgyUThITmJGREtuQmV0cHJiaUpfdGtGOXY5aEVvU3dVbTM0ZFFJTlcxVmY1VF9DYU12dnI2ZFM2cHViOHUyNEk5MUs4cDVxbEVEN01pNUVyQVdUSDNsaGNZeEdxQk1UUWd4Ym5LbkEtNnZCUG5HS2ttSTA2T2Q0dlFDUEY0UXBaRmUtbURyM25PbHJiMWJBNjVDRVA2dEZCcXZ5UmIyX0FpaUVxZHlPNk9pNG9LQ1BFeVVDUXpCMklUUW5OMDVLaDJjS2RydUdXUEpVUzhrcFZuMzFkMWsyU2tjOEJ5OA?oc=5</t>
+        </is>
+      </c>
+      <c r="F861" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G861" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B862" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D862" s="10" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau réclame "une demi-heure de travail en plus": "Tout ça n'est pas sérieux", déclare Jérôme Guedj, député (Socialistes et apparentés)</t>
+        </is>
+      </c>
+      <c r="E862" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAJBVV95cUxNMno3R3RkbUIzQkpoX2s0dzJRVW1PTWFkLXRxX0xXTXN6Um55U2daUDFBRGpRXzZMUTJUcFhPcDdlMnAtVW5lT3ByY0J5OXVPeVB5X1kxc3dlQXdIclZkNks2MzBRMVZ6V2tNZW5SaHpSU1F4bk1LQWV3NEtOZHE3ZXkzaE0xbDZObzNGYnN5YUU5ZHpFVkFyS2NWSmY5RDI5V0pZaXBKZ3gtTXQ0Rk0xSUpHNXFoY2x0eWdIVzZNZGRkQzdTNGVKeFJSVXMtNVo2ZWFlRzFDR2xtR0ZVcURucDVrMU43RGN6MFB0R2ZxVnpseXV4RlJFVDBTWHhwa2RwZGxUTm1FU2szeUNSWEl3LUdQeHB1S1ZXdC1PRHdPX05tTjl3V0xjOTRVOEFBNkdtd3FtY3lyWU1XNi12UUNvNzdnOGQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F862" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G862" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B863" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C863" s="14" t="inlineStr">
+        <is>
+          <t>Yahoo Actualités</t>
+        </is>
+      </c>
+      <c r="D863" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027: pour "donner le dernier mot aux Français", Bruno Retailleau défend une révision constitutionnelle</t>
+        </is>
+      </c>
+      <c r="E863" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNQnJIYTZoT01xUUtjZVlFeGt6ME5jdGQ4Zy1Dakt6UFAyaGlqYUVtZzlUTEVWaW5IU05IblNZd3dBNU53MmdWZVRyVUp1SGMyWGlOdDBFMU9hLVVtUFZxRms1ZElwSmR5MWRiZk5SQnE0N1Mxem5qSTBLdldRMGdrM1ItbUNVZ1R1SEMxQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F863" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G863" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B864" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>CANAL+</t>
+        </is>
+      </c>
+      <c r="D864" s="10" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau propose des prêts immobiliers attractifs pour relancer la natalité</t>
+        </is>
+      </c>
+      <c r="E864" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNbVZMaWNJczJsMDJzNHVtTlF1R1k5VTVSMWJtVGlvdUhTeVlWRlhYTi11dWVVcjNTTGR2ZTc5V1BtTnBaNnBSQzNrbkxpaUxBUlVIT3UzLWNTdmNwNUdXUUJGelpZSTFxTkhBTUFDbU40MTlmZ0xtdXpYSS0tb1dtLVlyR3k0RDk4YnNqUUFtdEVfMUhpd2k2RXRmR29Obzh2NnQyQU53cFlxSWRTbVNnNGM5bjNXYl8yTjZXUmxldkh2Ry00dndJYkVwOVFSaFNqeEdF?oc=5</t>
+        </is>
+      </c>
+      <c r="F864" s="8" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G864" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B865" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C865" s="14" t="inlineStr">
+        <is>
+          <t>Le Parisien</t>
+        </is>
+      </c>
+      <c r="D865" s="15" t="inlineStr">
+        <is>
+          <t>Salaires des profs, autonomie des établissements… À droite et au centre, le match de l’école est lancé</t>
+        </is>
+      </c>
+      <c r="E865" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxPbWZyVEwyY3pvYVNNY2dBb01SUWFUY1JaSDlfdjBVZlNjT29CUk03WUh2ZG4zMDR0VEZiOVBYRGdOX3hLeGp0Q3hDUHRSNEhaXzNWcVBaNF83czVaWV9ScGRzTUtOZEFfbERWODdaRTlaOGhGdlpuZGE1ZWVnVWhjUWF1THVCSXhuWUl3MTdNSHJMVmFzdWt6NUk5UFlWakpUOHBOTHlVSmNhV3h6c1Z2MTNJREh3d2xUanFnRzVMN1ZHUkY3eXlRSWphRS03RnNpUUZqVUJxNjhDcEd0SHZOOTlzQlMwVEtKVTJZLTJrcFFobHJrNEI4eVNFM3NQN1RsaDRiNm92dVN0bWNx?oc=5</t>
+        </is>
+      </c>
+      <c r="F865" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G865" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B866" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Les Echos</t>
+        </is>
+      </c>
+      <c r="D866" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : l'ennemi, c'est le mou</t>
+        </is>
+      </c>
+      <c r="E866" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNVW1oM1FNcWhuaTNiY2RlSmJjSFV4d1lDTjJXQzFUM0JRc013NUExRG9pSHh2UW5MMXhrek1ZY0NzWjQxNUMwdE5SMVpzbG1QOEQtU0JQQ2NFbUZfWmJMOXFKd3lMQlBVbGlpTHVqTENkVW9WYXNwLWI5a1JDRm9qUUpHNzFITHVzSG1zQWRmb1VtbGd4VEJWdmM3b0JuSWM2RUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F866" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G866" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B867" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C867" s="14" t="inlineStr">
+        <is>
+          <t>Orange Actualités</t>
+        </is>
+      </c>
+      <c r="D867" s="15" t="inlineStr">
+        <is>
+          <t>Expulsion de l’influenceur algérien Doualemn : revers juridique pour l'ancien ministre de l'Intérieur Bruno Retailleau ?</t>
+        </is>
+      </c>
+      <c r="E867" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNUE1wSW8tZ01lMDRHZW5mYjRnelkwWFZDb1U1R0k1dkxncnRfQ19HeU1SeUQyWEJlZmVINEg3d0sxU1RxLUp0ZXEwNGZGVFBvYWdCNjY4bS1wS2IyaDUtem9LSmhncjduRTZlLWozZThNNWUwa3g0M2dRbGttWVNXcWJrUzk0OWNxbWFMTDdPaDl3Z0VXUWVPUFExZlBnTXQ4dHBjUTFINzV4QXB1TUdUUVpwY3ZVd280T1J4dlVmM2xCb01WS09menY4aDhESXF5dkFleGNSNl9vc2lkR09DZWhWaER5Mk5HTmFiYlBhQTBEa2VvUm45aENjMno3TEdfZVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F867" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G867" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B868" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D868" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle : sur la désignation des candidats, il faut accélérer</t>
+        </is>
+      </c>
+      <c r="E868" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNeUVaZ3ZDaXBZeG0tOVpiLTJtOHhLSVZnWUlvbDVWdU8tLXhOVTZLc2NSa1N2WGVCUXJlc05OLURPQm1VcElyZFFJQVBYYXF1SzJTVmZiMnEzQjhaOHRVVUhZT0lVdlVhZGhoRkgxSF9VWk9faUxZeGpNTC1kdW5MRjZJYUF6QVpwcUdIanc2OUNTeHllNVo4Q180cU11Y1Aw?oc=5</t>
+        </is>
+      </c>
+      <c r="F868" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G868" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B869" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C869" s="14" t="inlineStr">
+        <is>
+          <t>Ouest-France</t>
+        </is>
+      </c>
+      <c r="D869" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027. Face à Attal ou Retailleau, « il n’y a pas match », c’est Édouard Philippe, dit Maud Bregeon</t>
+        </is>
+      </c>
+      <c r="E869" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPVmhrWFZYeTBMQ003cmhWSDkyWUxWcFlmdENlSWRLUTdNVlZGaWFhTFRWZDg1SjBXeEZ3YkdLZHVUa2dhX1F2ZjVzUnpHeloyWVlMMmlNbTVaTXdIUUtrSzZEd21tNXg4WVV0dHltdHZkY2d0VE9BUHdxLXJrUEtMalA1Y3IzcUZtUXlpMDUyaWJLanhBdWNEN0QwRFI1bVhnZTRxTzItZVZ2N2NlWm9hTzR2NjYwUVdMOElzR3pqZjkyemVuMWgzaS1zZnB3WFk3NnUtTVBvQmFMeGtpM2xKZHl1UFh2SWpidlJQWi1Wc1hPZC05Tmx4M2FuRW5FQkdvTWw2QjdEQkhFN1IzTHlqTGdvVHNkYXlMODFCdUFR?oc=5</t>
+        </is>
+      </c>
+      <c r="F869" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G869" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B870" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D870" s="10" t="inlineStr">
+        <is>
+          <t>« Dangereuse et illégitime » : à droite et au centre, l’unanimité contre l’interdiction du voile en public</t>
+        </is>
+      </c>
+      <c r="E870" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNNlJud2RGQkc4ajRKU3ctR2NpbG13TTlDWGV0eUVsdFZQcDM0SUZxZmpSZDFmbjJ5NWZZMW5JT0pGZzJUN21DdzRVQXd3UXhxcms4UkxHMWh1ZjZ1dHhCMEU5OHFSenRyQjRZQnVaYTRxRzVjQ1huYk4ybW1sNmtUNGowMzNDVGZVTURBLUg1VlNuUlB5MXpobnFWdzRvVXB3UWRvZ3k4YlBya0k4U2NFR3BvLUxnczk3RlcweDNVOVkwVVptR0JJSW5pRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F870" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G870" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B871" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C871" s="14" t="inlineStr">
+        <is>
+          <t>Ouest-France</t>
+        </is>
+      </c>
+      <c r="D871" s="15" t="inlineStr">
+        <is>
+          <t>« Entre l’ancrage local et les arrangements de couloirs, certains ont fait leur choix » : la députée LR évincée</t>
+        </is>
+      </c>
+      <c r="E871" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxOeE1NR2NTN1gzT2x1eEplUHppNWtBYXg3WERHYy1mR0tiUGEyY0tKYUpJSWV0cGREbzZpUjN5cm1hT0lTQW85eldDOUNMbkZZRUZQZVpRWlVRS3pyb3NXSlNNa1BVb2ZpSDBCSGpoQ3VYTWRldGhlNG8yVDd6YWZrV3QyZjlMUGpObzBEbGN5VUhjSzVGUC1TdzNjM1JTa042MkVDcmd5N3hldEV2aUJRNjFHT0YwZ1NNeUF2eUxaSGdaVzlUdDFLSmk4RGs1alZwQ09qTU9wOXM3Q0ZDT1VTanN4WDhGc2RiRFlqVHJZNDdMUU50dElMVmJWRTNYckRDdGdRSHBYX01HTFVPQmIzSkV3M1dCWVpfZUZfZU5vd3g?oc=5</t>
+        </is>
+      </c>
+      <c r="F871" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G871" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B872" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Le Parisien</t>
+        </is>
+      </c>
+      <c r="D872" s="10" t="inlineStr">
+        <is>
+          <t>Gérard Larcher : « Je prendrai mes responsabilités pour éviter un duel LFI-RN »</t>
+        </is>
+      </c>
+      <c r="E872" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNcllWVk9Qblhxdndtd1E0WnA4SlhYZzBIV3htdGZQV29UWVZtSzVHSDFZclRka1l0S2F2M0E3cjkzNW50M25mUWdmWHJXazhRQUhsSGFORmdxY09Vd3pNa1c5UGUtZGZFbDJRbEFLd25lQTZqRlBTNHJlekdTRElkTFQ3MG9ETVZPb0ZGUjhxc3ZrQjA4b214aEZmYkR2MTdva21NcUVVczJNOUxaZElFVVBJX0VoT2JjMDRETWE4TWVCNnZnRkxfN2VqYzNIQmh6dGtVSmJJV1N1M3dzNElKVzZGejJyaS0ySXlpcVJSb2w3TFc3S25PUnhR?oc=5</t>
+        </is>
+      </c>
+      <c r="F872" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G872" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B873" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C873" s="14" t="inlineStr">
+        <is>
+          <t>humanite.fr</t>
+        </is>
+      </c>
+      <c r="D873" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : et soudain, tout le monde drague les profs</t>
+        </is>
+      </c>
+      <c r="E873" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOQ1prSmFQVHFqaWotVk5QYTBhakVsdmZkbDNrUTVsUnNuX3pHNUxMcTVaeFlqcjNxMTktSGZCcWh3NC1Wd3BoQkVUa1M0U0txQUdMREZrVlhucWdvcjlvWWpxVUhXaDNYYTZVOVhRemRHSXZjQnVKSkdkRExTSHQteXdlMVBxOXFjNXB0NHVDNTJ4RW5FWktoSUVHdmE3c3hMUktHY3IwSU1pZVN6LXgyeHRR?oc=5</t>
+        </is>
+      </c>
+      <c r="F873" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G873" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B874" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D874" s="10" t="inlineStr">
+        <is>
+          <t>« La dispersion est mortelle » : Hervé Morin défend son idée d'une primaire de la droite et du centre</t>
+        </is>
+      </c>
+      <c r="E874" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQNXpTNnBsNHpwT2I3RkNLNnh2VnNmeHN3TTd6MkdxVzB4Q2ZCZEIxaDk1a0Y3UFBvOE1mQ05TUWxfM1hZUGhlSGNEYzRyMWt1dm5uSnF5c2t5QVFzU0ZBNXZxc0Rlemt1dWJfTlMxVDhIajRLVDh4TnBxYnR1SGZ4Wkg1cTd2d0NSTnlPUEJSaHFxZGhPVWxwQ1RrN2o1RkdycjNsTUtXWjFYVlRZWHRQb0pkVDN2V01CYU9xTEtiUFJWNU9oZ2I0?oc=5</t>
+        </is>
+      </c>
+      <c r="F874" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G874" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B875" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C875" s="14" t="inlineStr">
+        <is>
+          <t>Public Sénat</t>
+        </is>
+      </c>
+      <c r="D875" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : une multitude de candidats mais combien seront-ils réellement sur la ligne de départ ?</t>
+        </is>
+      </c>
+      <c r="E875" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOLWhma1ZnYldVTk5Xa3F3VkZwWnRNcXZrU2hsZXBYZHNEc240bThrd3NQajhhdktWdXNWVUI5VkJVTUhMN09GUGN5TFdEY05uSkZ3ejJyUUxhendjWllTQUxMMEhLRHp4UjhrMkZ2MnZZeldvdGlOUTlBOXVueUJaQXh2M21rSkxrajlaNU9CamZ2RUUteDhqNDAtNzdZQVdiNUdtU3E1WldNbUtpRlBKU0s4UHh3bWN2TFlrZFNPSVcwdktBSTdMVTBYSG1LVkoybVhqTm9JcmlUc3hmSTNJWWs4dElHbU0?oc=5</t>
+        </is>
+      </c>
+      <c r="F875" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G875" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B876" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D876" s="10" t="inlineStr">
+        <is>
+          <t>Salaires des enseignants : le projet de Retailleau promet plus de revenus, mais mise aussi sur une école plus sélective</t>
+        </is>
+      </c>
+      <c r="E876" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxQMFJQQUlWS3VVUkRicG16VjhrZlNoa0lnMUJyMklsMlJHa3ZvOFhORDRMNmpNNnI2Q2VNUklZVFFIcWl4UDVnUWUtYlQ0VHdlMFFlbThRcV9sOHo3blhGdjZadlhuTTJwcUc1d2dIMnE2Rm0tRzFTU2FKNlJPeGc1MjhySVBQTjVzN09DY2FnQ3FjVmVpT3dQQXAxNW1MN1dQSVBlREhVUWx4VzVpODU4VGp6ZXpZdGFuRndRd1VhQjBISUZpNFlacDN0ZUNJRTI1TnQ1MlZ4MjRPcGdiMFQzd2hhQVJlMk9YUG5OUmgxaGtrbDlaYjdJbDNpQTlkZUZldmNN?oc=5</t>
+        </is>
+      </c>
+      <c r="F876" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G876" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B877" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C877" s="14" t="inlineStr">
+        <is>
+          <t>leprogres.fr</t>
+        </is>
+      </c>
+      <c r="D877" s="15" t="inlineStr">
+        <is>
+          <t>« J’appelle au rassemblement de la droite » : au Mézenc, Wauquiez refuse de choisir entre Retailleau et Philippe</t>
+        </is>
+      </c>
+      <c r="E877" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxQcHJrX2xZTDNURF9Db0lURHE3WFl2OEYzTnRMczFlUzFlZUpDakYzZTliZVNrV1FDcWctUXl4RWlFY0ZyOF8tNGpsendNLUp1YmJ1Mkh6c2hIRXFjQUFNSVdGbkJuUmVIVml3a3VMZHNtZy1TYWd4SjNzVHlkREhVc085MmpOeV8ya0dtYXVIOEZnTnhOYWdNcEpGSE9SVFJFb0VSOG5VTk9td1dCWWM3ckFJV2dwbjBzS1UzakU1aEJwd3B3R1pUSWphdjFqQm5WSVVxVkpXSWE4MG9ZQ0Nqc0Y2UHJRQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F877" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G877" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B878" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D878" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Retailleau peut-il élargir sa candidature au-delà du socle conservateur de la droite ?</t>
+        </is>
+      </c>
+      <c r="E878" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOWlpPLUdoUDNBa01oUGlJVGRnUTNKcGp1dnd3SmxqNWYyT0RkUjBmUzRfRzZzWXRCWEVMQVVIUWtCYWNNZS1OZC0zUG1IZUx1TEFYLUNQTDV2VXlSS0JsUlR1bk1ZZmJZM2FHdDRTYVhKRGdLZElXX3BFM1hXMzBmMl9WWWtWM25KMHpPZ2xmeklwQWUyTElPb253WHM2TWE4S1hrV0VRUzJGYlJuX1hJMm1rekk1MnkzMC1zNURUNWpXY19udGV4UTVtT045Q2VvVUFSUnVZSThYWWJMMVh0NWdvMnROV1FlSUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F878" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G878" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B879" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C879" s="14" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D879" s="15" t="inlineStr">
+        <is>
+          <t>Projet école Retailleau : ce que sa réforme pourrait changer pour les élèves, les parents et les enseignants</t>
+        </is>
+      </c>
+      <c r="E879" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPdDZTTlZNcGY2amQwdTU1eUVnOEp0VXo2bzV0V01KZ1VUaXpZZnU4QjlnVFMxRkVNLWZIc3dSa011Q05PRjFiNk05Q1RkRHg3amxjaXpTTUtWeDRoTi10emJuLVBRei1lTXB1ODFudEpxSGR6VmFCNTdMbVBiVWZtMHFIenNaWmpOREpiRThVM09uR0ZHMGdzWmwzMXhXUUhSMGs0OXBQNVZaYkRfbFdvbGJoWDYtQXpxenZnbkNab2xMWGEyd1d2eGl2Sk9GcDBUOXp6VWxwcV9GVGtIRWMyS2dpRC1CUzNjTTZEX0VJWGFTSmVm?oc=5</t>
+        </is>
+      </c>
+      <c r="F879" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G879" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B880" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Le Point</t>
+        </is>
+      </c>
+      <c r="D880" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : le scénario noir des ingérences étrangères</t>
+        </is>
+      </c>
+      <c r="E880" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNWW44aTEydmFiNzdOLTRad2dEQjJzS0E3Yl9XUmdCWkFiSnoyZUtSWG40SHViRXVRRXN6eHk5QmZZM1VyRjczVTlBSDczU2FmLUkzMUtRTkJUQXZBdUFPWmVVRjRzRVJPMExlMWxfekFsdnJGdmRtSWljN1BDaXVWS29OdldIZ1lVdFpMejVJWU9IWGpwUlBvaXlldld1dlVhUjhrYXBKdmtLa182X29NbzlWcURMVEJ0UDlBaXJ6d1c1c2dBb0tB?oc=5</t>
+        </is>
+      </c>
+      <c r="F880" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G880" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B881" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C881" s="14" t="inlineStr">
+        <is>
+          <t>Le Télégramme</t>
+        </is>
+      </c>
+      <c r="D881" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle : les patrons de la grande distribution passent au crible les candidats</t>
+        </is>
+      </c>
+      <c r="E881" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQblBqMVV5dm9sMTRmR0VIRDdhcFFNbUdYN196YzFDVFlvNmNTclRmZk84blNzaUVpMkVoS0lhN0J0RW9jcU1NOGVycDdpXzZiYkVVRDNJOE85SE4tWUNWb0RWNHhpWm1vUnk3TEdEbnZ5QXpjWU15a1pvTWgxODVSWjdPY09mZEdJQVhtOE5kalY4bjlqQnNJMC15WUtCVzRuaENjWDhPQ2lIZFlOVHhvOUNjdXN0SXBoeDVfZ2xzcGF3UDBxRFd3eXdyeExSQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F881" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G881" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B882" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Centre Presse Aveyron</t>
+        </is>
+      </c>
+      <c r="D882" s="10" t="inlineStr">
+        <is>
+          <t>ANALYSE. Présidentielle 2027 : "L'économie, qui touche au pouvoir d'achat et à la dette, sera centrale", le politologue Benjamin Morel décrypte le débat des candidats déclarés face aux patrons</t>
+        </is>
+      </c>
+      <c r="E882" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgJBVV95cUxOOC1pWUhnSXAwbjYtbHBvLV8yU1Z2U19Zak1EYnNyeG9PLUJJTG1SdXhDQVYtZUVtNVhVTWRQeHh3YXE0Z1gtcDA2QWlyQ3lwMHd1VWhMT0ZCbmMwUUh1NnZ4OGdFWFRzcjFzcDM4a1ozTFZpY1NoQ0RIZnNoTGhOV2NHSjVSTVdOVUxSbmhGNlZlOU5GOVhQZGtyMklzUm5oeThmNFl3Y1lvSzlRUWZnUE45ODJxcFBoOHp6MTNBaFIwdDlBN2ZSeDJDT0UzakJlVGNTMzNOaTlrWDVsZHVYNFZ2cUJqVXFyeFYyNU1oWHA4RDVCLTcxc09EQUdmdEk3Qjc0REtFazZQaFZmS0l6T1czREMxU09yQkFlMzJrRWRKWHZ4d3FBdElsa3hidw?oc=5</t>
+        </is>
+      </c>
+      <c r="F882" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G882" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B883" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C883" s="14" t="inlineStr">
+        <is>
+          <t>Le Point</t>
+        </is>
+      </c>
+      <c r="D883" s="15" t="inlineStr">
+        <is>
+          <t>Éducation nationale : derrière la foire aux idées des candidats, quelques vérités scandaleuses</t>
+        </is>
+      </c>
+      <c r="E883" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOZ1htOGJnbWtlNE56NURVU3BQUnc3bjdMR1BBWVNhUE5ZLVhna1FrRjJmanhNZndNeUF2bHFNczR5R2paOWIyY0NTUzM4QkNLXzBXQjh2NFMyVDJscG9SeTFTM3JJN21USkRyak95b3lJeXNNSzcyeG4zbFVsZkhaMFJrM0VkZ2NHVkhDV2t1QVhBdnlKbXNzQklrcWJhTF9IZC1DRDdJQm1LbDVBN283QnVaSHJXcmhWbWRYVE11SHAybUxwSExuMndQajJwUy0zVkNyVnl0N0tURHpvNEx1XzB5RQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F883" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G883" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B884" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Maddyness</t>
+        </is>
+      </c>
+      <c r="D884" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : premier débat devant le Medef sans tech ni IA</t>
+        </is>
+      </c>
+      <c r="E884" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQY2VUdUlQWmhIYl84aEhHRXIxUkRaeHR0REhrYkNIcDMxdEJuODFwVXJia2Q4Skk0NnEtY1A5RDlmejNEOTMzUlJzNTAtU20xWXBWSFFBd0lUMEhrVFZCZ05PN0NiT0tEMGxqY3Z2X2dWRE16dEw0SHRhUmItOC1Eb0tMM3RpMEJHSTBORW5OMG5CVmYyd1QybVIwNTBrelBQQUNNVTAySG9SLXZmRU5pcmVtWlJGWWV4dTJoa1NYT0N6Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F884" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G884" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B885" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C885" s="14" t="inlineStr">
+        <is>
+          <t>tv5monde</t>
+        </is>
+      </c>
+      <c r="D885" s="15" t="inlineStr">
+        <is>
+          <t>Face à la poussée de Mélenchon, des appels pressants à une primaire de la droite et du centre</t>
+        </is>
+      </c>
+      <c r="E885" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQRjNiOXlaeUNadzVnNWREbFNYX3ZsZmtTdXRSdEtyamFZUnpCU3FpRldzckpDQW5PWGJSVFhuZ1AtZGw0Yi1uOGNKX3pyT0JpVmlCNEdEbHR3UWs1MmtTdHg5eXBiQ3dkMHJrSWVZLUxSSzJjVV9hOU80MTBjVmsyclF5dlhmWmZKdmdwb20tYVNLZDNLb2dIUVJpNUNudGtYTDQ0Q3hmS0ZUa2U0RHRsalJxUkYxbU9aeDJuZHlxaUNKWkhxSmZwVC1HM2ZPcERJUlladzUzcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F885" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G885" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B886" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D886" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : les électeurs de droite face au duel entre le RN, LR et Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="E886" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOY1JtdUVXZHk3cXB4MTN2SlZ6TTQzNXhxMExMTHFlSHlxNkRFdkJremZHeGhnUmtxall1OWhPdS1uUDVWQjZib0tpcGhmZ3FpeW9Sbm5KczdhU2JGVUZKSFRUdVdzdnpmM2loMjBnS3RTVXoyZGc2MWJOUHFlalRucEFEbEdySUxNMjZvWU41bENtZXUzZlIzNk1NRmluY3dOeU5XdzNfY2VtLWFrT2JXTC1FOUw0QjAwaDRldzlWcnVmanFyOTRDUG5ra3lqcDd4ZFRjWmcwUW8?oc=5</t>
+        </is>
+      </c>
+      <c r="F886" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G886" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B887" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C887" s="14" t="inlineStr">
+        <is>
+          <t>Libre Journal</t>
+        </is>
+      </c>
+      <c r="D887" s="15" t="inlineStr">
+        <is>
+          <t>Voile islamique : Retailleau s’oppose au projet du RN</t>
+        </is>
+      </c>
+      <c r="E887" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBvQUhlNW5WN09xMEVQYlg0cTRJNVZLOXJlbW5ucXoyVWxhajdmQktJR2NKdmFWMHhQUFB1YldNY3pQZGE2WnZEYmUtRWJTSmJ3SmFXMjJGMDdvNi0tS2RHdklLaDU4dkg3YUNv?oc=5</t>
+        </is>
+      </c>
+      <c r="F887" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G887" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B888" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D888" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : pourquoi la droite et le centre doivent s’unir pour éviter l’élimination dès le premier tour</t>
+        </is>
+      </c>
+      <c r="E888" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOV3NEYXQ0MVBzQ1ltdUl5bERFNTMzLVp3U1BDWjlWU0pXd0M0OVdOOW9sdmRxaWstWEhPNFFPblRnNTJxSzJSc0xVVl9KLUxLSFBVYTEtMnZrb0xMbExSR1ZIU1R2eTRoRlNKd2hBOHBGWHFHeFE3cWZJaTBMRllhSGxnSUEzSDBDZmVNR0Z3NmFFMl95RkxMcnFDLU1zQlBlSndpSXMtcU1lUFlETEJURkZfSThQcUVtZmJsaE4ydC1qUDJ6WGpmdHBLdVh4YVZBSllWcksxLUhPYkxyQUhTWXE3RmZXRXktZWs5R09oeVo0QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F888" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G888" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B889" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C889" s="14" t="inlineStr">
+        <is>
+          <t>Notre Temps</t>
+        </is>
+      </c>
+      <c r="D889" s="15" t="inlineStr">
+        <is>
+          <t>Premier grand débat des candidats à la présidentielle, sur le terrain patronal</t>
+        </is>
+      </c>
+      <c r="E889" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLUlvaEV5VWhmcHVlaUI3RFA3U2xvNE1WVkphcEtoQUdNRk53MHByRHZkWnFwbGRmTzNodUViQ1BnMmRwUXFxTTVCNzRoY0gteE1WYUxFZTRWd0U4LU56U2hMakdnWkFGRHgyS2JDRW5tbGVVemtuLUJROEx6cEtMbUlKWHJkU2VzeVBPYWhjemdzX2F6blF2X244bVZtdFJ0aEFjWFByclpuYlRpTVdHM2pxV1AxejNaM2J3RA?oc=5</t>
+        </is>
+      </c>
+      <c r="F889" s="12" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="G889" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B890" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>El Watan</t>
+        </is>
+      </c>
+      <c r="D890" s="10" t="inlineStr">
+        <is>
+          <t>Edouard Philippe tancé, Bruno Retailleau lâché par un de ses pairs : Les revers des candidats de la droite</t>
+        </is>
+      </c>
+      <c r="E890" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOSUZDOWhpeHlVRS1Ici1qWGU2czlEYnVvMzltYzd3cEV5SlhWd0dFdWtQb24wUU5YZzBtam0xN2Jxem9JcVpLY2Z6Q2QzZjNMcW5aNWxYWFNvOXdOZTJuSVp1aVdzeXlYR3ZrMzJ4cGhBUTV2YVRhT1FOU21VRF9aTVlBS3V3dXZWYVlHSERvcnF2UHhQVHIwU0R0cEVZOWdGblBQT2hvMXdBNEhSNmREZVFpVXdHUDV6Q2xIVS05eE4?oc=5</t>
+        </is>
+      </c>
+      <c r="F890" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G890" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B891" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C891" s="14" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D891" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : pourquoi Michel Barnier préfère un conclave d’élus à une primaire de la droite</t>
+        </is>
+      </c>
+      <c r="E891" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNUUtOTGdLMkh4Sl9VZGRjZzFOLWY3Vm1PSUE2eDZpQXdqN1dtZWVQempTZHRhekVCNEp3MHpDVGxBd1Rsa1VxLTFQMkViTlhtRlNRRUtyejNmTWlVRXUxTzFMMmRUUDFFNEFfWjhjQlBxZVBrZHBjUUFVOTdqLWUyWWd5U2lLbnJjSjI1REV1al9XZHdRU0FXeWlqOEliV0k5Z2x5R3NGT3gyMTJBSG1BNTVLdjZTSHJQXzhTZjdFRExYRkZJTFR4ZEpmMDV2dzdySzl0dVhsN0pnZnZpY1VuOQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F891" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G891" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B892" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>liberation.fr</t>
+        </is>
+      </c>
+      <c r="D892" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : la droite essaie (encore) de se mettre à l’écologie</t>
+        </is>
+      </c>
+      <c r="E892" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPNDk2elJybnZqMWRDcV84RlpWSEJDQmc5OGNCWkJsQmd6bTNxXzV0Vy1ndEhOaXhFTjljSGtQaWtkNzFrVjNXNlpQeUVvQkVjM2Q4U1o2LXpFREw4VlgxemdIX25MVi1fejU3d1NaeUdXclZSX180S0J6MDRva1IybkxuV0ktS2Rsc1Jla3YtM1ZzdUYwWWZsUGt2eHBjTzNsWHdIVWtFcFA4RV81QnRvQ2k1cnFURkVEdXdJNUxscG9VeGJoT0YzUXJxcVppVTlTeEItUkY2WjA?oc=5</t>
+        </is>
+      </c>
+      <c r="F892" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G892" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B893" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C893" s="14" t="inlineStr">
+        <is>
+          <t>lasemaine.fr</t>
+        </is>
+      </c>
+      <c r="D893" s="15" t="inlineStr">
+        <is>
+          <t>Billet. François Bayrou et la présidentielle 2027 : des moutons ou des ânes ?</t>
+        </is>
+      </c>
+      <c r="E893" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNYl9CR25JMGhxZkV6MVRBMkdHNVlRMUNnSXhkRHNlcVFlYzdkeDRXakNSUmxHdjJ6WVNyVTluTnpLLTdQYTNJc25hY0NKM1lGMjQ4ZEozSDNEbzc5eW9ZVEFYd3lfSDVIc3Ztam83Uk1WeHF3REhsWnJGeXRPZTZwTWpKazhJRm9ydkxVWlNSMk1CRHpYYjc2eTdFYVBnUWM?oc=5</t>
+        </is>
+      </c>
+      <c r="F893" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G893" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B894" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Le Point</t>
+        </is>
+      </c>
+      <c r="D894" s="10" t="inlineStr">
+        <is>
+          <t>Laurent Wauquiez : « On est en train d’offrir sur un plateau le second tour de la présidentielle à Mélenchon »</t>
+        </is>
+      </c>
+      <c r="E894" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOcURFNHh3Rnlzdjg4Z25ic2lBdFJ6ZDNUaXUtNzVzTWZ5NXVUNzd2UkZxdmc1SUtPVkJ5UkNtOXRMM1QyUXVKY1NFVFFTMFVLaU16cU82WnU5c1pVLWhJMVc0MHVlMWFNcGRYU3NiYXVGcDdBdmd6UmtPRS0yQkZuSklXZ3ZsdzFrQW1nRGc3cE9YMDFWbmJkOXVVM2JyV1hMblA2ME1LTFZCTDdVeVByamRUVWc0MDE4dnhvWGZpX1RiTFE3V0RxN3lrd1c5bVhvbXdUN2JTNnVlOWNjTzhLVDdiTTJGUnNybFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F894" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G894" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B895" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C895" s="14" t="inlineStr">
+        <is>
+          <t>MaVille.com - Rennes</t>
+        </is>
+      </c>
+      <c r="D895" s="15" t="inlineStr">
+        <is>
+          <t>Le dessin de Chaunu. Les principaux candidats à l’élection présidentielle font leur rentrée</t>
+        </is>
+      </c>
+      <c r="E895" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNWDBGUFVuWjY4RTNuem5nNlJoOGtRTUNENWlUOGw2cWE4LWJtU2xVMHhsQzBleHg0dmx3ckJJdlY2WTVCak1qQ3R0UGdqb0NGLVZkQVR2WmpsQndRU295c09lc3NJOFpiZk85NjhMMHRod3dfUWhFLW1wUUFnZVNaRTlack41a0wtTlAwNi1KZHF6Z2I2T0l2WUNuNDI5MXZFWEFrVklRcUNaOHZsNkYyei1zZTc0N1QzZjFqV3R5NG9GVXcySU8yNlY2c0xacmdlRnhONGhqdVBpS0p4WmFoeEU0bXkzYUlnUGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F895" s="12" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G895" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B896" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D896" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : une candidature unique peut-elle éviter la dispersion des voix à droite et au centre ?</t>
+        </is>
+      </c>
+      <c r="E896" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQUEI3X2hQamFvRElXUFpCbVpjS29BdEE5TzZDUUZCUVYwRE9sS1A0c3BlclRRNGp2S0JFNHVYNmlpR1pFemxlQlQwU2k0Q0NHSGM5MmNOZy1ZYTNYWU9UU3NYMmtkUmFHRFJNUDBlSENjXy1lN0t4cFJPSkpHSTJJZUtMWVBZZmRyQ1lEb19qTlpwZzdGSnFrd2EwdExfRk9BaEpzdWNSaGttVFFRcHJoT1hTc2RxQTlKRGx0S1dGZ0JBRGJfT29CT1B4Mzg2VERZR09yZnM0RXAtWTFleTRCZWJFUTdWdXROX3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F896" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G896" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B897" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C897" s="14" t="inlineStr">
+        <is>
+          <t>L’Éveil de la Haute-Loire</t>
+        </is>
+      </c>
+      <c r="D897" s="15" t="inlineStr">
+        <is>
+          <t>Question des retraites, augmentation des salaires, baisser la dette… Ce qu’il faut retenir du premier débat présidentiel du Medef</t>
+        </is>
+      </c>
+      <c r="E897" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxOVUt5QTdUNEpXd01VaXoxSWZhbnY0MUxJVHl1VUQxSndWTGJXc1JTRlJkRm9WcHp1Y3lIWlVPV3FTc2RFczZmYmhvckFfVkN6VVZJdHpfYjFQckFfdFlfV0x2aE9tOFNFaDE2NWtOQjh2azAzalNrdEdWU1UzNXFxQ0lCenRDZzlYSzJ6c3ZvcXd4bS1CMUhjT1JqejFsUnFpX3VOOXVHbDVXVnRzZy04TVFQb0h0d0NWemlOMDFCUFJ1Wm1pWVlhSXhZRFkxaDBEZFFmVkt4amV3MHdVQ01URGtoVnNQbW1uMUpaYnN2MUc0bmJIbGNQMTlYVGdINlMxU1VoLVpjT2h3R2Rfb1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F897" s="12" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G897" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B898" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>L'Expression</t>
+        </is>
+      </c>
+      <c r="D898" s="10" t="inlineStr">
+        <is>
+          <t>Nuñez dans le vif du sujet</t>
+        </is>
+      </c>
+      <c r="E898" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE4wTnQ3RE1hd0hwN3RuZWotSlRzSWxITUMtNi12aWx2WU1Dc1ZsbDBHVUVWZXZYd3E3QktUTGt5eWFldmwzdnhxaDVzSmxVeWJaSkhZYzJQcU1JYVNlWFNoMEo1LXZRSC1MN2Vsc2dUQVBHVFp3T29SWnd6RXltZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F898" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G898" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B899" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C899" s="14" t="inlineStr">
+        <is>
+          <t>ENTREVUE.FR</t>
+        </is>
+      </c>
+      <c r="D899" s="15" t="inlineStr">
+        <is>
+          <t>Voile dans l’espace public : Bruno Retailleau accuse le RN de « populisme » et de « démagogie »</t>
+        </is>
+      </c>
+      <c r="E899" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYlZYX1V3MTA2R1hCYU5wdjFxRWFRUmNtNDRtTkRkdDIxYkExU1BORS00WS1QSU9COTZCRzY2RnliM3lfRk80Rl91UGdrVGkxSS1pRmNRMWd0dDlTdUVxUUltVXhpUm1odzRoQ0hQUUxhdmN3clUxYWIzRWVaVDUxTXZUbzVQMGxlSkdYUTg0YTBWZEpVMFRZeVMxSFhMSFpUNnBPQTR0eU5DR05YcVhOSnQ5XzI?oc=5</t>
+        </is>
+      </c>
+      <c r="F899" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G899" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B900" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>upday News</t>
+        </is>
+      </c>
+      <c r="D900" s="10" t="inlineStr">
+        <is>
+          <t>300 euros de hausse et retour aux notes : le plan de Bruno Retailleau pour l'école</t>
+        </is>
+      </c>
+      <c r="E900" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNTTFxRThDeWhVbmZxb3pKUXNwMjNJMDYzdENIdHJwVjNFY2d2NUJSZi1XRDJuQzk5bjRYdWl6T0s0bEM4d04wV19GUTBicXJ0Sk5sdDBEeDgwZHBmUFAtMUh2ak1CNG94MWw4QVpVQklTMHVDbEFONWJyY0Q0Y2tvZGRydWxjQmRyNi1XS1lKOTl4WWdNVGJPUUtETU1IUFZqVmpxSXpWUm1HQk9FcmlkMnozeDZQZklHbDdmbVFwWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F900" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G900" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B901" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C901" s="14" t="inlineStr">
+        <is>
+          <t>ENTREVUE.FR</t>
+        </is>
+      </c>
+      <c r="D901" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Bruno Retailleau veut réviser la Constitution pour redonner « le dernier mot » aux Français</t>
+        </is>
+      </c>
+      <c r="E901" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOM2NqQWQ3c2N1RzVIT2VteDBYMDNWVXN6ams5Qi1YdWNJU0hjRGtiQWM3R051UFBNc3FvdGlxNDRvMGcxYnVaX0hSd1BWek91cDBBUTI0ZVMwaTdwSlpsUkVhTVdGaTBnSWs0MTRNU3BQS1hIckNsbmxzdFJFMnJLVFByZ2VQR2JRbldHNXA4MFZSQVlQUjFCV1Vqd09pamtYaEpvWTAwUDB3TElSV3dhSXRQNE5oc3pZYml2dktaU3FUZmd0aHNhLXYxVnBoUTNTejJz?oc=5</t>
+        </is>
+      </c>
+      <c r="F901" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G901" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B902" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>France 3 Régions</t>
+        </is>
+      </c>
+      <c r="D902" s="10" t="inlineStr">
+        <is>
+          <t>En campagne pour 2027, Édouard Philippe sert des frites avec Gérald Darmanin à Tourcoing</t>
+        </is>
+      </c>
+      <c r="E902" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxPZDgza2dCUUdLb0pERHdhc3Nqa1VyZmFsYVA1aG5iZHN0ai10MGNySHlBUVduSEJXdnpnY0NTbUZkOHdNS3h0TTJhUE9HZDhSd3ktbjgyQXZFb1JrWFVUNllZUTMtLXE3TU1iTHhSb1phVTFVdmlDNjV1ZGhFSlJTQ2g1Z0R6X3VwOTN2dW9ZdkhJV2tHcjVKbXdLNzljam1IYi1nTnFQcHhCbWtIbHlCbGJoTkZYT3huczVhSGVSV2lXZVlxLXpITWNWTEFDMGE4ejBKV1d4WXJ2T0dETkFZRmQ5UllWbXRzU3NTS2VKcHcwd1I0ekt5RzJaYkFDajFK?oc=5</t>
+        </is>
+      </c>
+      <c r="F902" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G902" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B903" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C903" s="14" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D903" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : «Il n’y aura pas de moratoire sur l’immigration de travail, dont nous avons besoin», soutient Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="E903" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxOajlmcDNQdE0ta1FObGduMkM4bHVBQVpmOUVHcHh4eTEwVmhjd3gzN2lRUWdwbDNpcUZ5T3d6NDRrVlB5QU1NYWw5cmo3TUtSelBZMzc2a3piTkRJUUw0LTU4RVEtd204a0VYdTRGakp1UW5ic2F4Z0Z1aERpckxkQ19UTk5Mby1LdUhEaTA0MFp2cTJDRWR3SjFvNXk1SDN6QklVanIwMWJZcDhVN24xMjUtU3BXS2ptZDhVOHlYckprUFRqbnRkLVlZcnFPOXpiWTNmb1JpRTBIZkp5dzI1NEtISDVFX1RmUnIzM051NUR1dzNKYm9abmVzekR3ZDJUeHN4cHdMOE4ybG92cjhHTjlndXozZXFsdnQ1YkpSMHU?oc=5</t>
+        </is>
+      </c>
+      <c r="F903" s="12" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G903" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B904" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>sudouest.fr</t>
+        </is>
+      </c>
+      <c r="D904" s="10" t="inlineStr">
+        <is>
+          <t>Élection présidentielle 2027 : Gabriel Attal assume ses différences avec Édouard Philippe et ses « idées d’il y a 20 ans »</t>
+        </is>
+      </c>
+      <c r="E904" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxOWXY2YmNydkJZZWYzME9iUE5pSlp4Sm94RGtYMGdpNWt0b2UxS2xWSkhxWTNUc2V2MnNjR0xZV2NnM1dTRzVTcmh5d2lFLWFqelRWSXozOFRfRXF0OFR3cElRM3N3YzByaGNULUNrNlR4azhoS3BBQXRYVWNNdzlNRzhvVWgxNWlXMkNOYXhIaFJjbkU0bVNXeVFnN29KeXFNYTZJVmNiVTRycDhHaVZJbkIzVlA5VWNydGZvQXBEOUNacG9tTFMyUURIeXd1U3JUUnJLQkVLejctUmVBQmpnaHFzS0M5Smp0cWVZWTFzbGlJQ3RNSzZuTVF1OFhrRXk2aXUzOVFyUUk?oc=5</t>
+        </is>
+      </c>
+      <c r="F904" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G904" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B905" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C905" s="14" t="inlineStr">
+        <is>
+          <t>Boursorama</t>
+        </is>
+      </c>
+      <c r="D905" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle: la réforme des retraites, "l'éléphant dans la pièce" de la campagne d'Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="E905" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxPdmpvS2EyeFNvbzBtUXpZVElTRlpYMFhFcWZSczJOdmI3U1hRT1hjMktHel9NekRIRFVIVjJDaHNYQlpIVW8tRHl4RURVXzVRUHBUMUdFbUJ3UGUxWGw1RUFYWXU2WDZJWmpJRGk4RE1GMG1WNkJiekV6Rk96QUdGb2J1UkJWUDluOXBFODFRc3cwdnNzdnlTTWZSQjRldko4UWN2QXNxNnNUWkhRWjkwQ0toUXZBOWotZWVBcU1USTZoMHM2Y3FNWXduTmhfRksxdnZzREotZ1RLT2pFS2x6UzhNeFZpNGdpQ3NXRnlyY0JQVUFHOF9RbmVuX0dKTWJyOU5reW9FRE1rdjI1QVFrd2Y1akVuTW04U1hJWThYUdIBnwJBVV95cUxPdmpvS2EyeFNvbzBtUXpZVElTRlpYMFhFcWZSczJOdmI3U1hRT1hjMktHel9NekRIRFVIVjJDaHNYQlpIVW8tRHl4RURVXzVRUHBUMUdFbUJ3UGUxWGw1RUFYWXU2WDZJWmpJRGk4RE1GMG1WNkJiekV6Rk96QUdGb2J1UkJWUDluOXBFODFRc3cwdnNzdnlTTWZSQjRldko4UWN2QXNxNnNUWkhRWjkwQ0toUXZBOWotZWVBcU1USTZoMHM2Y3FNWXduTmhfRksxdnZzREotZ1RLT2pFS2x6UzhNeFZpNGdpQ3NXRnlyY0JQVUFHOF9RbmVuX0dKTWJyOU5reW9FRE1rdjI1QVFrd2Y1akVuTW04U1hJWThYUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F905" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G905" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B906" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>France 3 Régions</t>
+        </is>
+      </c>
+      <c r="D906" s="10" t="inlineStr">
+        <is>
+          <t>Port du voile : Édouard Philippe juge la proposition du RN "inconstitutionnelle" et "scandaleuse"</t>
+        </is>
+      </c>
+      <c r="E906" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxOaGZ4dkZhY3c1dlJBbWdJc2hrTjBGZ25jcnExQU1RTEZvVkh3YThXRUVnZUJvTXJ1YUxEUUdvRC02amxjX2FCV2NveXhqOFB0T2JUVE5vM1VYNWNISGw4Z3VNRjJyV2dlQ21wZ1ZCd1hRN2tQUXBrU2RiMVlGX3REeXM5N1NjXzdaLXlGRzJnVXZFMjdwWlVwbmFUR3pCZW4wLWExYm9nZGRHbWpBYy00M1QySEtlZHFFbThsUXppME1XSUs5d21teF9IQWR5d0E0Z3NGeUkyc0ZDcmIybWZ2WHJ1UjFaVGkwUWFhWlplbXJFMXB3ZWJKT2dxTTExWDBWd28w?oc=5</t>
+        </is>
+      </c>
+      <c r="F906" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G906" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B907" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C907" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D907" s="15" t="inlineStr">
+        <is>
+          <t>"La politique migratoire de la France doit être beaucoup plus ferme", estime Édouard Philippe, candidat "Horizons" à l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E907" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgJBVV95cUxNZHlUcWw1NjIzSUIyUVJ1NlhzLWxOT0M1b2lBQXZmb3dDOWZveW04RC0wQ2xZWEk2dU9aSHg1S0h4bUtmTjhvdWhUbVRidnFpOTVHWjl4QkQ5RGx4VzVuaDFpbjNHM1cxdF9JWm5fQWsxX2p3TXlPZUZJZ2lhUDdORHRUYWVlS0ZJUEJKYjNVTnZYQ0ZYbFZUM1I5Wm5JdXRDcDJTemQ5UHZvel9TZU4yd0ZqblpTT2U3WTZTaFZQeEcxSTdzN3kzX05WdlE4RmNRaTNuZnh0RnhJaU15M2lnaWRsOHl2b2V6QXR2YnFoQnNacVpRbEFKZV9NSjhTN280ajJHUUVXdm50UElpdk81azRDRF9NYkhZT2VUeEhnd2hnYzZQQjZJNEQ3XzExMUlvLVBWVVltQWVEUGVMY3Z2eVpR?oc=5</t>
+        </is>
+      </c>
+      <c r="F907" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G907" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B908" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>sudouest.fr</t>
+        </is>
+      </c>
+      <c r="D908" s="10" t="inlineStr">
+        <is>
+          <t>Élection présidentielle 2027 : Villepin accuse Philippe de « faire le jeu de Le Pen » sur l’immigration</t>
+        </is>
+      </c>
+      <c r="E908" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQWjJlS1JTd3VPZ09KZm9aOHNSQWJlNHV5X19Yal9TcDJYa0dKTU5CX05kWmVyS1FBSUIzaEtyczQ0bU1fZHJRd2tPUHFaYTRzSkRESU5Dd0ZuTWFuUF9BYWMxNHZMVXBYM1VrdC05QUVtbnZ4Z2JlZWtMMi1VWFhmdE1wR1dZMUtVZ3p0bkRELXB5Q1NTZEtVc3lFZkNMNUQ3RVpyYWhiWEVtS256VmY4U3A0cExaWHJSWHNabmxiOVp4ZWtIOFdPTFlyVVlodG96MTcyZksyajRLY0ZxemdoYWJIVHprRE1OTXUyVlpXZU9ZckE?oc=5</t>
+        </is>
+      </c>
+      <c r="F908" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G908" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B909" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C909" s="14" t="inlineStr">
+        <is>
+          <t>Le Point</t>
+        </is>
+      </c>
+      <c r="D909" s="15" t="inlineStr">
+        <is>
+          <t>Laurent Marcangeli : « Avec Édouard Philippe, ce ne sera pas l’immigration zéro »</t>
+        </is>
+      </c>
+      <c r="E909" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNYTZjMmV1dzEwb3J3N1JNOE1sZnNWLVpQRjhORmwzQ3R4N2k1V19uYnhrMF9aRHVISnNoblVINTFWQ3lNUjRSUUJvT1pwSWV4T3kwZmxValBWUWpfdHFTamVrdXd0MmRtUnRJNW9iZmNwZnVZcWFsOExrSjI1Y0FXaVVicHhEeUVGQmFqUEpRaGJHQW9tc2l6SjRxbG9hNUo4QWV3ZGJ4aWhBQlI0RThCSDJqU3pNRmZabXRuYmxwOG5TQ0FXUVRUQTI0c2Q5Zlk?oc=5</t>
+        </is>
+      </c>
+      <c r="F909" s="12" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G909" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B910" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Anadolu Ajansı</t>
+        </is>
+      </c>
+      <c r="D910" s="10" t="inlineStr">
+        <is>
+          <t>Édouard Philippe : une immigration « beaucoup plus ferme », mais l'accueil des « étudiants et des compétences » maintenu</t>
+        </is>
+      </c>
+      <c r="E910" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxOZ1FmMGxNaldqWTNMWDViLVEtbFJ4T2h3LU5wcm9ic3pxMDdJU05xTkVRSjNwY2VlZThTZmgtaThMXzJ5amI3RS1VM0YtMzdRZFhCMnBkbjN4RF9JR0dLaVk4NFVKTG9sYlY4SFhhT1R2VlBvanVrYlFoa1JJUGJGc29yTlYxVEVDRWQwNzdyUDQ1eXJ4VzVlWHNnUlNPaXJPbS0ta3M0MFBRNl9kTEw4eEphbGhGTE8xRE1IOXBiY1h6dUxKX0pRR2t0T3ZlcmVsczNxR3lPVHdVUW5ic0xYQkpPUzZoUmZBalEwS0tzMkVPTW4yeFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F910" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G910" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B911" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C911" s="14" t="inlineStr">
+        <is>
+          <t>Le HuffPost</t>
+        </is>
+      </c>
+      <c r="D911" s="15" t="inlineStr">
+        <is>
+          <t>La campagne pour la présidentielle à peine lancée, Édouard Philippe pense déjà aux législatives</t>
+        </is>
+      </c>
+      <c r="E911" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOVlJxYlY1Z0RCczQzMm5FT1dfdFVjcUlqS2dTSWo3UkpUd3hGUk5WNzhHcVZ1ZjhkdmNIRXhYWjBRX0NOVDQxaHdGQlNuRFpDdWgyNE1velZpN3IwM01yVk1uZnZBUUtxZnpaQ0pZTEhuTFY4cVk2UktuQk5BRFk3dFZSTEJRT1BSVDNISlN0amxoOURGUFl2ZTdnOFU2XzFaZlZIWXhDcTJSZWhqM0lkcVlaQ2FZZ05USk9JSFlRc3hrWEg4ZTBFY09NYml3M0lqeGFPV3pWT0owNjUya05vYnQyQlIxbi1senc?oc=5</t>
+        </is>
+      </c>
+      <c r="F911" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G911" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B912" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D912" s="10" t="inlineStr">
+        <is>
+          <t>Marine Le Pen "est un mirage qu'il faut combattre", estime Gérald Darmanin, ministre de la Justice et soutien d'Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="E912" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQRXhlRlpsTnlMVjFLNmNGdzRWS3pPQjZ2dlNFblBZMWZZVkZkQUM5Z2ZRMEJrOXNONWF3WkgtY1lwMk44b1JXd3RudGpLQmtTcDVaWjRadFpaWjNtNW8tYjNxMWVCNWoyZVVmNmY4SUVWSlZOMnBrWFl1bmtZbmdnd3lwNWR0UUVTRnBFNUhmZ3ZLNHhjakxTWmNfR3JCVlRBUXFRckxkaWxCYkVMWWlnQ01aOHFMUzNoN3RLXzBUd1UzRlA3aWl2MmVvN3FNbnVVeVdsX2F3ZkZYMHcyRDJJLVk2MFgzWmlhUGxiZV9MTGVmalR4alUwVFQ5Q3VjOGVJaUQ3Wmp2amt4akQ0dEhqelNnYXp0V2xIdmRtZy1sQVgxMHJHLUlSbURYbGFIUExoR0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F912" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G912" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B913" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C913" s="14" t="inlineStr">
+        <is>
+          <t>LCP-Assemblée nationale</t>
+        </is>
+      </c>
+      <c r="D913" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027: à Sens, la nécessité d'une "union des démocrates" face aux "extrêmes" au cœur du débat</t>
+        </is>
+      </c>
+      <c r="E913" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNb0tVTlZkVWladDIwWV93c0F4UDVvanVQLXZJZFB6bzRWR3ZTWWNPdFA4S1d0QjBudm9va2kwQXl4cUlOOERyXzlxdGxjUW8wR0hRMjV3aS1BYnVUSlpDNDNDdFFBWjBoYnBpWndHVnNfUDliQnpTQkFQRXpKT29XeGd4LWpXQW5uU1BkQ05xWXdqU3VvalF5THVXUkxSdTZaSUJqdzFma0ZmVjh5NGYzYWk0MA?oc=5</t>
+        </is>
+      </c>
+      <c r="F913" s="12" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G913" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B914" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Charente Libre</t>
+        </is>
+      </c>
+      <c r="D914" s="10" t="inlineStr">
+        <is>
+          <t>À Tourcoing, Édouard Philippe appelle à l’union sacrée de la droite et du centre</t>
+        </is>
+      </c>
+      <c r="E914" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPQnZFeDQ4UkxtWGxPOU9XWElxSnlpSTB6TXJ6dmltU1BfWWJQalFwVnV6VU9DU1FGOHJnQ1ZUT19mZWdNc1VyT2R1QTJwQ0tsSldNcnZTUDdRRS1nR0o5azVMOENXNXU3ak8xUWtWVGoydk5BTU1NR3gyMmR1eU9rNng4aHJCazVsZ2pGamVzRl9GbWd2eUZOeF9ZRTMtazFmSjEtN243SVY1S2p0SDJ6VHlmYTREa2pPYlVLRzNadnQtMElIeVBNRzFORlNjcWljZjdEOVlOSF85Sk1PQm9CaTZmYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F914" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G914" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B915" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C915" s="14" t="inlineStr">
+        <is>
+          <t>RMC</t>
+        </is>
+      </c>
+      <c r="D915" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027: Gérald Darmanin accueille Édouard Philippe à Tourcoing ce dimanche</t>
+        </is>
+      </c>
+      <c r="E915" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxQN3pJMVlTWEs2blhvbkt2c3E1TC1WYWgwUWI3ZVJkU1d5alNOVUtTT1lZT19qbmZiUnRQOVc5WVBnQzZHMXZTWkliTjY3WnNUa3V4RUMwSXVpLUVibGlxeXJzdUcwOTlNQ29CM2NoX2FZVFprVmotUjZHZWJBdUUzT3VCemZSQU1qQnhhVDBhbmNaQTFrRmVBMDNhRDJtaWxlU1pKNV9feURxUW1laHNBR3lJWmd1MkxPcjRnZzNVWmFfalNncVdSMXNDZXI0d0xveFN4TDRraE1kblROaWs0NDNLVFB1a1RDcENoeXhBRHgzV0Vpb2pKQlJXY3U0TWJyeXdj?oc=5</t>
+        </is>
+      </c>
+      <c r="F915" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G915" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B916" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>La Voix du Nord</t>
+        </is>
+      </c>
+      <c r="D916" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : à Tourcoing, Édouard Philippe et Gérald Darmanin mettent en scène leur ralliement</t>
+        </is>
+      </c>
+      <c r="E916" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbmJpU1ZNQnJWeUxXQUx5clhiMzF3V1NXMHVYVUhrX1dVWWFZS2FqM2dqSzJPSHNicm9HQlgtWHdGTnp4cUxmVFVRZUFiMlVwSDBvbTFKRGJMY2VxSGVlU0RzRkZOWEVWS2VUSDB6bGpfRmtneElVUk1ua2IyWmpiNDBveUlNYkxvbkJiWTROWmRlVWlQQVp3RXpDZlZQQVZmTHRsM2UxZXRCMFotYlJ2X1dQa0VObHFpYXdjOFd2aDRmVUcxdHc4N3BIbw?oc=5</t>
+        </is>
+      </c>
+      <c r="F916" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G916" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B917" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C917" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D917" s="15" t="inlineStr">
+        <is>
+          <t>"Sans majorité absolue à l'Assemblée nationale, rien de grand n'est possible", estime Édouard Philippe, candidat "Horizons" à l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E917" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAJBVV95cUxPcF9oYUVHWEw4d1VxWVR4MHlteVBibW4tVms2RDNSSFIyTVRjWFJydXFTYzVMcXo3bWpqT2V3WVRFZlE1b0Zqazh4bXV0bWFzcUxVX1I1SE1CdVFTSDlrRGxoM0tTN2RqN2ZwM1EzeVZsTU5nSEJGWjJHelZYMExza0V2TlFGYkxwZE9oa1EteGV1YjFLT0hqYkFkQjlacUhXdnFQbllFY3lvZmtudlJ6YzBFUjEwQXM0b2N5azBHSl82c0hCMXBEZ1pfVXVFcXdQdHRLd2puSG9qbFZrS2JOM1VyVFBCcTgxcEN5dEZVX1FmUTQ0eDV5TFdtNkNUQnJUYklVSHdJNDkzMXM5NkFTam5QWHNXZC03bGx2cmZwdFVEQU5DY0MzQ0phOHoySTB4cVJlM0lyRFBPNU05eG1fYnJNOHRKQ1ExMnlsYg?oc=5</t>
+        </is>
+      </c>
+      <c r="F917" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G917" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B918" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D918" s="10" t="inlineStr">
+        <is>
+          <t>"À la fin nous allons devoir nous rassembler à droite et au centre", déclare Édouard Philippe, candidat "Horizons" à l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E918" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAJBVV95cUxNYU9sWC1DblFreEFJel96NTFoaXM2c2d2OVM1NlZUX3MwWUdhNGxhb21MVDBlSWp4THFCSDVPZWdMSFlnSHlVTEh4cklHMG1KalhzZnNsNjZEOGk5WUJFalppcDlmTVpndUU0Mjh3QW1UNk1sQWpFYUNIbmtiZlMzWXlCTXh0VWxJbnkwdldIS05qOENDSk5SQ19wQUQ4NzZPMDh4bEJzVTR6RU8xNXZfamFIemFtdE9oOVByNEZuRGxPMGRESHhsYkVlUEdDcDVOaF9qcVRxNUU5MHVLZmZXOEl6ZnlOOUkzUEdJTzlKeXEyVFhnWlJPMWlEWHdOaVhQTk1IUkdUNTRtSTdzcEZpSEt1ZVA0ck9JWXUzWi1kZHdKVHQwTGJBQ0xfTnE?oc=5</t>
+        </is>
+      </c>
+      <c r="F918" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G918" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B919" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C919" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D919" s="15" t="inlineStr">
+        <is>
+          <t>Rétablissement de la double peine: "Ça ne me pose aucun problème", assure Édouard Philippe, candidat "Horizons" à l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E919" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwJBVV95cUxOc2tOZk9UOHFtekhPVHpJSkI2c1lvSFBlWm5lQVh1ZkdvTmU5Zjc0Qzgtb2RYMGwwQXoydmxDbWJDTEVYSzB4b1VIMlJFRHBFTUdKTXpPTjI1UE4tSFVLVTh5WTE1VXlfVXNDS09qeWtWdE1zV3g3azZadjRVejVTUmZjZVJ1YXZtWHhUcnU4M2xjbmRjd1JVcVFneWFnMFRCbGExcEFXeFkzS0ZXM3A3TnQybGlWaUVCNV9PVWdyVHppaVFMTDlLelB6V01NNnFKLVNKSUs1aFFSMk0zbG1ZbXZnbXVMNnNZMVA3WldhNnROYXQ5RzdseXRubURoTUtjNFVsXzY1aThGYU1YOFgyYXllVFlpM3lqT1gwOWtXQXJHSUJ3Nkxv?oc=5</t>
+        </is>
+      </c>
+      <c r="F919" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G919" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B920" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Le Republicain-Lorrain</t>
+        </is>
+      </c>
+      <c r="D920" s="10" t="inlineStr">
+        <is>
+          <t>Politique. Édouard Philippe « le mieux placé » pour 2027, carburants, budget... Maud Bregeon se livre</t>
+        </is>
+      </c>
+      <c r="E920" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPME1fWm50YWU4YWlBbXRoTWtvdWJ4N1NWQTQwZFItdEY2TUhCUmkxSDNvd3h0YU8wUElyMmJiN2pvdHl4b1FXa3M3NTlCQklFR1B3ZENMeThVdXhZekFuNFEyUlNxMzA3QUtyTDZxbWFCZERtZ3NMTjhIMDVxZDUzcUlkUW9BMnRuSUMycHVWRl8td05xbTBLNzBiUWdvUVVtVy1VRjYzUjJvek5DcVkySXk5d0NPN3lVQUpsRnZjWWZCemV3UC1LYTRwTXFna1dBYkx0QnBvVTY1d1RELVNKVzdXdjRDa25vVDN5Ym1CQkthbTA?oc=5</t>
+        </is>
+      </c>
+      <c r="F920" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G920" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B921" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C921" s="14" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D921" s="15" t="inlineStr">
+        <is>
+          <t>Coup de communication d'Édouard Philippe : «Je préfère qu'on distribue des frites plutôt que des milliards que l'on n'a pas», juge Karl Olive</t>
+        </is>
+      </c>
+      <c r="E921" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOWVZvRXRQeUpoS2dWNElyVm5yYnAxMDFtZW0yNVE1OElNbEl6dTRsSGw1TGRHeEp6WHR2clFvTmtVVk0zbzNIZEpMTUNtWS0zMHZUWldqMmxoWFBQN05oZVBzejM5NUpOZUlnamhGWkV3S3c2c1lUamE2VFpFcHNxcHp3RUNtZWpwSWxEOUNGMjlhckhhMWR4SzRwdFdVX1JYOGRVRHJDTmoyZG5vTjZTSG5jamtNZ9IBuwFBVV95cUxQLTVfZkhwMmVtSDFaV21ibXdkLVBuMkNkRW1tZEtaTHVyUngweFpSbldWMkg1WWs2VFpTd1pBcUZTV0Italo3QWIyUVhxdGVacDZqdDRJczd2eTE2aXR3dTNBV3haWlpFb1hkUVZEQWV1ellhMG9XNUlremZNM0Q4VnJOZThEVllIUFJNOWhDcElaQXFIZ0NXS3NySEExdm1hWC1EekREeFE1cDhvM2dfTEMyM01EdWl0QmM4?oc=5</t>
+        </is>
+      </c>
+      <c r="F921" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G921" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B922" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Le Dauphiné Libéré</t>
+        </is>
+      </c>
+      <c r="D922" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027. Philippe s'offre Darmanin (et des frites) pour illustrer son rassemblement de la droite et du centre</t>
+        </is>
+      </c>
+      <c r="E922" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOZEZQTjRrWFlkWEhJc0hJdTM0RHhtUEhzSGI4Z25RbkQ3Tzd5Z0M4bDN4cEVoczFuT2x2aGRuVExPa3pILTJnSDYyV3k5R0ZsYTl0WGxzTC15S0JvMHJNX2tETFBvWEZ0UFVwU0pBNzU4OHBrbHFHSGtlTklwUFJteGFsVHhMcERSNWQtZDlCQWluRFEwSElBVGJ2aG1xcE8tWkNWUkh1cGJYUldCOVI1eVh6OWFzVzlTdDNOSmVjc0l5Q0NEeVQzbWtadjJXQU81UENBOEVjQlozbXo1YmpBX0VR?oc=5</t>
+        </is>
+      </c>
+      <c r="F922" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G922" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B923" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C923" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D923" s="15" t="inlineStr">
+        <is>
+          <t>Retraites: Marine Le Pen a "inventé la réforme qui aggrave le déficit", estime Édouard Philippe, candidat Horizons à l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E923" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwJBVV95cUxPWlR3UjNWT01oVnR0cmhaMzY1ZEVjR1k3TVRjdW9ueU42LVphd0R1Qm1jQmZyNmwta3N1aExPZW9FNG5hWGs2NHlZejh4RUtrTGJXQURnLTJSQzVVQmg0UXpfM3doMWhjclpfLXp1UFJhM1RoNVM3WmFoSk9mYVRYdnFfRWhJMzhBUF8tdHR1dVVDQ3VfbVo1TFRZUC1haVp3MGhpeXZ6cWRmM2FBc0o5TmhtaDlKWmk0SFAtS1NCb1N3WnFZRmJYemJHR01hZ0w0S3d4cjEwM096ek05d3RkMVBTVWhtbVlBbFdJQy0zUm9Ga1BwaGVzdERVYmdHQVc3MEZaeVFVNVNvZ2N3cHQtZzJDVTdBRWdmdzN0OTJra3U1ZUZDSHFYQkZlNVgwTUFZdWd5ZGpkT2l2ZHF5MmdCXzVHWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F923" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G923" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B924" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Gala</t>
+        </is>
+      </c>
+      <c r="D924" s="10" t="inlineStr">
+        <is>
+          <t>Édouard Philippe et Gérald Darmanin se retroussent les manches dans une cabane à frites : scène cocasse à Tourcoing</t>
+        </is>
+      </c>
+      <c r="E924" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQRnNFVkt6c3Y2dm9Dc0NWNjRsVmFoYUJmX05fWlliSHRNUTNEZE92djd6a2tvMk9HeUg3UGsxdm9WR0F3cjVad3pfVFVENUQ5M3hUVHc2SHBEZEstWWlYZUJUMzlYU012Wmp1OFVGeFFTaElFNTlMYndwMUVSZ0VzMC1Qc3RhS2MtWTJ1QnBSWXdoQUVGRFVtcHByT1NDWFNYeFdPalladVBPd0piQ2pIX1V5eHFiRUE4LUZMbHJiMDJIa3licWg1RFhyeEdpSXV1QXk0djRkSzJWRlRyOV9YSHRZRUo3cEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F924" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G924" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B925" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C925" s="14" t="inlineStr">
+        <is>
+          <t>L'Hebdo du Vendredi</t>
+        </is>
+      </c>
+      <c r="D925" s="15" t="inlineStr">
+        <is>
+          <t>« On se plante à opposer environnement et agriculture » : le message d'Édouard Philippe à la Foire de Châlons</t>
+        </is>
+      </c>
+      <c r="E925" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNM3RzSmJrdjZJNU9DUWk4NkI2WHhsWmxGOGFMVmlWZzVOdjZsT2lsc1RyRHVJRE1oeXA2WS1DSlNnSDRZd1hQNjdtbHJHUWtFZ2c0NkprQjh5Y1RVa2JHOUVVbWUtN3VYTEdwTGlDQjJiR1FFSnRkeVZaU0VsMEk4V1FEcW9Ra1ZDTGNxWmQ5ektDdGYwRHlZYVJWankxTFI1THhZZ1d2OTZnbUN4N08tWVFVWEZHbzVrd3cybFlEdVJ3T0txaTBobWxBYjdBZHdfcnE2bS0yek1jMERYT09NcEd0SQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F925" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G925" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B926" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D926" s="10" t="inlineStr">
+        <is>
+          <t>"Je pense qu'on peut faire baisser le taux de chômage", déclare Édouard Philippe, candidat "Horizons" à l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E926" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxQckllVzdueUdLMVZUZ0MyV0loZ19ibEpSNmxIUWJKa2F4cnh3dHNrWWM4MFFEZlU1cjB5TExBa25rOGNRbGwxOWY5U1RDMG9QNlV3Z1B6X1gwTzBJNDI3WVFkYWlCSllWNUV4X19IdXg3M0NsNHpMdW84LXR6UkxpVlZZU0hVOThSRWJvRGJVbDg2YVJHVTgxOV9VVk9VOFBiVDBwbEVQcXhxYXZJNU9TODgwa0diWV9UdHVFd3g1OXBjbWFoS2UyZ1JlalQ2QXpsVWJvSHUyTEdIY0tDSkV3bnJXSzNSOW56bkRuazZoejd6akRxZHNTLTJOdk8wYTI5RmVjSVRmdm1mWXQtREctSnJQUE5OUDMxcGV3?oc=5</t>
+        </is>
+      </c>
+      <c r="F926" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G926" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B927" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C927" s="14" t="inlineStr">
+        <is>
+          <t>Orange Actualités</t>
+        </is>
+      </c>
+      <c r="D927" s="15" t="inlineStr">
+        <is>
+          <t>"S’unir sur l’essentiel contre les extrêmes" : Edouard Philippe et François Hollande ciblent le RN et LFI</t>
+        </is>
+      </c>
+      <c r="E927" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNcjhHSlNqZGpyWnBIaTFOYmxQcTBmRkdqTkJuRXRFQzJUcS1xdU9RMC1xY1RYSkEycXhTUW82ZHpaZXhyRUMtbW1VX2lhcFFPT1FXZTRoWnhCVGh3R3doTDJLdmRBaGtrSTVaZnFXdmx1WlBwNUtYSDkzTW55VnRoRF8xLXlLREEzQUJVQXlaWVVTcmtmZVdyWThXMmhXNVAzTnpjTDZudGVHenplV1duYWMwTUlEdnpqQXRkVkQ3a2R5MENYNU5HM0dsWG90QW1tZHh5VTNIbjZ5UW1QWVZxazl6TUV5ZGh3eE85MGRRMHItdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F927" s="12" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G927" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B928" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Le Télégramme</t>
+        </is>
+      </c>
+      <c r="D928" s="10" t="inlineStr">
+        <is>
+          <t>« La seule personne qui peut avoir une majorité » à l’Assemblée, « c’est Édouard Philippe », estime Gérald Darmanin</t>
+        </is>
+      </c>
+      <c r="E928" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOdVpCYi1ZcXoyUEtMblRGbThrck0ydXRHQXQtVzZHODlRMnZSSnppampKRmJ6al9hN1FBVFNMTUhKU2wzZDNDbjZfM1dzMXEzcXk3NldDUUc1clNnbDJfQkMzMGhGT1ZBenFSN3Q0WnRENkpKLTVaMlIxRXd6ek1BN05mVWotLXBtMEJoMUZpSUF6WnN0SVhpZmVCMjdHdUNYdXZKcTNjdWFRYU5LZE5HVTZYVmFhYjhsNnlBcVhkX213dGVpVHY5VXRESFRUY2htOVI4UzdfMGxLR1EwLV9lNExHYzc?oc=5</t>
+        </is>
+      </c>
+      <c r="F928" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G928" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B929" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C929" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D929" s="15" t="inlineStr">
+        <is>
+          <t>"Je veux faire de l'école une grande ambition nationale", déclare Édouard Philippe, candidat "Horizons" à l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E929" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPc3pBc2FSVnJvdXpIaGdfRHExaFRnUFJXX3d2NWlkVS1KMHE0dVlUYlliQWdsSmtyZFJIak4tc2lsc2NSNGNsR0RwUXM4MmxPWTI5eWZiczJ0TVpscmxfaDFrcjBuS2k1WlRNVmR6RUxuQV9FdjV6bjFxNmlWUU5LRU5mbG96VkYwU0dyY0JQOG1WZE85a2tya3lDT2JMVlpqVFdnRThwZ0xFVG5kSXdqc0VFUzZSV1dBeXhBVnRQeHlOaXJHRERCQkYwd0h5eVh6RGpHS3hWSE52Z2VfS3RmdVZJc0daUDlZMkdhaW1oSWtNVDR3NHpWWWEzdU0zX2lsTWJMbjlJQTZ1Z29UU204dXlqZzBXdzVTX1poZjNB?oc=5</t>
+        </is>
+      </c>
+      <c r="F929" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G929" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B930" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Boulevard Voltaire</t>
+        </is>
+      </c>
+      <c r="D930" s="10" t="inlineStr">
+        <is>
+          <t>[ÉDITO] « Nouveau parti » : Édouard Philippe réinvente le fil à couper le beurre</t>
+        </is>
+      </c>
+      <c r="E930" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOWXl5S0piTVpURDE0Ni1XeFF6UEdveEtEemIySDlobWl5X2ZyUU13M0VNX05UWFE2ZzdqbUphTjVaRlBMbnNwRW9YNHN4UDRfbXZ0RVNqbGwyVzU2TV9peE0yaU5IbEZlOGUyaUtHR1owc0ZfSlVRM2Jheml4NFZ3QzFRLUUxX0NUUXNnT2ZIRmUtb3lpaHRFV1JtUmZuU2s?oc=5</t>
+        </is>
+      </c>
+      <c r="F930" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G930" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B931" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C931" s="14" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D931" s="15" t="inlineStr">
+        <is>
+          <t>«Protéger nos enfants est le premier devoir de l’État» : Édouard Philippe veut créer une «inspection nationale de l'enfance»</t>
+        </is>
+      </c>
+      <c r="E931" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQZmNsN2lQYjFzVWJ5ZWtZNGpnUTdqR2dfS0xnRnAwWE5oalVac1NRR0dhNE92cXdSLTVoU3Z6T0Z6Q0hEUVozLXY2UkV1emxUbmVJdFd4NW5QOGhybThhc1RIMkp3VGJtWGx2c0dqVXVJOXJLUzJ6UVRuS2Fud18wNkRrTnpLU3NPRTFnRmFwclFEUE5aWmVMc1VnNUY1dW1hQ0NGOGdkbnlNUEpvM0FFQkswUTJoLUlaUWJsWjAwTE5MVEpSNWotYnZPNmQ0eDNWeHNUeTZGOV9uR3FXUHFvWlYtenlTWGhuT2ZtV24tdmV5NHRSSW9xTDkwb2U?oc=5</t>
+        </is>
+      </c>
+      <c r="F931" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G931" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B932" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D932" s="10" t="inlineStr">
+        <is>
+          <t>"Malheureusement notre débat, il est trop souvent en France un débat de vieux", estime Gérald Darmanin, ministre de la Justice et soutien d'Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="E932" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxNZmhCVnE5Y25OaGcyME00TThKcVV5ZEZiS2RLc0NLYU5odm5rMzhYcUZnR2d0MF9WS1djU1R3Nlh2QXNRczdrNFNSUUxDRWJGYzVEemZYcnRHVG05djNxZE1PZmtBWDdZV05qZFZ3VEpkOHN1SEw3NjhmUXJCM1ZtTlVFUjJYRC15azl6MEZrZkJGbHlXcTlnbnBPMm40Tlk5eUFLMXBsNkg0dzkzOFpGZG9qblpuVVFnbFVZdWhxa01uTTJkRmU0WktGZExwTlAxUGFidFBqTWNTZkxMSG1sYlgzR2UwLW9nS0lVWWpvNXFDWFBiT054anc2TjRnM3oyUGpLXzRVbTB1aU5oQzJuOXM0eTZBOU0xVlNwVDBnSjhldDZYR0o4Z3FQMWRzMjZ3a2JWd1FWZFUwNk1PRkxMS2l2aG45NHVURHlkUUFrazdsTTFoUEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F932" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G932" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B933" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C933" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D933" s="15" t="inlineStr">
+        <is>
+          <t>"Je ne veux pas qu'on parle d'augmentations d'impôts", déclare Édouard Philippe, candidat "Horizons" à l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E933" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxOb1RjN3dmZ1NNVHpFdzJuTGtoOGMyczdVLU1OYVFsVmtBNEZGWHZOaGpRM2diblVYOHgzVlZYbU9jMjJNdnd6djBIbzZNQU1xeHJWNndCWkZFOXo1eVVjb0lkX3FMNkhnUkstVzM4Z0I1cEFteTEwd3JNWllNT3ZsWDg2dlMyMEhVcXAyR0VoZi1nMk5lUkpleFQ3QTFvRzlQYTdqa3FfVzNjbm9oeHFPZ2hKTGRTWjRZRTYzOFFNMC04Q3diSTFUYi1Xd1BWU0daVndGZFFHXzFYc2pHVnI4TGJXcEpHNVhya3Q3cEtlWmJLZEMtNmJCVXZSQ0FWQThUWkFnYkEtZGw3ZDNKWW4tYllmcThMYi11YkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F933" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G933" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B934" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>France 3 Régions</t>
+        </is>
+      </c>
+      <c r="D934" s="10" t="inlineStr">
+        <is>
+          <t>"Faire le rassemblement de la droite et du centre" : à la Foire de Châlons, Édouard Philippe plaide pour une investiture unique</t>
+        </is>
+      </c>
+      <c r="E934" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAJBVV95cUxOTzc2MGZfQXhqMVhBWkkwaFFPQlUydG8tZktUZE8tcDBZMGpZcThORVNMVG93cEE3a2pndzNjSG94QlBiazRWekJPNnI3aXJJdHhjQXpGN0dvcnBsMjN1SmFBdlI1QmdHZ01VQXJEb2twbF9teUJJRDdxQWVtNTk3Vm1jODBGMy1kTE9ZcnFnay15UGlnWkdYd1loS2tkcFlLMnhSTmNlaWFwbkpsTFRTUUNBM0RjX0pqWmxqbmhjQjRyd3RFYVdmbVAyZmdFT2ZOVUZwMXJ3QnpkaFB4YXJ3QldqczhKZFg0NjJpT01BN2MzbkhrWm90R1VCM2l0ZjFaRGZXbnFNcHczRVZJekZVd2xlS1c0YXZXbVV3ZzM4aEJyb1FpZmNjWmk5TUoxWEJ0NzhWQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F934" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G934" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B935" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C935" s="14" t="inlineStr">
+        <is>
+          <t>Anadolu Ajansı</t>
+        </is>
+      </c>
+      <c r="D935" s="15" t="inlineStr">
+        <is>
+          <t>France : Édouard Philippe juge « dangereuse » et « inconstitutionnelle » la proposition du RN sur le voile</t>
+        </is>
+      </c>
+      <c r="E935" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPd3c3TXdHZDlTQTk3R095Wk5NYkdrSVQ2TG9VY3R4ODNEaldMNm9rREg0U040dEUxd1IxOGEyUlczY0hPbWJNQ18xUDA4VDllMkcydVBfT1ZnOFhkZzQ2QWYwMjFSaUZSN29IdWxNeDlNSTZ5YXMxam00bXpoZk5oOGpneVVXX1ZydDVEZHI4cU03U3BGZVEyNXhZNzBoeXpmMDdJYmVWcHYyM2dZX0lnZEM0LWltNDRONFZrVVdTbndIb1Z3OWRaOW1YV1ZVcXNOdzRrR2o2dWE?oc=5</t>
+        </is>
+      </c>
+      <c r="F935" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G935" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B936" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Yahoo Actualités</t>
+        </is>
+      </c>
+      <c r="D936" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Est-ce que les ralliements, ça compte encore dans une campagne ?</t>
+        </is>
+      </c>
+      <c r="E936" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPU2JQVXBaanlmTXZYZ2hSbVZ2MGRxNFk5emQyLVpqa1BsU2pueThsZVJfWUVxeVczdTNEMlVFZW4zenVJeFJsYk1zOUZmWVBXeTQzMzE0RHFnWUNKQTUxSFhDenQ4RVZMSW40ZHgxTUMzVVNFZDhHa3I5aUxYVmgzNWVVV2Ixd2ZkcGZ2N1M0T3dOb3NVdU5z?oc=5</t>
+        </is>
+      </c>
+      <c r="F936" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G936" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B937" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C937" s="14" t="inlineStr">
+        <is>
+          <t>www.lamarseillaise.fr</t>
+        </is>
+      </c>
+      <c r="D937" s="15" t="inlineStr">
+        <is>
+          <t>L’eurodéputé Renaissance Grégory Allione soutient Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="E937" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQYVZCalRPWHZzUkRFcWVrVHNyMUl0MjJJaFlQdkZrbzlHazNfTEUyTndhZ0Vlek42cjR3RTFCYzBDblNVX2NMRzA2aUJ5a2lSZ2dQaV9XeXVZS2Y3LVNnSjQ2TVNSNTNPeUczWm1ic1JJQ2JRSFRoNXdPRW0wUGFzSGhhbmNiMTc0cV9mT19mXzhYdFUwOWxXZnMwR0lPb2VxN3FiWjZOTXItamNSZkRtalRIM2w5LXdB?oc=5</t>
+        </is>
+      </c>
+      <c r="F937" s="12" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G937" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B938" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Le Gorafi.fr Gorafi News Network</t>
+        </is>
+      </c>
+      <c r="D938" s="10" t="inlineStr">
+        <is>
+          <t>Après avoir servi des frites à Tourcoing, Édouard Philippe participera à un concours de tuning</t>
+        </is>
+      </c>
+      <c r="E938" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPNnV3a0VVYXo5NzBDckxXdFY2WUY5eVV4cVdZMm8zUVluN3BuRGVmOGt2RDBIZlF2ek4tT1N5a3RiSXQtQWlhaHNTclFNX3VLRExGTXpqLVRkT1Y2XzVNZzJNN1ktNTBiODQ4RnV4TlZoSmlWZEw5VjVDY2pjM3BMV3RKRjRwUjAwN3RtZVNraktYOF9vNmd0eXp0YXg4dHNEWTZ1SjV0UHFLV19zVHRlSjhxWmpNMDdXblo5aGQ2Tm51aENmT3JUWdIB0AFBVV95cUxNR1dOR0hrVUlBTHo2emJzS2tJMG9TYW9uaFY3bVdYQTRtNW11bFNsZTc0ZWJkM3pwYjFFNmt3WFVHMHU4T3BUY1NGSFVkMEhGWExFS1NtWUZaSGpDMzdjUEc4eGQyVzBMeDBjdlVtVkJQaEhLYlpJdGg2T3ZGNGhzOXhsV0NEZnA1eE1UdzJxX1gwMDRsejF4c05sZC0ybDJEUmJlRUpoNERhM0ZYcTBWYjNncG9WZ1BrdXR3emxqTG5KSnFoQlQxNjdWa2Z4TkhQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F938" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G938" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B939" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C939" s="14" t="inlineStr">
+        <is>
+          <t>capital.fr</t>
+        </is>
+      </c>
+      <c r="D939" s="15" t="inlineStr">
+        <is>
+          <t>«Nous allons tous devoir travailler plus longtemps, mais pas dans les mêmes conditions», affirme Edouard Philippe</t>
+        </is>
+      </c>
+      <c r="E939" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxONF9DeC16TVU3VGJCM1FNQWNhWHpQOTJMTFg1NWpsdUx4dlcwdWM1bWUxV2FNVjZMMDJGUW5LTURmSU9Lc1o1REFPZV9ORWdjUG9DRWg5QnRCN3VRUHVLN2RTRkZqNnpZZzhqVW8ya244V1NaSngzVzNvT2U0d25PYzZiQTdRVF9NQjUtR1MyZlBvMjYyNWc3a055ZTBmT3BuN09HNDFtaHg5Smt2NHNhV1U3THBmcEJxOHF6bFRZR1VZaDlhS3VtcTNDMXNFQ2M1MV9aeGJ6TERuUjBsaVAtMzZvbDhHbTk2S0xN?oc=5</t>
+        </is>
+      </c>
+      <c r="F939" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G939" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B940" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D940" s="10" t="inlineStr">
+        <is>
+          <t>"Épargnons à notre pays ce terrible sort", lance Gérald Darmanin, ministre de la Justice et soutien d'Édouard Philippe, évoquant la possibilité d'un second tour entre Marine Le Pen et Jean-Luc Mélenchon en 2027</t>
+        </is>
+      </c>
+      <c r="E940" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_AJBVV95cUxNdWpjZFR3UHBPai1fWnllZ3NOUWhCdWNhMUZ2Q180d292dkw2cEE0RC1KMER2dVBFSTVjTWkzbUg1MWZBU2s5TVFnbkNLLWMtRV95WnNaeFdFdTY1WnZXWXBrVWZ6S1g4SXRKbXprUmxXdm5hVFdYQmxXWkpGaVlxZ0hjbm1rSWtHZExveXY2ak9EcTdyMnlQSjJKSGJJaWZtWDEwdkxpQXNkcWRrSmxRQ25zOUZFSzZYbWRyTDhkUnJ3T0dLN1Z3TlRDLUc5RUtBT1JrX0RMZGNZeldLbUdkOVBBQTU2UHk3UG9SVlBJYTRXNEJJOG9UdXVqdUFweGducDN6b1czWWl1WG5NZlNkR3hlblBpXzBUTUlsQXFGeGZCQUNGYjhkcWV2UXMyS1J0WFV5Q3l2TzBGN0VPLU00ZFVlUFU1TFhnR0FUci1rME5hMkd0T0NJWUFnZjVWLW9jeHRvQklwNHFlMGdiQVJ1NXhJTVZFZTdxT21WQw?oc=5</t>
+        </is>
+      </c>
+      <c r="F940" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G940" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B941" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C941" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D941" s="15" t="inlineStr">
+        <is>
+          <t>"Nous devons régler cette question des retraites et pour la régler il faudra que chacun travaille un peu plus", déclare Édouard Philippe, candidat "Horizons" à l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E941" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gJBVV95cUxQVkt0dHppdUtsOUJBTkRkQVFGNWJIU01fVU1BZS1yOXZ0YUtiNEUtQzQwTUJyRUYzZzhhXzRjaEI2a29id21FZlFEODU2SUxrRmtfdkJLRkJKYmZ3U2EwTEgzbFZRdkk3RzRsYkhvTE80VnNoZUVFQ2VJUlVqSGZFZzlzTzNkOWNCdDc0RTFoV0puZnJ2YTVSdEZ5Y1pBWmFjYXYyS3gyaUFvMWNCOVJHbDdiSEtVUFBiZ0NlUldMZi1xUGJaMGVPZWljajItajEwZ1MtRHI0cWZOalFYQUJhbXp2dXBkdm5kbi1NbFVYcGRoZGJjU2tZY3lWdFNCaXQ0dnhzdlFyT09VWVNNRXJuNlhDSnBadFE0a1I0cDh2RFhWOUc4T0E0ZGp4dGpzNHZBTmRJOF9KTVkydy1naHBxQWZHZVdualZZWGxnUEdvZUh6Q3ZJSzNLdDYyQmJoTXBGZ2NfTGtn?oc=5</t>
+        </is>
+      </c>
+      <c r="F941" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G941" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B942" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D942" s="10" t="inlineStr">
+        <is>
+          <t>"Il n'y a pas d'opposition entre le travail et la solidarité", estime Gérald Darmanin, ministre de la Justice et soutien d'Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="E942" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAJBVV95cUxQY2EwR0lZeXIweFVPaUlaOTZfMzFHOTNjallXWXRSREx2a1Zsa1RPUGliUnN0ZE1DU0hPMXNYUjRxOWJrOHR1d1dhaUxxNkZXV3JRdlc3Z1ZBb2NKMjhCZjJoWFFPazF3QUNyR2N2N0xMRUIyOGhjdWNIajhmaEhEck1lZXR2cXpyY0RHX1RHeWNvMWtlaUw2M1pFbm9TS1JfRzNUWFNoczFRQUtXYThCSExiZmloV1QtT2d0QnFPZFotUmVIOFZueVNOTmVXR2Q3R0FXbVdEc1hfcGJaTzkwNVd3bW9XWWk5RVc2MHVNV3k0dVhDX2psNTRSSXRzQjZuVi1NcHZBM2FjMnQ5RHlDODlsdDFmUTN5ZW5MTllvNXNYUy1nVGx3bndaS1JNYnpKMEZRdi1panJxbHJDTjh1UA?oc=5</t>
+        </is>
+      </c>
+      <c r="F942" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G942" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B943" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C943" s="14" t="inlineStr">
+        <is>
+          <t>La République du Centre</t>
+        </is>
+      </c>
+      <c r="D943" s="15" t="inlineStr">
+        <is>
+          <t>Une “confédération de partis” : Edouard Philippe veut créer une nouvelle formation politique en vue de la présidentielle</t>
+        </is>
+      </c>
+      <c r="E943" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQZklpU0ZrckhIbnlodjhGLU9OejFPUENRVnRCdnhWQXBvcURqRVZyd0tOY3dPT0xISDV0NzFqRWdYX3NGQUFYVThRbmlfUGtac2EycUt3dFhmTW1IV2U0MFBWcnVpTkszM1YxMXdyTGRrSjVUZlI0V2N1Q3pXTFBUVjVyRm5MdldjYkdGb1VYa0VvVE5qYXRrVkVrNzZqVlJTX19oZjNwam5yQ3cxajVuaUIzeGg3ZjFHWWlIQkdCbHF2R3N5ODk2MXZ4MUN5VUhyTFdVRG94MS02SHlucUVMUDZLQ0dkWnIzd1BYUG5GWEo0S0pJRWFxUFBxeE5MUlRB?oc=5</t>
+        </is>
+      </c>
+      <c r="F943" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G943" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B944" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D944" s="10" t="inlineStr">
+        <is>
+          <t>Référendum sur l'immigration: "Le référendum n'est ni un totem ni un tabou", déclare Édouard Philippe, candidat "Horizons" à l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E944" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgJBVV95cUxNNE9saWlTTFU1SDBfYnVLbzFLMGxpdGZ1bERSTmwwWGVKOEV0MFFBZmcwcjhqYUZFRHZCaWx4VkZxXzhBZjliX3FhcmpBZmNIRWJUU1RFM1F1OERrLTFGSGhOUU00cDVjdWNIOVZCVG1QOGwyV19mU3FhdW9nUFU3T2dHZV9Oa25sbnN0ajhvZ3ljTGtqSnlpUUhkcHo1MEFFdlZxOGpwVUJKRU9OZkVTbzI3N0JpT1BtMldYS1NFbEV4bXFIaXoyMnV0VkJYbXQtVElCaEM2TDA0NG1pV3Z1X05HUmNVVG16UWFYUzR3Xy01SnJhbHJmVVZCa0lOT01Qajk1YzdqSzlZRjJVaXpJUHYzaGZYbjRtLW9FS3Y5MW45eTBESW8xSGtINDBvTHZLSzhxQXJn?oc=5</t>
+        </is>
+      </c>
+      <c r="F944" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G944" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B945" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C945" s="14" t="inlineStr">
+        <is>
+          <t>Le Télégramme</t>
+        </is>
+      </c>
+      <c r="D945" s="15" t="inlineStr">
+        <is>
+          <t>Dominique de Villepin « veut être candidat » à la présidentielle pour 2027 et tacle Édouard Philippe sur l’immigration</t>
+        </is>
+      </c>
+      <c r="E945" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNYTEyNDJGOVNRSlpZelVzTllMc2NLbHRkN3dNY05UenB2THl1eG5jT3VuVnpOSXRuWF95WEJSTEYyUFdwaFhBdnRQS3R1VlRyTGNCa0VaSm9YZ2xhbkRJMVZ6RS1qemd0Q3Q2cHIwakRKTGhKQ3k1ODNiRDBMeHFfRGlWcTJ1TnI0VXRmV1Vralk3dzdENEpmREtjbFNZbjRDYU1SQ3NmLXlCbTNlaUltVUQ0RWxGRFpYbWtJUzN6NUJUVTd2ZmVCYWV5T3pES0FaUDF3U3ZMYXFfajR0OHl1TG5WSW5iQWVtWW01RWJ1MmcxQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F945" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G945" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B946" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>tv5monde</t>
+        </is>
+      </c>
+      <c r="D946" s="10" t="inlineStr">
+        <is>
+          <t>Face à la poussée de Mélenchon, des appels pressants à une primaire de la droite et du centre</t>
+        </is>
+      </c>
+      <c r="E946" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQRjNiOXlaeUNadzVnNWREbFNYX3ZsZmtTdXRSdEtyamFZUnpCU3FpRldzckpDQW5PWGJSVFhuZ1AtZGw0Yi1uOGNKX3pyT0JpVmlCNEdEbHR3UWs1MmtTdHg5eXBiQ3dkMHJrSWVZLUxSSzJjVV9hOU80MTBjVmsyclF5dlhmWmZKdmdwb20tYVNLZDNLb2dIUVJpNUNudGtYTDQ0Q3hmS0ZUa2U0RHRsalJxUkYxbU9aeDJuZHlxaUNKWkhxSmZwVC1HM2ZPcERJUlladzUzcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F946" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G946" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B947" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C947" s="14" t="inlineStr">
+        <is>
+          <t>melty.fr</t>
+        </is>
+      </c>
+      <c r="D947" s="15" t="inlineStr">
+        <is>
+          <t>Édouard Philippe veut "mettre fin à l’open bar" : moins d’indemnisation chômage et des arrêts de travail davantage limités</t>
+        </is>
+      </c>
+      <c r="E947" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOeWs2YURxZzFoeDMzZnNNcnJfdlFMcDkwTVJyS3ZtbGh1S3ZRRWd2VUNfdDlhdzFpdVc1ZHF4UmN2cHF3cVJOdDliRmVwVTVZODRydmwxSUtaWTYwc3BRVExlUjl1eUN1ZFk2ZC1pN1RjMXExcjlUOXhoU1drVzF1ZExPNWFyV3l2YUt3dVFUdkpDcmZYMlNHbWxRZjZUbU04eVBzdkF0a1NYUTVSb1BwUG5MSnE2SHJraGhoRlgwZ18zSjkybXBDa002Z0kzUFVSQ3NPLURfLUJxRnp3N3NQS1ZHNVV4bEJHMmZPZnZ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F947" s="12" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G947" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B948" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>capital.fr</t>
+        </is>
+      </c>
+      <c r="D948" s="10" t="inlineStr">
+        <is>
+          <t>Salaire des professeurs : ce que proposent Gabriel Attal, Raphaël Glucksmann, Edouard Philippe et les autres candidats</t>
+        </is>
+      </c>
+      <c r="E948" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxPSGpZZFVONW14aFZYcF82by05dVY0WHVVNDlSalp5UUg2T0ZEQkowS21OZXZiYVlURFl2ZVQtYUgySEIzZ25DUDBvUk5mb0xrZm1ZS01xcGp2akxsT2dFYUdzX1A2cXJyLXE2cWlpa3BTRXNmTThyVjNaZHh1SmYtUFBxQUlyY25Kd1ptUUhsX1ZnWWljaEZvdl9SSDROQWRYdzltdjcwaWVwdUJoN0RYTUNaVndRYzRISV9NYlN1UFJQRGxvYmk4RVBYNWpSRmRDWWJpaHEtT01XRDJhaTVWNDU2NVBUaTNkdk12SkdSWFBHSGY3dTBv?oc=5</t>
+        </is>
+      </c>
+      <c r="F948" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G948" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B949" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C949" s="14" t="inlineStr">
+        <is>
+          <t>sudouest.fr</t>
+        </is>
+      </c>
+      <c r="D949" s="15" t="inlineStr">
+        <is>
+          <t>Élection présidentielle 2027 : Gabriel Attal assume ses différences avec Édouard Philippe et ses « idées d’il y a 20 ans »</t>
+        </is>
+      </c>
+      <c r="E949" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxOWXY2YmNydkJZZWYzME9iUE5pSlp4Sm94RGtYMGdpNWt0b2UxS2xWSkhxWTNUc2V2MnNjR0xZV2NnM1dTRzVTcmh5d2lFLWFqelRWSXozOFRfRXF0OFR3cElRM3N3YzByaGNULUNrNlR4azhoS3BBQXRYVWNNdzlNRzhvVWgxNWlXMkNOYXhIaFJjbkU0bVNXeVFnN29KeXFNYTZJVmNiVTRycDhHaVZJbkIzVlA5VWNydGZvQXBEOUNacG9tTFMyUURIeXd1U3JUUnJLQkVLejctUmVBQmpnaHFzS0M5Smp0cWVZWTFzbGlJQ3RNSzZuTVF1OFhrRXk2aXUzOVFyUUk?oc=5</t>
+        </is>
+      </c>
+      <c r="F949" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G949" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B950" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D950" s="10" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau et Gabriel Attal y sont déjà passés: les patrons de la grande distribution recoivent les candidats à l'élection présidentielle de 2027</t>
+        </is>
+      </c>
+      <c r="E950" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxQNERzLWRnNzFVeXJnZEZYYVItdmlNNkNEdXVPR1p1cTNRdFBwZ0p3ckp1V3RKWEp4OW1KdV93TmVkZVM0SUJhYTVOSlMySDRrZkREWWlkRVFCVU0zN3owT09oQ2h3dE1qRnRaUU83SnNBaThaUWZUNmxlYmZQN3JoZjdFSDZ2VmFHXzNCS0xsRDJUODQtUUwyeUNfb3FfcEFyNC1zX2RYaTl0NlFOQ2JLOFBIQndmTG1CRDlpWXZOcnhDanhSaHh5YWxzSXMweTVvMEtEU0ExSE1BTFJzWUlwWFRxOEZPYkY4dGJWNFR1SkZYRUpBSDJCdk81NEdobHk4bjNJU3FfLVJQZkYwWkFnZXB5eDJkc1lzQnhNSHdhX2UtM3g1ci1qTWtjOHlWSmlGNVgwVFJVRXZ2dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F950" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G950" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B951" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C951" s="14" t="inlineStr">
+        <is>
+          <t>RMC</t>
+        </is>
+      </c>
+      <c r="D951" s="15" t="inlineStr">
+        <is>
+          <t>[Podcasts] Policier, journaliste... Gabriel Attal dévoile sa liste - 02/09</t>
+        </is>
+      </c>
+      <c r="E951" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZEw0NFRBN0Y2UDdMNW01RkYtUHk2cXFmSkRaLTBHbEpNODVBeVMwcjc3WVhrbl9ac19RdUZIRjBqVTJiSVdhWVJHMENEZ2hLOFFUTzNqSFF3TVlHa1VPM3pBWU5CTkNMUEZaRXl4bG1ZT2dwa2hnMzhWd3VxQkQ1S2ZBdFhqeXdLLVN0LU50RHZIcVdFRzdmdWRiSG5HM0NOazRYN1ZJTnM5bEVhWmVYYWtYdi1QTXBwR3VXRlBUUlI5cWxaNmxEaVM0Y09GdzQ0d0FR?oc=5</t>
+        </is>
+      </c>
+      <c r="F951" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G951" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B952" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>france24.com</t>
+        </is>
+      </c>
+      <c r="D952" s="10" t="inlineStr">
+        <is>
+          <t>Attal "n'a pas peur" d'une primaire, renvoie la responsabilité sur Philippe</t>
+        </is>
+      </c>
+      <c r="E952" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQVWRqcm1MUDFqTUlpalVpcnlXZ1dpakVQb0xDR2oyT19rT2tjOUtsZkxuazVXU0NzUzZXMFpHbVZ2MUNZRm01YnF6QkVMSm5DNjVUS2VGQ3ZvOEloYkV6dlRGWk1GV3VIa2ZMT3hSaTI1UE5aTndUaVZEbVIwTG5HVWQtc3BreFI2S0FXM2NNejJZbGFfeHV4ZVoyZVgtRVFBYTNkUW5sZXRUa0pPZjcyYkdlT2pFdHpjdVZxZVF1ZDBTa05PbzhVaXhR?oc=5</t>
+        </is>
+      </c>
+      <c r="F952" s="8" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="G952" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B953" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C953" s="14" t="inlineStr">
+        <is>
+          <t>Actu.fr</t>
+        </is>
+      </c>
+      <c r="D953" s="15" t="inlineStr">
+        <is>
+          <t>Mélenchon, Tondelier, Attal… Où et quand voir les politiques présents à la Braderie de Lille ?</t>
+        </is>
+      </c>
+      <c r="E953" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNNGIzakc5S2VoRFJxSk5HbTVmV1NfaGQ5ZHAtY05MTWEzYk5nN3NPQllFZ3lqcGZKVjI5WWFudzkxN2UxZWVZOEpjTTFqc0Jfd0FkYXNuTTdxSmtfSnJFcUlhRE5pZXR3VzJtelhFY2otb2Rrck1aSmhJS2xuTjNqcXJ0NDBBcTMyaHFmb0llY3ZER1hWVUdJT0h0M1FKMjBTZEZhRF9paWhTUkY1WVFfelNxdXluaGE5S0loNFBSc3hDY1RCRUw3U19BMlN3QVdvNDUtcWxxYk9pRWd1TTlkSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F953" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G953" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B954" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>tvmag.lefigaro.fr</t>
+        </is>
+      </c>
+      <c r="D954" s="10" t="inlineStr">
+        <is>
+          <t>Judo, «Stade 2» et «L’Île de la tentation» : le parcours étonnant de Céline Géraud, nouvelle porte-parole de Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="E954" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNNWM3LVo2MVZNXzJRNDh1ZnA0SlY2MFhqM2Q4Z0VFQVhXaXJwVER1QzNuZWNOMlNfZFJIWC1qbjFKSjN4OV9Cb2tnS3lpZDJydFpsSkRRcWN2d2xmcTU0Q1NfQjlRNWtzaFdIRWZ3ODRTVU0yUGZtNTNHV00yWWgxejZtT1pqazJ1S2NuZ21OeFp0Vl9pN3VXaktGMkF5aDRTc05LMXhUNS0wRUdIVVVqMmNwdHpJRGljeGd4YkE3WWlTWEVIbmI2QlFDbldwQk5EYk02V01rUDZwZnpVZ01kNmw3RVN5alZ2d29ia2oyUU9lRVNBaUVoQ1dqcVFqY2UxNkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F954" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G954" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B955" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C955" s="14" t="inlineStr">
+        <is>
+          <t>tvmag.lefigaro.fr</t>
+        </is>
+      </c>
+      <c r="D955" s="15" t="inlineStr">
+        <is>
+          <t>Céline Géraud, responsable de la communication de Gabriel Attal : «Je suis prête à aller au combat»</t>
+        </is>
+      </c>
+      <c r="E955" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNc0JIdlZrSXFsUzYwdUFnOVpuTmhaSnh2cDQ1VDJvUmhxVkk3U0VkSlNvbFJ2WUlwXzdjN0Rqd0NrM05GMGlkV2JPQ1l6X2p5Z2I5TklHRHVCaE0tdHQzVllVXzlJbnhwREtBTzZpZjNjMk1Yd2lZYnU4T2kwQk53dWpvVnFXQzBwUlNSVmJ4eTJHZkE4VVNVZW5hSUp1b2E3LU1saHZQRWFaZjU2OW45U2lIcEthOUNmMjZsMmlnZHZ1TFFFQjJDQlNSNDNDT0FNUU9YaHZoQjZUb0NsbGd0WE8zc1JjTWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F955" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G955" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B956" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>capital.fr</t>
+        </is>
+      </c>
+      <c r="D956" s="10" t="inlineStr">
+        <is>
+          <t>Salaire des professeurs : ce que proposent Gabriel Attal, Raphaël Glucksmann, Edouard Philippe et les autres candidats</t>
+        </is>
+      </c>
+      <c r="E956" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxPSGpZZFVONW14aFZYcF82by05dVY0WHVVNDlSalp5UUg2T0ZEQkowS21OZXZiYVlURFl2ZVQtYUgySEIzZ25DUDBvUk5mb0xrZm1ZS01xcGp2akxsT2dFYUdzX1A2cXJyLXE2cWlpa3BTRXNmTThyVjNaZHh1SmYtUFBxQUlyY25Kd1ptUUhsX1ZnWWljaEZvdl9SSDROQWRYdzltdjcwaWVwdUJoN0RYTUNaVndRYzRISV9NYlN1UFJQRGxvYmk4RVBYNWpSRmRDWWJpaHEtT01XRDJhaTVWNDU2NVBUaTNkdk12SkdSWFBHSGY3dTBv?oc=5</t>
+        </is>
+      </c>
+      <c r="F956" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G956" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B957" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C957" s="14" t="inlineStr">
+        <is>
+          <t>journaldunet.com</t>
+        </is>
+      </c>
+      <c r="D957" s="15" t="inlineStr">
+        <is>
+          <t>Gabriel Attal affirme au 20 Heures de France 2 qu'il faut une "réforme constitutionnelle profonde, pour mieux partager le pouvoir" dans le cadre de la présidentielle 2027</t>
+        </is>
+      </c>
+      <c r="E957" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwJBVV95cUxPMGJkVGZuR2c0VEIwRS00dkRsVFJsbzBua1owUnJyaDhEd2ZSTGNKZmxmcUpHczZ6WTkwa2dLUTFvV0NEbXl6amoyOWdhUGhZWF9tX0ZyVDdFREVBdGY0N1Bjc28yMW1XRENSbkFuMHZrQXJRc0RHeElHcXg5Z3YxMGRKd3BYVEtzNUJOeFlFVUFsWFZyUUI1eWN6UmVyMWtIRnQ4bExaMkFwM0xtNTJrVkRaaDFCcUtqTm9OWjB5NkJZN3o0SkdGYnZTRGRLSDRGRzllMEpIaDh6LS1obFpkdWprc3BnbnZXYjc1UmxQaUdNbFZqMl9IOHdGZHZUY0VNZUxjbzUxcUx4eXRoWjg0c1hZM2VTVmpaQ1MzQW5SMVRxcFhPeU9Hak9OLUE1ZmpPQUJMQzJaR2hZdWhXeXd1T1QwQ3o0dFlwdndOOC1KUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F957" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G957" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B958" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>dna.fr</t>
+        </is>
+      </c>
+      <c r="D958" s="10" t="inlineStr">
+        <is>
+          <t>Rentrée scolaire : quand Gabriel Attal réutilise une vidéo virale de l'équipe de France</t>
+        </is>
+      </c>
+      <c r="E958" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQaHZTWmdLUWpFdURUbjh2VDV4T0ZEYXpXazVLbTMyM2doYWFybGVjMXkxQ3hULV9EaWxVZDBkQjNoaENlWW5Xb0FWOVc1a080REhMdS05OWt6N3lMOTFSRC1YMXJpUWNuM1dUTXdOaFhELTVXMjl0WEdsNm12cVBFeHNuR19EREVYOWJWYmF4QVFjSnZ1YzNjQlZIWnJzQkRRMVZHd1lTaGJfUkRxZS13bFdOc1Q0Sk9CTWR4bjVsNktEMUtFaHV5bmVsalJkMjBv?oc=5</t>
+        </is>
+      </c>
+      <c r="F958" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G958" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B959" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C959" s="14" t="inlineStr">
+        <is>
+          <t>closermag.fr</t>
+        </is>
+      </c>
+      <c r="D959" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Gabriel Attal veut racheter les dépenses d’Édouard Philippe pour s’offrir son soutien, "un chèque qu’on serait très heureux de faire"</t>
+        </is>
+      </c>
+      <c r="E959" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxPQTJaeUFycktTTUhQRUYtOGlYQ2Nxb2hET0J4VGJUdXBTREowQmw3TGprTjlyaG5YZkFuZ2tsTnYxWEE5NVF5alQwRlEzaVdyUktCYXN3NkVZM3NiQ1RoWkEwYUlYTDYxZjFQc0F1Q3E1VDFBck0xQzZqSUJqV3pkdDFLNnFRQjB6NENOSFJ4Uk0tZVZvcVE4MkFreTNidkxBR29uYTF4UllLS1dkODVZbEd3c3h2d1YxSkQ5NjZURzNVZHpiV3l1RHlOSXFuVkJBSzhMSkVGSjdxRGRTRlhfOUItRV9xUHpBeHA3aGJ0elMwSGZPQThhTTlKT0FKb2ptTTlHbjdnSFY3NEpvWlVZNk9VaWR4WFpXT3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F959" s="12" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G959" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B960" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D960" s="10" t="inlineStr">
+        <is>
+          <t>« La dispersion est mortelle » : Hervé Morin défend son idée d'une primaire de la droite et du centre</t>
+        </is>
+      </c>
+      <c r="E960" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQNXpTNnBsNHpwT2I3RkNLNnh2VnNmeHN3TTd6MkdxVzB4Q2ZCZEIxaDk1a0Y3UFBvOE1mQ05TUWxfM1hZUGhlSGNEYzRyMWt1dm5uSnF5c2t5QVFzU0ZBNXZxc0Rlemt1dWJfTlMxVDhIajRLVDh4TnBxYnR1SGZ4Wkg1cTd2d0NSTnlPUEJSaHFxZGhPVWxwQ1RrN2o1RkdycjNsTUtXWjFYVlRZWHRQb0pkVDN2V01CYU9xTEtiUFJWNU9oZ2I0?oc=5</t>
+        </is>
+      </c>
+      <c r="F960" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G960" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B961" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C961" s="14" t="inlineStr">
+        <is>
+          <t>Public Sénat</t>
+        </is>
+      </c>
+      <c r="D961" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : que proposent les candidats pour l’école ?</t>
+        </is>
+      </c>
+      <c r="E961" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPbWNSc056ZllXUE5DVWRyb3BoLVprSkRMNWw0NWYwa3VkcFc1T0hIZ19TbmxoYlhyTFkwNW5EUFYxWUFBMkpWbEV1eE5Xak83NGNWeDl3Y0FlRHUtWV9XaFhvckU1UTQ0bm92OF9UOERFRFBGMnZMczlLNG1PbnB1U2FnT3lrM2phLTNzMElqQ3M2SldDd1doWkpsMW56R0tqYnJvNlZSTG42ZkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F961" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G961" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B962" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Ouest-France</t>
+        </is>
+      </c>
+      <c r="D962" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027. Face à Attal ou Retailleau, « il n’y a pas match », c’est Édouard Philippe, dit Maud Bregeon</t>
+        </is>
+      </c>
+      <c r="E962" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPVmhrWFZYeTBMQ003cmhWSDkyWUxWcFlmdENlSWRLUTdNVlZGaWFhTFRWZDg1SjBXeEZ3YkdLZHVUa2dhX1F2ZjVzUnpHeloyWVlMMmlNbTVaTXdIUUtrSzZEd21tNXg4WVV0dHltdHZkY2d0VE9BUHdxLXJrUEtMalA1Y3IzcUZtUXlpMDUyaWJLanhBdWNEN0QwRFI1bVhnZTRxTzItZVZ2N2NlWm9hTzR2NjYwUVdMOElzR3pqZjkyemVuMWgzaS1zZnB3WFk3NnUtTVBvQmFMeGtpM2xKZHl1UFh2SWpidlJQWi1Wc1hPZC05Tmx4M2FuRW5FQkdvTWw2QjdEQkhFN1IzTHlqTGdvVHNkYXlMODFCdUFR?oc=5</t>
+        </is>
+      </c>
+      <c r="F962" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G962" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B963" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C963" s="14" t="inlineStr">
+        <is>
+          <t>Boursorama</t>
+        </is>
+      </c>
+      <c r="D963" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle: Attal regrette la "tambouille politique" dans le bloc central</t>
+        </is>
+      </c>
+      <c r="E963" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNM2dqM01yaGRhakJ5ZUFJS0s1S2U1bFpWTG1BTmJBU2xyMWhXWlducjhDaWxqQ0dpV0cxOFo5WFBGaGo0Qk5nYmtEc2d2Q1R1T3FxanVFMV9YTlNiSExRZERWQUZScVpyei1wUFR4dEtCX1AwYm1VamxBRW1oQndNcDNDQ3RQazFCc2V1Q3VKM25sVzVrUFFzZ09IUk9MTEFnbjZnMFk2NTlnVXBscEM4UC1GYTBUWm1GYmsyemYwMmxMUGEwbHNvSVprVDJPR01hWHdiVHpfMTVfVWt6RldHYnpMVlFfLW_SAewBQVVfeXFMTjdOSlhGamNSbFJjYnRkOGthSFl3OUFfSFJQQ2FhYXpOUHpBUEpXTF9qREQ3N0hYSFIwOXl3dlRqdlZNZVdsdjRJcXh1aF9tUnFabkxLaUpXRmhFbzV3NHZiQnFOMUZmZmgwYWNRYmZxNUlmSm1sLWdRTGp5Vm13dTRreDQxc1c2UXQxLTM3S3l5Q1IyY2tTTFJMY0JqUlluQkFBR1RNVEc4dWIxVVM2OWhoYldpRGpEeHZwR2VDSmFTU3FDWl94eGNXb2wyb1BJT3ZqenIwYjNCc01TV29iVnp5RGlSZTNIb0pRemg?oc=5</t>
+        </is>
+      </c>
+      <c r="F963" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G963" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B964" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Yahoo Actualités</t>
+        </is>
+      </c>
+      <c r="D964" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Le « bloc central » est-il forcément de droite en France ?</t>
+        </is>
+      </c>
+      <c r="E964" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNR2ZxZ0hyN2pmcDlOQ1VuY0VodjVVS3hFTlNockRvTHlkck5OVm1XMHZSc1JILUpSMVowRE5KR0x5ejV6UG5XT2RUa0x4NWhNQ0hyTDF3RTlSY1dPZXVBOWd3WUZ0VkpsSEl1UWNoTW4xNmkwZy1jY0JKOWlWc0V6elRYcFlfUHRqUGV4YVhOZVNTYVhtdTdCRE1MVnNGbnh6?oc=5</t>
+        </is>
+      </c>
+      <c r="F964" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G964" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B965" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C965" s="14" t="inlineStr">
+        <is>
+          <t>jeanmarcmorandini.com</t>
+        </is>
+      </c>
+      <c r="D965" s="15" t="inlineStr">
+        <is>
+          <t>La journaliste et ex-judokate Céline Géraud rejoint l'équipe de Gabriel Attal pour l’élection présid...</t>
+        </is>
+      </c>
+      <c r="E965" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gJBVV95cUxQVF9wOWt2dENfajJvNk9UYjhYYkhPdk0zU25MTk5iWmQ0VTh4ZGlwSUgzYTNHNjJPenhwRzh2OXIyU1IwSEpJUUxJVldxM0txRWZsa2Z3WUlfSmhISzA0ZGFoRFFKby1uTExGR2Rvbmd4bnBId21iWWlUaHZSZXVFQ3E1VjdaUndVdmRHVGRSMXZac1laVFdka0dzdFlhMnoxMW5JbUJhaUNCV2xwb1E1bmVnQ19NU1I2UE5sZktEaVNmdXU0THV5LUlaYTZUUzhtdnU4d0EtNWZQeWNsNmsxbHpWWU1rNGdGT2JrZ2JYM29BQ2dXeF9OLURPWnFST3JmTGpzSzdVVWQyVmdocjJCbVE0aUJ2WVlmMmJldXZnXzYwc3FIOVVTNEpMXzlIZmhacGp5ckFEZzgtUDYwMldHNzViMVFnNi13VTJOdUlnUnNxTVA1ajhFWFFrMV82Z9IB4wJBVV95cUxNVi1DZDRyV0x3bmUxWVlmR29wNjk4WmxOX1JWUlpsMkpwWXhaVjdYTklSZDltS0s5REFPVHBNYS1ITnpILWhlV01UTTBtdXpyUDBIZDFrWE9veHYtbS1EQ0VOcHBFTkV6SUQ3LU1sdm4taFg2ZWN0Vi16UVZldXljdVlqQi1ialBZd2tKdmFyZktxTTRnQURhaTJ4OV9FY2UxLVlrbDYxaTBwQ19aWV9wMm4wby1lNTYza2w0TUNZWGhjNks3c2xWLTd2VWRPM0RnOHozcUYzS0dyVVVoQmctWF9heVZVeTVMS0ZIY2REamVKMEpKOXdZR01mQVd3Ni1VY3dXRUFJNWlIV3N2VTRiOXpKbkJiVXRfNGtDWXA3azJDclZUTzJWMExiNVdyVWtxZUR5eHo1cU03UzVEb0dIb096d1NEVGZNWlFQcUFkYy1Fczh5aUF3N1dLQlBIWW5TbE0w?oc=5</t>
+        </is>
+      </c>
+      <c r="F965" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G965" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B966" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>programme-tv.net</t>
+        </is>
+      </c>
+      <c r="D966" s="10" t="inlineStr">
+        <is>
+          <t>Céline Géraud : Après le judo, le journalisme et même L'île de la tentation, elle s'engage en politique aux côtés de Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="E966" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPRVBWRDZCSVBXVW5EY05rWlYwbDhHRmF6blh1M25FMnFIcjRrblREX214TzE2dEQzd25TdW9GQWNULXRURnhMZ0pITk1nYkhhZThqNFV4SlBncnR0NU44czh0UWFlVnhZYlY5RlVvWEliTk5JRTZnWEZWQkt1YWZXMU5ETU1nZ29xMmptbXZFYjFTdndremF0aW5iV3NmUklka1F1MzZ0NnJSYVVXejFLS2lUQjVhTzhKMUpvSTZLbDlsVUFKQmxuLWtyQmNqVTBKRGt4MGhtc2wxYk5NZFBtSEVoZGJuVTl0MmFDOEdDTkI4QjZzbGktSUY1UzY2blBSbURCbl93?oc=5</t>
+        </is>
+      </c>
+      <c r="F966" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G966" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B967" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C967" s="14" t="inlineStr">
+        <is>
+          <t>Sud Radio</t>
+        </is>
+      </c>
+      <c r="D967" s="15" t="inlineStr">
+        <is>
+          <t>Édouard Philippe s'affirme à la rentrée politique à Tourcoing</t>
+        </is>
+      </c>
+      <c r="E967" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNTDFKUW5ma0FvZXNfSmE4X2I2SUZBejdwdml5M1prV2RvS0F4MkdYdXVzYmQwSF9nRFlaT0NFM1doeXZCYUpFc0Ixb1pKQUE1aFl0NUtoSHZzeVZqb3ZrN2VNa3VFT3prNC1TdjRUbFl2VXZ4c3ZHZ0VFZFlRYURmcmkwaFZnbFNIWFpSWWl5M3o3d1V5ZDBHSGhWUlJFT3NnNEV5T0VYVEhYcnIzTzIzSmE5dGtIZkhGRnFEdEdR?oc=5</t>
+        </is>
+      </c>
+      <c r="F967" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G967" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B968" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D968" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : «Une jeune fille, de 5, de 6, de 7 ans, contrainte de porter le voile, doit être protégée par la République», estime Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="E968" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOVFc3WF80Q3IzMXB2ei1qckl3b0h5NEkyV0tNUFlsOG85MTNBVFRTdDdmc2szdGVlTHdVSzB3WEtfYXpHVjZrY0ZrN3NBaXpzVFhxUUNIdDlVdVhyV3NDTWc1cTItOXlLQVFiRUlPc0ZZMnc4RkVpWDZjUjd2SElHQnh5d1dUN1ZVUzVzWHA1eTg2UXktak12R2w5Y2NhaU9XazA2QVgzT2NuVWwwWVh1ekt6SDdhdFdHSVB2WDJ30gG-AUFVX3lxTE5UVzdYXzRDcjMxcHZ6LWpySXdvSHk0STJXS01QWWw4bzkxM0FUVFN0N2ZzazN0ZWVMd1VLMHdYS19hekdWNmtjRms3c0FpenNUWHFRQ0h0OVV1WHJXc0NNZzVxMi05eUtBUWJFSU9zRlkydzhGRWlYNmNSN3ZISUdCeHl3V1Q3VlVTNXNYcDV5ODZReS1qTXZHbDljY2FpT1drMDZBWDNPY25VbDBZWHV6S3pIN2F0V0dJUHZYMnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F968" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G968" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B969" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C969" s="14" t="inlineStr">
+        <is>
+          <t>Le Republicain-Lorrain</t>
+        </is>
+      </c>
+      <c r="D969" s="15" t="inlineStr">
+        <is>
+          <t>« Tu retrouves tes potes et tes amis » : Gabriel Attal reprend un extrait culte de l'équipe de France</t>
+        </is>
+      </c>
+      <c r="E969" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxQdEIyOFFtMW9aNm5YMEFEXzk1QkRBZjJRSEp2X2ZHdWhFNEUxRWoyUXRqZXdxWENsMG5icURBbUE5dmJVUVh1SDd0cXUzelgyU21tN1VZejN0ZXJuaHVmeHROSkktaHA0VHNxNjFZN1lUQWZRazc5ekR1YU1RSk9sZmU0NWhpQkRMOTJmaDNXRkVCOVp6STF5dWdtcml0LXBPdWNmX180RGs0WWJRQmkxT2pHT0hHTEdBTVJxR0ZBMVJqQVZkdHhjbFpmLXZHZC1HSk9tVGJOdjdwOWxuTW5UUlZpVXRqUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F969" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G969" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B970" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>tv5monde</t>
+        </is>
+      </c>
+      <c r="D970" s="10" t="inlineStr">
+        <is>
+          <t>Face à la poussée de Mélenchon, des appels pressants à une primaire de la droite et du centre</t>
+        </is>
+      </c>
+      <c r="E970" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQRjNiOXlaeUNadzVnNWREbFNYX3ZsZmtTdXRSdEtyamFZUnpCU3FpRldzckpDQW5PWGJSVFhuZ1AtZGw0Yi1uOGNKX3pyT0JpVmlCNEdEbHR3UWs1MmtTdHg5eXBiQ3dkMHJrSWVZLUxSSzJjVV9hOU80MTBjVmsyclF5dlhmWmZKdmdwb20tYVNLZDNLb2dIUVJpNUNudGtYTDQ0Q3hmS0ZUa2U0RHRsalJxUkYxbU9aeDJuZHlxaUNKWkhxSmZwVC1HM2ZPcERJUlladzUzcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F970" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G970" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B971" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C971" s="14" t="inlineStr">
+        <is>
+          <t>Revolution Permanente</t>
+        </is>
+      </c>
+      <c r="D971" s="15" t="inlineStr">
+        <is>
+          <t>Education : Attal, Philippe et Retailleau veulent en finir avec le collège unique</t>
+        </is>
+      </c>
+      <c r="E971" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNMEk0RkFqRXRqRThWWVJzTTBwTDVhdllYdE4zQ2FKVkhKMl9LQ3B3RExnbEw3UkdrY0drdUJQZGNRTkFLcE5EMHJnbXNSZ2tQRmRHbXpHZDJxNEZxWTNPVzZXcUNSc2wtcEMtRUdERlExb2dEaUNsdnJTdEJvWHdzTEE3QkU3azJ1YXIyamthdnJYeHpKd2NGdWJSYUN6ZGNONE51X3V6ay1uSXBxTGhSSDczSWTSAbwBQVVfeXFMTVhkZVdGOEFLN1Q2RW43R1ZYdk5tT2hHNERoTGxrWnh6eWllVzJIVnFPUlJrUHdFSHhtM2tfVVhQcm02SEFHcHpPOHB2OVJmcXZzbTY0SzlvWW9wOGRWRnNoVjE5V2tWTVFLUWQwd1I2QlFEbGFtSlNTN09iTHhNRVZPcXV1d2dlZlFobS1xbnBlbVBtN1N4VUE0d2RPakQ5SEZnVDluaUl1c3VtMlhiQ2dBRnBFN2ZfWTlucm0?oc=5</t>
+        </is>
+      </c>
+      <c r="F971" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G971" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B972" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Ohmymag</t>
+        </is>
+      </c>
+      <c r="D972" s="10" t="inlineStr">
+        <is>
+          <t>Débat présidentiel 2027 : Gabriel Attal, Édouard Philippe et Raphaël Glucksmann égratignés par Pascal Praud</t>
+        </is>
+      </c>
+      <c r="E972" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPUm1VRXhmeGxjQUFUaDdVbE5WMjB2QmYxSGQ5a2JGSnVWQVY0eHZEN3QyczluNXVwTmxTS2FSMUdqcHFNOVh5ZTZHMVYzT0ZlMXp3OFhMMzJETFBqM2ZFN0ExN2JfMHJWRkpTM1IwQWh0WlQ5RTZHeWxFclQ2dVFmOExYNkhJSFd4ZXpjaldnTk9NbzBBQkZVNlFCc1lVOGFrRm1kdTJkdGExSTZJem5mQWVQUHNyLXFjaG54NGNDQzZZV0MyemlFQmdwemphV0xVT21pUXoxemlfYnlBRVUxak5NUmtfM2UyTE5mLU9SazFqVHk4?oc=5</t>
+        </is>
+      </c>
+      <c r="F972" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G972" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B973" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C973" s="14" t="inlineStr">
+        <is>
+          <t>Atlantico</t>
+        </is>
+      </c>
+      <c r="D973" s="15" t="inlineStr">
+        <is>
+          <t>Édouard Philippe et les affres des sondages : après les ralliements, qui pourraient être les premiers à le lâcher ?</t>
+        </is>
+      </c>
+      <c r="E973" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwNBVV95cUxOU3EycjZjQzNsV2JYVlI5R2hGTGlIT0wtYU1Xa1NZS2xoNGg0UW10LTd5ZHRrczFHaEtDTDhUOU5sbWh0cFluN3dfTXlrTW96QlRVV094OUtwdUU0VDA5Z0JqRXBDSnp4U2NHT1UzMXhMckFOd21HVUhldkNkX0ZxRVB6OU4zU0Nla0NfTy1ERk1VLXpIRXNPVkd1UlJRejd0MHZ5bklDTTRKbUVqU1lmV3RVV3ZDcDZSN0l1MjlWcVhoR2dOa2lfdUR4c3UxSE9BX0VuOUJGVHpNcWhTMDlYVjZXRkpxbEpBN2lZLV9BOEQxbE5nQ2p6NHQ0NnpiTXVhNWhnZ0dfVk5RTmhXYmdKOHNweGhaYXF2Q2pUUTFvMm9XT3A1WjM1OEhtSTliMnJRREpfT01vdkRuU1dtZEF0YjU3MGYxeUZCNEk2cldFZlRQUE4xMmIzd21wLXEwMXlxMFJhU0tZZWlXdy01UTlMNmx6WEdYYXJFUWZjTFVKODNwNjdPOGtaak9RSzdPanJOSGhYSi13QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F973" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G973" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B974" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Planet.fr</t>
+        </is>
+      </c>
+      <c r="D974" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Gabriel Attal annonce qu’il vivra à l’Élysée avec Stéphane Séjourné s’il est élu</t>
+        </is>
+      </c>
+      <c r="E974" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPLVgyNGdvU3FXU0pIU3Q0Uk1RWWhvcTk0RXA3YVp6VGtRWldGY1ZFRnZVSzVNYmU5NGRldHQ4TnFpQ0pzNFE4WVNtVlZlMVVRcjVWeTlwUm9ZRmI3ckp2amlPcDlMVzFIQ0d6MWc1U3B3RUxIOENCbnNhTDRHMkp2UEp2bF9Uc0tJbFB1aGtqTUgydUlZV1pyMUozOFU2em5EQnZ3azR4VXJBc3M4Y1VuSDdicEF3TjNveHZ2eHB1MXNHY2tCM1Fmalp3dFBHeTNzQmxXXw?oc=5</t>
+        </is>
+      </c>
+      <c r="F974" s="8" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="G974" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B975" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C975" s="14" t="inlineStr">
+        <is>
+          <t>Gala</t>
+        </is>
+      </c>
+      <c r="D975" s="15" t="inlineStr">
+        <is>
+          <t>Claire Chazal a trouvé son pull doudou : un intemporel au coloris automnal qu’elle ne quitte plus face à ses invités, de Gabriel Attal à Julien Clerc</t>
+        </is>
+      </c>
+      <c r="E975" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAJBVV95cUxORGE4NzlsVENSMDdUaU1jT0Jza21pb1J3LTZRTkxybUdiMGJDRXVQdVNSLTNMTUdwbUZtNEJyQVF4a2d1eUJOUHhpc2ZIWnBQQkYxNlBPTDdQbE1OeEozSkVvanVPcU80LUVqRUY3dl9oLXNYWndmcjJxcWVUcmxMR2lCMmg5a2hRWFc2WEJtMXBIUXF3UnJOSDdaTkZDb1NpdGNKNnp0MXBsT1E4cGk3MmlGMU5JZGFVTXFRQkg0WG42QUtDUUVqMEZUTi0zdlljemc1QkRWdi1DLWU0ZHd5bWJZQ0dkckEyZmNTRHBrcmpISkhhWlF6VUY4TUk2b0NyYmYtRmFEUTdMNEx0X2JXbER6bXBRTGlnRlBjalNwYWJNcE9lbVRERw?oc=5</t>
+        </is>
+      </c>
+      <c r="F975" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G975" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B976" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D976" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : le duel Attal-Philippe peut-il empêcher le centre de défendre ses chances au premier tour ?</t>
+        </is>
+      </c>
+      <c r="E976" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQeW9aT2JTZzc1dlpsTnZPakgwWlFGSTJ6VFdkM2R5SlpTSGVabTFWOFl2SkV5V1NYWk9IM0RWWEdXcF9vNXQ1Ukt5YVhsQjdyQ1dFcDNfUkFFYnRfR3piM1pxaV9qQXhTdWxtb3Z4dGZrbGJpckFlZXMzZDRuSC02WEs1cDlaNXlTU3FzTTR3QUFjZHAzTGRYaWNnQ25FREhCUF9JemV6eTBlbjlfWlhvNmFCbTFFWmJ2bmtMR3RtZVh5TWZTTHZqLXdXV0tKYjRpRVc2TG5xOXduWm12VmI5b3lobHI5bmJ2Q1BiNlByTGU?oc=5</t>
+        </is>
+      </c>
+      <c r="F976" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G976" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B977" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C977" s="14" t="inlineStr">
+        <is>
+          <t>Orange Actualités</t>
+        </is>
+      </c>
+      <c r="D977" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027: "Je crois que c'est possible que la France redevienne la première puissance d'Europe", pressent Gabriel Attal, candidat à l'élection</t>
+        </is>
+      </c>
+      <c r="E977" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxOMHF1MERKcE95VmhKSGY4NzhtbDdHWXhMaDBYY2xvblJrNXBVWmdpQTlmSWhZcC10TjFGR0RTVEhZN0R2NG5jazFNdENFWDlKOEdQeFczbjMwaWZqdEZ1Y0RrVHVKZm9GYmF3MG1jZkgyYkx1akladnZGWHZDeFpENkc2eGFyOFh4aGRyZ0IzZ0Z1ZmJseUdpUm9MbklsV3BkdVgzczVkOVB4dHQzekJDY0xMUjZSWW4ySjhRYVl4MzdLVEExZ004QWczLXE5cmJkc3U2aXA3RVpseGRZWVVSTXFNdEpXa2FwZnNBejdyajNQV0NucTNkUWt1Mm9yN0NtSm4zeUlEMU15YUtQc0hnVVpZdENLc2xWeUVKOHlXUjR2XzZYRkl1eWhNdTZWLWJGZ0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F977" s="12" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="G977" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B978" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Sports - Orange</t>
+        </is>
+      </c>
+      <c r="D978" s="10" t="inlineStr">
+        <is>
+          <t>L'ex-judokate Céline Géraud s'engage en politique : Sports - Orange</t>
+        </is>
+      </c>
+      <c r="E978" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOU3dkU09WRmx0OGVQenZFYlZ1UmxsLWRNWVc5SlpyQWMzRkRCM3ZURzdtVUZ6RjVVX2VGbXpGaUlqY1NOWjFmWXBBQVUyOF9OTHJxX3lzY3J5bDhqT3RuUU8tNDJxRXZlNS03OC0tQTVsVEpsd0dzSTIyUVZEaExkY1pxOGhaS1VmQW14TmhENHJWT3hYeHVNUkFHU2d6SmFQd0J0RmJLTFJ6YXcwZi1NVFVkSTJSRERyUE1vUGZR0gG-AUFVX3lxTE5Td2RTT1ZGbHQ4ZVB6dkViVnVSbGwtZE1ZVzlKWnJBYzNGREIzdlRHN21VRnpGNVVfZUZtekZpSWpjU05aMWZZcEFBVTI4X05McnFfeXNjcnlsOGpPdG5RTy00MnFFdmU1LTc4LS1BNWxUSmx3R3NJMjJRVkRoTGRjWnE4aFpLVWZBbXhOaEQ0clZPeFh4dU1SQUdTZ3pKYVB3QnRGYktMUnphdzBmLU1UVWRJMlJERHJQTW9QZlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F978" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G978" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B979" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C979" s="14" t="inlineStr">
+        <is>
+          <t>Le Point</t>
+        </is>
+      </c>
+      <c r="D979" s="15" t="inlineStr">
+        <is>
+          <t>Éducation nationale : derrière la foire aux idées des candidats, quelques vérités scandaleuses</t>
+        </is>
+      </c>
+      <c r="E979" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOZ1htOGJnbWtlNE56NURVU3BQUnc3bjdMR1BBWVNhUE5ZLVhna1FrRjJmanhNZndNeUF2bHFNczR5R2paOWIyY0NTUzM4QkNLXzBXQjh2NFMyVDJscG9SeTFTM3JJN21USkRyak95b3lJeXNNSzcyeG4zbFVsZkhaMFJrM0VkZ2NHVkhDV2t1QVhBdnlKbXNzQklrcWJhTF9IZC1DRDdJQm1LbDVBN283QnVaSHJXcmhWbWRYVE11SHAybUxwSExuMndQajJwUy0zVkNyVnl0N0tURHpvNEx1XzB5RQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F979" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G979" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B980" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D980" s="10" t="inlineStr">
+        <is>
+          <t>Tests antidrogue dans les ministères : le cas Attal relance le débat sur la prévention des addictions au pouvoir</t>
+        </is>
+      </c>
+      <c r="E980" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOd3RGTERjNzIxRnJjMTlwUVBUbHhDNG5hZlBHQWdhRW83ZHQtdjRkZ29DZWR0amZZSmZhZHhOaWlITE9MSG5LOF83MjV5MWhNY2lfWlBRMm13X0xnV25NSy1zaGdHRGd5WTh1dFdQeWZlSENSeEF4VW1lejJhbXEzMkJpZGFTU1FBTElocjBWVzJBeUtzSE5KVkd2ck9wQy12NFdvZmktUEFTZmIyUXFucEdVUlBJaDZDLVBoUG52MkEzWXhuWTZnYm9SNEZiblJ3VmE2NWpfYVFCeVhfZUd5MWRIbjVnb0RiLU16ZVJoSHZGYTBjYVNzanVwVVpuMEU?oc=5</t>
+        </is>
+      </c>
+      <c r="F980" s="8" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="G980" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B981" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C981" s="14" t="inlineStr">
+        <is>
+          <t>Boulevard Voltaire</t>
+        </is>
+      </c>
+      <c r="D981" s="15" t="inlineStr">
+        <is>
+          <t>Islamisation de la France : pas de problème pour Attal, si les femmes sont d’accord</t>
+        </is>
+      </c>
+      <c r="E981" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOS2ZyQzViRDR4d1dwX2JOTEh4dGVaWXNqQ2dvRUZuMGFXbEVhWFNuMHR1eHVhTlFrUWJTYWVWcFpBZi1yY3NOR3dfX25LcTZsUVpDMEJRRVB0MDRjMGFnbXE5OVJwWkV0c0k3ZExDX0VSM2dEanlLZll0Nmc3X1ZMMkI4djJDT3pFRHhMVXBnRW55TjhIZnVYRjh1dXplR0FLdy1qTXBwbTI?oc=5</t>
+        </is>
+      </c>
+      <c r="F981" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G981" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B982" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Europe 1</t>
+        </is>
+      </c>
+      <c r="D982" s="10" t="inlineStr">
+        <is>
+          <t>Immigration : Charlotte d'Ornellas juge «impossible» la priorité au travail défendue par Attal</t>
+        </is>
+      </c>
+      <c r="E982" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQRmZkV1h2cExQR2xfNTdUSVVEeDdmcEJ0VFFyYVdBemFKdzBVTWhDNjRqSUU5UUVtYlJDc056SVV6QjN4R1VwbGJENlhvZG1BQ2VBUmtPSk15QktSNlZtbWtPLTI3T1B6VWZmZFpQSkYtbU9UYXppQUJTb3JENk9vOEJyS09pQ0lRaXo1T0pQdlpZLTZqa1MwVXFVdkVtaHVWQng2Z0liSVdZc0FkbVlDUWw2eTNmeUNEZmJtenptS24ybGs1MW9RRmdYNnIxUG9ETjI5T0xRSFptWDVjQ3lr?oc=5</t>
+        </is>
+      </c>
+      <c r="F982" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G982" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B983" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C983" s="14" t="inlineStr">
+        <is>
+          <t>Le Quotidien de La Réunion</t>
+        </is>
+      </c>
+      <c r="D983" s="15" t="inlineStr">
+        <is>
+          <t>Face aux patrons, le premier grand débat des candidats à la présidentielle</t>
+        </is>
+      </c>
+      <c r="E983" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOdXJsT0VVdk1fS0lSUlk2eFlDWmpmWkVoYW0zQVo3dHVPaWZOemROMmdqZ21EMnRPYXZYbjlweEw2dWFxb3F1c3Y0OUVTUUVTeUhFaGpia0FINmdacmRXYlYzSERDaEY3c2RBUW9YOXR2Sm1lS1I0OHFyb3Y2Z0VWX0RBVklva3NRSmN4SlB3NVZ0SGdYWTBPa1Q4cElNZEpScE9XYTdGVU1hN1RtTWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F983" s="12" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G983" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B984" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D984" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : à gauche comme au centre, les primaires peuvent-elles vraiment éviter la dispersion des voix ?</t>
+        </is>
+      </c>
+      <c r="E984" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNYzRBQzBKelhTUVZMbnJ5aEZSR2FNZk12UHJEdnNibnFTNzJ0RVRXc1B4bWl3bjVtU1gwQ3pjYUhEOXNpc21QeVB3S2xLYzg0QmVIRWFVMUhrXzlzd1lOVHRlbHR6ODdLRlNuYVMzMFdmbVdqbmJFWkZyUmNvNVRmOHYwSmNaRV9jUkZiYzRrVTdSd0hmaGJTWWpqM0ZkMGxKLTZSWER0ZlFjMENJbmRiV2dUTElTd3NnNEk2M2h3MmhVN0ZtV3E1eXpDV2JjUF8tTHFMMTlpdVB6OTZmUWNDTEZfUXBabFdPekxfejNGWmFUQmM?oc=5</t>
+        </is>
+      </c>
+      <c r="F984" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G984" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B985" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C985" s="14" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D985" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : une candidature unique peut-elle éviter la dispersion des voix à droite et au centre ?</t>
+        </is>
+      </c>
+      <c r="E985" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQUEI3X2hQamFvRElXUFpCbVpjS29BdEE5TzZDUUZCUVYwRE9sS1A0c3BlclRRNGp2S0JFNHVYNmlpR1pFemxlQlQwU2k0Q0NHSGM5MmNOZy1ZYTNYWU9UU3NYMmtkUmFHRFJNUDBlSENjXy1lN0t4cFJPSkpHSTJJZUtMWVBZZmRyQ1lEb19qTlpwZzdGSnFrd2EwdExfRk9BaEpzdWNSaGttVFFRcHJoT1hTc2RxQTlKRGx0S1dGZ0JBRGJfT29CT1B4Mzg2VERZR09yZnM0RXAtWTFleTRCZWJFUTdWdXROX3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F985" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G985" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B986" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>jeanmarcmorandini.com</t>
+        </is>
+      </c>
+      <c r="D986" s="10" t="inlineStr">
+        <is>
+          <t>Audiences 20h45 : Malgré la présence d'Angèle hier soir en plateau, "Quotidien" sur TMC se fait battre p...</t>
+        </is>
+      </c>
+      <c r="E986" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gJBVV95cUxQbXlyOFZHUzVfUUdBWkRfY0xsMlctWEV2dzdIVTQ1ZVZKRnNLczRvOWhOZXB4OXg2RGlrZFRNVkJ0aS1wcFVzNFYyMkRvRWpzZ1pRalNRaDlLUEdHQWg5RkJZS20yWUtqYzdrRnVjMDJJNnB3VTNTOVBfcXNCM0ctcURDdmJ6cVlITy1zdTJGYVdfVU1XV0J2UGdSRlY5R25uZ2xkRnBHNGxSdXBuQXU0cUFHeUllbjZsdXdrRWNHTVMzMEE0eEQ2T3dsc0N1X2JlTjJSbXFuaG9fZWtNTGpZQVhjYXZPY2ZXSGNNenZnZFo3cjFIMmU0LVdEcGRYdHluOUFhdXR6UnNCQ29BV2RUZkswd3dRc1Rvemo4bDNGUjF4dUh3SHdveWlkWlZUUENJd3l3SWRwQUIyaWR4VmRnQkdTbE5XTTdMeUc2NFVaem1kMDE5NlFSeVlWS0hTXzNKbmN2VE130gHmAkFVX3lxTFBteXI4VkdTNV9RR0FaRF9jTGwyVy1YRXZ3N0hVNDVlVkpGc0tzNG85aE5lcHg5eDZEaWtkVE1WQnRpLXBwVXM0VjIyRG9FanNnWlFqU1FoOUtQR0dBaDlGQllLbTJZS2pjN2tGdWMwMkk2cHdVM1M5UF9xc0IzRy1xREN2YnpxWUhPLXN1MkZhV19VTVdXQnZQZ1JGVjlHbm5nbGRGcEc0bFJ1cG5BdTRxQUd5SWVuNmx1d2tFY0dNUzMwQTR4RDZPd2xzQ3VfYmVOMlJtcW5ob19la01MallBWGNhdk9jZldIY016dmdkWjdyMUgyZTQtV0RwZFh0eW45QWF1dHpSc0JDb0FXZFRmSzB3d1FzVG96ajhsM0ZSMXh1SHdId295aWRaVlRQQ0l3eXdJZHBBQjJpZHhWZGdCR1NsTldNN0x5RzY0VVp6bWQwMTk2UVJ5WVZLSFNfM0puY3ZUTXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F986" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G986" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B987" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C987" s="14" t="inlineStr">
+        <is>
+          <t>Le Club de Mediapart</t>
+        </is>
+      </c>
+      <c r="D987" s="15" t="inlineStr">
+        <is>
+          <t>Si jeune et pourtant déjà si vieux</t>
+        </is>
+      </c>
+      <c r="E987" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPTWJjb0tqVlJSZUE2ejh3X2Uwcnpicll4N1RXaGNVLXNUOGdUZUZ5clZ3R08zSTk4ZURuZDZZaDBEN1lxbEF3N252cGdoN1pLWERHNnVmdmdlSnV1TXNSOF9aTnZjWWM0eUNNNnR1aWJlZ2UydkNVSDZSWHdLRXpkcHc3ZG11a2MzaFhUeGZBakU?oc=5</t>
+        </is>
+      </c>
+      <c r="F987" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G987" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B988" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>RadioJ</t>
+        </is>
+      </c>
+      <c r="D988" s="10" t="inlineStr">
+        <is>
+          <t>Patrick Kanner : "Le RN veut instaurer une police du vêtement"</t>
+        </is>
+      </c>
+      <c r="E988" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPMlRYQkxFQkNpTjNTYnVBamxLeFhyYzBjQ0Y1NnZHeXlEdjVCM2hpdzR3bjI2WHFKZTZnRXZmUjk3Mjd3VEl4dS10bXFFNjVaLVBHVkVjLUtrbXB1ZHZ1QTJtd3MycF9KM2xtYnJaeGJtWnBxSU40Yl9YeENmT1JUUy1zSF9fWTNGZFlVRFdHdm51ZnJYaWxKU3NlUkFnWXVr?oc=5</t>
+        </is>
+      </c>
+      <c r="F988" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G988" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B989" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C989" s="14" t="inlineStr">
+        <is>
+          <t>NextPlz</t>
+        </is>
+      </c>
+      <c r="D989" s="15" t="inlineStr">
+        <is>
+          <t>"Marine Le Pen, très bon coiffeur, Glucksman, un grand mytho et Gabriel Attal éternel étudiant" : Emmanuel de Villiers étrille les candidats de l'élection 2027</t>
+        </is>
+      </c>
+      <c r="E989" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAJBVV95cUxOTzNPeU9JRlFIUUVXc2RzczZQQThQVkVZalZJYXg5RU1kOHBRdnhYNnVacUhIMG80dUE2b0RSU2ZnRy00eUlNczVkMlNGdnZjYlBuVnRZSXAyYTRDOW5Ma2s1NXl1ck8ySGJqRW9jQ2Mxb1dnbjRCRzByWXpGWHpQWGlMQmRBWU9Xb3J4MXFZUzcwWTBqdnpkamZvdlh1Rzh6MmtCN2tObGFRWng0SnF4dXlnOEdSd3YzeVNrcFRHaTZ0OTY2YlA0d0ttUi1kbFJJel9NUk1aOVlpX3FpUFdaT0V3YzdseGEwMl90aFViOUoxdUY1Y3J4VnpJYlVrYUwyc1J1WkJ3ZEx4TS1LSnJyYWFCMi1YZlJK?oc=5</t>
+        </is>
+      </c>
+      <c r="F989" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G989" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B990" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D990" s="10" t="inlineStr">
+        <is>
+          <t>Gabriel Attal CHOUINE et Édouard Philippe se fait PIÉGER.</t>
+        </is>
+      </c>
+      <c r="E990" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9mWHlFNUhKMkJlOERwRkhLLTh5bmRtdnNtc2ZEeG1ZTnVmNGhxcHpUZUkzYXFPVnpnbDNBSnZqaEE1NTk3UlVwOFRKV1ZUTnZHSlBld1BlWXhMNlR0?oc=5</t>
+        </is>
+      </c>
+      <c r="F990" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G990" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B991" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C991" s="14" t="inlineStr">
+        <is>
+          <t>Orange Actualités</t>
+        </is>
+      </c>
+      <c r="D991" s="15" t="inlineStr">
+        <is>
+          <t>Palme d'or, Attal candidat, canicule... Les 9 actualités de la semaine du 23 au 29 mai</t>
+        </is>
+      </c>
+      <c r="E991" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPME5SUmgxclFlbUNYMmQyZFlWdUxkSHRKak1MNm1mVGdhaGNyVWJwaXdIM0dNOVA3MW5SN1o4RERDNm9iUkVvT2N0T2x3LTc3N2pJc0pTc0tBc2hzNmRfYWNZTW5xY3hsbDE0S19RRlZiNlFhN3NfektfMkpvRkhqaEN6QkVFOHpWUEduMFZhLXhEY3huRkJUb2RnNFYxclVFcnBkRnlwbmUwTWxzWXlkb2N5S0dKWXM4R2dZdkUxRW03QUc1SjFzUHlzNjNGS3RZQlREQndjTkFmQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F991" s="12" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G991" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B992" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>ENTREVUE.FR</t>
+        </is>
+      </c>
+      <c r="D992" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Céline Géraud, ancienne présentatrice de « L’Île de la tentation », rejoint Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="E992" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNTjNHRVU1eWt3YzR5T2RDUHUtVVdYaVZxVTVpUWFoT0l6dVFhWjNMYTBSNVFSaGxhel9OR1VkYWZkTFhiNzk0NklpMURJQ2s0S0tkdlhWbU5OZEpVLXlzblpfYWlzdGxQbEdlT29XZk9lNlQ3cE9EMFY0bVUzMW81OG41Y202UTE1andEanI5MFlGNl90SURXVFZWZk5YSlZUMW9heG5kam82MEdUaXVhelY5XzJHVTFfb3MyQnZKeU9xd2VLZUwtaUo0SzQ4TWFIYnp1eGhxVHdBWVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F992" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G992" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B993" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C993" s="14" t="inlineStr">
+        <is>
+          <t>ENTREVUE.FR</t>
+        </is>
+      </c>
+      <c r="D993" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Gabriel Attal attaque Édouard Philippe, qui l’invite à viser Le Pen et Mélenchon</t>
+        </is>
+      </c>
+      <c r="E993" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxONFhQQTJjcEgwWkFRSFA1Y3JfbGtXTklhM2k0QUVzM1ltbjJrVUM0NlJ1Y2RxSk50ZlltNjV1QlZ6d2pyTVZuT1FldXZTWmVXSzZIUndWYnZ5d2cxOTBlMTFXaU1FbnFZRUctYXZFd3cwSkk3Mm8wSHNlSlJ4UXgxbTE0b19VSzAyaWNydU8zZDlNdWM1TGFKOFNPR0EwTFZVY3NvRHJmVzZ4UWMwbFJSZExCLVVXUTVad3dMSnBSbVZPbDRIcktZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F993" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G993" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B994" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Seneweb</t>
+        </is>
+      </c>
+      <c r="D994" s="10" t="inlineStr">
+        <is>
+          <t>“Of course we live together”: Gabriel Attal and Stéphane Séjourné ready to form an unprecedented couple at the Élysée Palace</t>
+        </is>
+      </c>
+      <c r="E994" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxOYXpWbzRUS3o2U0VPVFF4eW1CdUNEdDdsem04M1l5T294ei1vZU5GUXVnLU9zNUZiT1djbmdaQ05EZ3BNNVk0aUNPNmxoNElZTENsR21Ld0wwaFdURnZzVlpsOWRORElSd3BlenB1Q2VReGtxeFRyd2U4ZzJLYmhoVmZxTWtySEU4M2pnbW1rZFJrTHdXWWRPb3l0YUVwZ0RHcTF3YnFfcElEeUlwREd5YlBxQW9EZlVmd3NXLUlSZUhmV2RHMjVVeWRROEpoMmR2RHNNc204eTFhX2VkcTB0ZkxmRDhhRlZpanc5aGRPWGR1eXVEdmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F994" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G994" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B995" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C995" s="14" t="inlineStr">
+        <is>
+          <t>lemediaen442.fr</t>
+        </is>
+      </c>
+      <c r="D995" s="15" t="inlineStr">
+        <is>
+          <t>Après Stade 2 et L’Île de la tentation, Céline Géraud va s’occuper de l’image de Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="E995" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUEFjai0yc1pmUnRQZWxkeTAxYnVxeklyVXZxZFlBSjdUQ2NhdFNWbmFwWTM0U0RaUlZjXzNvOGZqSTJRT2I2dnhLWVI2TU5IaWt0OUpMU2NSTUJ0YlJBT2pZMFhQLURwMUNvTjItY0hQWnI2SEpfUUdMdkhER1Q4a3V1S3ZZQUFTRUNid09qckVxTjFWbVpRbXBLS3MzQ3RjbXVrX3hpTE5hWkhnQTB0dGF0RENWUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F995" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G995" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B996" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Le Canard enchaîné</t>
+        </is>
+      </c>
+      <c r="D996" s="10" t="inlineStr">
+        <is>
+          <t>Eviction du conseiller spécial de Jordan Bardella : Marine Le Pen en pleine purge au RN</t>
+        </is>
+      </c>
+      <c r="E996" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQeXNRbGxCV01vNW5jSEJUTXRXRFUzcmJjempCbnk0WVZDdlZYQ202ejJTeU5HQWNiS3Z4a29IYlNmU0JJYngtTWpxU200eGU3dzlaaG5fMDBuQVh0RmMwaXFSTHU5OFhDa2Z5OVN0djlZR2paWGR5NkJRQ3NERFk3VjZraEcwNjE2dzdz?oc=5</t>
+        </is>
+      </c>
+      <c r="F996" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G996" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B997" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C997" s="14" t="inlineStr">
+        <is>
+          <t>RTL</t>
+        </is>
+      </c>
+      <c r="D997" s="15" t="inlineStr">
+        <is>
+          <t>"En solidarité avec les femmes forcées à le porter" : le RN prévoit de sanctionner le port du voile par "une amende"</t>
+        </is>
+      </c>
+      <c r="E997" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPLS1vc1JKZUl3czRTRldqWlotdkE3YmRkRkJuMFRndFQ5akVXNldFVTJYbFNDSksweVJQSTJfdG1MLXU2LWtyMHRFbVJZbVNxemN2a1BZTlJOSGlsalN5eEZaQ05TTEh4dmRocFVvRi1FdzF4UnZPTHpDYmVVUW96RlBFMG9VelpvelcyOXNwZ3ZmOEZ0d3JxeUFiSGswS3lzZ2xkNm54dmRKT1RWczZqRl9IOEJVQlhkSVNnVWVSbG1fOEx3U01JUFNSaHRlSTI3YUEtaDYtejJBeXBhLXhLak9JaWVtUUppZnRN?oc=5</t>
+        </is>
+      </c>
+      <c r="F997" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G997" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B998" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D998" s="10" t="inlineStr">
+        <is>
+          <t>Dette: "Le premier qui doit faire un effort c'est l'État, qui doit baisser drastiquement son train de vie", déclare Marine Le Pen lors du débat au Medef</t>
+        </is>
+      </c>
+      <c r="E998" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxPXzZ2VjZxbDJkS3ZYR2NyQ0ltXzgwTWJUTzhsMTZDbk5pVE1acWlHQWpqbzNaV1RCVFotWDBWdDNqZHdsMWdjT055SGdGdWh6VWE5cVZyWGFtZDlvc19OUVU1ZW5wTW9MMWs1TzhmUzRXN3NwdEFoSkR6ZTgxRFdyQVVXYVlMUTVYVVQxYkVWZTFFUFFkbnBDRTZ2dDNuTFZMLXlWdUpMM21Zd01yQ1g4MWZJamo4WmdhWGlITER3WXZNckpiMU5SQlM2b0RTUjFfM0J3MFkzS2JJLUdCX1FsTVZacUQtVHB4RWNiaGl2RzdMVUZzRWJvVkVXTHJlTHcxVXhRdVZ4XzVUR0k1T1JOODJIT2JvMVZOcHZpczVaRmZoLWVkZlNHTnJIYnZqSUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F998" s="8" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="G998" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B999" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C999" s="14" t="inlineStr">
+        <is>
+          <t>TF1+</t>
+        </is>
+      </c>
+      <c r="D999" s="15" t="inlineStr">
+        <is>
+          <t>Marine Le Pen au sommet du Medef - Edition spéciale LCI : Présidentielle 2027 - Le débat</t>
+        </is>
+      </c>
+      <c r="E999" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNWE4yRW1ONGNsWmRWTVlnRGlFU08zN1NuVzF4UW9BcG5UZ2dvLWpwVVZWRWF2SjJUMWR4Tm1Fbi1TNVNUbHZUSGpNUUtyT2h6NjJ6djVZSndRUl8wbDAtN3ZSQUtxNEN1QjlTSU5TWFBPNTVUSDE0WW03RlREZGQ0N3gyczFpcHpoWjZJZmhPclZEYXhyLXdDbFJxZTVKdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F999" s="12" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="G999" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1000" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Revolution Permanente</t>
+        </is>
+      </c>
+      <c r="D1000" s="10" t="inlineStr">
+        <is>
+          <t>Marine le Pen devant le MEDEF : une opération séduction dans les pas du macronisme</t>
+        </is>
+      </c>
+      <c r="E1000" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQaDh2SVFhZXFzRGU1R18zOHNtTkZETU40bEtJMTdDeHZTOWxzcUh0QlJzUXNWY3p1MDY1cUxhQlZTNzVMQXhtRWdzUVdhcDl2Vi1jb3AtVkRsYXEzMnRJbDg1ejFjUGdmdjd3Uk9DRUdhcGJQeW1xc0lYcHZWQUxJbW9nVVNUOHpmU1ZzdmxUVmw2R1ZfdmNfRkRmQjRpeTRHdGRVWUdydFhEVWtNQ3J5QkY2NlVvTXPSAb8BQVVfeXFMT1FLQ25DbmxGYVI1Y201bGF1U1dVVU5xT3R0a2dLeHdwbGgwb1dNTXJMZUwxbXkzNThqQ21UYVFrVlB4a0xYQmtsc2dtZUpoNTVwQUhENXNhNEpBYzZrclRyRmdqMTJjNUlwX2ExRUNUaDNVZVExcnVxMUItWERaSE9yU2c5dXJnckNtc0xKWHVoQjZxb2k3YjNhYy13MkZ6WTNodjRvcU5xU1VBUjRSdVl3V3FtcVI4RGZfZV93U1U?oc=5</t>
+        </is>
+      </c>
+      <c r="F1000" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G1000" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1001" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1001" s="14" t="inlineStr">
+        <is>
+          <t>L'Express</t>
+        </is>
+      </c>
+      <c r="D1001" s="15" t="inlineStr">
+        <is>
+          <t>Interdiction du voile : "La destitution de Marine Le Pen ne serait pas impensable si..."</t>
+        </is>
+      </c>
+      <c r="E1001" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNYk5rSFU4TmZPU2tlY242UzRMOFVKczQtV0lIYUc1VFB1WXNsTU4wRGNkVW80YVg0MExwSmVaZENSdl9zYzk5UVVvTE9jZUhlOWlRM0tzSG9VUG00Qk5FSzdUVEpBOHp5SXVQaTk4ZlpPSzFTLWpvSTdvRWFCWlVaYjBKcnI4Q2htdnNXMUFWUDRTbG9SWmZJMXZhcG1JY2dhS203QVRmcVhNZkZHLUk0aXoxWjBfNlhuVEotazNxNi1YUWYyOHVFR2hYakk2S3R6R3d4TU1OZno5dzQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1001" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1001" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1002" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D1002" s="10" t="inlineStr">
+        <is>
+          <t>Le Pen-Bardella : tandem cherche mode d’emploi</t>
+        </is>
+      </c>
+      <c r="E1002" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNYXpIX2hVMmhwY004YTBNa3I2Wnh6UGFqQzE3eGtJWTRNZGs2NjBYbDNGcTVRcmhWclFrTGhGWnotaDljMU1tSk4tUWZkY0dSU1JaREJUdkUxcVAzYWFOd1VWVGlSaFhONUdXVHFmT1JEMExWa0UyZDBJeGlkdDBFMk0yRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1002" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1002" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1003" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1003" s="14" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D1003" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : « Jean-Luc Mélenchon est nettement plus rejeté que Marine Le Pen »</t>
+        </is>
+      </c>
+      <c r="E1003" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQLWZvX2ZjNmZWQ3o4YWJMb1MtLXh5eUlEN0xWcXUyMExkMDFkZFZoZ1RXbGJYVW81UElKUmNmSVppOE53YUx6SWI1Y0dqZ09ON2J3V29QZnRoZmxCaDBURGFSdjhMQ2wxOXlQVU92eXNmNlpWUUhJSGJIRk5Ua01zNVdRMlZhLXRGbzVNN1VEVFJIWk95Y195NktNNzQ2TUZoN2Y4dUJjWUxrMzdfQ3B2YmxpN3M4Q0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F1003" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1003" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1004" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Les Echos</t>
+        </is>
+      </c>
+      <c r="D1004" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : la rentrée mitigée du RN pris dans ses contradictions sur le voile et l'économie</t>
+        </is>
+      </c>
+      <c r="E1004" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxOa3B2NVo0ZnNUSXBFX3M0NWhFRktwM3ZUSGl3SDVIVjFjR19XdWlwVU9BdHdpc3V4TjBjYjVxWWZ0MnJQaFBLeEdhWEI4VjFfYlJ2dHhVRVBCbkI3VXNWQUFTTDVpRkdxUmFBSXBScU9hTHZMUWlKaXIzR3V0ZDR3M1VtQ0ZRRWljQXhCM1NRN2pqRDlPUG0xdGlwTXNGZnRkUUY1WG5UaGlfUENGd3lWMEItaWxnZmRPaEtLa3ppYXlMQ3RvY1pOSVFFc3ZTRzA4VVZaOThtSld4Vm04SXVqNlE0aFVQM25UeHdMVA?oc=5</t>
+        </is>
+      </c>
+      <c r="F1004" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1004" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1005" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1005" s="14" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D1005" s="15" t="inlineStr">
+        <is>
+          <t>Voter Mélenchon, c’est élire Le Pen</t>
+        </is>
+      </c>
+      <c r="E1005" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBhNUVmYXM3eEZ3NUkycHd4MlExNDJkeXFINlpSN0lfNFBrQWdqSlY1LWVxZ1h4UC03bG5lYWg3a1hEQ015NjktcU84alZiS0E4S3BTUDd1Q2pRdzNBSThVQWhlWU15NE4ydWlXOE5IeEp3U25UaEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1005" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1005" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1006" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1006" s="10" t="inlineStr">
+        <is>
+          <t>Jordan Bardella "a la confiance absolue de Marine Le Pen", affirme Jean-Philippe Tanguy</t>
+        </is>
+      </c>
+      <c r="E1006" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNTktvOHM4bTdUR2t0TXBQM3Q0dUo2SlY1RWFtMHc4U1A3cDViMkZfNVBBeWV5RnFSa1Q0RFdEOXdsekhmaE1oc3JRSUZUNkV6NFI4czZ5OWp1VWQwWFBvck1uUTlESUpqd0tfeFV2SWNrXzdTWE4wbzhBVDI1c2puY1hKM2F1S2loTjR5ZVRUOVNaYk1jT2Q5YjgxN3BYV1BaTVVFWF9rTko3eFZKeFlSUldiejQ2eWlaejI4bG5BdF9mZXM3djN0OFpFMkRrNEUzSUs0ZWVrMmY5Mklnd1RHc0haT19CdWxjSVNHVGxwUzBLbWYzOEM1MEkxb05pQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1006" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1006" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1007" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1007" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1007" s="15" t="inlineStr">
+        <is>
+          <t>Retraites: Marine Le Pen a "inventé la réforme qui aggrave le déficit", estime Édouard Philippe, candidat Horizons à l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E1007" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwJBVV95cUxPWlR3UjNWT01oVnR0cmhaMzY1ZEVjR1k3TVRjdW9ueU42LVphd0R1Qm1jQmZyNmwta3N1aExPZW9FNG5hWGs2NHlZejh4RUtrTGJXQURnLTJSQzVVQmg0UXpfM3doMWhjclpfLXp1UFJhM1RoNVM3WmFoSk9mYVRYdnFfRWhJMzhBUF8tdHR1dVVDQ3VfbVo1TFRZUC1haVp3MGhpeXZ6cWRmM2FBc0o5TmhtaDlKWmk0SFAtS1NCb1N3WnFZRmJYemJHR01hZ0w0S3d4cjEwM096ek05d3RkMVBTVWhtbVlBbFdJQy0zUm9Ga1BwaGVzdERVYmdHQVc3MEZaeVFVNVNvZ2N3cHQtZzJDVTdBRWdmdzN0OTJra3U1ZUZDSHFYQkZlNVgwTUFZdWd5ZGpkT2l2ZHF5MmdCXzVHWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1007" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1007" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1008" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>franceinfo</t>
+        </is>
+      </c>
+      <c r="D1008" s="10" t="inlineStr">
+        <is>
+          <t>"Après des mois de normalisation, Marine Le Pen réactive un marqueur" : pourquoi le RN replace la question du voile dans le débat présidentiel</t>
+        </is>
+      </c>
+      <c r="E1008" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAJBVV95cUxNWndXRTRRUllSUGNySURHOGpsSm5uVWZCTmtoT0wyY1Z5ZmVmSjdtRDlfbDBtWllGYUdQaGNuSUpvbVBhWm5SUFhBaVRIaE0wZmRsQUJONEtnYmpHYzN6UkF3SEpHYWNsMlZhNG9DV2dWX0kzS2tIUHZEaFJ0TXZGMXFlVkNGYlVEMkJaOUFCX1NyaEhFc1JZTXVnOUxybmlCQmgtQUdNSm9ieWxUYXExQmJZQ05RMHlla2VqaEpfS3lCWE85MUFzTEJyNXEyV3ZzeVNrOTlLcGp0aTNnZHUteFdXbnJTOWVqSnh1YkluSVNYLUVpSS1Va09CUEVCbHdBRndlM0c2azZEMjBvOTJQQnBPdUxqSmRlc2tmSXU1THV5Njc2enBqYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1008" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1008" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1009" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1009" s="14" t="inlineStr">
+        <is>
+          <t>Nice-Matin</t>
+        </is>
+      </c>
+      <c r="D1009" s="15" t="inlineStr">
+        <is>
+          <t>L’édito de Baptiste Bize, directeur de la rédaction : « Marine Le Pen remet le cap à gauche »</t>
+        </is>
+      </c>
+      <c r="E1009" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxONGZ4Yk1qRHpteUZCQ1phbUpWRmg2bUpZT0FzTm5Hd0RZV244dk9TVWZwNHg2NWRKUFdPXzlIUWhSNlFQc3J6aE5OU2tTQk9udmRLaGRFa29LRUdSSTVCaWFMbGR0UlNaYm80dG9iZnRLQ185dUFrVlctcEZ3XzR1cVVETnliZEJkNXoxRXhScUtBMDg1cklscFhTOUdIakRuLTBYRXBGcEF2VTkwQTNyWTZRYVlQQXdiT2RoVXZCc09NUkFNb1ZwcUtJcWFtVDBjUXItVVFTd2M?oc=5</t>
+        </is>
+      </c>
+      <c r="F1009" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1009" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1010" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Le Canard enchaîné</t>
+        </is>
+      </c>
+      <c r="D1010" s="10" t="inlineStr">
+        <is>
+          <t>Interview fictive : Jordan Bardella : « Ô Marine, faut pas putscher</t>
+        </is>
+      </c>
+      <c r="E1010" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOb25qdUg5MEIyMHljOGNGc1RwNWpEYThTRXRjc3hWWG1lY0t6bXprRFJWX04yc216ZnBhNFdMd2VUUDlNanFSUXVFemg4MmwtSmZZeHlHd0FNN0E5SUlodGtkRmRtVTgtSHo1bDBTa0tMTVZHV2NaQXE1MU5EVzR5S0otaHdycHpRWmtnN21JNk92cFdS?oc=5</t>
+        </is>
+      </c>
+      <c r="F1010" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1010" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1011" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1011" s="14" t="inlineStr">
+        <is>
+          <t>L'Express</t>
+        </is>
+      </c>
+      <c r="D1011" s="15" t="inlineStr">
+        <is>
+          <t>Port du voile : ce que révèlent les divergences au sein du RN</t>
+        </is>
+      </c>
+      <c r="E1011" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPU2FIUE5pMFRSZlpNSDF4M3lpaGRWR0pSMjcxQ0RJUHFuSW9BOHhaMHdmSVJaaXBZQWxab2piSEZaSy03NHJ2dW4xR1BfWDU4YkJfZXVjbU5TbjZ4MUszV1JESjRITXZNVVZaSjlVTHd6cG9ReE9qdC1Ca0l5blp3YzVvaHV4WDJvTEdrVXd4TmQ0SzRmaFdIMUVfLTRRRWxzWkpUamR1ZXd4QnhxOUc2SEpOdU5VMnZfZzl5UnhiU2VUQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1011" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1011" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1012" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Radio France</t>
+        </is>
+      </c>
+      <c r="D1012" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle : les électeurs sont-ils perdus ?</t>
+        </is>
+      </c>
+      <c r="E1012" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNbWJ1ejRMcFVOM0FqRk10WkkwakNPb1J3Y1BIcGFlWXlnbE9jc0o1VGxmWjRZdGZMd0s2SlZpMmNPaURKUEFRQnI4NUFQVzltZEl5bW5Ibm52ajJuTGx3Q2JPUXA2VDlreXRjczNFUGxGMFdsLXZvRDlsdFJJVDFhMGNST2hsdV9SXzFJQUxpQUp0eE9VMWNHTllaOGlwdDl3aFBRQzhfdjlibjF4SWVpajJObkswOGJNRzF0Y2pLWnZ3RDV5T0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F1012" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1012" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1013" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1013" s="14" t="inlineStr">
+        <is>
+          <t>L'Essentiel de l'Éco</t>
+        </is>
+      </c>
+      <c r="D1013" s="15" t="inlineStr">
+        <is>
+          <t>Bardella / Le Pen : la rupture est consommée</t>
+        </is>
+      </c>
+      <c r="E1013" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5RQ2dVQWJKaVZ2WUYwNkRLdDhWUXNyemQ0eTFrbzRWNVpGZTh6T2drbDlDR3FHcVhZaTYzaWtsMm1KcW1YODN0Y0JXR0xXTVIyWlpCYWJPSUQxMnZodFZKNDQ0TjFGb19UbHhBSXU0WU5PZnp4eHp3UEY5RmhCck0?oc=5</t>
+        </is>
+      </c>
+      <c r="F1013" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1013" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1014" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>franceinfo</t>
+        </is>
+      </c>
+      <c r="D1014" s="10" t="inlineStr">
+        <is>
+          <t>"Absolument pas crédible juridiquement" : le RN peut-il vraiment interdire le port du voile dans l'espace public ?</t>
+        </is>
+      </c>
+      <c r="E1014" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNekt0VVdWSld1VUN2SjBNY1MyUXk3XzUxczhTbUI5ZF9VZ0dSTGJkQlZVcWZhZEgtSzYzOG5kLXhGZkp1SGRyMDNoWFdDQk1jN19ad1FXcTJ2cFJDY0ZhbXg0Zk5QVVpjQzdXaW5wVkZXQWFWZVZkUmdiZV9mMUVXU2xuWFZOajdjZnhZaFhDVDYwejRNbG16dnM2ZVVERHFCSnpBeXJ4ZEd1UzNzNVBYSmcyOUx0Nlhnd29jU0tTdmxuWGg4LVBJc2FXZExHQ29UT3BiTHFYNkxhcEtFeUdOejMyR3czYmRIall4bmhCQk9UQkQtR3BxYkN2NVFwLS1kNmFZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1014" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1014" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1015" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1015" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1015" s="15" t="inlineStr">
+        <is>
+          <t>Interdiction du voile dans l'espace public: le RN assure ne pas "attaquer un symbole religieux" mais à une "idéologie"</t>
+        </is>
+      </c>
+      <c r="E1015" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxOemlCbmVQR284SmNpSHlGN0xfMWFXenBkRlJJZkdFd3pfVFBJaTExWkw3eHhxMnNUOHJmdnlORFpMREM5eFJ1bnY4NzNYTVFGRGNwUHYwSno3aDF4dmJxZk5STHNsd1cxdExib3IxVlcwdlZvSDYzR1BQWmJqYlhvX0pvSUZGa1hTc2pOcGlsdTBhQXROd2tXOWJtRnl2cFNMZmF0N0ZmQmlIZ1ZjT0J1TURld2JxWXg4ZDF0THJNMGlsQ09pR3lIQjZURWJuS3AxdDJjOUN6MXh6TXBWX3Jqci1LTVl3R1FzaUlQOVAzekFMWTlELVA2dXJnMURWak1kXzczSXljLU5JOVl3Ync?oc=5</t>
+        </is>
+      </c>
+      <c r="F1015" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1015" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1016" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Europe 1</t>
+        </is>
+      </c>
+      <c r="D1016" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : derrière Marine Le Pen, Jean-Luc Mélenchon recule et Raphaël Glucksmann progresse</t>
+        </is>
+      </c>
+      <c r="E1016" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNTHRvWVNLV2QwUld6cnpDTDBkYUlGaGd3SGRZY2lfbXFoVnBiYk1JRVZZelcySWl1aWpSZFVSMnZKdkJZZERnNG5CbG9kcVYyQVR5Y0xfVTdJM1dteTFJVDlpd2RJTk9VdDFiNzlVVi02N0t1RF82UFJtWDNTWWp6ZVBYSkwwSU5oOHRWdHp4N3VtQjA0bVVpM2ozZ0tIaGdsV2kweFZHbE5OaElZSEQyUFFQZmhMQkFndTZuamFjYm5acjg2V0lMLUZFMUxWa3pWSk9HM1dkYnbSAd4BQVVfeXFMT3B1MU84ZnRLYkg3UFdIdjVSaFIxV3BjQmZwRzE4N1Z1ZGQyZWVfb0pkclFuNTZJNkdPUmc0MmxEVnBZUU9TUUpSdzRtM1ZhRjhJYW1WYXVVTWlXZVQyZGcteXNNZllJbER4WFlQZFBvX0V5MTZqWml2amp0TVFFUDVCZ0RqMXVSaWwyaEtwRWtLbUpiX3JTSWFQTHFOMnduYktxNzE5bVVDdEh4MV9RajhWWTJnNlhzWVZ0ZVFIMW56MWowMWxMYngxTU1DMEM5WENpYWpDWExWN0lDR2hn?oc=5</t>
+        </is>
+      </c>
+      <c r="F1016" s="8" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G1016" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1017" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1017" s="14" t="inlineStr">
+        <is>
+          <t>sudouest.fr</t>
+        </is>
+      </c>
+      <c r="D1017" s="15" t="inlineStr">
+        <is>
+          <t>Éditorial. Voile islamique : le pathétique contre-feu du RN</t>
+        </is>
+      </c>
+      <c r="E1017" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNTlFnNTBSR2dVelJIZ1hQMUUxLVdtN3dCQ0U5cE9ZdTVhUjczLUtfYVZBNXBjQW5zVThEX0NSNlZnYTlyZGlQN0ZiUm1XSDdmVXhDQUVkWXpMS3dueGlnc3BLRG1ZXzFPaWliZkw3aXd1RmFLcTFhT0cyMU1XWFBtV21wZkI1bzRyZF8wcS1JaGgtN1R5VTh6aEZLTXFzUEFZRkEwT1duZFNIQkZ4UU5BaThCQlFweFAz?oc=5</t>
+        </is>
+      </c>
+      <c r="F1017" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1017" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1018" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Fonds pour une presse libre</t>
+        </is>
+      </c>
+      <c r="D1018" s="10" t="inlineStr">
+        <is>
+          <t>« Regarder les choses en face » : Pourquoi nous lançons un appel à projet pour la campagne présidentielle de 2027</t>
+        </is>
+      </c>
+      <c r="E1018" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOcXlMUUlhNU9iN2dUcGJLMnlfc2dVTkU5cW51Z2NlazBxU3I0ckdpR2pxeFZCdjFVdVZrOU93VnlXajU5Y25oYXZQcy1iSS0tdVJMcE1MbXpLYmdJbk5JY0hJLU1RSXQ4RjZ6MlRERVZoX1dBcUNfRksycm04S29zbm1GYjIyU3plaktwTmg1M2xDenZNWjBsbFpEWTRqVkthekxpb0liclNLZ1FQcmdrd1JHdmUtb0VwVzh3My1id0RlUlN4UldONVE0emREbFpaM0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F1018" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1018" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1019" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1019" s="14" t="inlineStr">
+        <is>
+          <t>Gentside</t>
+        </is>
+      </c>
+      <c r="D1019" s="15" t="inlineStr">
+        <is>
+          <t>Marine Le Pen toujours largement en tête pour 2027, Mélenchon perd du terrain</t>
+        </is>
+      </c>
+      <c r="E1019" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQU1diLXN2QlBmb3NveDRqNDhMckpPWHJqV2VKQ0gtSGtlMUZhbElCdTBfNkxJQUFJcmJlT1o2cEx6Snh4VWcydFd0LW8wVkhMa0NGTDRsbGc0enZNV3NHbGRQal84RUxBcFp3MER0aVlzejBPZTVaMTd4NFlRa1JpbXZ3OExPM3Y5WnNFeUtEbVpmdmN1bW5TU2FGRWVXOXU0aWJNaHNicTczZVJmTjF0RE0xcFVZZWI0SDdTdlMybVNuS0FhMHh6NFBLRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1019" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1019" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1020" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>RFI</t>
+        </is>
+      </c>
+      <c r="D1020" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle en France: le RN revient à ses fondamentaux en proposant à nouveau l'interdiction du voile</t>
+        </is>
+      </c>
+      <c r="E1020" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPc204VXd0TE45bldiSUE4d0g0U3BobzBxSDJUZzNRZUJaMFRWOHpFc1dxXzlrYWRsd0lhV2tHdF9EUmhqc0NEaThmbk5IZXlCSVdZeGYzTWJVVFV4aDF4ck1wMDhIcjNwVTVaSjlKa3FiQ0FQNWRsZUU0WXJQUzNpQWI1UXpMcGpHWVhmSE94Ym1ta1RMVVBNSUF3LUZPQjd4SURNRGZwVVBpczNDVUdkQ2dmYWpFdlNlaW5aaGRzLUR1dTRSNTF1ek5Fam1Qa1ppRmtvSjkxUlZUVng3N2N2Uzdfd2E5UHVYRnJGeTlR?oc=5</t>
+        </is>
+      </c>
+      <c r="F1020" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1020" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1021" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1021" s="14" t="inlineStr">
+        <is>
+          <t>Valeurs actuelles</t>
+        </is>
+      </c>
+      <c r="D1021" s="15" t="inlineStr">
+        <is>
+          <t>REF : Marine Le Pen déroule un programme libéral, sauf sur les retraites</t>
+        </is>
+      </c>
+      <c r="E1021" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPSnBqQ0YwQlZaS0JjT2hTOFBLV0l2Rm9TTnBVSUE4VEVGa1c2Q0lqaU5HOHFkVGk4M2tIVUV6Q3Y0M1RHdjRWTDZwZmtQa0k1eUpZbk9iTHdJZTh6SnEyUHI3QnlBblpqNEZYaE4yQmtDRGtrUlNhaUY0OWw1eHVicThvRTlpNTVIdmdmU3A0Zk43bTNieUdkbnFENGRzcFFoRTFSTnVsXzh2UlIyUUtDSXh2cWVoWE5mdVdXWmJJYThMb1BBV2ZaQUNiYXJXaXZEc0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F1021" s="12" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G1021" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1022" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Valeurs actuelles</t>
+        </is>
+      </c>
+      <c r="D1022" s="10" t="inlineStr">
+        <is>
+          <t>[TRIBUNE] Référendum sur l’immigration : Marine Le Pen peut-elle reprendre la méthode « de Gaulle</t>
+        </is>
+      </c>
+      <c r="E1022" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNOUg4SXJWLXJCbjBlc2JxTXcwblZzTGZhSzFQQmJzVjJzR0N5eXVfM191YmJGeHR4eDhJeVZNYWtsX3hnTVJpOTFxMUs3Qy1VUnA1UnlIYWFUY0hXaWRfZERUcTZob3FPR2trVmFUanRRTGJsQ25LQ0FKRGFvY0tDUHZ3SmM4bUd5aWFkNDBhUUMyWnBvb3R5UkxVTFpUMTJGNG1PbHZrTVA2cEVKQnhmelRhR2FTd3o3Nk5YTm9ON3dmM01GZ3VpTnVWSmNEdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1022" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1022" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1023" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1023" s="14" t="inlineStr">
+        <is>
+          <t>20 Minutes</t>
+        </is>
+      </c>
+      <c r="D1023" s="15" t="inlineStr">
+        <is>
+          <t>L’exécutif doute « de la constitutionnalité » d’une amende contre le port du voile</t>
+        </is>
+      </c>
+      <c r="E1023" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNazNEVVQ0UkNHenVJVGZMdUJmbGxjcWhESmx4VlI5Ym0wUTUtOF8wN193UHRxaFE1ZDEtRmt0bkV1ZHlkTkVZc0Q2Z0dUTW9tMjNNQlRnMjFSM3U4ZS0tNjlld3RObFdtX3pBZER3MEk5R001VlB2X0JCd0Z3eHd1X0JjVXhIVUp4QzR5d0l0MktZaEw0aDZCV0dfSXhYb29vMmdncnhRYzRsalZRclJLdDhjc2FmOHNxLUpaYVJPbmFmU1lQRG1SZW1NTGdJZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1023" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1023" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1024" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>TRT Français</t>
+        </is>
+      </c>
+      <c r="D1024" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027: Marine Le Pen promet un référendum sur l’interdiction du voile</t>
+        </is>
+      </c>
+      <c r="E1024" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFAzN2Q0Qm5GNEJVa3YxRFJQNVEtZS1GbXU0SWNvLTZ1cTVBaWNvQnFUWFppRWlZalNyV1RSRldQcjJUdTB4WWVDSkFWYlBtM2RvYTdZNkQtYU5rZ25R?oc=5</t>
+        </is>
+      </c>
+      <c r="F1024" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1024" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1025" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1025" s="14" t="inlineStr">
+        <is>
+          <t>frontieresmedia.fr</t>
+        </is>
+      </c>
+      <c r="D1025" s="15" t="inlineStr">
+        <is>
+          <t>Le festival Rock en Seine relaie sur ses réseaux sociaux une insulte contre Marine Le Pen diffusée sur scène en plein concert</t>
+        </is>
+      </c>
+      <c r="E1025" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPNW1VZWIwTVphZDdLcWEwY3ZGSVkzVHU4TmwzWE9NWVA2QUZzYVdUZ0FrcFQ3TEZINlJwQ3R1eElFcVRjdk44cENHVUxrNkNXVUY4eDhweUxBNkRLVlJ5QmZWbWtzeGY4RF8zbGVBZG5Ua1RUZ3BsbDNkcHQ1SU9rdHlZVXBTNVMweGczekF3QmNLaF83X2Vuazh0M1ZYak9HYXJMUHpac1VFaGpPY1FvSE1TYXBINHItUkktcVRwWF9zZGppN2k5d0w1bVhHX1c4YTk5cFVpbG5YOVVrMl9fXw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1025" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1025" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1026" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Marianne</t>
+        </is>
+      </c>
+      <c r="D1026" s="10" t="inlineStr">
+        <is>
+          <t>Sondage présidentielle : Glucksmann progresse, Mélenchon recule, le Pen en tête</t>
+        </is>
+      </c>
+      <c r="E1026" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxObEwzckF1VkxQTEw5enhLcjZ0UExwc2ljcXdQUzFYczg0Ymw0SDZCRDVLa3I3RG1YeFcyYVlMSE9BcVFYcUp5ZXJYMTJFSEl5dzZDVTVLOC1WcmZicVNDNkRmLWt2SW5SQUpiNy00cmpRelN6WVVHYTh5TDdTWnVpUU5QV1VzSGhvb3VHLWkzRnVyNldFSFVucVc5Q3F1VWp4RXBMZDlickxRX1B1ZDduZkRn?oc=5</t>
+        </is>
+      </c>
+      <c r="F1026" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1026" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1027" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1027" s="14" t="inlineStr">
+        <is>
+          <t>lejdd.fr</t>
+        </is>
+      </c>
+      <c r="D1027" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2017 : François Fillon «n’appellerait certainement pas» aujourd'hui à voter Macron contre Le Pen</t>
+        </is>
+      </c>
+      <c r="E1027" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOczQzWmQzOFNyS3IyQmtCcmpPbUNaamlXSmowQUtwNVBhUFlzYzJaUFlDNE41OFFGLWtSbkNEcU9IQ3RpQ3lVSlZtVnB4RTlqODZvamNYcGxvQ0otbkZoY3plcUd4c2ZVdFlUZ1lHSkNfVUwwR1VWTFA3Y1lJZlJSQTdkYW4wN1pnc05RX2JwNi03amRVdHcwTGFhUno5YzBxMnk5Z25PVWFPNmlneTRzN0hYdVU0bm05aWFUNnBfaHo2RGZSbVJR?oc=5</t>
+        </is>
+      </c>
+      <c r="F1027" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1027" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1028" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D1028" s="10" t="inlineStr">
+        <is>
+          <t>Zemmour prépare son assaut contre Le Pen, saison 2</t>
+        </is>
+      </c>
+      <c r="E1028" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOQlJ3M1RUalNVUGhDZF9qZmJDSmp4ZXptTTJvVGp5UGhRdTdPQlBnWHFLWVVCbXRvZjBlLXRiNHJSZExXamtzcml6SWQ0T3NMYWF1b2FyUTZtNkQ1eGF1VkNDcHQwcWZQQ1Z5d2lrenVVOHFmYS1zT1AzYkZ4VHA1QTJfYXl2WHlKdnNr?oc=5</t>
+        </is>
+      </c>
+      <c r="F1028" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1028" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1029" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1029" s="14" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D1029" s="15" t="inlineStr">
+        <is>
+          <t>Voile, fermeture de mosquées, expulsions : ces mesures contre l’islamisme que le RN veut proposer par référendum</t>
+        </is>
+      </c>
+      <c r="E1029" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPcWtYU2EwTGJ0TERiOVJKcWpFcWQ1eXlUY2Q3bVdzRkhHUnJtUWNodEpzOXJaY1FBZ3ROTVE2TmVVY290ZWlOcE9QamtiUkhYdHJYdWVnWnRkcUFxc0ZVSXFBYlFwSzFWaEl2R3Jna05XQjZyallxbFJ4N1A0SURmZ1MzM1I5WlFMekFFRUFNUDYtWWNMZkRjT2s2WlZacTEzaWtaV3gxcnZvQ1pTRUF2c1RZMkhMSjBKQWJIZGYwaU9JNjdidkpSQmF6MEpMTEZsd1drZkJrdlRnMmdfT2JTUEdpVnJlUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1029" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1029" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1030" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>ladepeche.fr</t>
+        </is>
+      </c>
+      <c r="D1030" s="10" t="inlineStr">
+        <is>
+          <t>Il avait incité Jordan Bardella à s'imposer pour la présidentielle : au RN, le départ de François Durvye, conseiller économique de Marine Le Pen, ravive certaines divergences</t>
+        </is>
+      </c>
+      <c r="E1030" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxQWGEyczJzMHBLNFlSRGVfRG93bWpwUzdEMjB6a3hyUEFrRHJOWmlRNUl3dGNlbDVhb2k1QVp0cVlHNThRYnlPNE1KMDJPckxrNlpLY1hkak02UkZFTHE4NTFPX0h4NEFXZ3NDb2VoU1QzalZldWRGWk1oaGJ0NG9yZG4tOTc1NXMzMXNQZjVGcHgzeDFiandhd0dvRFdhOGNuRFljdWJXclVsYUFEaFloRTNsUWVvNXdITnYzZXJlbmRJMWlQUzROV09UUjBHRHdRRGx3RnhEZ3NxTGx1TjlXV1IzMGlXVllnOC10ZERSeHJ4Q0dWLURPRXkya2pmVmQ5VmRTZmZCUGhHVmwxeW1UMkxTNUR4M3NEaEJrS3E5UF8?oc=5</t>
+        </is>
+      </c>
+      <c r="F1030" s="8" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G1030" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1031" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1031" s="14" t="inlineStr">
+        <is>
+          <t>Valeurs actuelles</t>
+        </is>
+      </c>
+      <c r="D1031" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Marine Le Pen séduit de plus en plus la droite traditionnelle, selon un sondage</t>
+        </is>
+      </c>
+      <c r="E1031" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQaXlsT2RVWFlmSzMzQmg1QXp4X3ZNS2R0OWJ3bHFSbGxCN29iNU5uMlJwSzQ4OTNvS2h1OU9YYS1mNjgyM0gta3dzYUh4MXdsaENucXJtd0ZTM3ZDQ0xFRm1ZWHgya09ucHFlbUtpYnJESzZuY1lHMHJMbDBVVVRFOGJZWWtnTnJ6WHdJUTNuREVuNEpFcDRzR1dsN3VReDB2a3pMTjllOERyazVTelNHaEU4T3lMY1pzR0s4TlJ2YkxaY3FpVUFrR3NvUGEzSnlYWFk1VTdaZHI?oc=5</t>
+        </is>
+      </c>
+      <c r="F1031" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1031" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1032" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Boursorama</t>
+        </is>
+      </c>
+      <c r="D1032" s="10" t="inlineStr">
+        <is>
+          <t>Pénalisation du port du voile : le RN pousse un marqueur du lepénisme et propose un référendum</t>
+        </is>
+      </c>
+      <c r="E1032" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxNYmlmR2Q3WkpfX0FRQzVudEZEZHlRVldMQU9BSHZSdWktb0ZPZWZkZE5wNXpQcHRJN2VzcHR2Vkt6ZGNXMmR3RVhLMlhEVEFZeTdaVEx1OEpRZmMyYzQzQll3ZTRwRl84UUxqMkx5Nm1vdVB4TWJlWEZwelBPUkdGZmQxTTl5VWdtdGZtaVlJMm8xUlRsRS1nRVpINUhkaTRQa2FaMnYza0FYR1dmZ0d4Zlhkbm9RU19OTURqd2JIUEloVS1ZdkxUSkFBWGhGdjJTVl9iREQ4ZHkxMkJORGwwSFlRM0wwSGw3THpwcDNBS0JBNUY2VXY2YnJTczQ3c29qZXpoRExVU2hFQnRSSlk5X2ZPSlBCUUHSAZcCQVVfeXFMTWJpZkdkN1pKX19BUUM1bnRGRGR5UVZXTEFPQUh2UnVpLW9GT2VmZGROcDV6UHB0STdlc3B0dlZLemRjVzJkd0VYSzJYRFRBWXk3WlRMdThKUWZjMmM0M0JZd2U0cEZfOFFMajJMeTZtb3VQeE1iZVhGcHpQT1JHRmZkMU05eVVnbXRmbWlZSTJvMVJUbEUtZ0VaSDVIZGk0UGthWjJ2M2tBWEdXZmdHeGZYZG5vUVNfTk1EandiSFBJaFUtWXZMVEpBQVhoRnYyU1ZfYkREOGR5MTJCTkRsMEhZUTNMMEhsN0x6cHAzQUtCQTVGNlV2NmJyU3M0N3NvamV6aERMVVNoRUJ0UkpZOV9mT0pQQlFB?oc=5</t>
+        </is>
+      </c>
+      <c r="F1032" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1032" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1033" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1033" s="14" t="inlineStr">
+        <is>
+          <t>sudouest.fr</t>
+        </is>
+      </c>
+      <c r="D1033" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : le RN est confiant sur ses parrainages mais y voit une « mauvaise procédure »</t>
+        </is>
+      </c>
+      <c r="E1033" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNOGxyUEdJeE5wc3BwSjM0SVFXS05scUY3Z2JNQm1mTnJaNEJDRWRZZklZNkZkaGhVMVZDY2dXNFdnb1gxQmppU1ktWGtLd29TMkQ2bjVvcHlXSjlBSGc4MnBGc2JRZGphX0xIV0lrYkhVTHhKRWZfU1NOWV9jQTRwcEU0V3B5ZkMxaE9TVnRvTjBUQ3M0ajFHZ1Zrb3Z0VGZ5akI1ZG5YR09ZbFBGTDBxVk5rZHBHa29vWVpHU201N2NaX0hDZjZudVVhRklVNVQ5TTAtMWx2cw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1033" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1033" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1034" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Boursorama</t>
+        </is>
+      </c>
+      <c r="D1034" s="10" t="inlineStr">
+        <is>
+          <t>Interdiction du voile et amendes: le RN pousse un marqueur du lepénisme et propose un référendum</t>
+        </is>
+      </c>
+      <c r="E1034" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxNbThldXYxZnhqd3JOLTlsS0hxNXMzdTh3VlFkOFJoMlpIaVpWV3dhOC1QSXRpYWJaOVZOVEZtQkpkSHBYQ2FaOFVfR2l5cTFhTmRrcVEwd3NZVXdZZVVnTURsM3B5dmRBMllfRDhQYjRVUkRTR1dRdlBhRkhGXzh1NHFzSG9vYWdOenRZek1POFE0VlYteGpud3h5YVczYnFENzI3VDFnZmZYSnkzekRfRldWeTlfcnhmbEpTMUNTVGl6TUZkRUZ6MTNkSDFmbjhvQjZLRVRjNzFtdXdNTW01TUg4aWNfVUU3N283UjJCUkJUbFA4YTQxSmRCVEk3aXhWMmd0cVQ1YjdSSnh5SXl2dUhNQjFNMUFYQVBn0gGbAkFVX3lxTE1tOGV1djFmeGp3ck4tOWxLSHE1czN1OHdWUWQ4UmgyWkhpWlZXd2E4LVBJdGlhYlo5Vk5URm1CSmRIcFhDYVo4VV9HaXlxMWFOZGtxUTB3c1lVd1llVWdNRGwzcHl2ZEEyWV9EOFBiNFVSRFNHV1F2UGFGSEZfOHU0cXNIb29hZ056dFl6TU84UTRWVi14am53eHlhVzNicUQ3MjdUMWdmZlhKeTN6RF9GV1Z5OV9yeGZsSlMxQ1NUaXpNRmRFRnoxM2RIMWZuOG9CNktFVGM3MW11d01NbTVNSDhpY19VRTc3bzdSMkJSQlRsUDhhNDFKZEJUSTdpeFYyZ3RxVDViN1JKeHlJeXZ1SE1CMU0xQVhBUGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F1034" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1034" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1035" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1035" s="14" t="inlineStr">
+        <is>
+          <t>euractiv.com</t>
+        </is>
+      </c>
+      <c r="D1035" s="15" t="inlineStr">
+        <is>
+          <t>Le Pen lève le voile et donne le ton pour la présidentielle</t>
+        </is>
+      </c>
+      <c r="E1035" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPWHpHRTNMVGdvVUFCRV9WR1RldGU3cWczV25Fd0lqOUI2LXVxRFNDd3lUOGRLUXFqME5SdkE5cGtObEZNMS1Sb0hlM3pjdWhMbFRZLWdDSzhvM3VJUjZ4ODRHM2VxZUNRMlJYRXJxZGYwWEI5VlI2SDV5Y0xSbjcySENsMFllUFI5Y2F0VDVzaFkyMkk?oc=5</t>
+        </is>
+      </c>
+      <c r="F1035" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1035" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1036" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Public Sénat</t>
+        </is>
+      </c>
+      <c r="D1036" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle : et si les électeurs français étaient moins indécis qu’on ne le pense ?</t>
+        </is>
+      </c>
+      <c r="E1036" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQclpSdkZSTkFaRTBoUk9uNU56Vk1rWWE0QVlsQ3pzV0xXTnBiSHFpRGZuMkpaanRVc05UeGlzVDd1Vno1ZTVQRjZwUWdkVkxrWnNYMzFwckdyQllUNGNrMmJvQmxHSHRVemVQaTRsclF6Zno1aEt1ZzRGZU15M0dka05Cd1JCUTc5c3NBZmRQdW9jeHk5ZXdVaTJnVU5MSTdIYzVJM01qTEJ5MDl0UkRJWFVvRUN5ZXdWSTRFVUNQRGdOTXlCV0tBTGFB?oc=5</t>
+        </is>
+      </c>
+      <c r="F1036" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1036" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1037" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1037" s="14" t="inlineStr">
+        <is>
+          <t>Boursorama</t>
+        </is>
+      </c>
+      <c r="D1037" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : l'électorat français reste structuré par des préférences bien marquées, avec un RN assis</t>
+        </is>
+      </c>
+      <c r="E1037" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wJBVV95cUxPaDQ5VS1GeFlCSkxQTnAwcGNqQ3RuSzQ5UF81SUtBVHRydkxVeDZPTEh1Y242Q1ozRjZYNWYxZWxwUkY2NmZFY1dxSXB3dVZKdndPcjI1OFB4TWZzS1RzRmNRQ3Z1UUtBZFpnTmU2c0RIZjhtTmo0VXotaS00NnhvUlhVQndMRTMxSjMxdEJPOHhmMndVLXB4UGowWGdtQWJrRXVmb1A0Z3p5SEZpYjFaNS1BQWU3T1ZOc0g3aWY5UlozcFBDUnhQczhqUmktQndZWG0tQkRfNG1tR3cyS3VrTmhOMmpYaF9aMXJHQ3ZFb3U5Qm1ZazVJaWRRbUhSQ3ZHenFJZTZ6a2g2NnJhanZnTXlSZkh0NkZPc0hfclo2R0JkV19IMHZBUXhhQlNsd25NRmZOdU9fWTBEelV1MzNoS2tMLTZqblRXWW44anh2bVM4X1Q3V09SX0tqYkVXMXhWZVZkYm41SdIB5wJBVV95cUxPaDQ5VS1GeFlCSkxQTnAwcGNqQ3RuSzQ5UF81SUtBVHRydkxVeDZPTEh1Y242Q1ozRjZYNWYxZWxwUkY2NmZFY1dxSXB3dVZKdndPcjI1OFB4TWZzS1RzRmNRQ3Z1UUtBZFpnTmU2c0RIZjhtTmo0VXotaS00NnhvUlhVQndMRTMxSjMxdEJPOHhmMndVLXB4UGowWGdtQWJrRXVmb1A0Z3p5SEZpYjFaNS1BQWU3T1ZOc0g3aWY5UlozcFBDUnhQczhqUmktQndZWG0tQkRfNG1tR3cyS3VrTmhOMmpYaF9aMXJHQ3ZFb3U5Qm1ZazVJaWRRbUhSQ3ZHenFJZTZ6a2g2NnJhanZnTXlSZkh0NkZPc0hfclo2R0JkV19IMHZBUXhhQlNsd25NRmZOdU9fWTBEelV1MzNoS2tMLTZqblRXWW44anh2bVM4X1Q3V09SX0tqYkVXMXhWZVZkYm41SQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1037" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1037" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1038" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1038" s="10" t="inlineStr">
+        <is>
+          <t>Immigration: "Édouard Philippe fait le jeu, à travers la surenchère, de Marine Le Pen", estime Dominique de Villepin, ancien Premier ministre</t>
+        </is>
+      </c>
+      <c r="E1038" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxONWNBcGJRUnRlVXhjUDRucjJmaUk1ZzJvZkVFbFk4Yk4wRW5rSjExOFVnOGZKSE4tMDVDVVpaQ0Q2ampBT0FHcmRURmJPMk9uM0ZHbjJPN25jQ0pMVnBsb2hwWnBYTEJMR2MxcUctdWJrS25RS0o1QXkwN21jd21taDVhTlRCdGdacEYwZXFZX2FpRGZnNVpoM1dfS29OaHRucXgwdVFKUFBJaU9XekhYenpuSTBsRi1FdGlncHlrRndIMEF1Z3RrX0VEd3hyTDNGaW4taVJFTEd6MkZiS0FzNHpYOVg0eU1paUd5YzBaTE9mdEdGdkFCRzdSSnU4UmJVMzZ1NGxiaklYQzlCbVRIdGh1VzJBOTFHd216NHJ5WjVrSEZ5b21PdzdvaWpqOGpoZHY1ODk4RDZaZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1038" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1038" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1039" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1039" s="14" t="inlineStr">
+        <is>
+          <t>Orange Actualités</t>
+        </is>
+      </c>
+      <c r="D1039" s="15" t="inlineStr">
+        <is>
+          <t>Marine Le Pen renonce à sortir de l'Europe mais "elle la hait", constate Alain Duhamel</t>
+        </is>
+      </c>
+      <c r="E1039" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxQeUxzZVg2MVJwa05FRHhEZHRDalMycHpPRXE5dWFCQThKWGw5Wm1CUUd4Z1JfT3ZPai12VWhDYUJodFVEWEJuQ3diUlVPaG9zdzN2bXFPNEN0VElqcnlqY2FXLTdmcFJQZ1kzd3c3WXAxY1h6b0dBTUVVVzRwWEtQRUNxRmRBLVNZY216NllKc1JFNEdRTlljSWJjSmxMRkhZeWdfUXJmY2RKMDRLbmlkTV9Ic1NlSlJkRm1TWUU5TEUwSmxYOVUzMUY4ZEJvUlRuSWpQUXhyM1BOR181WS1yWjNkTFFERVhWZGxJNVZfNjdiYTYxVjQxSHZOZGVsVzk4Zko2bg?oc=5</t>
+        </is>
+      </c>
+      <c r="F1039" s="12" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G1039" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1040" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D1040" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : le RN peut-il imposer un tandem lisible entre Marine Le Pen et Jordan Bardella aux électeurs ?</t>
+        </is>
+      </c>
+      <c r="E1040" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQOG85OG8tOEhFbFotWEw0c3JKSVFvZ2FlcDQ1UlFDMlNuVWJjRGUxbGNNYjJVOXR5ZkdTM29OQlUxSnhHQURaZ0g2UnZUa19aNzhLZzZsT0xFUThqWGg3WjNVeFNMaUJlbGs3Rk1aRkJ5OXBWSmE1NWxsLVp5RGM0ekQxLUxmUHdyTGFvMGg5UEdsTnF3VkFCVEI2R3pza2tlZVJmUHVTaWQ2d3pyRnBRc2Y2X2VYRjFaLUJUY2g2UGRyQUo5QlMyZG0tYTljR0I5TVlyX0hadWhUVVA4WE85Z1ludVdtWnlueTc2TzJseVdFTk9z?oc=5</t>
+        </is>
+      </c>
+      <c r="F1040" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1040" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1041" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1041" s="14" t="inlineStr">
+        <is>
+          <t>Atlantico</t>
+        </is>
+      </c>
+      <c r="D1041" s="15" t="inlineStr">
+        <is>
+          <t>Retraites et dépenses publiques : la lourde erreur de Marine Le Pen sur l’emploi des seniors</t>
+        </is>
+      </c>
+      <c r="E1041" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNVlZiX3JnelNVNzFORWhYNnRpVmpZZjJrR3R5MXgwZFEzTEtqc251ZXowQlQwZVRLaGhlLURSYV8wbFloM1VRNTZBcEVGNFNqdXhPdm1kMF9USlRjTFF1MVZoa1BGUklNNElfRXJrOHlsbGFZS3ppVVFHdFY5dTRTRXIzRnU2dWZocWlMc0UzNzhVcU9sNWI5VGY5MVdEdG1UQzFyUzJSb1pDR3BiSERZMXNlS09hc2VuQVRqLXMwdlIwaGlGOUtuek9abXRMb0lHMXA2S213ZVAzNVdLQlJJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1041" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1041" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1042" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>ladepeche.fr</t>
+        </is>
+      </c>
+      <c r="D1042" s="10" t="inlineStr">
+        <is>
+          <t>Jordan Bardella : "Nous sommes un duo pas un couple", le président du RN met les choses au clair vis-à-vis de sa relation avec Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="E1042" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxQYTAxOV9KcVRVLU5TQVpWb2NOckNNd2F2TG5vM2E5WWliTWVxRjhHYTBlNU9TYnVlM1hOVkJaLVVFZ1ZhdzI5dExkVXd5WHhvNzRIcm5lckFYX3o4eEt6bkJOdjBna25iVzdFSmZ5ZmQ2d2JJdlhfTGpZRk5hSHNfb21udnpCM3lZWTZRZXQyd2NBWnM1Ym5TOEhvN3drZFROQzFVcVZ2M0hqLTlCcjd6akpWbXNtcVlfd3IxbUZTVlc2bFltU3ljYXNuNHUyV19BWXBPUzYwYVZkUmdhMzU3dVdFMDVwMVZUQXB1cTloV1NGekJsU25KOVQxbjRFQTJodVBlclhETmcxRUI3RWlHQm93?oc=5</t>
+        </is>
+      </c>
+      <c r="F1042" s="8" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G1042" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1043" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1043" s="14" t="inlineStr">
+        <is>
+          <t>Le HuffPost</t>
+        </is>
+      </c>
+      <c r="D1043" s="15" t="inlineStr">
+        <is>
+          <t>En recyclant cette vieille obsession, le RN se prend (encore) les pieds dans le voile</t>
+        </is>
+      </c>
+      <c r="E1043" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNSkt1dXNMU3paVDFqLU5neGM3ZmlrWk5qTjdoZlJRaGVld0NZZWlvdVljd2MtSTZ2Z1dzSFJNYVZMOWx0YVhLVndRclA1NmtBSWt6M0hvTUxoOVJ0UVBoX3ROQ09uSnJWeTdvd3I0ajJIaHN3ZC1FNzRQNC1WQkFzX3pNSm9BN1RoWThhMmtXWDIzRDg4bEUyVjM2SjZEb2xQSFZJaTByeFhGT2VjRFhTSWdfS1d2X2RpdGFpV1RNUnM3dElvbC1iT082elRrRGNWdHJxYy1GOU4yZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1043" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1043" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1044" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Le Nouvel Obs</t>
+        </is>
+      </c>
+      <c r="D1044" s="10" t="inlineStr">
+        <is>
+          <t>Ces sondages précoces de la présidentielle 2027 qui nourrissent un débat “purement spéculatif”</t>
+        </is>
+      </c>
+      <c r="E1044" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNTTRTaVM1T25VUkZtTnJoa0hlQkE1anctVXNMRHcyUkI0Wkp0ck45ZG9hWWhPT3UzZXZuRHh3a0hzSmVHcjlLTmg5Y0dpcTlmb1BKVm9XWDFZbVFnVTBxQWF1T1FEOEJUMzJONnkzbl9Wa3VZRkxzeEdNQmxUbktmS2NLdWFCSjZUV3NvUmV4WTgzb0hsdHlmbWJmUDVXZmVKVEhjZUNJWTFSVjI0U08wVkhtbVlLLXotUU80THlRWC03VVI2VE1rSjB1Tk9YYXFFWTluRTRTQmVzR1VtakE4Z1ctM0R3cjA?oc=5</t>
+        </is>
+      </c>
+      <c r="F1044" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1044" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1045" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1045" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1045" s="15" t="inlineStr">
+        <is>
+          <t>Est-il vraiment possible de sanctionner le port du voile, comme le souhaite le Rassemblement national?</t>
+        </is>
+      </c>
+      <c r="E1045" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOSVk3NmNoUEhiY2U4M1FSM1BvS2N1WWV0MzRySGZXLXI2UERPZVZYY016REdSNGpHZTZiWHRpTlpXQjBMTVgyZnZnZHQwbHZtOXBNQ2JZeEFLcm5NNElrS3FQMGN5a3ZUSFFlbzlCblFQU250TzR2cU9VZWdOSTRWN0tUdnJBZC1aeFU5Y0FWT1J5eVEtU29namV2c1RGbEU1dWR3WnZJQXBzOTdGaTlSUlJjNVRqUF9sUWRoN2tTOGVYQzRDWlhDdDROVVdqR2xMdGRuRDlLajBtejE0VWN3ME9NdW9FSnZod2p2RjR4WVdEZnJVN2dFdmF1VVBNYnJPZkZGcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1045" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1045" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1046" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1046" s="10" t="inlineStr">
+        <is>
+          <t>"Épargnons à notre pays ce terrible sort", lance Gérald Darmanin, ministre de la Justice et soutien d'Édouard Philippe, évoquant la possibilité d'un second tour entre Marine Le Pen et Jean-Luc Mélenchon en 2027</t>
+        </is>
+      </c>
+      <c r="E1046" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_AJBVV95cUxNdWpjZFR3UHBPai1fWnllZ3NOUWhCdWNhMUZ2Q180d292dkw2cEE0RC1KMER2dVBFSTVjTWkzbUg1MWZBU2s5TVFnbkNLLWMtRV95WnNaeFdFdTY1WnZXWXBrVWZ6S1g4SXRKbXprUmxXdm5hVFdYQmxXWkpGaVlxZ0hjbm1rSWtHZExveXY2ak9EcTdyMnlQSjJKSGJJaWZtWDEwdkxpQXNkcWRrSmxRQ25zOUZFSzZYbWRyTDhkUnJ3T0dLN1Z3TlRDLUc5RUtBT1JrX0RMZGNZeldLbUdkOVBBQTU2UHk3UG9SVlBJYTRXNEJJOG9UdXVqdUFweGducDN6b1czWWl1WG5NZlNkR3hlblBpXzBUTUlsQXFGeGZCQUNGYjhkcWV2UXMyS1J0WFV5Q3l2TzBGN0VPLU00ZFVlUFU1TFhnR0FUci1rME5hMkd0T0NJWUFnZjVWLW9jeHRvQklwNHFlMGdiQVJ1NXhJTVZFZTdxT21WQw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1046" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1046" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1047" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1047" s="14" t="inlineStr">
+        <is>
+          <t>Var Actu</t>
+        </is>
+      </c>
+      <c r="D1047" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : ce nouveau sondage bouleverse la bataille derrière Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="E1047" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaHBiTU9TY05ENnRCWnBGT2VEQUxZUTdVZk1zYVoyNFc1d1RnejI5N1BhOHUzZVMzUENrLTVQQmY0cHZaR2Vra0xqbWdUVXg0RWp6LWZYZi0yQ05tMTRsQU83SmJ0R3V3ZkN0VHJZN3JSVXhDNnNMZEdOaGh3aURabkk3cFMtZURNMHQyRnI3dGw1c2FvOVd2akpFejgzQnVDREY2aEd3bXRiT3J5?oc=5</t>
+        </is>
+      </c>
+      <c r="F1047" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1047" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1048" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Le Point</t>
+        </is>
+      </c>
+      <c r="D1048" s="10" t="inlineStr">
+        <is>
+          <t>« Ils n’y croient pas eux-mêmes » : sur le voile, le RN embarrassé par… sa propre proposition</t>
+        </is>
+      </c>
+      <c r="E1048" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQYzhPeXY0Z2R2RHRXbi10U1VPVWtaby1uZnNoUjZsazhzMjRvemtKVjVRX0hVaHV2TWVhdG42dmg2UV9XTHBSNUtCRjM0UFVIWXc2YmZ6QTN6OUFPOTVOaXFsZ19GXzdibzYzRFpoSFdXQU0zQ1pCS2JNYTJ6N2pIYVBkaVYtVG1GQmhMUTlSLXVUR1MwemduUkZGRTZEV2pxelBId1Nnb1BReFNoR2VHMHJ3TFIxenE4RV90RTN1RnBuc1ZxTThZbVNMQXZ6ZG5CcW5Ubjl5V01ROG85RkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1048" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1048" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1049" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1049" s="14" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D1049" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : à huit mois de l'élection, les autorités redoutent déjà des violences partout en France</t>
+        </is>
+      </c>
+      <c r="E1049" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQUE5JQzEyZVhoQ0lhX29fNkg3SnZsejVrOUhwbHVTVU9aUXNBUFYwRTQwRmMyNzU5Q2syUTJXdExfNWl5cUJFZnZZQmJxN0RpdlZHMGh6bzVJcnVBdmVvTEJwb2tYbjdfOXN3bUQyZlE2UDhTVV9TTUwwdkdHeGtrNUR4UGZWMEFFc0hHRWVhWTVPTkxYVXlIZ3hPVnc0SF8zRWJoMFBHWi1zOTRGZTUxcEc1aGpCNEY30gG-AUFVX3lxTE5adXRxdi1zZXN0S1U4NDFRdTRjUUdsTmdOWV9Ccm15ek9HbXV1UjMwdnBVYWFLdUE3eTg0UzVkODVtTHhPUzFqUmpaSk9ZNlZma0FGaVJmb01RVTBXNUV6RWtFWTRVSnhlWHV0Rzg1UlltNGdENTNhZ1R2R0dwdk00bmpGLXB0dloxN3lEREFmRjhybzQzbG5OX2xDRTdoMmhQak5RV2o0RXZISWtPYXhVR0lhRk9NRWxJQ1F3aWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F1049" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1049" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1050" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Les Echos</t>
+        </is>
+      </c>
+      <c r="D1050" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : l'ennemi, c'est le mou</t>
+        </is>
+      </c>
+      <c r="E1050" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNVW1oM1FNcWhuaTNiY2RlSmJjSFV4d1lDTjJXQzFUM0JRc013NUExRG9pSHh2UW5MMXhrek1ZY0NzWjQxNUMwdE5SMVpzbG1QOEQtU0JQQ2NFbUZfWmJMOXFKd3lMQlBVbGlpTHVqTENkVW9WYXNwLWI5a1JDRm9qUUpHNzFITHVzSG1zQWRmb1VtbGd4VEJWdmM3b0JuSWM2RUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1050" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1050" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1051" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1051" s="14" t="inlineStr">
+        <is>
+          <t>parlons-politique.fr</t>
+        </is>
+      </c>
+      <c r="D1051" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : le duel Le Pen-Bardella oblige le RN à clarifier sa ligne et sa future équipe de pouvoir</t>
+        </is>
+      </c>
+      <c r="E1051" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPSnF1WTM5elJMOFJfWXJDclJQRUZJam9TUkRwb1RwMUdSSFA1SlZPTWZTVC10ZVlkTzVfSnhURkwwZE9ZUHVaSmsyUnNuQ0h0VjZmMmRRRDA2YjExeVI1RGpPWFZfY0JYMTB4ckhxbDctcHphM3BhRGxXRWJCZDYySmFuaUt0UFVVSTQxcWVXNHBORk9GdDJVcVZsWlJyZUR1dUtmQmxWeUNGN2ZoWnRhWFBVZXoyTGtpaUk4U3Fma29wY1VMRTJFWVJpX19jMzJNWktxc1ZpSmlocFZHU05sOHVnQnhTVEhBSzI1QWI0Yw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1051" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1051" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B1052" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Le Nouvel Obs</t>
+        </is>
+      </c>
+      <c r="D1052" s="10" t="inlineStr">
+        <is>
+          <t>Un électorat stable mais un front républicain qui se fissure dangereusement : l’étude de Terra Nova qui inquiète</t>
+        </is>
+      </c>
+      <c r="E1052" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOLVNZajc4NjB2MWJBU0pIbGtycmFkbUtrMGhkVDhsNTdiRkNMMkxTSVhTa2doSGJJVXZLQUEtZ1pSenFuQXdMbUh0RXRMRnhzbkFTVUJYZjFqdzFKUnVYSEVXSFhJWEZLcDliZlF6Z2txZUpSelBHcE5YZ0EtM0lWWk1vRnA2cW9zWjhVY3IzZnd0YjhMNzRudnZtcUV6MDlpSlJwNzkzWVhXSTNSSzA1QzBhXzdvY1lIZzNLX0hfS05acjd1eG1kMFV5U1pqN1B1LVM0cXNTXzFvQWNkOHA0SFk5a3dad2xuR1VJbW9FekZKOUFhdi1sYl9UbVc1cUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1052" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1052" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G837"/>
+  <autoFilter ref="A1:G1052"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -33053,6 +41008,221 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E835" r:id="rId834"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E836" r:id="rId835"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E837" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E838" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E839" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E840" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E841" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E842" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E843" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E844" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E845" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E846" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E847" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E848" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E849" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E850" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E851" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E852" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E853" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E854" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E855" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E856" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E857" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E858" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E859" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E860" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E861" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E862" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E863" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E864" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E865" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E866" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E867" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E868" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E869" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E870" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E871" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E872" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E873" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E874" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E875" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E876" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E877" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E878" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E879" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E880" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E881" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E882" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E883" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E884" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E885" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E886" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E887" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E888" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E889" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E890" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E891" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E892" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E893" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E894" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E895" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E896" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E897" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E898" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E899" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E900" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E901" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E902" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E903" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E904" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E905" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E906" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E907" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E908" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E909" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E910" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E911" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E912" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E913" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E914" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E915" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E916" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E917" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E918" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E919" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E920" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E921" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E922" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E923" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E924" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E925" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E926" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E927" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E928" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E929" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E930" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E931" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E932" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E933" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E934" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E935" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E936" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E937" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E938" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E939" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E940" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E941" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E942" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E943" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E944" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E945" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E946" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E947" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E948" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E949" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E950" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E951" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E952" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E953" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E954" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E955" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E956" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E957" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E958" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E959" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E960" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E961" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E962" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E963" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E964" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E965" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E966" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E967" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E968" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E969" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E970" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E971" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E972" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E973" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E974" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E975" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E976" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E977" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E978" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E979" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E980" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E981" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E982" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E983" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E984" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E985" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E986" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E987" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E988" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E989" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E990" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E991" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E992" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E993" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E994" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E995" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E996" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E997" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E998" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E999" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1000" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1001" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1002" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1003" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1004" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1005" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1006" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1007" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1008" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1009" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1010" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1011" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1012" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1013" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1014" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1015" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1016" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1017" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1018" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1019" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1020" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1021" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1022" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1023" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1024" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1025" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1026" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1027" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1028" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1029" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1030" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1031" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1032" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1033" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1034" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1035" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1036" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1037" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1038" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1039" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1040" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1041" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1042" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1043" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1044" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1045" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1046" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1047" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1048" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1049" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1050" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1051" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1052" r:id="rId1051"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33088,7 +41258,7 @@
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>Articles detectes par le radar - GDELT + Google News RSS (secours) - 02/09/2026</t>
+          <t>Articles detectes par le radar - GDELT + Google News RSS (secours) - 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -33158,81 +41328,81 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>371.875</v>
+        <v>185.483870967742</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H8" s="25" t="n">
-        <v>108.4905660377359</v>
+        <v>158.8785046728972</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>Gabriel Attal</t>
+          <t>Édouard Philippe</t>
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>541.1764705882354</v>
+        <v>483.3333333333333</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>340.625</v>
+        <v>1291.666666666667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Édouard Philippe</t>
+          <t>Gabriel Attal</t>
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>1100</v>
+        <v>118.5185185185185</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>900</v>
+        <v>506.4516129032258</v>
       </c>
     </row>
     <row r="11">
@@ -33242,25 +41412,25 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" s="29" t="n">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="D11" s="28" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E11" s="30" t="n">
-        <v>241.6666666666667</v>
+        <v>153.4883720930233</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11" s="30" t="n">
-        <v>541.1764705882354</v>
+        <v>875</v>
       </c>
     </row>
     <row r="12">
@@ -33270,19 +41440,19 @@
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" s="25" t="n">
-        <v>1100</v>
+        <v>855.5555555555555</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>0</v>
@@ -33305,7 +41475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -34323,6 +42493,626 @@
         <v>4</v>
       </c>
       <c r="F40" s="36" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C41" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="38" t="inlineStr">
+        <is>
+          <t>Relation et rivalité avec Jordan Bardella (tandem RN)</t>
+        </is>
+      </c>
+      <c r="E41" s="39" t="n">
+        <v>25</v>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>Le Pen conserve une large avance dans les sondages mais doit gérer des tensions internes au RN (rivalité avec Bardella, départ d'un conseiller économique) et la polémique sur l'interdiction du voile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C42" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>Voile islamique : proposition de référendum et d'amende</t>
+        </is>
+      </c>
+      <c r="E42" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="F42" s="36" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C43" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="38" t="inlineStr">
+        <is>
+          <t>Sondages présidentielle 2027 (Le Pen en tête)</t>
+        </is>
+      </c>
+      <c r="E43" s="39" t="n">
+        <v>13</v>
+      </c>
+      <c r="F43" s="40" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C44" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>Programme économique (retraites, 125 milliards d'économies, règle d'or budgétaire)</t>
+        </is>
+      </c>
+      <c r="E44" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="F44" s="36" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C45" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" s="38" t="inlineStr">
+        <is>
+          <t>Départ du conseiller économique François Durvye</t>
+        </is>
+      </c>
+      <c r="E45" s="39" t="n">
+        <v>11</v>
+      </c>
+      <c r="F45" s="40" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C46" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>Alliance avec Gérald Darmanin (rentrée à Tourcoing)</t>
+        </is>
+      </c>
+      <c r="E46" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="F46" s="36" t="inlineStr">
+        <is>
+          <t>Philippe s'impose comme le candidat de référence du bloc central, entre ralliement de Darmanin et concurrence directe avec Attal sur le terrain économique et migratoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C47" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="38" t="inlineStr">
+        <is>
+          <t>Rivalité avec Gabriel Attal pour le leadership du bloc central</t>
+        </is>
+      </c>
+      <c r="E47" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="F47" s="40" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C48" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>Débat avec François Hollande à Sens</t>
+        </is>
+      </c>
+      <c r="E48" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F48" s="36" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C49" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" s="38" t="inlineStr">
+        <is>
+          <t>Réforme de l'assurance chômage (indemnisation réduite à 12 mois)</t>
+        </is>
+      </c>
+      <c r="E49" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" s="40" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C50" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" s="34" t="inlineStr">
+        <is>
+          <t>Politique migratoire plus ferme et refus du moratoire de Darmanin</t>
+        </is>
+      </c>
+      <c r="E50" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" s="36" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C51" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="38" t="inlineStr">
+        <is>
+          <t>Rivalité avec Édouard Philippe pour le bloc central</t>
+        </is>
+      </c>
+      <c r="E51" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="F51" s="40" t="inlineStr">
+        <is>
+          <t>Attal structure sa campagne (équipe, soutiens patronaux) tout en s'opposant frontalement à Philippe sur la ligne du bloc central.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C52" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="34" t="inlineStr">
+        <is>
+          <t>Constitution de son équipe de campagne (Céline Géraud, recrutements)</t>
+        </is>
+      </c>
+      <c r="E52" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" s="36" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C53" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="38" t="inlineStr">
+        <is>
+          <t>Rencontres avec le patronat et débat Medef</t>
+        </is>
+      </c>
+      <c r="E53" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="F53" s="40" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C54" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>Hypothèse d'une primaire à droite et au centre</t>
+        </is>
+      </c>
+      <c r="E54" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" s="36" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C55" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" s="38" t="inlineStr">
+        <is>
+          <t>Programme retraites (capitalisation, âge légal)</t>
+        </is>
+      </c>
+      <c r="E55" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="40" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C56" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="34" t="inlineStr">
+        <is>
+          <t>Programme pour l'école (internats disciplinaires, collège unique, salaires profs)</t>
+        </is>
+      </c>
+      <c r="E56" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="F56" s="36" t="inlineStr">
+        <is>
+          <t>Retailleau tente de relancer une campagne poussive avec des propositions clivantes sur l'école et des attaques appuyées contre LFI, sans décoller dans les sondages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C57" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="38" t="inlineStr">
+        <is>
+          <t>Rentrée politique et campagne en difficulté dans les sondages</t>
+        </is>
+      </c>
+      <c r="E57" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" s="40" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C58" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" s="34" t="inlineStr">
+        <is>
+          <t>Hypothèse d'une primaire à droite</t>
+        </is>
+      </c>
+      <c r="E58" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" s="36" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C59" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" s="38" t="inlineStr">
+        <is>
+          <t>Attaques contre LFI qualifié de "parti de collabos"</t>
+        </is>
+      </c>
+      <c r="E59" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" s="40" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C60" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" s="34" t="inlineStr">
+        <is>
+          <t>Réforme des retraites (âge légal indexé à l'espérance de vie)</t>
+        </is>
+      </c>
+      <c r="E60" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" s="36" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C61" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="38" t="inlineStr">
+        <is>
+          <t>Appel à une primaire ouverte de la droite et du centre</t>
+        </is>
+      </c>
+      <c r="E61" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="F61" s="40" t="inlineStr">
+        <is>
+          <t>Lisnard mise tout sur l'organisation d'une primaire à droite et revendique une dynamique de parrainages, malgré une faible notoriété dans les sondages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C62" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="34" t="inlineStr">
+        <is>
+          <t>Annonce de 500 promesses de parrainages</t>
+        </is>
+      </c>
+      <c r="E62" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="F62" s="36" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C63" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" s="38" t="inlineStr">
+        <is>
+          <t>Hommages à Philippe Bouvard lors de ses obsèques à Cannes</t>
+        </is>
+      </c>
+      <c r="E63" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="F63" s="40" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C64" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>Débat Medef face à Fabien Roussel</t>
+        </is>
+      </c>
+      <c r="E64" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" s="36" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C65" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" s="38" t="inlineStr">
+        <is>
+          <t>Propositions fiscales sur l'héritage et les donations</t>
+        </is>
+      </c>
+      <c r="E65" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" s="40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -34378,7 +43168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M58"/>
+  <dimension ref="A2:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -34512,19 +43302,19 @@
         </is>
       </c>
       <c r="I4" s="5" t="n">
-        <v>107.1</v>
+        <v>106.8</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>115.9</v>
+        <v>123.8</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>106.5</v>
+        <v>106.7</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>120.9</v>
+        <v>125.5</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>104.2</v>
+        <v>107.7</v>
       </c>
     </row>
     <row r="5">
@@ -34554,19 +43344,19 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>111.4</v>
+        <v>124.7</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>117.8</v>
+        <v>133.3</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>106.5</v>
+        <v>109.1</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>124.5</v>
+        <v>136</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>106.5</v>
+        <v>113.1</v>
       </c>
     </row>
     <row r="6">
@@ -34590,6 +43380,26 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>130.1</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>137.3</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>114.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35591,16 +44401,16 @@
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D52" t="n">
         <v>15</v>
       </c>
       <c r="E52" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F52" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
@@ -35613,16 +44423,16 @@
         <v>22</v>
       </c>
       <c r="C53" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F53" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54">
@@ -35635,16 +44445,16 @@
         <v>11</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
@@ -35654,19 +44464,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="E55" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F55" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56">
@@ -35679,16 +44489,16 @@
         <v>19</v>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D56" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57">
@@ -35701,16 +44511,16 @@
         <v>5</v>
       </c>
       <c r="C57" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E57" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F57" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58">
@@ -35720,19 +44530,41 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D58" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" t="n">
+        <v>17</v>
+      </c>
+      <c r="F58" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>4</v>
+      </c>
+      <c r="C59" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" t="n">
         <v>0</v>
       </c>
-      <c r="E58" t="n">
-        <v>5</v>
-      </c>
-      <c r="F58" t="n">
-        <v>7</v>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/articles_presse.xlsx
+++ b/articles_presse.xlsx
@@ -14,7 +14,7 @@
     <sheet name="_donnees_graphiques" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ARTICLES'!$A$1:$G$1052</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ARTICLES'!$A$1:$G$1189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -408,12 +408,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$59</f>
+              <f>'_donnees_graphiques'!$A$3:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$B$3:$B$59</f>
+              <f>'_donnees_graphiques'!$B$3:$B$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -444,12 +444,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$59</f>
+              <f>'_donnees_graphiques'!$A$3:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$C$3:$C$59</f>
+              <f>'_donnees_graphiques'!$C$3:$C$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -480,12 +480,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$59</f>
+              <f>'_donnees_graphiques'!$A$3:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$D$3:$D$59</f>
+              <f>'_donnees_graphiques'!$D$3:$D$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -516,12 +516,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$59</f>
+              <f>'_donnees_graphiques'!$A$3:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$E$3:$E$59</f>
+              <f>'_donnees_graphiques'!$E$3:$E$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$59</f>
+              <f>'_donnees_graphiques'!$A$3:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$F$3:$F$59</f>
+              <f>'_donnees_graphiques'!$F$3:$F$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -675,12 +675,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$6</f>
+              <f>'_donnees_graphiques'!$H$3:$H$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$I$3:$I$6</f>
+              <f>'_donnees_graphiques'!$I$3:$I$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -711,12 +711,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$6</f>
+              <f>'_donnees_graphiques'!$H$3:$H$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$J$3:$J$6</f>
+              <f>'_donnees_graphiques'!$J$3:$J$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -747,12 +747,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$6</f>
+              <f>'_donnees_graphiques'!$H$3:$H$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$K$3:$K$6</f>
+              <f>'_donnees_graphiques'!$K$3:$K$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -783,12 +783,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$6</f>
+              <f>'_donnees_graphiques'!$H$3:$H$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$L$3:$L$6</f>
+              <f>'_donnees_graphiques'!$L$3:$L$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -819,12 +819,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$6</f>
+              <f>'_donnees_graphiques'!$H$3:$H$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$6</f>
+              <f>'_donnees_graphiques'!$M$3:$M$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1052"/>
+  <dimension ref="A1:G1189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -40169,8 +40169,5077 @@
         </is>
       </c>
     </row>
+    <row r="1053">
+      <c r="A1053" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1053" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1053" s="14" t="inlineStr">
+        <is>
+          <t>Atlantico</t>
+        </is>
+      </c>
+      <c r="D1053" s="15" t="inlineStr">
+        <is>
+          <t>David Lisnard, le candidat libéral que la droite et les médias ne prennent pas encore au sérieux même quand il joue ses universités d'été à guichets fermés</t>
+        </is>
+      </c>
+      <c r="E1053" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioANBVV95cUxOSGt0YVprZWZJVGJXOWVuUDhtd0U5ZjI4Z3pHaHJER2NHU21PVGpsYVVQa0U3ZHJGbS1KMXVCNW1RWHU0WVpXYThTUVpaSjFPQ0FfbVp4ZXJGTTZxYkh1djhrUFM2bkdQa01YWkJ2anU4OXBtOHVzUFNLSUNablZNU0xvaUxEbzBNZHZBcVpleVpGVGRUNFRycE10RDlRQnRwVmJ0VTBWVklPTFJxVDRlVEtHcEUxa0h0cElCVS0yYjlBUTMyUW5jQVNoQUVNVU9BenR3QU1Hb3V5d1QxLUFFWVg4Ykp2MVl5eEFxdC1IMnpUTE5ZbkxZOW9FRFNqRHF1OXVndUpDQVFUd1NxX0E1UmQ1bVQ4emVQbUZ4SVVIaGVicWNGSHM1d0lINjBKZ28zUDluMlNtcjI3SURHd0Y1YTJxaGlzUFJOMnMwQmN3MnBpUVktZ3YteWZBRkx5MkxjTEU4aE5ILWMtOTRVbm5Wb0dUX3BJMzNXRHNaN3ZMYk1vQ2FjeEpnNElKVXNvUWZYYXRhSGZNUWVJb25XWm5jNg?oc=5</t>
+        </is>
+      </c>
+      <c r="F1053" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1053" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1054" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1054" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027: le maire de Cannes David Lisnard affirme avoir recueilli les 500 promesses de parrainages</t>
+        </is>
+      </c>
+      <c r="E1054" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxPdFk1VVZEV1YxbVp2Tm45OHFQdkl4N09wMjJIZmpOTTJRSVp6MDlBTTRpLWN4cEktRmpaQ0U4TEhiaFlRTnprSHVGcWR2YU01a1MwZXcxejZfQ0NDRlhpZWRsWEppREhZelU5bmM5cGszNFVxaUQxWkw5LTlnZlpFVVJ6NnJmdUk0Snl6cDRRelBSbEUxWWZhYU1lT3NNckFXVkNLVGt5Rjg0MjA4UFY3cmVwRTBvSHl1MkticGhtRE8zRnhvbzI1NnVmQTZtV3I3N2lleG1fenlDU1pIZm1QNW93a1RCZkhhaTJNd21qQUowSDNBU2RQSVZqTncwTG1YLVI3TXU1MzRCR3lqbkJEejVpZlh3Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1054" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1054" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1055" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1055" s="14" t="inlineStr">
+        <is>
+          <t>Nouvelle Énergie</t>
+        </is>
+      </c>
+      <c r="D1055" s="15" t="inlineStr">
+        <is>
+          <t>David Lisnard est-il candidat à la présidentielle 2027 ?</t>
+        </is>
+      </c>
+      <c r="E1055" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNR3BhTEZDeWxFQ21CSzF3RDBBN3BMTFFIUzVMT3o0ZmpsSWc2STNCNmoteGNVX3ZsNDNzQ1lpZm9NMDRGWFFTQnM1U3Awc2pETDN3d3dHTjZFcXNNTXFDWk1EUnhkREh0OXJwNW8xYjhmdTNhS1VGMDQ2eS0tWktOamprRU5ieWx5UkFPSXdHdWtQdlNMQjRRWEt0RTc1elZa?oc=5</t>
+        </is>
+      </c>
+      <c r="F1055" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1055" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1056" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D1056" s="10" t="inlineStr">
+        <is>
+          <t>« Il faut éliminer les macronistes » : David Lisnard veut une compétition à droite avant le 1er tour de la présidentielle</t>
+        </is>
+      </c>
+      <c r="E1056" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gJBVV95cUxNN0ZxOFJZeVhaWVoteFNYTVpQUTlRQkZDdGxNSUZSUmV0ZkFYOVR3RHdLZnB4TXk0YXc0ajJIQnRkY0pHN1g4UFk2ZFBXa25QVlVBUGg2QjkzcG41U25kbmhxeGkzTzNMNFBjMEE3M1JqUGtzSzhJSDVZbk9ON01aMWtzUl82WnhIZmV6T0Zua3BJNEo2WEFSQ1g2bXR4SlBiODVGTm14SndEc0haS2xicEljUmxTMGxZNXBVN013SERUeThTY09iYWtCVXhwZ01TcWFVbVA3ZElBcWJsUks0Ri00VFB4TmJSeUQxdS1SV3Q1WXVMcWROQW41T1lIN3RieXpIVnNMUi02bU44NnpSODJvWkhiUnh3T05ZNjdCc1FGNTJtWmpjS0FYYnU0YnVTZDRsMkJxNjZMWmdnWE40ODdVN004QkNvWF9VWVZJVDY3dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1056" s="8" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G1056" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1057" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1057" s="14" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D1057" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : David Lisnard veut «rétablir le délit de séjour illégal en France»</t>
+        </is>
+      </c>
+      <c r="E1057" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNUElySURBRkZLUVpaMTYxVzcwZGdKZmVOdTNndDh1dFVzTjktLXVOcGUtS3dqM1dHN0dnRjZDUlVnQ1o3alFRb2RvQjJHRzEtdldka0c1QmJFV2FCQTQxdUdMWmR6TGxsanprWmJGRkJFNXhiZmJMWlExbU0yZWdTRFdMQTNZU05uUGVLOEJya25xbUN0aXdGRVhQaTNEZTFHcnJPRXBUc0pmbUFQY2lST20wMkhtckxlVzdtNC1COFZiR3I1X1pJMjAxd0YxQmxISHdjQW1RN3NaMTZHdHN1eF9Sc0Y2aTFNT0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F1057" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1057" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1058" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D1058" s="10" t="inlineStr">
+        <is>
+          <t>«Jean-Luc Mélenchon a viré dans le neofascisme», avance David Lisnard</t>
+        </is>
+      </c>
+      <c r="E1058" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNeXJLemd4NGZUVVN3VmNoRmJGODhoUWFoTldHeWZNZ19IQ1VkZkNZNF85Wnd1eUlyd3dzU3RZdWw5WkZaVXppSktxZDFJSlZoVlNpdUN6TDZLZEp2ZmRhaE5XYXNTMFN2bTliLU1NN0podXhtR1JTU3UzeFhpcnpzNGFqVmFYcjNWVGZsMjAzdTUzSjdSUjBXcWRvcnlPakVXTnY3cGdlbnExd1NZT1JJMdIBtgFBVV95cUxQTVBqUmZSaW15SjMwOTl4cF9ZMVljQzZBenhuYWt0bmRFYkhLbVhyUWNEMTZGMjV5anJKaVhoa2l3TkRBNUhoS2VRTzI3MExfM0w2Y3FmQVdfUlJWQmI0bWlTVE5wZFpZbWViX0tGbm96VG83SGIyWEk1RTlnQ0VlLXRZXzREbXdIV2ZFMXM1N0tzel9KeV9iZkFGZDFTLXZVR3VHbktvc2hsdXo3bVQzMzRoRWpWUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1058" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1058" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1059" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1059" s="14" t="inlineStr">
+        <is>
+          <t>Europe 1</t>
+        </is>
+      </c>
+      <c r="D1059" s="15" t="inlineStr">
+        <is>
+          <t>2027 : «Édouard Philippe a peur» de la primaire, juge David Lisnard</t>
+        </is>
+      </c>
+      <c r="E1059" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNZndVWm9oQkhjb01tMTdMeGU2V0ZIS2dwUmIzSTNuLTJUV0k2ZVl1d3NuX0I5dm85X3A1cEFQbDhJcHJHbS1IRFo0bkhzc2Q5NmdVZ0lJc1p6RHV5TkRkSUswMHotcjFwRmtCVjNkVGEzdXNfTVhKMGFMVEZNRHBsdXREMDRkUkZUZUh6MVpOV1JkcUxqUlVPQ0ZDM2ZGWlBvVUtpN2ZB0gGrAUFVX3lxTE9hM2EyczJqMkhkcXEtTkhqaU9maURKTHF3aWNoN2pXdFNSRkYyNnUtV0hCUTdkTmJyNC04QmVqREtoUzZaWUxWUEhaYWxucUpoSTAzWW1XMlQwMkFZMzctZXdKQzhyMUtoVktxUTZzV2xRLXd0ZnBoY1FrMk90dXRjTml1em52UVd4dVh6MkdOcEE2UVVoQ2RKVDR2dXRXS0pJZC11QS1yM0tmcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1059" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1059" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1060" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Europe 1</t>
+        </is>
+      </c>
+      <c r="D1060" s="10" t="inlineStr">
+        <is>
+          <t>«Ils exaspèrent tout le monde» : David Lisnard dénonce le mouvement des syndicats de Radio France contre l'éditorialiste Charles Sapin</t>
+        </is>
+      </c>
+      <c r="E1060" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxNS3JwVi1JcGozNGJuN2w0d25CLXBCZjZUOGdHQl9xRGVNU2dZTEdRSEd2eTZLZlE4UE5IeVNKc3Q1bmt5dzE5N21NNXhVWXhOZjVyRU0tWk4tSThFZGl4ZkZxR1FUM1gwUHhaUm1VMGtIR1h5SFVITTJXLXkxRUZyZHd0V1B5dTJMeVNVbWRMMUNOc0Z4NWxHT1dmNFNPZWFCRnBOVnhINE52RkRUTVFCekdsNnlNSDZWZzBtaHlPRkJ6VE02QnN4QVJtYjVDNWd5bTY2WG41d09UdDdPWXo3Y2c3WDU1TF9jRGZFTGtoeGdQQzVHWk5oVl9MczfSAYICQVVfeXFMUFB0aGw0RWdKM1F5N21IZFpHSlhZNG5LM18ydGZNRUlHMU1mVGVENWpDc01GVHd0Tm9aZ1YwZEN4dVdfcHd3RWRGZlg0UmdhaVhwUTYyUEpJTUVDVlFSSFdfNVo2M3hPNTRBS0MxS2NFc29abVVSSEVLbFhTS0tQenZ2Wnc0aGN6cHdHSWdGc2JlSHJHLWRhczZ1NFhtZUgwZjgwUmpxOVRWR1htUGE5bTg5cFZ5Q29WdUl5aUtscjNKTDhQTW12YUlSRG9PMnZPZFdZVTFfbWEzdW8xNXBHd0NjUnZ1elNENWpHdGZ4akU0STJkWlloQUN1QTFDU2JWTVN3?oc=5</t>
+        </is>
+      </c>
+      <c r="F1060" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1060" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1061" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1061" s="14" t="inlineStr">
+        <is>
+          <t>Nouvelle Énergie</t>
+        </is>
+      </c>
+      <c r="D1061" s="15" t="inlineStr">
+        <is>
+          <t>David Lisnard sur CNews et Europe 1 : «Je veux une alternative, pas simplement une alternance»</t>
+        </is>
+      </c>
+      <c r="E1061" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPdklnZnZPN1lWRDBnYXVIVkFJWUJwQ21XVkswR203a3MySEF3TE5BaXo4UDNKWkVZdkJKTEEzYXBNWXdWRUY1amtLQUhLWjktbWJIQjJxN0JldGpMNXpKS1FMSnU3cnEtRUtZQjllVUdaN0xHTDNoRGJaTVVnbHNZVFhRSnB4bHpmek9tdjU1eW5HemtHMy1EZkFfMF9ieUQxSWNodGEwM2RiOFp2Qk9GVlU4VG05bGRzcVA0YmFIdFhWWWM?oc=5</t>
+        </is>
+      </c>
+      <c r="F1061" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1061" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1062" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>lejdd.fr</t>
+        </is>
+      </c>
+      <c r="D1062" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle : David Lisnard affirme avoir déjà réuni 500 promesses de parrainage</t>
+        </is>
+      </c>
+      <c r="E1062" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQangwVGhINVVKam1oaWZtdmxuQ2pqc2xqbW5SNkRkanNSV25yWG5La1RHNlhVR1lWbkNOQlJkTkxjLUdtSV84MkNoYVBpTWh5VDhSVkgzckFmcm5WT0NDU21mTVIxaGRGS05NU0JXTXl5SDhlanhRcTk3LXNrSGtvZ214WkM5OHc4QjE3Zi1FcTBndlpXamoxckN6UWx5QlRRYTRTUjF6NEtqcW1PZEJicWpjdUVSbEpJWnhB?oc=5</t>
+        </is>
+      </c>
+      <c r="F1062" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1062" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1063" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1063" s="14" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D1063" s="15" t="inlineStr">
+        <is>
+          <t>«Il faut rassembler les voix de la droite et du centre», martèle David Lisnard</t>
+        </is>
+      </c>
+      <c r="E1063" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQLXhXYVdmdVpxYTlPU0w0SWpOZmlPTEJROXpRM0hyazhPTmdhRnZTOWRlZF8tNzZZcWZITVpOajMwUDhwT3E0TFpHclFXZUVMWmk4YVNXQjZib3l4a3NEMXczT0dqcTJCNmJNX1RTZjZuUE1UU0Zqc1lxRFJxb3dpbkx3NWRLSld6MW94dmwxRHJRUFhudlVleVJfeG9wTUFkT2hVZDZickRJd09zcFNzQUVVMEjSAboBQVVfeXFMTWY0ZzVTMlFDci1qblRvSDVpOXNmTDZGWDJXaENBNnpKSmdvdzVnaWw3ZlVaX3RDNTdocEtZZEpDemRpNDJwNnEtZk95dHNQQllhenJfWnk1azQwNVo5RDJJODJtcHlIMk1Jbzg2aWR4SnotMV9yR00xYWI2alMzV2ZicUNTYnptSjVQU1U1S1ZpWlNLMXFiM2ozbWZBSjFNYTdfd2xiajQtZzBSeU1CSHItbFBDUDRFd1pn?oc=5</t>
+        </is>
+      </c>
+      <c r="F1063" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1063" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1064" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Nice-Matin</t>
+        </is>
+      </c>
+      <c r="D1064" s="10" t="inlineStr">
+        <is>
+          <t>« Éliminer les macronistes avant le premier tour » : pour sa rentrée politique à Cannes, David Lisnard réclame à nouveau une primaire de la droite et du centre dont il espère sortir vainqueur</t>
+        </is>
+      </c>
+      <c r="E1064" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AJBVV95cUxPYUdmXzl6MHlZVmE4WWdrdHVwbHdLQVpfRzJTR1FBb3YxUmdKWGpHXzdwQS1uV2FHSGJaa1VLUEZKRUNGNVIzYmlTNmJyOG05OUJkMkZ6NFhNc2dveVZETHdGaWRYREJiS2NwdlNpWFJVUUY3OEx1Z09idHhJcm9Ob2J2N2JXaDA5UXVtd1hFS2ljeU9zQTU1eU9laU1fTlQ3WE5Ld0JGWnkzeHM5b3ZzNzRkZGIzalVwNVhPY09iQzVxWVdmRldwTnczOGYyQW1yNXhjTHAxY1BUNFlqY05HdUVYMF8wNjJuOHZVbXRYNTcxeG1lRWd1SkltcEY5ZmZVcGRYQ0diZFppZnloWHZJV1dGc0R3LVNqaldEU2ZoUnZ5Q2hKLU5BRXppMUEyN0JwNkJvQ1pRaGlhcFJWdXlLUlFTbjlxTXI5aHhfckVZdzRSZ1ByLW9LMQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1064" s="8" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G1064" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1065" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1065" s="14" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D1065" s="15" t="inlineStr">
+        <is>
+          <t>«L'Etat-providence est mort, il faut un Etat-performance au service de la société», estime David Lisnard</t>
+        </is>
+      </c>
+      <c r="E1065" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQM0JleFZOQzNmLUVDcTl3VjdXVm9OLTBkckZvOE95V3ZZYThVQ1NPZzdyYW5iTGFrcXZjSUJDWTZORGEwQTlYY0ZrVjVObHRVR3pla3NNOVhZaU1DcXEwdHRaZ1QzTlY5TjB5SFpubFptWXJCelN1TFJGdUFLbDZCQ3o5VWRFRjFGek9BNjlERV9BUVRjMTRpbEhmS0p2bEFhMHBtN2xmQ1AzSk5YZHJERnFDd2haYVdX0gG-AUFVX3lxTE9IaVc5WkdTT0cyNndBM01QQmV4a0J1Ynd1ZDk2WWVPMDJqNUhYY3E5ajRSUzB6aU1EY2t5N3VIU18yTjR1SjlWT0NCZkNPSm96elRFTGdLVnVfQ1U0cHdoZXNBLWV3N1VHU3czWlRwQktaZFR0QnZoa25vWjNSQTZQQnh5c013NTlGX1VFdnJZRlEzRXFRVG11M0dlN1ZDUEYxU1JkUnBzSkNuNE95bDgxbjI3bUJJbzd5OXFLX0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F1065" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1065" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1066" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Yahoo Finance France</t>
+        </is>
+      </c>
+      <c r="D1066" s="10" t="inlineStr">
+        <is>
+          <t>«On plante les générations futures», David Lisnard candidat dénonce la dérive des comptes publics</t>
+        </is>
+      </c>
+      <c r="E1066" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPbmw5VXhQelU0M0xsS0VKa2UwYmh2NkFxbGRQOUdlMl9BYVV2bWE3bDJfX3cwZUNqTWxzcGdZeFhvYXJ3cV9mZTdaNURrUkxVeUdyTHRUaW52OV80ZEJYNG5GazdWbHJtak9nQWlGS1JWbWFydkhWcHdkTFlPeUE4dlhuOXo4OHpsRGlweVR5VTFqUHJZR2padlIyVGx0UjJoc1l5eEo3ZWY?oc=5</t>
+        </is>
+      </c>
+      <c r="F1066" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1066" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1067" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1067" s="14" t="inlineStr">
+        <is>
+          <t>l'Informé</t>
+        </is>
+      </c>
+      <c r="D1067" s="15" t="inlineStr">
+        <is>
+          <t>Léa Salamé, Patrick Martin, David Lisnard… Vae Solis fait sa rentrée au Pavillon Élysée</t>
+        </is>
+      </c>
+      <c r="E1067" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNb2t2ZU9McjJQbUdhS1hQT0Q3UjhPc01LX2ZUVVFBMlpnOURrMWxOMURfM09BWmRSQVhNWlhSWjJHUTV2bDV0UHUtYU9veVNzcFpPNDg4Z2pYZ0JITHlhVnB5N3RURHNNeGVEOV92c3NadERlQU5YTzA3MnFNLUZXTUExZW14LXBub2pmdlg2RkRWX01Xc1BlU3BNWWF4UV9SX1NaWGtRR2RSSld4YWhqYS1tNXNtTGlQUk5JS3p5bmtiQ29HMHNqVVU0c0RubW5sUjJpRDF4YS1sZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1067" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1067" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1068" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Europe 1</t>
+        </is>
+      </c>
+      <c r="D1068" s="10" t="inlineStr">
+        <is>
+          <t>«Il faut casser les ressorts de l'islamisme» : David Lisnard réagit à la proposition du RN de sanctionner le port du voile dans l'espace public</t>
+        </is>
+      </c>
+      <c r="E1068" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNWGNsTTRVY1lDdl9OcGR0WTF0eHpzeUI3NHhDT1VGdjdBTGpXVG84NE0waDJPWTkxcXk3V2ZGT1JkbVpqSTNybGgxWEE1eFRyeS1NRzZNcDdVdTRFWV9oc3BRS21SdUtpUXFpUXczdWFOVUx2NlZFcDRHX1JrVmhTaEdvekxBbVlqZ0JNWmNGUDF4UTdOYnRtRlBKRHJEbVIzZnp0TjhFY1BCR1JzYXZ6VFkwSWdISHkwbWNIZWVXMUJiZm13bVNUd1lrNUhVYThLOEkwZVRiSW13SWdfaVRfRVlqblhRNFJOZnlJRnJGbE9pT3RVT3BiMGZUeTQzOW93TFBsVk9oRGwwUdIBjwJBVV95cUxNNkk4N1VwcmdnVkdyWV9iOTdOeGw0LW51QWVpdGtENGNkTlVURkw5b0lFS2ZWVUl1ZWVsc0x4UGRoT2lQYUZRRlJOdmtXclgwdUkwVE15MWM1NUNUYUZsamFRZVBHd3hyMzFSbmdUb2RTQXdDNmtvNVplb3gxeXlqR3YtNEtzbzEzLTRVQmRBcGtZWENWeVRxdzlPZjhuS0E0YjZEbmRhVHRrdG50NVBvTm5jclhZU3FXdzV2TnVLaW01YmZWdEx1ZXl0aGdqYnR5QnY1clFLUzg2bGQ0TURuRHhvcDV0S3NhMm1WbmlPR0RsRTRfQWx1V1M3REltR3VJNDV2b2RhQzZFaWJ0TWtF?oc=5</t>
+        </is>
+      </c>
+      <c r="F1068" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1068" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1069" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1069" s="14" t="inlineStr">
+        <is>
+          <t>Nice-Matin</t>
+        </is>
+      </c>
+      <c r="D1069" s="15" t="inlineStr">
+        <is>
+          <t>Coups de feu tirés à la Frayère : le maire de Cannes David Lisnard dit « Stop au déni ! » et égratigne police et État</t>
+        </is>
+      </c>
+      <c r="E1069" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQaVUzMFI2cmdiZWlxR21RZy14Rk1mRHp5emkyWHN4SUpMbzYwWkR3U1lpUXBaZVc1bjE5cUVVN2tIOGl1QlRYYWNPbi1TVU00MkphLXAyM04wbjctTjBLMzM5THpJSGJoSDJZSUFlbFROZ09UdUpiTjhVeGxjbUxEMUZkOWJCRUpCM3l1RGhkZ0N3TkduNW5JaHRfeS1qdFdhVzRRNkhTLXBUdjdoYmc1Q2JtR05zNFVYSWxvWk5zMmY2ZWFiSjNTZnR6aHRpLUEtUWUyN3A5YjZuZXNIT2lzekVGWXIzRUhNN0VfcWlvX0J5WDQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1069" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1069" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1070" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Nouvelle Énergie</t>
+        </is>
+      </c>
+      <c r="D1070" s="10" t="inlineStr">
+        <is>
+          <t>Cannes récompense l’excellence et le mérite des jeunes</t>
+        </is>
+      </c>
+      <c r="E1070" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOT2Y5NkJTTHhMSkJ5OXFzTkRmTFE3b1FHT0JNRWRHYUgtSkNoUkZiYlBBekV4cmhvYzFTMWUxeG5zaXAyWW5QQVV4SkdtbVgxVGFBcnM1M28zdkE1eW84TXl2TnRENkplZ181ek1CMXJvank3MHZKYkZuV21NWk9nUEk0TG43YnVuMlRSMGdwdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1070" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1070" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1071" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1071" s="14" t="inlineStr">
+        <is>
+          <t>Orange Actualités</t>
+        </is>
+      </c>
+      <c r="D1071" s="15" t="inlineStr">
+        <is>
+          <t>David Lisnard interviewé par « L'union »</t>
+        </is>
+      </c>
+      <c r="E1071" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPUjlnSl8xd0pJb3VFU1UxOV9nMElrVkEzdm1SQmdCZzNTVmY4OWlfUXEtOGR0SENaWlVOaW1XZkhEZWdKU0FiZ2pIYV8zc3Z0RlVVb0tVRUN4dUgtOXFheV92M0JyWkY0NDMtNldlR1R2RHhaVnZLclVCaTZMLVloUGtjbS1jZjlxbTJZMXlqMlo4UWUzZ3FjSFRMMXQ1VTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F1071" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1071" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1072" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>lejdd.fr</t>
+        </is>
+      </c>
+      <c r="D1072" s="10" t="inlineStr">
+        <is>
+          <t>Immigration : David Lisnard compte rétablir le délit de séjour irrégulier</t>
+        </is>
+      </c>
+      <c r="E1072" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPaFJQeXQwekJpWkxKX2prZmtuYkZ5SmhSbUtuVUtDRHJXRTZ0eVBGT0NISHczS3pFUEo5OHpQcGdGZ21GVHpwUmMwbmhhanFGbVBLZlg4UVZIMUhqTzlkYXR4d2VZVkdxMWdnUjNMVHZDeUtLV3BkVlpVRjgtWEdEMVM3Z1VCM0NwU1gtd2xSY05QMHNaOFZPODRBWmJaQmtDT1B0UWc2ZTRVeE0?oc=5</t>
+        </is>
+      </c>
+      <c r="F1072" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1072" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1073" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1073" s="14" t="inlineStr">
+        <is>
+          <t>frontieresmedia.fr</t>
+        </is>
+      </c>
+      <c r="D1073" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : David Lisnard plaide pour le rétablissement du délit de séjour illégal</t>
+        </is>
+      </c>
+      <c r="E1073" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQd2Y0aUE5NTNUem55NjBURGwzSkE0SnU5NzI0VmxzRzNXcERmU3I3anZrX1RObE4tWjhsTW9Ic1pHNmhyV3RmTUEyb3FrTHM3LWhCY0tNSHV5VkJ6cjJrcDJuX0VIeGpKUUVQTnozMjlsVFhzd1M3azdDdWdiWFFiRng1cXZSWUNEWk1tWFdfV2NTOW5nWWQ0ek9WRFJlcU1CcjlVSVBuNkxHQ05Mc3IwanFlbW9FLWsxemg0bnlIbnE1SGNvQ01fSHp4T2pMRXU2ZGl1dkdn?oc=5</t>
+        </is>
+      </c>
+      <c r="F1073" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1073" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1074" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Europe 1</t>
+        </is>
+      </c>
+      <c r="D1074" s="10" t="inlineStr">
+        <is>
+          <t>David Lisnard réagit à la proposition du RN de sanctionner le port du voile dans l'espace public</t>
+        </is>
+      </c>
+      <c r="E1074" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQTUtiY2dlZVJJaTREUGhoRTlpYnh0UTkwRjJhTk1LN0hsVFRDRWs4cXM5RGNiVU54VGdlX3VWYmdwN2g0RFJwT1RKaGlaVDU1MDVqc2JKV3BLRkgweEJCV3I2MldRNGMyUzBTUjY0NjhBekYzOWpUR05yS2ltQWtfME5zRmhya3Z4ZnRheVhoZVY3VlpWemhHOG03c2lhYVlUd1pvSjRlREJDd25uVVFtVFF6UVRsMjdJY2R3eG83bExNQ3dqUjgyeWhTSHJpdG96TnZUWmZvVkh4SlBjNXpXS3B4TFEtcms?oc=5</t>
+        </is>
+      </c>
+      <c r="F1074" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1074" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1075" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1075" s="14" t="inlineStr">
+        <is>
+          <t>frontieresmedia.fr</t>
+        </is>
+      </c>
+      <c r="D1075" s="15" t="inlineStr">
+        <is>
+          <t>« De ce point de vue, on est tranquille » : David Lisnard affirme avoir déjà recueilli 500 promesses de parrainages pour 2027</t>
+        </is>
+      </c>
+      <c r="E1075" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNUHhsTFJpRDNsNU1qWFlyZlVpOGhWQnpjY0x1bVRlaDhkQTZxM0ZtMFZNT1VVMUJlem41VnFvZWtTUHRMVFRmbWFhVDZROC1JVExaenVwQnRkLWktdnpvamdCczg4TTZyNW1hdWg2anctbzhFX3dfV2lxZXFKWUhGbFZqUk10U2xpbUszd2s5OFQ0NU1QSUVHZ0xaMElnOHdwLVFYOTR1WXNrSGlSMUpDckJueTMxSmNodnRFUXFuVWRpVURXMjB3NDdOUC1kVE5uazRxdXJDWWtZdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1075" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1075" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1076" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Nouvelle Énergie</t>
+        </is>
+      </c>
+      <c r="D1076" s="10" t="inlineStr">
+        <is>
+          <t>Facturation électronique : "Les PME aéronautiques n'ont pas envie de voir leurs secrets commerciaux d'Airbus se retrouver dans la nature", met en garde David Lisnard</t>
+        </is>
+      </c>
+      <c r="E1076" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxPOGlqbEV0Y3BaOGh4TWkxaUEzOXhQU3RwVW9PRGpYWWM1WGN6ME5WU2RNbERKbDZNbnNoQzd2cUExTXdjdWw0QXN0Y05qR0pEam00Mm9pYmJxdUR3RU4yeWpXOHZ5bDRqTVJZcmh3QnhoTmNsSkpORnIyRzdzSWRVRHd6d256TmQ4RlNOa19QUTlGUkU5c3dGa1RWUENOeERUdXhVeEVLejNlRlVyR01sUklJTWRndE1SS3REVjhwc3NWdnBiQ0xodlBPSktEOE9SNlpzenVKS2dKT01JN3ZJT1k1Ql9NOGYtUTFCaXBHUzhKQW9CVkRCeEp5a3pFdjhLblhROXl2WUpCSkxlWDlhcDhxbUVpLU5PZ3hjMw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1076" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="G1076" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1077" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1077" s="14" t="inlineStr">
+        <is>
+          <t>Ohmymag</t>
+        </is>
+      </c>
+      <c r="D1077" s="15" t="inlineStr">
+        <is>
+          <t>David Lisnard décroche les 500 promesses de parrainages pour la présidentielle 2027</t>
+        </is>
+      </c>
+      <c r="E1077" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNR3h6ZjRZZVhXZTV4a2lfTWpUeGN3WXBGNG04RzItcUphZUdoNHRHUkx6bjFyajNiSlBvZ1AzNVpnNGxnbDF5WVotSVFUUHcwQmNKd0FxSDBIQkVscU8zUTdpS1hBbFIybnFVMWw1bUxJcnlmMjhZX25zbEZoQ0lNOHFDcy1xSC1SUVVZd0NJUWZFVzM0azBhRWNoempGU1FwSHo3R0NpTC1ZdF94U20ybTZLS1R4Tkx5RlN2TkYtVlRZZExUTE1VMHdIbG41cTU1V3Y0YUFXQ1I?oc=5</t>
+        </is>
+      </c>
+      <c r="F1077" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1077" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1078" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>L'Union</t>
+        </is>
+      </c>
+      <c r="D1078" s="10" t="inlineStr">
+        <is>
+          <t>Marine Tondelier, David Lisnard et Claudio Capéo... revivez cette sixième journée de la Foire de Châlons</t>
+        </is>
+      </c>
+      <c r="E1078" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOenNWMXJYRFFNaDd5cVUtdHFZQ3lXa3M0RGt6dDdaSFJkT2NLNGxUVG11X1pKcXFxNUJReG1TRm5NTHlvM0loYS13WGwxYThXX1ZhWjFVLTZTSWtKVDNkT19ZR2lWOFJvMEZDN3d3TXFKTloxQ1AxT3Y1dkpyOU01R3VCdFJScjlvSmdQRzFSbWxabEowdEppcnRUcTgxMzE4X3hYdDRqMGFxb28?oc=5</t>
+        </is>
+      </c>
+      <c r="F1078" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1078" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1079" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1079" s="14" t="inlineStr">
+        <is>
+          <t>Europe 1</t>
+        </is>
+      </c>
+      <c r="D1079" s="15" t="inlineStr">
+        <is>
+          <t>«Jean-Luc Mélenchon a vrillé dans le néofascisme», lance David Lisnard</t>
+        </is>
+      </c>
+      <c r="E1079" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNQnVfZFVZSDF4OE9ILWxKT2pZTHhPNl9veWhsRVdOMUExanlUc1J5ekVrd3d1MGZnQ1k3dW94YWxBMHY5R0x1NE96WnlreVowZ0gyLTZuN05TSmF2MVdVMHZCMVhXQU1vdDZYRFNyN0Jna1JBR1JlLWVIeHpqWTM3NHBfOUZZYlh6MHdkZ3Z5c2xnVUNYNGE0clBCQVdxeWhkc0xYNHZmNm1ucGR1YWpxdHdfZFpCa0lnVTBRX2I5Vko0TWtlUnRuUXJ5Q0d4T28yQVlOdi1JcFlsMDA?oc=5</t>
+        </is>
+      </c>
+      <c r="F1079" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1079" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1080" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Orange Actualités</t>
+        </is>
+      </c>
+      <c r="D1080" s="10" t="inlineStr">
+        <is>
+          <t>David Lisnard : “Je n’irai jamais avec ceux qui ont mené le pays au désastre”</t>
+        </is>
+      </c>
+      <c r="E1080" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQMG43VHBBdUtwa2RHZUVGTVplXy1nQU1JRlpWcWpZX2NNQkRYQXQydWxRQ2NfbHlKQnc1cDVQbTZrTGRLWVhJdnlqZ2tsM3Y5Q1JIZHNnN21GOG1oWHhqOFpxZVlpTkJTbEpFbkxSLXpUaUJ4aE5qS2dGeGxHU2ZRdlZ0Wmh2ZTExa0QzcWQyV085Vk9tV09IUEpKeVNaeE9Ma2x5RGZySnE0aUUxWXo0MzlObHIybGRMVGMwOEVmSXA5dGlKMTB6dHBFZUJDLXEx?oc=5</t>
+        </is>
+      </c>
+      <c r="F1080" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1080" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1081" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1081" s="14" t="inlineStr">
+        <is>
+          <t>Le Dauphiné Libéré</t>
+        </is>
+      </c>
+      <c r="D1081" s="15" t="inlineStr">
+        <is>
+          <t>Ardèche. Présidentielle 2027 : François Arsac, maire de Chomérac, est l'un des premiers à soutenir David Lisnard</t>
+        </is>
+      </c>
+      <c r="E1081" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPWjVXbFRDTUczZkszcm1JYS1vRlRyMFExbnZjVTh1ZmhxRzRRWXNHZ19ZelAyWmlBZUlfVTZScXdBVVF5TWRJejJEWWx2R3R2enUyREdWNERsSGFfYU45MlBtTzRwX2FtVDR2LXk3WHNMZjJjSm5LdjZUWkhxYkFsaGtVTGExZWRmcjFRa1FBQTFlOXYyZU9XbFpaSDV1NXNDdjdvMzlBWGhKcjYtclA3OGhGRUhLd28yS2M4SmZ3dEs?oc=5</t>
+        </is>
+      </c>
+      <c r="F1081" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="G1081" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1082" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D1082" s="10" t="inlineStr">
+        <is>
+          <t>En direct Présidentielle 2027 : le RN dispose de plus de 400 promesses de parrainages, indique Louis Aliot</t>
+        </is>
+      </c>
+      <c r="E1082" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNOGt3cllHUlhSRzJqSnljYmIxT1BKbGh0dVhDcVZDajlEcmN1ejZtZkNLTUwxeHQ4MFBPZTh1SllNUTRldDdoSlF1eklmY2ZySXNJdl9tVDBXcHZyWDZ0RnJVTVAzT1Y5RS1QNkdHdUU4R2JxRlBZSThXY1RBYzlfRlMzYW5WVlJrWWZPdjh2d3JQdzRxWGE5ckJKdFNzVU12ZmRMd2FjZHl2Zk1NaV9PY2paT2EwNTAyMzIwRg?oc=5</t>
+        </is>
+      </c>
+      <c r="F1082" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1082" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1083" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1083" s="14" t="inlineStr">
+        <is>
+          <t>purepeople.com</t>
+        </is>
+      </c>
+      <c r="D1083" s="15" t="inlineStr">
+        <is>
+          <t>Photo : David Lisnard - Sorties des obsèques de Philippe Bouvard en l'église Notre-Dame de Bon Voyage à Cannes le 31 août 2026. © Franz Chavaroche-Denis Guignebourg / Bestimage</t>
+        </is>
+      </c>
+      <c r="E1083" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxOXzFGTmwwRnB1VnRFLU9SaWd4ZWo0RXh6X29mS0RDQ1Q1UEFiVUZnVWtpa3FCR1AwNkJzYlV3YlQ4VGNKdEJhNXpMWGVGRmprc2VoWHNucmhjMG54QVJKQzVuUTBuc2JjVGIzM3E5TWUzSlpoSks5SVowVzEyUWpLUjdrc3dJVlcxTm9taWpGcWwzMDlBcGlMc0QwYloyZlZhT1hVQkQ5cjlWX0pwc3M0cDI1clJ5Vkk0elZTZno2eUd3MjgtV09TczAxMHppNDdKWmwwaHpjUEJTYkZZdUVRbURXRVRrczA2MnQ0T3JxWU1QdndtaE9vZ3RfNENQRGZmNHV0MEJBSzBTa0VZdFFObm81Vnp6ZmxHYTcxMzY5RUc1Z2ZVbk1QZkJMZUplTlBEVEgxTndpdHZTUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1083" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1083" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1084" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D1084" s="10" t="inlineStr">
+        <is>
+          <t>La grande interview : David Lisnard face à Laurence Ferrari</t>
+        </is>
+      </c>
+      <c r="E1084" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5GRDYtLWxVWWNlaGs4ckMzSzNhR0ZyUG82dndYb0IyS3VYMmVvSGo5dzE2bkY1VUg0enp6YW52NllmamVfRmRTa01TRjZGTzlYQXNtTTFuQUUtY24t?oc=5</t>
+        </is>
+      </c>
+      <c r="F1084" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1084" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1085" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1085" s="14" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D1085" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Sarah Knafo juge Éric Zemmour «candidat naturel» de Reconquête</t>
+        </is>
+      </c>
+      <c r="E1085" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQUW9RUVVZcFlYaHlvcTBrcUNlYXNJcWZFVkprd1VYTzZoSmtzMDJCRTg4em95T3pydXRjbzl6WG5seEhqalBSWTVkUkQ2bndEbDVLeGRaNjdLTjRTOFlGQmZ6S1NCQU5NMmF2LWhadUhoSm0wcWFZSl9jWEJscWppaGZIWUxTZ2Ztcl9oOUtNOXFUYXlfT1ltOXBFQlFvU3ljUDJLYjZDUlhrY1JmbkJHSXJuMjB4RUwtTm1ldEFSdEjSAcABQVVfeXFMUFFvUVFVWXBZWGh5b3Ewa3FDZWFzSXFmRVZKa3dVWE82aEprczAyQkU4OHpveU96cnV0Y285elhubHhIampQUlk1ZFJENm53RGw1S3hkWjY3S040UzhZRkJmektTQkFOTTJhdi1oWnVIaEptMHFhWUpfY1hCbHFqaWhmSFlMU2dmbXJfaDlLTTlxVGF5X09ZbTlwRUJRb1N5Y1AyS2I2Q1JYa2NSZm5CR0lybjIweEVMLU5tZXRBUnRI?oc=5</t>
+        </is>
+      </c>
+      <c r="F1085" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1085" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1086" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D1086" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : «Je ferai connaître ma décision» à la fin du mois de décembre, répète François Hollande</t>
+        </is>
+      </c>
+      <c r="E1086" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOclVHS0ZBRW1EQ0dQQTJBQWtrdlE1LVhWbklfZ1JoeGV0QkNCaUF4YnJiSy1aM2NXQVRneU54N2ppcEVfbFh3NGxlclhMU21JeUtLYlg1UEg2ODZZeGlwLUlnMlhzOS1TZV9GYlFMOXcwLU5EcE5EcWN5ZG9vSWRNWTVCbGNSaGtMMTgzNzBPMHRLQnlvemRlTTdsRHFMSzZydEw4QlQtcUVCdHBIV0JsQmtGdks4d3PSAbwBQVVfeXFMUE95MG4wWTJmLW5wV1piUHVPVjAwWURGdElranBtRmhDbTlnd3M1RHJPc2FYNXdXcDd0Yi0wZFVtN2ZPWFNkTnFnRjhwTnpYUTNONDRJY0pSSTZRVlVtaGVXeThxLXlpOTRkSkc5Ml9MR3E1c2ZtNDFxTWI1ZDVnbXBTd0ppdlhHOEVOOUdRSzZvQVhLLS02QUhXVVlmZEt2c2NnMmhNblZraGhnSG96bWhqNzZBX0ZWYzJndkQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1086" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1086" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1087" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1087" s="14" t="inlineStr">
+        <is>
+          <t>Valeurs actuelles</t>
+        </is>
+      </c>
+      <c r="D1087" s="15" t="inlineStr">
+        <is>
+          <t>Éducation nationale : Lisnard, Bellamy, Brighelli… leurs solutions pour sauver l’école</t>
+        </is>
+      </c>
+      <c r="E1087" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPOURDMjB4THljZzJka1RMMVBOX25IazhNU1JXM2NBUzFGMFJvUVh1WXV5M0lKc3pjNkhQaERyU0RIbXJvMjZFdFlyYnhxY0FMOV82SFI2RFVjZktSQ1kyNnY3T3RUWjF3LUx6bzJRa3o4d0c4c1BHTm1vQUVVZTI4NV9JeTlYcHFUekgyNm9lLWh6WDc5LUNXS0ZMdUtWZnRxUEJURlBwRDNfX0hJVmRQQ0thUlZMY2FzYll3TkdnY2VCUngxZUJ5aUsxZ3Z1Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1087" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="G1087" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1088" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Europe 1</t>
+        </is>
+      </c>
+      <c r="D1088" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle : «L’État-providence est mort car on ne fait plus d’enfants, qu’on maîtrise plus l...</t>
+        </is>
+      </c>
+      <c r="E1088" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxPSkIzcTBfeVJ4U0VST185MzRZUzNTTm9RYlc2YlExR3FGa0RFcmNwN1ZaVGRzNnd6LVo3MVROaF9QZ1NHOXlBejBMVmliaUNtc2ZJYVNnakx3V1FXZnM0aU53eEVRTHMyS1VERTl6MmNNNm90RTRGTHBqR3dhSDM1b2U3aEctcmtPdGd5YXRlV1hkVHgydmQ3YndOdlE5bXBwbmhjcktjRW41UU5vNUJMRWxrZE4wakZVTlFldkw3b0NWalp5UzJEV2VjR1BMblVULUJlWmhDeFFRU3JsZ3ZWRkJDcllQUUFlalVPaV8xWF82MllHa0U2NkNB?oc=5</t>
+        </is>
+      </c>
+      <c r="F1088" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1088" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1089" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C1089" s="14" t="inlineStr">
+        <is>
+          <t>DHnet</t>
+        </is>
+      </c>
+      <c r="D1089" s="15" t="inlineStr">
+        <is>
+          <t>Philippe, Melenchon, Lisnard... les candidats à la présidentielle française font de l'oeil à nos élus belges</t>
+        </is>
+      </c>
+      <c r="E1089" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOdXZlLUJlTFBOeDJHYlptcG1nTUxTZkU5RHIxMFAyTG9mLUFQcUpRVzZVSUVLU0xCejlGa2s0bW55UTRIVDdDUXJSenYxNzRLRk1uNzFsVzZQcHBlNThkemxDTEd2MmNaOFB2NWh2VElZenU4b2FneEFiX0pYWm1taTVCWlR4Uklid19qWUROQ2E4ZlhUdVVRcU1lSTlxVU04WG5LY2kycm1uY1pOa1p3eE5fSnpEdUJjY2o2MC12bHBzUG9mR1dlakJhU0gyQ2MxazN2aGg3VjZNcVdvZXd1YUFadWMyRTNyeUV6TUhKQWUwX3JCMWJfcnpZRUhpZWk1OE5Rd3pucw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1089" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1089" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1090" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>liberation.fr</t>
+        </is>
+      </c>
+      <c r="D1090" s="10" t="inlineStr">
+        <is>
+          <t>A la foire de Châlons-en-Champagne, Bruno Retailleau doit déjà lever les doutes sur sa candidature</t>
+        </is>
+      </c>
+      <c r="E1090" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxPaXU5VlBtYWM1YmxVR09LZ1VRaUVOcXNzcDZDUXQ1cFFVOTJiX21Sc0xMamEtV0tETUR3V0V3NEUwU3dSd3NQeVVoU21OejlXZDNZckU2QXR5aGpkWEVXQzloaFVWdWtLLUc4eWRGc0RRcUNTUjd1b2pBT0k5N1lGWkM4RTRTaGRDN3lMQW1uWXc4REFaWUdJODE4RDZaRHQ5elpyZ2pnVjZTQnEybnFpRHIyTHFkN3hTX25LZzRYa3gybWg0QXg4WUV2STJOX3c3SG9pOHhxTzNZdll0ZlVFb3JCQjMyY0JmWXBENlZ2bUpCaXNMTUhDaXlISVFuRUk?oc=5</t>
+        </is>
+      </c>
+      <c r="F1090" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G1090" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1091" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1091" s="14" t="inlineStr">
+        <is>
+          <t>Public Sénat</t>
+        </is>
+      </c>
+      <c r="D1091" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Bruno Retailleau veut « renverser la table » avec une profonde réforme constitutionnelle</t>
+        </is>
+      </c>
+      <c r="E1091" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOYWgzYUR1Rnlia2JlQTl1TWNVeHEwSjI5MTNXNmZBNlpwdXpobmRMcC0yQXZsVVRRV0ZEaHlRMzRFNllneXRlenByaVN3a0gwaWZkZTlUbVN4cEZiTnJRblE0alloWFp1X3RwN2FYWFhaYUlGUDE1YUFIdmptRU9IbEQ3bW9zMUxSTjgyVV93RllVY3d2VEdmWUgtSkFqb21yazBsUVpmOWJaU3AwR3dORTd5Tk82akhlS2hPVjdmeUxXT0Q2bVJnYTRPSklwbFNmSFU2ZnN0YXhSUzFSeXo5VnRscGQ5Unc?oc=5</t>
+        </is>
+      </c>
+      <c r="F1091" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1091" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1092" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D1092" s="10" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau au Figaro : « En France, la seule cour suprême, c’est le peuple. Je lui donnerai le dernier mot »</t>
+        </is>
+      </c>
+      <c r="E1092" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxQeTJjTHVkV0ZBSnRSTnpWSm1BLWJSdlJLR3YxS1c3V2RGTlIycFlNOVUzb21QeWRFN1NadDZZOUY5X3pERHVKOTlRU3ZwSWdSYjQ3MEp5eUFiMk16ZUNDSDJWMjl6TlhUQ1NVaFBJaU94QnZpYi1nUEdwS3FKQXMxdlVleTJCUmU3eUo0cmk2dHJDal9uQTVVTHp2cDRpeGh1REwtZDRCTHNzb01nQmZJWEVJRTk1eUdSbHFXNUJNaEt3RDZ2U3Q4OGFEQ3NNN0QxRnhQVW5aUlVFWUtfUVI1dzR5c1dOUHM2S0xCRGJucjZ3VG5WNzNCRGtIVUNVOWFibVRINE9B?oc=5</t>
+        </is>
+      </c>
+      <c r="F1092" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1092" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1093" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1093" s="14" t="inlineStr">
+        <is>
+          <t>Le Monde.fr</t>
+        </is>
+      </c>
+      <c r="D1093" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Bruno Retailleau promet une réforme constitutionnelle pour donner « le dernier mot » au « peuple français » sur certains sujets</t>
+        </is>
+      </c>
+      <c r="E1093" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgJBVV95cUxQOUZ1Z243bU5KeHdBMURhVWUxbzV4eG1PR25RaUpDSU9VT2N0akNpeTVCV25HNjV3MXA3TmIyYzZCRG9GNV9RUl91ZjJJQ1ZGbHZRVnU1UU1fSUpsTjUzU2lkaURmbm9WOVZNcHRmUWdWRG1MRHUybmJoZzZROHhWZFhaT0JhT1M0TjVXQzVnSlBSMk5WSVROQ09STk1oRnQ1ZHdLdWNkcENKZU12YXhYZGdIUHhoODlNNXdaUzhuNm9rRTJQR0tJbnpzR3duNkFsOVpkZm5TX3pHWWFDVXp1d2JYV1VkNzdTcWZMUDNhd2UxeTZyNm9PN0dwdkpHWm9kMVc0RGQ5Y3lIVVN5UmpmaVhIZGk3c052S2dEaEZINk8wWHEwSy1iVm53akZDc3dwbHQzcDh3?oc=5</t>
+        </is>
+      </c>
+      <c r="F1093" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1093" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1094" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>liberation.fr</t>
+        </is>
+      </c>
+      <c r="D1094" s="10" t="inlineStr">
+        <is>
+          <t>L’hallucinante proposition de Bruno Retailleau contre le Conseil constitutionnel</t>
+        </is>
+      </c>
+      <c r="E1094" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNUmFNejlUcm5LUkNHaXhnYWw4OUdpcVkzdXJSSnY3V0dlak9fNWJJTlpEOVl2cHZhZEhTdkltLVhJX3plOFRQSXVzYW1nQTIwa25TMlF1d3lmWUhfRWk4ei0wN2hqQzdaN1FEUGotSE81RFFsR0sxT0R1RnhFOTdod2RKQmppTEQ3UUE5UmlWbnFhbEM3V0RhYmRia2hVRjA3N1pDLVl6LUl2Zm9OemhXS1F5MUR4WXRibXVUcDZfVk9nT21XdVFwenZZWU9sbXJRXzNlT2NGYXE1N0pjWGU4bm8zS2tLSlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1094" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1094" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1095" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1095" s="14" t="inlineStr">
+        <is>
+          <t>Public Sénat</t>
+        </is>
+      </c>
+      <c r="D1095" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : « Bruno Retailleau propose une révolution copernicienne » dans laquelle « la Constitution ne serait plus le bouclier » qui protège les institutions, relèvent les juristes</t>
+        </is>
+      </c>
+      <c r="E1095" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxNd0lwMElVYVFXeFU3UmhBaHFvcGIxV21UOFV2YUF2S3VFdml2M0RsMDNEZngxaE1ISDF1MlIyTW1fX0lJeTlpYVZ2MEhfcVUzaVZFY3dUcTEtWXBzT1g1TXg3clkxbkdieU9kNUU0eFhINl8taDYyTndJeG5nZThTajB3R1dWZjRYTlJYa1BxN0Y5TkRVYzJIZVl2WTRocDhyVUpWRVcxS2cwSnlPVWM3S1RpM3BZcEZrLVI5N3hWNlpfSkZSbllkQ1FhOGU2ZTBKV3JLSUhVeS1zRzFScTEtdC12OWotbVRVZ1JST3NnNWl5SFFqREVEd0stMjczbWd4MVVQZ3F1MkdRcmlITTRjRWVuUV9SNjA?oc=5</t>
+        </is>
+      </c>
+      <c r="F1095" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1095" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1096" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D1096" s="10" t="inlineStr">
+        <is>
+          <t>« Réconcilier l’État de droit avec la démocratie » : ce que contiennent les deux textes constitutionnels de Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="E1096" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxNc1FsNkNkX3gxeEFZTmF2RFo3d1htVGV1U1l3YmthaXBlR3pYemhWZVB5V01FN25kX1dPVEhqWHRwaFI2NndVaTNGM1AzMHcxbmlJZHl4NmNVS1NJSXBWZEhDTjdHdnp0R3g3Rl9VM2l6eGNaZVZMZVZ6LVlZZ0ZrZFBKcjNWdGdKSDVGR05wTEFNYS1EXzBzUlppWHBSQWRfMHBLQVdqaFByQS1JUk1qaHpod2duY1ozSlByUUZmOGNqWTMwWlYyS2FhWTgwdm5NdHgxMmNPRlFpSmRwVmlYaFhTVFBKRVpqTVdIMnhYN0dSSzQzV25FcVpMZEItbkNqbUtvOGlHX2RsT2s2TGwwMzYzc1ltcFU?oc=5</t>
+        </is>
+      </c>
+      <c r="F1096" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1096" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1097" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1097" s="14" t="inlineStr">
+        <is>
+          <t>liberation.fr</t>
+        </is>
+      </c>
+      <c r="D1097" s="15" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau n’est pas un potentiel allié d’Edouard Philippe, c’est un agent électoral du RN</t>
+        </is>
+      </c>
+      <c r="E1097" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNWFlDZnA0WHcycEQ0VEFfdDhvNnNqRHlyTXlmT1hjc0NScUhEWU9Qb0tTTGU1dWxjNUViMS1faG1rVGxiQ1owcHBiem9yQnlIelhTbWdsLVI0RGl5THdBNWlPNzVNRWRiUUptSlpaT1oxcy1mekZPZUYzR3ZFOWZGWFFnQjZhMVVUNXM2c2NWUGstdngtNDUwMldZc04tT2xyMlV0QVhYQzVjUHV3QkJyU3BBTUhPblI4bkE3azYxVWIzblU5YnJZNkRqbDZ5Qm9LWUx0QnI2UlB2aUtLZUVhUXR2Z3NSVzNieTVNdEU4ejE2VWlTVXFxaA?oc=5</t>
+        </is>
+      </c>
+      <c r="F1097" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1097" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1098" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>ladepeche.fr</t>
+        </is>
+      </c>
+      <c r="D1098" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : avant les universités d'été de son parti, Bruno Retailleau fait des propositions choc pour tenter d'exister</t>
+        </is>
+      </c>
+      <c r="E1098" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxPS0ZuNFJsUGtxbng0c09xMU5YaVRMRUJxNlI3T3UtWlRKdUNONzdVVVpSTTcwaTJBYlpjMGozZG1lRVliQ0hFUnp2clJPczI0LXJIT3d5R1dIbTFyLVZPYWV6VTYxMmhqSG1GcXVxenlOWktnR0FzejBtcFdxV083SUp6c094QVA3THUtaGJWWEFybDJlQU9xRVdFNjZ3R1pXaGtTaHRsMXd5amU4U1p3X2ltMFlrM21xeE4yZkFLalBURk5COXV3TFpaaDRnT3ptZkFoYVdMbl9BWUx1X1NaaFo1eGV6ekQyRUFsU2ZxenpEN1UwNkNQdVpmZk9tM1dtT2NF?oc=5</t>
+        </is>
+      </c>
+      <c r="F1098" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1098" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1099" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1099" s="14" t="inlineStr">
+        <is>
+          <t>lejdd.fr</t>
+        </is>
+      </c>
+      <c r="D1099" s="15" t="inlineStr">
+        <is>
+          <t>Immigration, sécurité, justice : le plan de Bruno Retailleau pour «restaurer la souveraineté du peuple»</t>
+        </is>
+      </c>
+      <c r="E1099" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNUGl4S1dtclQ0U3NUMlN0MVRhOVQtUks5TTY2SXQtbm9ET0l3d0xVX1F5eGRWZ25jNjlYdnRNeE9rb0lfV2o1WmI4LVVMSlY4VGVsaU9LR2dEWEZjcC1ubWRoX0ZHR1pWUExiOTAxTmZwcWFrSlU1eGo0cks5aFFPakVmTUttS2NHaE1IelVBMWpMZkVhNzhzZXo3VGN3QldkNE84WmV0ZV9qNUd1d1U3eUVOTWg2TElZa3BocnY5YWdwUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1099" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1099" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1100" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D1100" s="10" t="inlineStr">
+        <is>
+          <t>Michel Barnier soutient la réforme constitutionnelle de Bruno Retailleau et appelle au rassemblement de la droite et du centre autour du candidat LR</t>
+        </is>
+      </c>
+      <c r="E1100" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxQem1VNDQ1TDVVakQ0UVZweC1wdGNCUjhLUFQxbHprcFpiM2Q1Tk9Td2RJS0xsMko5NzdGOTg0STVnR2VDRi1WOHlxQ3VzbFJhZHE5WTlFcHBIOE1JRTNWVUswRDBmeV9zX3ZLdDBiRFMyOVlKT056ZXRqZ2hKUXBtYUhsVTJiaTEzbEZaSHV4cGFIbzVEaWNpbmdnZVkxLVNaR1lQc04taVMzd2FqZjlQWmhDWmwxTmFnbi1WYmlHUkxOT1Y0eVBaSXlBOXhtY1BoWDA1V1hRQzJJbXZ5Sl8xM2FQZkU2U0ZrNy1sUy1rMFdLb0ZmbkVraVNaWGdqR2VtdW1jd084Y2hpc1JPV0dDN21fRm4tQktPb05n?oc=5</t>
+        </is>
+      </c>
+      <c r="F1100" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1100" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1101" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1101" s="14" t="inlineStr">
+        <is>
+          <t>liberation.fr</t>
+        </is>
+      </c>
+      <c r="D1101" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : à droite et au centre, privés de primaire, les unitaires amers</t>
+        </is>
+      </c>
+      <c r="E1101" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQaGQ4SU9VRTZXNWZwQ0pCT2gzVUFqOTBsS1BiSUItVlpBZTdDcDZLcGpZcmswME05SGdDcWZINGxwMDE1bFdndXlfZTExRVQ1MUxJb2xsOERuMUJsY2VtalZGNnBUY3d1dXRxZjFkNWpuMFgybklaT2NybUowLTF0V1ctSDhwb1hSTDhPLUtCbUhZUTlrdkRIVmc5N1VuYTlnMDVSY3ZKcXRyNjE1alREcFE5RXFGRFk4SmtCMF8xOVlzMmZkYk5DNGxaTTBYZTVERUZuZW51ZWNhVXBRVmVmcFdjTGNHVXdu?oc=5</t>
+        </is>
+      </c>
+      <c r="F1101" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1101" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1102" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D1102" s="10" t="inlineStr">
+        <is>
+          <t>Retailleau charge l’Etat de droit, Attal et Philippe temporisent</t>
+        </is>
+      </c>
+      <c r="E1102" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNdFVsUzBYX3dyZ21TelJ2aXVyRFgtNk9EeE5ITFRwN0J5S3FPTmZKWko4X2lzdGJaWWdpMVBXOUFuWjVKSFNGNkcwbjAtbFgtSU1POGtacnlhRHYyWi1zMlI5azZmeWtZMXdIX09DLXlPcnFSUGtYa0hyT293TTdVMWFFT3VqSldqd0Q4QUhLb043eXFnU1ZFRVd3V1I?oc=5</t>
+        </is>
+      </c>
+      <c r="F1102" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1102" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1103" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1103" s="14" t="inlineStr">
+        <is>
+          <t>Europe 1</t>
+        </is>
+      </c>
+      <c r="D1103" s="15" t="inlineStr">
+        <is>
+          <t>Primaire de la droite, révision constitutionnelle... Bruno Retailleau se livre à quelques mois de l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E1103" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOZndtWmRmWVN2LVJRTUJOY3g2eGwteGI1ZG9RRjd4YXF6SlFGMjYxQWNpeXNRU1BuMzQ2V1ZNdVFkU0hBVktMT2Q2b3VQZGJpNndiX0l1aVNPZDA3S1NHbkJWSTIzUDRDQlk4NGlDZlVhOGpHSVZpd1BtUkFld0VZdXU2dXNDeXFlaGJJVjVMbjVUcnFxZWkzVGpLS1h4cTN6bEowTDZqRUxITkpHLXlmTERqekVvdXhlbGQ5WjI2djFDS2VqdnJNN0hZR0U1YVJmaExzbzJXUUFVWm5hVnd3cnZVVXk0SER4WFUtbVBEVmPSAfYBQVVfeXFMTnJGRy1LY21XVUZrNXFMUV9MVnFkZ0pmNVJjTEt2QmFRZ3pzamNlSHF2MzloVTQ1SGdwUFN6MVJuNFdTWDBZdDlwX1ZsUi1SS3B0VjRoMG5KR1ZOcWhnMHhldldQOVM3ekF1Q1VjellBR0hkUC1YVW1PcU1EWnRIQUJtRWx5cEtyekpjdGU2ZlJHeVh6VGZfR3R2QkphQTlwbDhtR0hMRXNDTHA3N0ZrQnZtWWh4X1RfMUJKdUlHaWNqQTd0NEhLUEZzWnVtemRzWUZIMERwU0xPLXB2dGdLZ0dudGVKVlRsU1hFRkVUSFN6dXhHQ0dR?oc=5</t>
+        </is>
+      </c>
+      <c r="F1103" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1103" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1104" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D1104" s="10" t="inlineStr">
+        <is>
+          <t>Guillaume Tabard : « De l’utilité pour tous de l’offre Bruno Retailleau »</t>
+        </is>
+      </c>
+      <c r="E1104" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPMHE0dEpSbkJvLURVTG1NaEdGcWNEd2F4VWRZa0dVRl9wc01adlEzRkJiSVU0TERPZ2lYUm1WbXFkcm8xeEVMemVUS3FxRXlrazItT1A3d0FmTWhZc3hlblBkYXpSeUNyME4xVTdlZGJxZVlVeGlJci1kYmhYWGFWSnBuTm40anVGS1BjRmZWdUtLMHNPd1k4OVoyVjNtSk90S21rUFlybWNESzdaSTNqeGE5a0tKTGpKT1o0Njd6c0g3aFpiaXcybFBRSVV5VUtIMzJV?oc=5</t>
+        </is>
+      </c>
+      <c r="F1104" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1104" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1105" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1105" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1105" s="15" t="inlineStr">
+        <is>
+          <t>Proposition de Bruno Retailleau de réformer la Constitution: "La Constitution est notre bien le plus précieux", s'offusque Yaël Braun-Pivet</t>
+        </is>
+      </c>
+      <c r="E1105" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAJBVV95cUxNNmlFTUhSNV9ZbXF4dmpTY1hHU1F6LURISkdXUzVXc3RyQWNEUDRRWThqZkY2ci1FdUJkMjZRR3ZibXl5RzB5MEN3ZVgxZzc5VkJwLW52SThWdFYwYnBfcW8yU3FVVGJKWVZIUHU4WlMtZnZVajNkNVlvbDlQV3lKYm12aWVCTlowTWVJUnY4cUZsSGRiZVljNkY5cDZkbzQ1QzVOd0ptSElMNW5ZQ1U5N1lIMk1CUmpvbi0zNkd0YmJPOEhDQ0Jnc281VXNzR0YtdUJZNDUtVEx0RDl2Nm56UmN3SzMydWM4THRET1dTaWladlQ1Q1lkY0swTjd1cjUwZUtIRUVwNTFMalhTc3N3VjVvSUd0VVEwXzhFX29DY3hzM0JzUzFLWkQzWlZNZ0FoeXV6V0NFbW5DRnJwempEdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1105" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1105" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1106" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>lejdd.fr</t>
+        </is>
+      </c>
+      <c r="D1106" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle : Retailleau tend la main à «tous ceux qui portent un projet de droite solide et crédible»</t>
+        </is>
+      </c>
+      <c r="E1106" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPdU85SU15Qzl4M1JORTRYWlVYZTRQQWlSaElhOGwtRHZOVndDbVZuanVEX1dzMTl3dklPMXJZNC03eTZVME5fSUpJRnRhNmVVbGZXUklVY2pYREd4dnRONmlpY2Vua0Z6OHoxaFRyVk9fazFzUkRraVRGVzFDZlFOdGRiQUFDenNsTlMwREktRDdHd21yUko3NmVobW5ZM3NnMXlyMlowelpCblBiX01ieEgxdzJCRUhXcE1veVM3R0dQcFdqTXd1b280Q3F6SnUxZkFpV3JR?oc=5</t>
+        </is>
+      </c>
+      <c r="F1106" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1106" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1107" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1107" s="14" t="inlineStr">
+        <is>
+          <t>Atlantico</t>
+        </is>
+      </c>
+      <c r="D1107" s="15" t="inlineStr">
+        <is>
+          <t>Révision constitutionnelle : le pacte de Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="E1107" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRPM0FZQThjZDZMcGh5R1lPTXNwOE1qN0FkRGU2d1FfSm1jNjZqZHB3NVRUcThpSldwXy1pdlhrMDU1VXFJNmFNVDhRNUFJeXlVclh1V0UtcnEtdlltOFFaYWxLa2VnXzRpOEE4NDNSZkZnYzVPNkVDdFFfTXVGWFN1Qjltby15TS02WXA0ZGlfeHdNT0MzSlV3ejVFa1JRZllUa1JoYXh0QzhDeVlSejhub2VwWnl2TWNVVmlNaXVPZVpSOGlhYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1107" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="G1107" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1108" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Marianne</t>
+        </is>
+      </c>
+      <c r="D1108" s="10" t="inlineStr">
+        <is>
+          <t>Cécile Duflot a la flemme face à 2027, Bruno Retailleau est "plus waouh" pour la rentrée : mieux vaut en rire</t>
+        </is>
+      </c>
+      <c r="E1108" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPazloZ2E4MXotaEwxNnRBTm9Ndi1Ma0tZa2gwWVVpNEhoVXdOaWlNOHIxTnVCWWxwb2FWXzJCeWJXVFJuZ1dmNE9Pd3FnRGpOVGlFXzBuRVRnTTEwNU1Zdm00UnBpUndfdXg4d1h5MHJWWWlvSEdFNDdySG1DckNiMHZ2YzdmMVpnbDV1bDhoNmhDeGJjREFEQlpzZHZjWUVsNXl0QnVwS1BKVGdEUGpkX2RzNUM3ZzMyNnlURVRyaGtWTlY5XzY0Y05mLUxtMExqbDNJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1108" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G1108" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1109" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1109" s="14" t="inlineStr">
+        <is>
+          <t>Contrepoints</t>
+        </is>
+      </c>
+      <c r="D1109" s="15" t="inlineStr">
+        <is>
+          <t>Impôt sur les successions : Bruno Retailleau relève le niveau</t>
+        </is>
+      </c>
+      <c r="E1109" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNjYzV3FzaXVIWWZWdkw4aWRTcC0xNDM1TlNZdVZuQjk3MVN3bGdWQ3pva1ZvaTRXcTBiSzZJYXZsNnBzdjZ5ZHBNY1ZrWGVWdVBwYUxJSWN4SVZraFhaekNqTHUwZWtpVmVVenFFWlRkcTgyOUNPRXcxRVlIRXZsN0JzcDAtQ2c1N0ZRdnJB?oc=5</t>
+        </is>
+      </c>
+      <c r="F1109" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1109" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1110" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>lejdd.fr</t>
+        </is>
+      </c>
+      <c r="D1110" s="10" t="inlineStr">
+        <is>
+          <t>Réforme constitutionnelle : Yaël Braun-Pivet dénonce la proposition de Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="E1110" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNSUp3cXdPcXhqNUdTVXM4TnY3bTlZbjV1X1dWbHJ2YkVaR1RqVFBSUXBCNUktNFUzcHNSRGViMDJqRmNiclBKakRiYjYxbVJCNVlfSGgzdWVXQnRWaWc3X2xjczJnbDlsY1NmZ1ZrR3dLbUZaQUlmOG9CUnZmc004YndBSXNVU1RqZG40aE12cGRzT0FzbTVCWFNnQWVrOXpQaE1LUk5RQ3RnUF9zWE01M0Nienhnc3pWOG1yMDlvRXE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1110" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1110" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1111" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1111" s="14" t="inlineStr">
+        <is>
+          <t>RMC</t>
+        </is>
+      </c>
+      <c r="D1111" s="15" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau veut créer des "internats disciplinaires": "Il ferait mieux d'aller sur le terrain parce que ça existe déjà"</t>
+        </is>
+      </c>
+      <c r="E1111" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxQY0RUYWFJV3IyU1BUdWtieWMzVlV1b1dZeHJEb0dscUZfN2R1U1FUdUlzR0QwR1dMb2wwUWNWelU2TnNqaHd3ZlJUcHo0bG9iQU4taGV5ZzJ3bE8wSERUYnVPMy16bHA5RzdUUlQ0NXJUWmZiMXhIWkRYVG93bmJxbUxSNWNiZ1laR3QtWHdBRFFjZEc2SlgtenhnQTVMeVRFRmZEaXFIOUVuMUJFVGZ1cnZLelBMcWxLX05mU0RDLS1pcEl1WmdVamxydExsWVYtNGMwWkpIN0d3ZUxfLVViNjJQQTJILUw5ZFNxS29pWXYxVDY2Sno4Q1A5ekd3SUZTMkdteXBGVVJRMF9xNmNVcmdpWDl1Wm05SlFjVw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1111" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1111" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1112" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D1112" s="10" t="inlineStr">
+        <is>
+          <t>Le niveau de vie des Français est-il vraiment inférieur à celui des Européens, comme l’affirme Bruno Retailleau ?</t>
+        </is>
+      </c>
+      <c r="E1112" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxOTUpHTWtaV0Z5cGVXOFpQMXVCc09WajhDTUVYa2MwTkVaQ1IxXzYxUXlaLVV1UHlGaURwV3diSndNeWV2eElNOXZuQ0xhNnRBcU1BcFVZSzJUVUIyaHA0cHoyYlVnQ2VhdUVZbmV6UVMxMmNYUmd4ZlhJN2lNNzAwM0dBbVk0T09sOXJZd0R4aENBV3JSTWFIcjhqSUdiVU9qYm4ydEoxX1ZRZDVBaHNUY3ZEa0F3Q0Q2aTVIaUJyeFJwVnBUQ2RqcjJOSXQxcTVBZ09DVDVVVHE5bWVuV2VMR09YeGd3Z2R3VmZHc1R5RVFPbThSNzJzWWYtanotUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1112" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1112" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1113" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1113" s="14" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D1113" s="15" t="inlineStr">
+        <is>
+          <t>Attal joue à droite et à gauche mais fait monter Retailleau et Glucksmann</t>
+        </is>
+      </c>
+      <c r="E1113" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOVnVoeE53VEtFZ2RWcUl1OEhKVVNnZFFEWklaNzVZU25YTDFlTjZxRkpwcUNzdXlnd3hwaDNITDVvLVZlRVNUWU1zb3F0cnFTTy1YUE9GaXVOV3RQMk1lcGFBVVpleEhFajNVREEtaG84RTB0R0p1emRTLWtBSC1LYWlXUExwV3pGUjA4bGxnUDU4Y2llS3ZrOEFzY01kLWJKOEhMVEczU0hLbFU?oc=5</t>
+        </is>
+      </c>
+      <c r="F1113" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1113" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1114" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>L'Union</t>
+        </is>
+      </c>
+      <c r="D1114" s="10" t="inlineStr">
+        <is>
+          <t>En tête à tête avec les militants LR à la Foire de Châlons, Bruno Retailleau flatte la « France qui se lève tôt »</t>
+        </is>
+      </c>
+      <c r="E1114" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPc3BiSGJXbjhIdmxzeHBKa0o1ZU5qRlhRVTVpQ1I3eGhtX2RtVDdmVzhyMVpNdmZGRV8xVDZBNVN4YzRxWkFvREQ5czZtUjhFVVJadDVBT2xlTk1Wb3NxTnd3LU53YU01TWpyYlN4VlFoLUVrSHMyZlQwMnlEcHdRejJUQjYtTGdRRjN0MjdPYkZmallTX052OHo1YnFhc1dhbTI3SDdXRWtob1R1UTZWZVVGNUFzUDZCZ1JDQlVSeFpHeDg?oc=5</t>
+        </is>
+      </c>
+      <c r="F1114" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G1114" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1115" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1115" s="14" t="inlineStr">
+        <is>
+          <t>sudradio.fr</t>
+        </is>
+      </c>
+      <c r="D1115" s="15" t="inlineStr">
+        <is>
+          <t>C'est quoi ces "internats disciplinaires" que propose Retailleau pour les élèves violents et harceleurs ?</t>
+        </is>
+      </c>
+      <c r="E1115" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPNUloS2xnRF9BRWhleVg4YlRoVXRLc19Tb08yLXgxWEhTZXIyVi1vM0VqTzRKNTYzR0hiWHZZaG9KTUxBbE13YUxfR2lnM3hlR1dDRmlKY3pmMGRQSlE2bUY0cU9EXzU2TE5ST09HQkpDNlpRbUM4Zjl5YlV0dWFQbUo1ODgwcEk5dzF4U1I5UnlFd1o0ZEF4cWJUdGx3Qjd0NjB1NkFWVDM1YTk2NjBCSnAyTkNvUFZNQmpydGUxeUZxWGdsekYyM3Btb1Ftek0?oc=5</t>
+        </is>
+      </c>
+      <c r="F1115" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1115" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1116" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>midilibre.fr</t>
+        </is>
+      </c>
+      <c r="D1116" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Bruno Retailleau veut rendre l’apprentissage accessible dès 14 ans… voici ce que sa proposition impliquerait</t>
+        </is>
+      </c>
+      <c r="E1116" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNN3R2S3NVcHIyaWZlYktEWkw3WmNPMW1vbWFLUjVOcFZfbVVwMzcxM0hoVUFzYlh1YzB5V2RndXExZ1ZKZXhfb1ktY2ZjRkJaaGtRSG4tVEl2OGdzeGFuU0tzSTJmTGFCX2xXSjJ4SU5NR3hJcWYtSG02QXE0ZzFZeGRONlRJR0xYd041Wk15dFZpU1R6c0JfajlCMGFaYnFtNnl4X3VMcjNVVHZSVlBRdjdnQjBWbDFOemFMSjRjQUFXZ2RxVEtFa0NTWm5XdER1QlphNEpqY3h4NXZtNktJMXNOX0I0eFlodTVUQzJoVUIyRG05M2YyNzVIQzJuRE5rYUlRRzdB?oc=5</t>
+        </is>
+      </c>
+      <c r="F1116" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1116" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1117" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1117" s="14" t="inlineStr">
+        <is>
+          <t>Europe 1</t>
+        </is>
+      </c>
+      <c r="D1117" s="15" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau / Richard Ferrand : le peuple contre les juges</t>
+        </is>
+      </c>
+      <c r="E1117" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQjg3YXQ3SFZzdDJzeHhnQTFwdjRlOGQ0SG1KeThvNnBrX2Z3X2lUSVdVOUVuc1BlUmlUcDUwaHV4dmVwcU5QQ08yNjNvWUdXTkZ3TW9IY2NDRDFNbWdQSHFxQVh4N0d6b2hONW84UEgxTmlza2I4aUhLTEtnbGNHdmhYRlBKQUp1NW5WUmNNem5OUTZOd0pxcF9zdzd1V2RvZ0tMMlpxLVZXNS1PalFON3lxdDBhWHQt?oc=5</t>
+        </is>
+      </c>
+      <c r="F1117" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="G1117" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1118" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>lesechos.fr</t>
+        </is>
+      </c>
+      <c r="D1118" s="10" t="inlineStr">
+        <is>
+          <t>Edouard Philippe : la bataille de LR a commencé</t>
+        </is>
+      </c>
+      <c r="E1118" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxON0JTekd0QnI5bEZhcUdzazViZFRxSEJSTWozaUFfQlBYZU1WUHByYWFhSi1TbmR1QU9SR0FOQzBWRThlSVZuVUhaRHhETU53QloyXzJHSllLTC1DX2lYbEtyYmxlMU1yZjJadW5FTWF6MVFnVEZKMmo2cUIwejZEcUh6cDNmTS1fbUI5XzVqLWtad2ktSmtTQzR6WWhWU3c3d3MwMg?oc=5</t>
+        </is>
+      </c>
+      <c r="F1118" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1118" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1119" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1119" s="14" t="inlineStr">
+        <is>
+          <t>rfi.fr</t>
+        </is>
+      </c>
+      <c r="D1119" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027: « Il y aura un bulletin Retailleau au premier tour», affirme Pierre-Henri Dumont (LR)</t>
+        </is>
+      </c>
+      <c r="E1119" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxQQmlJSXY2UlVTN3ROYnFERWVzeWlzZlpacS1yQktRbk83cDhiaEFqZUdWTmgyYlJfNGZEdG9pYXJUeDFmZ29TdVZNUjZJYl9Hel9tbk5OS3YwVmVmaklvVFlocGQxNjBmV2FsamlnSU9qajJReFVDNHYwUGtCSzZGd3F2ZTM2bWFvQUl6ZDNVSGVNeWJWWUpNSEN5Q3lwVUMyamsyT1U1S0hIX3Z1Q2puVlAwMFliSlMtakFfV0l1QkpNa1ZQazN3bzZRMzdRNThKcEliRXZfWTlwODZldENXd0lKSk1OUk5hZjBPU1BPNUJub2g3d3FqY3pn?oc=5</t>
+        </is>
+      </c>
+      <c r="F1119" s="12" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1119" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1120" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D1120" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Bruno Retailleau propose une réforme constitutionnelle pour que l'État ne soit plus «impuissant face à la submersion migratoire»</t>
+        </is>
+      </c>
+      <c r="E1120" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQWDZDcTlSZFpYN0k3NnVVQnBJUVo4S082SEM3THY0R1VRYnF5UXY0c19fdnkzSzZhRE1IdGVlZHlUdGR0aGliOEhXcEo3Z0ZQTUU4SnpVRFFxUUl2OE10b0lVb3plYTl1bmprazRET1NtaTIxMF9GLW5ZOHFTaGhQaGNyWGY0ZDI4T1EyNW9IYlZadHI3Nzc1TGg0X1Zic1lNUzdVcnhFanpwM2FXWlVHY1hVUnM4SjhadkFGbTkyQdIBvwFBVV95cUxQWDZDcTlSZFpYN0k3NnVVQnBJUVo4S082SEM3THY0R1VRYnF5UXY0c19fdnkzSzZhRE1IdGVlZHlUdGR0aGliOEhXcEo3Z0ZQTUU4SnpVRFFxUUl2OE10b0lVb3plYTl1bmprazRET1NtaTIxMF9GLW5ZOHFTaGhQaGNyWGY0ZDI4T1EyNW9IYlZadHI3Nzc1TGg0X1Zic1lNUzdVcnhFanpwM2FXWlVHY1hVUnM4SjhadkFGbTkyQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1120" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1120" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1121" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1121" s="14" t="inlineStr">
+        <is>
+          <t>20 Minutes</t>
+        </is>
+      </c>
+      <c r="D1121" s="15" t="inlineStr">
+        <is>
+          <t>Braun-Pivet recadre une proposition du candidat Retailleau sur les Sages</t>
+        </is>
+      </c>
+      <c r="E1121" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOV0ZROTFvQjhOR01jZlFMYnRlLWVORmJOc2kwbEtqNzdlaEF3XzcyX0JLN0JuMUpSUklPa0RickpoVXBBZjNZaFh3Um5VMjY2ZEpxUmlieVYtdHkwTjAyRlYweHY4RVBKdTEzaDlhcktPX2xkYzh0U2ZxdlJlZnFxSFJsYVNrMjBOXzViT2pobng3cThaUnZKLXZRblRsUWtLaERRWWdRQ0RzN2xMMmVIMkRNZEhKaTBRT2hlS0o5R3FaZXlIQWZ3Z3RVSkJPN1dNaFczR2o0anE2R1BSMVRF?oc=5</t>
+        </is>
+      </c>
+      <c r="F1121" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1121" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1122" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1122" s="10" t="inlineStr">
+        <is>
+          <t>"Passer outre" le Conseil constitutionnel par un vote des Français? Yaël Braun-Pivet "en total désaccord" avec la proposition de Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="E1122" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwJBVV95cUxQbkJSZ05saUs4bXRRVHdXR2M1dmlIM0s4amMzaTl1OENYTFZFZ1U2WV9ETXROR0JoTFFhbFkyZjg0T015LUo2UFNaa1k1S0ZaOFYtNWpuMVlEa1dkQnZXVXpLS1dJdkV3M0t0UU9Jc0xlNkZVS3ItTUZQanF4TUl4YTVQR3F0aGVwa1JkOV9BWXZWT3JOZFhwSkYyOVZHd3lqcnRjRXBlMGZ4WThQSGY1QUtZSkxlQ1A5ZlQ0OG83UTJpalh4UTBmb0hXcmw1NDI5RGRaLXJIbUlBc21BWUJEbjdJVFB2RG1jRk9QWVZXZW9RYUJwQ256cHRsNzVwX0VickkyTlI3aU5pSXBWSko1ajhPVGpCMnI0VXdKcmk5Zm5xLWNjdlNpNGJ4VmpodUdNckRKNE1CTFgzOUl5TWZV?oc=5</t>
+        </is>
+      </c>
+      <c r="F1122" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1122" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1123" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C1123" s="14" t="inlineStr">
+        <is>
+          <t>lepoint.fr</t>
+        </is>
+      </c>
+      <c r="D1123" s="15" t="inlineStr">
+        <is>
+          <t>Édouard Philippe : « Il faut être ferme, très ferme, sur le régalien »</t>
+        </is>
+      </c>
+      <c r="E1123" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOU1d4NjUwLXBHbWJpcmpXbnZxRWdVRFRnYmJxclhDUm42aWd1Z1VJd2pNaVZNck00Q0pUYmR2RjBuc1JPek81bjBWNmZZV0ZKV0hteTV2dW00YkUtWFgyTkhnNUNYU2kwZ3E4SzJUclJ5WE16TkxHbmd1YjlYZy0zUWpOYnlBdDBXY1EwNmpuSzNBSEZUSUliTGxrcm1EUWhNaGF5Q0VzSEY2RktqaE5jY251RTh0Z1UzSXR1c05SOHo?oc=5</t>
+        </is>
+      </c>
+      <c r="F1123" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1123" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1124" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>lepoint.fr</t>
+        </is>
+      </c>
+      <c r="D1124" s="10" t="inlineStr">
+        <is>
+          <t>Édouard Philippe : l’équation difficile du « moins mauvais » candidat</t>
+        </is>
+      </c>
+      <c r="E1124" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNMlZpWHA3NHRfZnZRMm9YSEdUbWt3UVRWOERVMUpUMmJVbHVZLTc1WklXenFlOEcxVlhfaWQ1X0lQSGFBYWtFTlBZUGFjaFM5U0R1d1ZJaU4yLXctUS1EckdlRjBnTWJlUjNZN09Tckt1RmNpVUl5MmdhWm9uQmltZDdLS1dibHdBdm5fRVJucjF4M2NuQUtzNE92a0tLZ3pUTGt3anlZajhGbDBQLVM3TXpFdXF4Y0VNTE1UMw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1124" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1124" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1125" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C1125" s="14" t="inlineStr">
+        <is>
+          <t>ladepeche.fr</t>
+        </is>
+      </c>
+      <c r="D1125" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : des compliments à gogo et un atelier frites partagé main dans la main, comment Édouard Philippe et Gérald Darmanin mettent en scène leur alliance</t>
+        </is>
+      </c>
+      <c r="E1125" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxOTmR6V19OODl5a0hGSXk5SllTOVNlMC00VERNY0prQTNVaExKOXluOHJVT1R5aEo5dlZXQXYtWDBMZFBHbU9GTzA3Z1VmSzVZTkI5NVpZRjYydXEyYnV1d3lqRXBqcncwMXM3UlNzMzk2ckJCWWtMVm9qS2c1VUdwZFJOd0xXVjRhekIzYWQxMDRuQU04VURVLWUtSkhEbDZDcXcteUlxQ3M1R0RhWWp0cXUzaUFLVEs0TU5hWTV5YWlMUjRCQmNkbGJ0c1VzUllvOEdsNjdvTmhXXzNRc3pLaEhLVlBxWVRNRGlUcUU0VTd1TVZMUkVVeHFBVkRaZEl5VDNWbnkzSTBUSHVPUl9QRTFrM1JDQjNrc1JMazNTUXhHdUVUY2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F1125" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1125" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1126" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1126" s="10" t="inlineStr">
+        <is>
+          <t>Édouard Philippe, un homme en campagne - 31/08</t>
+        </is>
+      </c>
+      <c r="E1126" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQR1lWUmVBN1dQR1BZci1NV0h4eEpmWXRDamExM1NtXzB1UmkyMUIwdU9QSV9DZTZSdWFWMTBfSVRJNGhmR0F3VkhFNUduV2hqWktxVF94TmdnVnpqMkR5WFE2aFlPalZid1lXbnlSUFVFZW94NXpkNm8taGotRTJVWkhzajR0WEp5Q3JXb3JSN184T05ubEJVeXZGWGFseDNKX2RNN1B4ZGducDNtM1JodnpjRklkUWFxRW5BVHhzTklGZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1126" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1126" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1127" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C1127" s="14" t="inlineStr">
+        <is>
+          <t>Ouest-France</t>
+        </is>
+      </c>
+      <c r="D1127" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielles 2027. « Acceptons l’idée qu’il faut stocker l’eau », dit Édouard Philippe auprès des agriculteurs</t>
+        </is>
+      </c>
+      <c r="E1127" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxQTnczWnNnb2ZNbVA5ZkZ4ZTVjN2hyTWdHS0xNcnVTNW1XMGxfa09Oa0hfd2RGQ0pUTFByaFJKeWZXVEl2NFRlQXBWUXI1aERhRU5xV3pkQ09PeW1XSUZhLVY0VE56MTlmak5xZktWZFhmVHdXZm0yeDMxcDBMdjhsd1dpMGRVV0t5T3pJX3A0QzFHaWZ6alJ5WTlsSUhUSmM2NDJudVgwakczTUd1eVJ2cG9kQWZ6TE5iZWdyVmNSd2RmQ2V2Q0NPZXQtaHlhcEx1NE5Sbl94R0RhVUF6RE43OUdVUFVTNS1NMUlJUG5pNDRhYVpYb1dheEROM181aEJlY1hIVUxRYXlJN29CMjQ1OV9peDU1T0lLWmVXWVhVWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1127" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1127" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1128" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>France 24</t>
+        </is>
+      </c>
+      <c r="D1128" s="10" t="inlineStr">
+        <is>
+          <t>Outre-Mer - À quelques mois de la présidentielle, Édouard Philippe et Sébastien Lecornu dans l'océan Indien</t>
+        </is>
+      </c>
+      <c r="E1128" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxPdkhYb3VnVXJpYV9jME5iSzF3SHR2dWtxemJ1NWkzbFozLWdVcXRIa3gtTkU0anUyN0hYUU1rSHc4UXlib2xZaV9lZzY4c1FxT1ZJM3RQdWhTbEs1a3ZySTEyR1pEZEtwUWo4YXRCYVQyZlVvQzV5NVZtd0JfVTJ1Z0dDdmFVYzZaVDNESHhmNzJWbkc0cHpzQTVmek40c19BRUNsOVZjTEs3SGxKcVM3TUR6R0hBWXVxcXBLTC01Wl9EQ0otZkliLTdEOTVLWkNEb3lQYlZnVGJyeFhTck0yeWhqcXVHNmxvanFOSkhYUnl6R0Q3UzU5c2lEZ01rbkdlU1B5Z2ttU3NGM1R0dlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1128" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G1128" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1129" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C1129" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1129" s="15" t="inlineStr">
+        <is>
+          <t>Futur Premier ministre, retraites, attaques de Gabriel Attal... Ce qu'il faut retenir de l'interview d'Édouard Philippe sur BFMTV</t>
+        </is>
+      </c>
+      <c r="E1129" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgJBVV95cUxNSnlPdnlBa1B6Y3ZiaC1yTkFacjdzd25Ca25zazExN0RLRVBxbTU1c3JxR2h4bmc5MFh6UWxOVFlMZ1NmUFoyRnhaTnJTdUxZZVN3bzc4eHM5ZlRhVFY1TkpfdDVtb1MzM3JLdUItcUdCdXUzNHAzVUJCSFBkeGtCeG0tODFQcDBla1NIUERqenR4T3M2LVphNkhMYUsxSWtBOUVMOGNmZlV3SzJIcmVBbk5yU2g3Mk1LcEZMbHRMb0daWDdDSmd0bUZYSHMtdU54U1NiUFhVem45ZVRiTHNvclFYSndIOWFwS2lBdU1yLW9IOERrbmVUR0gtaWdsQ3prTmJHZlFoeVpwbGpuc09OU1ItRlRLa3Zkd0NOVjAtQl9WYVdnWjhkTjJB?oc=5</t>
+        </is>
+      </c>
+      <c r="F1129" s="12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1129" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1130" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Europe 1</t>
+        </is>
+      </c>
+      <c r="D1130" s="10" t="inlineStr">
+        <is>
+          <t>2027 : «Édouard Philippe a peur» de la primaire, juge David Lisnard</t>
+        </is>
+      </c>
+      <c r="E1130" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNZndVWm9oQkhjb01tMTdMeGU2V0ZIS2dwUmIzSTNuLTJUV0k2ZVl1d3NuX0I5dm85X3A1cEFQbDhJcHJHbS1IRFo0bkhzc2Q5NmdVZ0lJc1p6RHV5TkRkSUswMHotcjFwRmtCVjNkVGEzdXNfTVhKMGFMVEZNRHBsdXREMDRkUkZUZUh6MVpOV1JkcUxqUlVPQ0ZDM2ZGWlBvVUtpN2ZB0gGrAUFVX3lxTE9hM2EyczJqMkhkcXEtTkhqaU9maURKTHF3aWNoN2pXdFNSRkYyNnUtV0hCUTdkTmJyNC04QmVqREtoUzZaWUxWUEhaYWxucUpoSTAzWW1XMlQwMkFZMzctZXdKQzhyMUtoVktxUTZzV2xRLXd0ZnBoY1FrMk90dXRjTml1em52UVd4dVh6MkdOcEE2UVVoQ2RKVDR2dXRXS0pJZC11QS1yM0tmcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1130" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1130" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1131" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1131" s="14" t="inlineStr">
+        <is>
+          <t>LCP-Assemblée nationale</t>
+        </is>
+      </c>
+      <c r="D1131" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle: Gabriel Attal présente son équipe de campagne et promet de ne pas faire une "saison 3 du macronisme"</t>
+        </is>
+      </c>
+      <c r="E1131" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQeWNVdTRzb0w3Sy1LRHlZX3pLTGZEeldER1VTQVV3UGpPNmhOZGxweFhZRktIOTBLZWNNUDhhZjkyYU1jaGM5M3J4ZjRjZktsZmV6VHNQWmFZSHFUTlVNekxnNlNISHNvQmVSU1d3U09sTWZYd2s2WUZLeVV4Y2wxQUZPQi04WFVUWXdPUUtsYmQwQ3oyTFVDTUhpTFdKQUFxTHdkWnZRb2JGTWRFQnlpRnFn?oc=5</t>
+        </is>
+      </c>
+      <c r="F1131" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1131" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1132" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Le Monde.fr</t>
+        </is>
+      </c>
+      <c r="D1132" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Gabriel Attal présente son équipe de campagne, avec Céline Géraud comme responsable de la communication</t>
+        </is>
+      </c>
+      <c r="E1132" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxPeG9tcWhNek9kdkdQb3Jod2tSMnM2RkJ4cW94UFdmckxQdmgzdGlsVU1yZGRoY3VQNHNSS0Zlb2lRd3JtclpTWFdSb29mc2d4NThwZFNHMVRfUThQblF1OFJGTHpxc05wZlpYdlBrSmhXT1VISVR3MDN5M3pNVVJKdmI3c0hEWG10WThXS19ZbGlsc0RORTR0eHI2RkFfZ3pyTnlfbGZzY0xfWHZZb1VyaHhET1NRZ193WnZZVEVEVjdRdDh6VllOMDdUXzBEMmtWRHMwMjVNUEVwQXFOQlN0X2J2eTNkdmRSWU9Oc0hBak0tWHNlMXJCSVVCWXlCcnVFbklMa2xwOVF6bmhzOHI3N1E0NDNKbjF3RmtnakR2VQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1132" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1132" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1133" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1133" s="14" t="inlineStr">
+        <is>
+          <t>Gala</t>
+        </is>
+      </c>
+      <c r="D1133" s="15" t="inlineStr">
+        <is>
+          <t>De France 2 à Gabriel Attal : découvrez l’ex-animatrice star qui rejoint la campagne du candidat à la présidentielle</t>
+        </is>
+      </c>
+      <c r="E1133" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOWkhpeGhoaE9OY3owSDlrVFdFWkdQalhHZ3Z0NEV4bFlrS25FNEh3Sl9fQ1I0Q09rWDBwY2o1RHhBVlFEWkhCbUNPVFNlQXVuMmhOWDhyRlhQaTlueThjUzR2cERXWE4weHB5azlOSjh2TVVnc21MQjFzaHU2ZTFxVDhHd2hyd3k1V01XTkExOG1JdzRRc3E0OEtPdTY5Wk5vRWtjSmFEZGo1NnZ5M2VvRjZ3NVNlUkhEUTdTZkZlLW5rMEZMMkp2ZFRZZlNIYTJ2eDhYQkVjMFdNQlo0Vi1lOVR1NVBUeHVz?oc=5</t>
+        </is>
+      </c>
+      <c r="F1133" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1133" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1134" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D1134" s="10" t="inlineStr">
+        <is>
+          <t>Attal joue à droite et à gauche mais fait monter Retailleau et Glucksmann</t>
+        </is>
+      </c>
+      <c r="E1134" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOVnVoeE53VEtFZ2RWcUl1OEhKVVNnZFFEWklaNzVZU25YTDFlTjZxRkpwcUNzdXlnd3hwaDNITDVvLVZlRVNUWU1zb3F0cnFTTy1YUE9GaXVOV3RQMk1lcGFBVVpleEhFajNVREEtaG84RTB0R0p1emRTLWtBSC1LYWlXUExwV3pGUjA4bGxnUDU4Y2llS3ZrOEFzY01kLWJKOEhMVEczU0hLbFU?oc=5</t>
+        </is>
+      </c>
+      <c r="F1134" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1134" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1135" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1135" s="14" t="inlineStr">
+        <is>
+          <t>lesechos.fr</t>
+        </is>
+      </c>
+      <c r="D1135" s="15" t="inlineStr">
+        <is>
+          <t>SONDAGE EXCLUSIF - Le match « perdant-perdant » de Gabriel Attal et Edouard Philippe dans l'opinion</t>
+        </is>
+      </c>
+      <c r="E1135" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPaUhkUDVaNzQtYzc0Zk1zcmVsQkh2Wk9XM0ZOckxtLS1aM3VBSWFlVnVrNk9ESTV2RnNPZ205aTc4MnYxV0dqMlpaRExFLTFMNjAzNnBmODlRY3UwcFlfR2NCLWpXdHN1dzBsOVA5QVdKUWJqRmkzNm9ZcXhZSkp1OHhINVNkNlNXZ2hEMVV4QUl5Q1NhSlAzVnY5Q1U0MFVtNW13XzZyMDVhNFgtUFFRdUpFNHFmRW02TXdJc2VsczZzUlY4dWZTdHlxeEg5ckpsUXQycGllNmQtSTcxTGhrb3BkUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1135" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="G1135" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1136" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D1136" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : à défaut de ralliements politiques, Gabriel Attal s’entoure de «nouveaux visages»</t>
+        </is>
+      </c>
+      <c r="E1136" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPd1RXVHpCbHJ6c2VEQjFKMTZYXzdPZk4yZmNPSlp0UzZ3dlRJelVVZk1Vd2R6NzlIVktpcDRLbE5nQ2NTcUtUd0hYNVFqeFQ5Q0w0QzZ5WEo0R3p5bXNpQ08tVkRTdTMwNnlfak1JNWFOZ2pJcTFNMzIyUnVJc29Pa19Jb0U1bzIzU1JoLU41VTVqQko2TkZmQ1NNajJHeVRIZktFdTEydUxVckZiSm1tOG9QWVZwWldCdkFEY1pKZ0o0ekpxa3hhSzkyLUlOWGZMWUhsWXNFd3E?oc=5</t>
+        </is>
+      </c>
+      <c r="F1136" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1136" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1137" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1137" s="14" t="inlineStr">
+        <is>
+          <t>Le Monde.fr</t>
+        </is>
+      </c>
+      <c r="D1137" s="15" t="inlineStr">
+        <is>
+          <t>Gabriel Attal dévoile une équipe de campagne présidentielle sans poids lourds politiques mais avec de « nouveaux visages »</t>
+        </is>
+      </c>
+      <c r="E1137" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNSmlUQXFZUEZoSzhyMVJYclJLUWFGNVJXR29XT2JDM3J3MDV5RDhUT3hOdzcxRENxWWtwMVJ6OGVOUS1uMnZhZ3ZDSG5oTzFZMW5mSTNJcmJ2OTdoZUp4bzlWVlNCM2JhdUduUTBFTXFoWGxPTG9iN25uR0NlMlQ1ZldWS3AwZUN1QWhVa1l2NE9ZakNTekZBS19QbHdXNFp6RjN4WUZVcDVUTWJTYjFZSjhSVjNpZXQwSnpuSmJFOWUxQ1NRNjViajVEcUFpd200dHNabUhLcTNhcmZqaldpVG9sOEVNaVh2RTJtWVdEMW5ROWEwME93RTZrbjZGd1ZyMkNCRnU0amRvT1g5eks4dW9XY0FhbUVGWlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1137" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1137" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1138" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Le Monde.fr</t>
+        </is>
+      </c>
+      <c r="D1138" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Edouard Philippe tente de prendre de la hauteur face à Gabriel Attal dans la campagne</t>
+        </is>
+      </c>
+      <c r="E1138" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQUndlZ0lnNks3ZWZmQUVZalZxei1NMHZWQXhSZlAtZXRaMUpVZWMyUHRmSUd5S3E0clNUOUlQNU9UWk5FWFZXUjIta0hnc09zbkFGWVA5YTFxNi1mb2dCdnhFT2ttOFgybDN5aVdNN0pkVDZSWWctOTFMQ3M1RmJUbUdUV1YtRHU4a2RrdWFkZjJvQjdabEUyWXQ0SC1iNzFjUmxhdWNyX1hrVDg2LUV3SnUzSjFfSFp1NlJpb2lVeUNSSzVDS0ZPTXJxUkswY0ZnZW1SZmJsZVhXaEhyaGRBRVoyV1FfWVVCT05Tem8xa0JsYXlmRDB6NUVZejRBdmZXSHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F1138" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1138" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1139" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1139" s="14" t="inlineStr">
+        <is>
+          <t>Public Sénat</t>
+        </is>
+      </c>
+      <c r="D1139" s="15" t="inlineStr">
+        <is>
+          <t>« Ce n’est pas la saison 3 du macronisme, ni un retour à l’UMP » : Gabriel Attal joue la carte des « nouveaux visages » pour marquer sa différence avec Edouard Philippe</t>
+        </is>
+      </c>
+      <c r="E1139" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxPczVETVRGV1JfZUVlbVY1TGRYYVVwc1ppU2NkX3NYSnVfTFVFSGRndGZJNkNUMS14YlBDMk5HUFN6dTljRWY0YTFvMDctRkh1U3JOZnBKXzdqU3pHdU9vVVpCLVo5Qm5GSm9VMzB6REtoSHJSVmNmOXpsVHlxQ1VieW5uYzBWOE9NQ2VCejgtWUxOaGtQVlRRYkNzclpXdlpxYm9najNSOFdhYm5FVTlDX1dyMnZoRkVab2xZRjNXS2I1cW9GX3d3ODZvS016YU41eV9jajRxVG9GeEFXQUY1WDZ5Y3dRVHlEVHhwNncwSkpvbFpETkNrS0pwaWl4TmRzVHhXdg?oc=5</t>
+        </is>
+      </c>
+      <c r="F1139" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1139" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1140" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Gala</t>
+        </is>
+      </c>
+      <c r="D1140" s="10" t="inlineStr">
+        <is>
+          <t>“De la résonance nasale” : Gabriel Attal dévoile son exercice rituel avant chaque grand discours</t>
+        </is>
+      </c>
+      <c r="E1140" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxONmgzb0xlQmpDc013U0VvcHFDbVNBRjY4QkVQeEdvRmR0WWh4dkFYcDZOV0g0RFdNZnEtbzdGS3FHYWxCc2tvMmJFNW1KYWtTZmpPVzg3MWljMUo3clczb2RXX2Y0ZkdkZXpiYjZwZUkwZDZ5ZldxSnRmVzNvaDdfeFZQTktaVnhOano2MjVtTFk4ODVBWHFSTEItNkRjUk8za2JiMHpkdzJObHNiVkQ2bWdnNmplY1FmQnJLYWRoVVhhRHY1SG9Ed0FFUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1140" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1140" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1141" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1141" s="14" t="inlineStr">
+        <is>
+          <t>20 Minutes</t>
+        </is>
+      </c>
+      <c r="D1141" s="15" t="inlineStr">
+        <is>
+          <t>Non, Gabriel Attal n’avait pas d’oreillette pendant le débat du Medef</t>
+        </is>
+      </c>
+      <c r="E1141" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPSzdmWjhpLUdmM2FGSHRKSnFpU1YwUzRTS05vZU56NzRacENiM056eHdEOTB1cm5MVDBfbVRqbjdCN1pFRWoxWHhxOVpYWTFDNk5CRVdXdFB2TTl0bzktNXBKTE9FQmFJTGFLOEwxX29iNEdBd1RmV2gycmFrc0tuQ3B1NUloN3UwVVVRS1JnVm9ORUMzaWtOZXptS2pxMHZCdmZnMjlGanRQNHNwNWNuZktjOUw2ZmlId0ItS3hZdmF0M2hqeHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F1141" s="12" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G1141" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1142" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>France 3 Régions</t>
+        </is>
+      </c>
+      <c r="D1142" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Jean-Charles Orsucci porte-parole de Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="E1142" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdEV5ZHUwU0pka25tclgxWG5FbWhyM2phanlJT181RkRSYXd6SmVHUEp3NzVLMDNOWkRHZWlCclk0UU91aWNueUpNVjR3MmdEMU9QVkpGeWlhTkxkb1lXd2hScHpocHhxc1RrajlhbmdQSmlWUnBiZnhEc1U4Y3Q4QmEzbGN4dDhwTm40SHBDcVdYdm9xY2Zma2U5WUFMVDAwX0JRNFVLbllfWUYzWGpVanVLeWdTNFI2ZWE0WEp4dHBIa3ViUFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1142" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1142" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1143" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1143" s="14" t="inlineStr">
+        <is>
+          <t>ici.fr</t>
+        </is>
+      </c>
+      <c r="D1143" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Jean-Charles Orsucci intègre la garde rapprochée de Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="E1143" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPYU4zb1hnUVkxVFRaZ1JSLTJjUi1hTkhIS1pMU2gzbVhvTkZGMHhWd1ozV1pMdWVHeHJ0Qmc4YTBIRktrcUhwY2xCa3hqQWFWX05sdkF6Vk10OHBTTFJJNzVsbmtGMzZWQTQ1ejc1eTdKVzBDRkdLU2FqY1BiMDJsSS1JVmg4RU01ak9jM3JSOFRRRENCb3NSVFdmRkFRZDlyZmhkZ09NNGdtSUtrVDE2Skx5OGxnbEhoVTM3cU1JV0pRdFY0aXBF?oc=5</t>
+        </is>
+      </c>
+      <c r="F1143" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1143" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1144" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>liberation.fr</t>
+        </is>
+      </c>
+      <c r="D1144" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : à droite et au centre, privés de primaire, les unitaires amers</t>
+        </is>
+      </c>
+      <c r="E1144" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQaGQ4SU9VRTZXNWZwQ0pCT2gzVUFqOTBsS1BiSUItVlpBZTdDcDZLcGpZcmswME05SGdDcWZINGxwMDE1bFdndXlfZTExRVQ1MUxJb2xsOERuMUJsY2VtalZGNnBUY3d1dXRxZjFkNWpuMFgybklaT2NybUowLTF0V1ctSDhwb1hSTDhPLUtCbUhZUTlrdkRIVmc5N1VuYTlnMDVSY3ZKcXRyNjE1alREcFE5RXFGRFk4SmtCMF8xOVlzMmZkYk5DNGxaTTBYZTVERUZuZW51ZWNhVXBRVmVmcFdjTGNHVXdu?oc=5</t>
+        </is>
+      </c>
+      <c r="F1144" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1144" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1145" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1145" s="14" t="inlineStr">
+        <is>
+          <t>France TV</t>
+        </is>
+      </c>
+      <c r="D1145" s="15" t="inlineStr">
+        <is>
+          <t>Gabriel Attal, invité du 20H</t>
+        </is>
+      </c>
+      <c r="E1145" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPTjM2akZSVl9tODBhUmdTaEtPbkRMNGMxUE9UV1NYX3lYXzVra1QtSDVtZzJGYXFRemU3Y0thMl9BbTA3LUhQS0NEWXR1cnlRMk8yUFU1Y0wwZzEtc3A0OU5UN3VjUm9RQUVWd1FiN2FvbVM3bktHQlplbXh0RmdNcFp0MllvdktiLTBsZ0pB?oc=5</t>
+        </is>
+      </c>
+      <c r="F1145" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1145" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1146" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>sudouest.fr</t>
+        </is>
+      </c>
+      <c r="D1146" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Gabriel Attal présente son équipe, la journaliste Céline Géraud devient responsable de la communication</t>
+        </is>
+      </c>
+      <c r="E1146" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPbGdWMkVxYjhkcnVqNmJZQ200dmd5Vm1WYkw5OHNodGJqZG15amhOd2lJa1QzbTVTNDFVemdCRnZ4ZkhDajhLMmJjWFh3Q3FaNWJqZnJaRDU2bEpQekE0WDdtOHVpcVdSTEZjU1dEMHZnV2d3c2RJektsZk9kWmw3ZDk2QmZNV01OQ3Nyay10TVNCVHFJRnJyWkk0VnNnMnY1ZmNXamp6YmRXZTFQRnFPa2tCYWx4REtVUm1xYjdPbTBPcFlJdlJ5V2FFeXVaa2dJOXFZZFJPWEE4b29PSl84ODNqa1BFMnI3eE1rVXhfMGtzZlc5TWZORENuTnFRQWsyaVJNT0JlbFBTWGVhU1JwS0dB?oc=5</t>
+        </is>
+      </c>
+      <c r="F1146" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1146" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1147" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1147" s="14" t="inlineStr">
+        <is>
+          <t>L'Opinion Indépendante</t>
+        </is>
+      </c>
+      <c r="D1147" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielles 2027 : après un été pied au plancher, Gabriel Attal poursuit sa campagne permanente à Toulouse</t>
+        </is>
+      </c>
+      <c r="E1147" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOd2RlX0pYa3pDeTRfN21VeHFvU2k1d2pCNnh1dzJhMFY4QXZRYzJyeTQwSVBfOXA4RHJyZFJfc0htUlB3UTV2ZDI4MnJ4azdkd0l3MlNLYVhhb001OTRRY2E2NE9pZHdBb0NpbmppekZxNExCTkFjT09pVTBRVF9PdkprN2FkZThTSEhaVFh2aDBUWmFNUFBsUzVNUjF3SUFyMTY4TzJNVXgxUGJNdXNYZTlsbHQ1M2hiSmRYSi03X0VhNjhLMEU5Q1JyaTl5ZlNvZzVqMTBrdHUzSHZvSkdXZmt0OFpoSTJTMUgtRTFR0gHuAUFVX3lxTE53ZGVfSlhrekN5NF83bVV4cW9TaTV3akI2eHV3MmEwVjhBdlFjMnJ5NDBJUF85cDhEcnJkUl9zSG1SUHdRNXZkMjgycnhrN2R3SXcyU0thWGFvTTU5NFFjYTY0T2lkd0FvQ2luaml6RnE0TEJOQWNPT2lVMFFUX092Sms3YWRlOFNISFpUWHZoMFRaYU1QUGxTNU1SMXdJQXIxNjhPMk1VeDFQYk11c1hlOWxsdDUzaGJKZFhKLTdfRWE2OEswRTlDUnJpOXlmU29nNWoxMGt0dTNIdm9KR1dma3Q4WmhJMlMxSC1FMVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1147" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1147" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1148" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Ouest-France</t>
+        </is>
+      </c>
+      <c r="D1148" s="10" t="inlineStr">
+        <is>
+          <t>L’ex-Premier ministre et candidat à la présidentielle, Gabriel Attal, attendu en visite à la Foire du Mans</t>
+        </is>
+      </c>
+      <c r="E1148" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxOSE5WRlVIX3VSZlVGdEUwNmdYaFYxenJiOFFsUmdKVjB4cXF3T3NiM1d1aXZicUVHX29rcGxORkxZdU83ZmNBRWFCYXpfalBSdUIzUUpnN055bkxYWFNmZGVLZEFGbW1iQmRzd0Zhd2R0a2VOSUU0UGxPLVpfd01iSmJxcm5SeWlncHNKaDlWcFZvQlVXUUdEb3RGXzFVR1pnYUhSQUJYOUhYYTVjSUk4SkNyeHh2TWluUzRTdVB3MXZ6bjZwWTJ6WGcxMWZJZHA3SGFnRG92Q2lybGdtRWxMck1CRUxWNDFHblZXMm9ZRDA3OFBLNWNxRzF5MjJSWmVYbHpaeTVjeVA1LThpd18wYWlrd1MwNG1JYmlCRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1148" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1148" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1149" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1149" s="14" t="inlineStr">
+        <is>
+          <t>20 Minutes</t>
+        </is>
+      </c>
+      <c r="D1149" s="15" t="inlineStr">
+        <is>
+          <t>L’ex-judokate Céline Géraud devient responsable de la com de Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="E1149" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQV1VWVUJXRFRFOWtmZ1AxR1hKN2Z1YUlISEgtVno1RkZlSmI0ckZMWEdUWUhab1hfU0ZsdENwTDRYNHhhSjA4OVdpMVhQNnY0bFlfd0Fkd1hiSnZtRzlyMHFkWHdnd2JpNDluSnRvdTdMbnRaR0ZSTExjZE01RURUSmJOOV9rcU91VU1wek5Ob3pZMjFDcFQyWlY0eG92Y1ROVDZicTF3aXozSHNIUWtuNnZHUnl4d0JZQ25NMlluSTJGeFpsaFNmY0pHaUFjQUI1RkV6ZTh4emZlMlB1VXFyTE9VUnBvZXlrWnZz?oc=5</t>
+        </is>
+      </c>
+      <c r="F1149" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1149" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1150" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Ouest-France</t>
+        </is>
+      </c>
+      <c r="D1150" s="10" t="inlineStr">
+        <is>
+          <t>Gabriel Attal, candidat à l’élection présidentielle, est attendu à la Foire du Mans</t>
+        </is>
+      </c>
+      <c r="E1150" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxOVUYyM2lweWxkeDJjSzhFRV8zXzljVGdxdDVORVhLTDVwM2FBQTdhNF80cjl5aGxUY3hZS012N2JvY3Z2OGcwckFrcVBTczEtU1hfWnBhaEhQMV9nYkRFVWQ4eTlMd2pwUUZoTkwybEdjNVFYMFJxb3MwSnlRckZuby1fOFpvc0VUMFFxWTlzTnNMWExseEJ0Wjl0dEVrdTRmeW8tUThiUWRPYnFPczNnYnp2QzZYX0NJUmNHdDFQbHByVWItQzYtamprOWw2d0lsZTlyUENQZG9iZXYxVkI4eV9DNExFanlTOXN4N3FKZlNlRkJFS0wxT3F3X3FHdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1150" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1150" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1151" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1151" s="14" t="inlineStr">
+        <is>
+          <t>sudouest.fr</t>
+        </is>
+      </c>
+      <c r="D1151" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : le maire de Bordeaux Thomas Cazenave dans l’équipe de campagne de Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="E1151" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPcjdYWVVYVlZ1amFOeVE2eFlWb3pPYmxXTHR4UFdod3pUQ2lYRExCQU0ybjhfMzY4NHNDdUVCTWZPUWVtZVdwTS1GV2ZaNndDNkR1MjIxWHRkV1lZUFdzWlE0RVN1NWM5c3VSTUtyZWVLOXFGUmczOUt3a28wM19iZXJkUV8xOTJ0UERjTktIekhhM0lHTGxIR3VxSnRqT1laUm03Z2M2aE11WGx5VTlNZUVueUlCc1c4TG11VW5lRkZFbDFxZVJtVGdzU3RsWjg3eU5nMzk0VmhCdzNiX3NlbnpYWm54Xzdx?oc=5</t>
+        </is>
+      </c>
+      <c r="F1151" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1151" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1152" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>ici.fr</t>
+        </is>
+      </c>
+      <c r="D1152" s="10" t="inlineStr">
+        <is>
+          <t>Le maire de Bordeaux Thomas Cazenave dans l'équipe de campagne de Gabriel Attal pour l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E1152" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNa2pfN0hiQ2VzS0o2amNYc3lmNjVKSWF0c3d0QV9GYnVsdjdJRHhyeWMxZXV3VnNmRFlKU2tES0tUTmJYa0t3RGZlaHZvcHdBdFRTVnVCdkxIdDBRQ19fQlhLQVV0bTM1WkhKM1dWdDJXTmxBQS1ST1RNTnFKR3BfYVlVZ1pUck1NZmtpX0VTQWRXd3ZoWVk2dGJiMW0ydHZRX2NJSlcwejZiZlZuZEtiSmpQNUpSLTFvc190SHdGdnc5WUhyUER4dm5EMlM2elpTT0dSM0Z2dmJ0V2pHZ3pmbE5fOF9ldkk3THYza1FpOVMyU2RFbWQyRDV0cTd0bHJ6UzF4cUVQaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1152" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1152" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1153" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1153" s="14" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D1153" s="15" t="inlineStr">
+        <is>
+          <t>«Un renouvellement des visages» : Gabriel Attal présente son équipe de campagne pour 2027</t>
+        </is>
+      </c>
+      <c r="E1153" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxObDh2d1NwTkduR0tPZTd2aE5tSkw5Zkc2SmQ2cFRJd2NTUkRrV05fTy14NVdlYWlnRklodllxbDVHRnFMTDR1OEpubHc2eFJZenJNUHYtcXFzaDh1bVJRNUN4WGJuWTBwTVBHZzA0VmxXU25LX05vME1naWEtWGl4akxQVXhyM3BmZXR4Rm1XcjZKYW05QnB0eml1a0t3N1hNMV9UcUxOdWFhTW5NbTJYV2tQQU9OR1N3aHM40gHAAUFVX3lxTE5QY0xrLTh6N0J4TFhKNkg0NVYtczZvbVY1VWREdHJLZkNaYjFVQ2ZBWVB1Tk1kTkZUZGtqQjVaV1NfWVh1dmJ6R1N5THJrNkNFUkVjUnMwY3JCWU1xa3M3Rl90Rmdid2g4Sllya2d3RGtYZWNYZ3M2cGxnOGR1ek5uNXVOZlBCZGhfeDV6S192eEVSWGwxMDE5dVJzSVA1T004bmRZaUQySlJjOGg3UVExSjgyc2NnWnAxNXA5emtxUw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1153" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1153" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1154" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Le Gorafi.fr Gorafi News Network</t>
+        </is>
+      </c>
+      <c r="D1154" s="10" t="inlineStr">
+        <is>
+          <t>Gabriel Attal propose de réduire la durée d’indemnisation chômage à 72 heures</t>
+        </is>
+      </c>
+      <c r="E1154" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiR0FVX3lxTFBQdGJKeWhzdnBlUUV2NHlNS2dpTUhxSTMtclFGdlA2ZV9wc0NBcmJxMVd0MUswOGdfTmoySS0zRmZ5eUdKWEJJ0gG6AUFVX3lxTFA5ekRyTUI4a1BCT1JSeUxuVnN5M3F4bTB2dzB4aWVSOEptZXZ3WHhGWWp2TnVHMlg2di04Y1MyMl91dl9qclkwRWJlR1ZaaWVNMTN3YWpMemh2amdkS2xkQlBFN3JjUjdkaFdNV0xfbV92NkZ3VjRRN1VDVmZPMzJQVnpPamFLNFpFbll1NnJ1eDFCZnNqYThaRVNiZHYxUWpHS2lhUXBKTFh2dXJ6d2FMQ1Y2YzVGU3lBUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1154" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1154" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1155" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1155" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1155" s="15" t="inlineStr">
+        <is>
+          <t>"Je n'ai pas le même projet que celui d'Edouard Phiippe, sinon je serais au premier plan de son meeting" assure Gabriel Attal, candidat à la présidentielle 2027</t>
+        </is>
+      </c>
+      <c r="E1155" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwJBVV95cUxNMHFaOXBYdFZxdW9VQUJ4MUpyNTZOTFlVS21DT2NQbGNEQ0NublZLN0ozcHFOcVJsVTZPajdEZmxNeTJCQ3BHZjVrdmlHTW5IaGU5MGMwZTZwNEpUZ1A1dlBKVlV1a2JoWXhsamtBZnZBQ252aTdudTRFRGE2QkVGOW5XQ0JpbU93dmZSdFdYMmZISmhINXBiMlBjSHBLMks4WEFLQThEMjJnWDV6RXJHQU5KY09kTVdESmhMb25CamY2VWQzRmdISjRpaXVEc1JqalNtTlVKZEVTUXA4UHRWMmZPYXowb0FobVFaSGszWG1BaXNrRWxkTkFSX095eWk4WmV1SXR5T2EwcTIwUno0RHBpN2dBMUZkaklVMjNxMm9oUkxxNlNZd2JsamtfVmp2RTFvRUR3eUF1SU0?oc=5</t>
+        </is>
+      </c>
+      <c r="F1155" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1155" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1156" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D1156" s="10" t="inlineStr">
+        <is>
+          <t>Retailleau charge l’Etat de droit, Attal et Philippe temporisent</t>
+        </is>
+      </c>
+      <c r="E1156" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNdFVsUzBYX3dyZ21TelJ2aXVyRFgtNk9EeE5ITFRwN0J5S3FPTmZKWko4X2lzdGJaWWdpMVBXOUFuWjVKSFNGNkcwbjAtbFgtSU1POGtacnlhRHYyWi1zMlI5azZmeWtZMXdIX09DLXlPcnFSUGtYa0hyT293TTdVMWFFT3VqSldqd0Q4QUhLb043eXFnU1ZFRVd3V1I?oc=5</t>
+        </is>
+      </c>
+      <c r="F1156" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1156" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1157" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1157" s="14" t="inlineStr">
+        <is>
+          <t>Contexte</t>
+        </is>
+      </c>
+      <c r="D1157" s="15" t="inlineStr">
+        <is>
+          <t>[Présidentielle 2027] Gabriel Attal dévoile une partie de son équipe de campagne</t>
+        </is>
+      </c>
+      <c r="E1157" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPZ2tfLWEzMmNwcmt0QmhVaXc3Y2RlazZkckxkcmZ2cmZuNDJXQjhTcG9mTzBmempxcTFxcjVLajNZR3JaeUZ6Q0VtYkdYMHlUWEVaX2s1VTVrNjdMbkJtTnZVLWZXZGh3bWdVaHZQR3Q1bWR1SGQzbEhnMEc2MW1aMnh4Szlkdm42WUk3RXZ4bG93SGJsZzhNQnYyOTAtU3RZekh3M0hWQkFTLU0xOV9JTHN3?oc=5</t>
+        </is>
+      </c>
+      <c r="F1157" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1157" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1158" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>ladepeche.fr</t>
+        </is>
+      </c>
+      <c r="D1158" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Le Pen en tête, Philippe et Attal décrochent et Glucksmann progresse dans l'opinion</t>
+        </is>
+      </c>
+      <c r="E1158" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPd2hYc0pwZFVpSTdSOHFfTDF3Rm9lc0tzMFEzVXpDM0w1azhYS0Q0Z0FlT21TRkFjM2hEWGF6SEpNMm1qYTBLaGpzd0ZKc3RHRnlZSV8xY184el9XOFMwb2JNRkZxY3JJcnI3OUJkdGpWTXUwM3ZPZ3pRcXlTNXRoLWozQk5FRlczRTJadzVPd0RiTnVJUlZtN3dYVVkxSC1qaUgzdlNDWlNKSFMzdi1iVTJEcWdFUXhaMG9HaTNTQU1YN2o0Zno1WFBIUUIxVWFlMS1YYVhlbTNrMU96ekROZWdnNlQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1158" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1158" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1159" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1159" s="14" t="inlineStr">
+        <is>
+          <t>liberation.fr</t>
+        </is>
+      </c>
+      <c r="D1159" s="15" t="inlineStr">
+        <is>
+          <t>Faute de soutiens de poids, Attal présente son équipe de campagne</t>
+        </is>
+      </c>
+      <c r="E1159" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQZEVOSl9URDI0MzE5cS1nVXJDRGdWT1FueXdaNElHMXdQRVloaWhNMkhSbnNrSGVUdzJzQVpqU1Z2Um4xOUFuQjFJNF9va1FVc254a1gzQ1BTWnlVRTk5YjFPSkViblR3VXFWbzNTMnB0RlVZZXpzbUlhX1dVem9tMnFkbTNCaDc2Nko3eHpKbVNyR0E1RnBfUUxyYUlvYmlVNGd1WmtHSEVmdmphMWdiSHp1aTNDZEtpTTV2QnI3eHAzWUxtZm9iMzBlVnUxcEttaFBqNElCMGVuRklfcHJ0Yw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1159" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1159" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1160" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Le Parisien</t>
+        </is>
+      </c>
+      <c r="D1160" s="10" t="inlineStr">
+        <is>
+          <t>« On renouvelle à mort ! » : Attal s’entoure de nouveaux visages</t>
+        </is>
+      </c>
+      <c r="E1160" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOUWNHV2k2MVcxQ3FIaTJDSm5sbHRWRVcyZkxxRzA3dDlCb1RwemVNZ2pJWTRQZ0FySGJzeDd3Z0N2UkszV1RXaE50djQ0ekhXZEhsZllBWkRSRHFsS3IwdmNlZF96dkRoMmVoUDJJazQ4dERObXl2bDdlLU1lZGFVcVg5SFdNV0JtZlllNE1zX1M4b0JGMkthaVkwdzFGVEJqVXlLbVpTMzJ4UXVCRV9jX3pTTFljcnA3M25fSG9ZSVk0Z2E2R0Z2SDczWG5NRDc1ZEZWUnhCaEdtOGNQeDhlMXZR?oc=5</t>
+        </is>
+      </c>
+      <c r="F1160" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1160" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1161" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1161" s="14" t="inlineStr">
+        <is>
+          <t>Gala</t>
+        </is>
+      </c>
+      <c r="D1161" s="15" t="inlineStr">
+        <is>
+          <t>“J’ai l’impression de débuter une 3e vie” : Céline Géraud rejoint l’équipe de Gabriel Attal, l’ex-journaliste de France 2 explique les raisons de son choix</t>
+        </is>
+      </c>
+      <c r="E1161" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAJBVV95cUxQWTRsVW00c1kwWVcxM3huNHNkMTk5WGp6T1QxOVNKMTZwZlNHWTMxc1pPelVMMjZzTjlHQXVEenFLSndJTWFvajh4MDNWOXVkM1R5dDRva3ZLcUZ3cnNkVnVRZHFNcnVYNlNGdUNiZVNidjVnM2NFOHpZYXZ6WF82dVNLVndtQ0dBV2l2SHpUZnNHZXE4c2E5eFB2ZkRWcTF3WGo1b0d1dUYybXdxTU53Qll0V0JsVDJUMjhsM3h0OFZwbkdBNUFMZGlNTjc2dnFXRUZnNy1Cb0JINmRkdVFfN2tzM1ZBOGtPYk9kTDBVeWZkQnpuNlY4QThlZFJzT3h5QVVNTE8wZS1fQm5GNUtmT29NWF84aHJi?oc=5</t>
+        </is>
+      </c>
+      <c r="F1161" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1161" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1162" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D1162" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Attal «assume» de vouloir augmenter le salaire des enseignants via des économies dans la sphère sociale</t>
+        </is>
+      </c>
+      <c r="E1162" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxPTWdKOGE4QTRPdE54VmlLUTd0QlBlTll1VEhOOFpXWldCb0xnZWFKMV9DTXNjaEliLWZKcy1MaUR5TEJITnBraDVGb2VYSk5hbXJnUjNseFZLYmE2bG9RUjhseWMyQWxUZE9IaFZfdUZDSHZ0c2pSMVRBcFg0MHBpVlA5X2dCaTJYQXRLRkRQR2Q0bURLcmp2dkxXTWNkSzN5MTNmVXAyN19BRV9sc3ZZODFrZkdVYlNlWk1wRkFkQ2NBejUwMzAyUUNuSG1Eemp4emlaY3Fta1pnU09NV0twZFE0c3FfSHB4SlhUaXVTU1Z5ZVJZd3BtVUp0a3FhWUVaemFVM1l2UU5GS05z?oc=5</t>
+        </is>
+      </c>
+      <c r="F1162" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1162" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1163" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1163" s="14" t="inlineStr">
+        <is>
+          <t>Le Monde.fr</t>
+        </is>
+      </c>
+      <c r="D1163" s="15" t="inlineStr">
+        <is>
+          <t>Gabriel Attal arrange son bilan budgétaire de 2024 en ce début de campagne présidentielle</t>
+        </is>
+      </c>
+      <c r="E1163" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOQXp0R29FamM3c1kzX0JLZnozaFdydTBXSW9MZ21qam5LSjJ1VlYyZFM0VHllMUxWcjhReUFJU1V0Ykl5enFKd0ZRREI3VEF2YXh6VTBMS091VzA2R3lKbWt6Qm5pcFVtRENOMV8xbHVLRGQ2eEd6ckdJVTA3Mm9kdWljN3dUUmtZMzFGc3F5SzR3dW15cVByZ2tPTEtyZ2lOU0NSem5fZmdFNHUwRGQxNHJob3V4TnpuQXZvSF9fbEgyaHJPSVdRb1hWZk82US03Z2l5NmpOUmlzTDNqdkUzcWdlczlJTWM2ZWdsdFlpZ1ZQS1gxN3BoN3Jn?oc=5</t>
+        </is>
+      </c>
+      <c r="F1163" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="G1163" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1164" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>liberation.fr</t>
+        </is>
+      </c>
+      <c r="D1164" s="10" t="inlineStr">
+        <is>
+          <t>Après deux ans d’expérimentation, l’uniforme rejoint les placards de l’éducation nationale</t>
+        </is>
+      </c>
+      <c r="E1164" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxNZ2NXN0hncnRRaWNXNG5VYklITnVDTDQ3QUFQcXE0Vmo5Nkd1bUFHS1h4STkwRmJVaXJKUU9nSnduZTlCOWJxZWZubXJab2ZKZjM3a0NraXFiT05KdlRYMXBaXzBlZVR6c2djeVVBZ2VCREtLNGZVUWhIdHg5WlMtOVMtaEw3R0lKZWhMZVhaQzhoWTZQVTFOaVFid296OGR2cVJ5VUM3R1BQbG5GN3Bpbmc2cmU2M3VkNV9QTjRPVUFqbmM5bFU4NTdlRnN4ekRQT0tjVzA1Z0NKRWdTMlBKNG9pM3VjTlN6cE9GVU1ZODRTbnFyLXlSYUlXOA?oc=5</t>
+        </is>
+      </c>
+      <c r="F1164" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="G1164" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1165" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1165" s="14" t="inlineStr">
+        <is>
+          <t>corsematin.com</t>
+        </is>
+      </c>
+      <c r="D1165" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Jean-Charles Orsucci intègre l'équipe de campagne de Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="E1165" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNUzNTdlJoMDd0cmFIMGRqNFZJZUJTME5yYzJwMW4zYVg0U0xsTWRRR3VlNnp6aGw0VTZ1WEpJQzgweHRWUWM1VVVJZi02MFpZbnpCU3FkQUxLejBSaTRXOXpFOUhvZGdPcGVzWUs1N1dIaXpOQTBTdmpENVREemdCNGlHVWdwZmRSSElRNEF2TV92NGZqaGZTbWpocV9ZVVRWalBvdHIyOXpwT093SzBDckJQVVRDYzMybk1idzI4XzM0emJHQ2cyVnJuaXNQWXBRQ3VrSEQ4MWlRZFhjTzFWSA?oc=5</t>
+        </is>
+      </c>
+      <c r="F1165" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1165" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1166" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Contexte</t>
+        </is>
+      </c>
+      <c r="D1166" s="10" t="inlineStr">
+        <is>
+          <t>[Les gens] Gabriel Attal choisit trois codirecteurs de campagne</t>
+        </is>
+      </c>
+      <c r="E1166" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNSTVLU0FrdkFOdmdmcWxQTnZqeENHMnlTMm9sUDNiSFk2N2JHYUdaNXlVMHlZN3E2b0F6VmRaZ0hnVFRPQmpkWHY1S09mUkRwbzh3QTBLVFNWUl81eWJneG40b0xDZXF2cVZkY21VT29UUHR6OS1BYnhIck9TSTdIb0tKOTBQZnVWdG11dXlLdXE3bXFYTDM5a2FfQV9UOVhRdmZkdjMzWG1vdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1166" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="G1166" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1167" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1167" s="14" t="inlineStr">
+        <is>
+          <t>franceinfo</t>
+        </is>
+      </c>
+      <c r="D1167" s="15" t="inlineStr">
+        <is>
+          <t>Marine Le Pen se sépare de son conseiller économique dans la course pour l'élection présidentielle</t>
+        </is>
+      </c>
+      <c r="E1167" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNQU04VXlha2JKdHJBRnJiOGRkYWJmdl8tNFFCSjgtU0NUU3h1WTBBVDNQTTYyeXNCZk84dTFCUFhXWDVGbnFxSHBYMXdLdHpvMmRaeXhZYV9vTnB3Z2IwOE00YlNYVnNoS2U1cTU4a2FIZXFRNEJ3NnVPSUxzRTRzSFVQdUlabmFUczNYTUpCYXBxXzZfcm85ZWJMOUZrMVlLQjBRZVZMbW9WS2txUFVjVjd0VWhsUFJxdm1KcTUxSUt6TEI0UElKdlpodHY3NmZzTFJtLUZELXJ1ZnBJSUx2QjBUSlJUN1QtZVBqeVBqZWc2NG1M?oc=5</t>
+        </is>
+      </c>
+      <c r="F1167" s="12" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="G1167" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1168" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D1168" s="10" t="inlineStr">
+        <is>
+          <t>Procès des assistants parlementaires : Marine Le Pen a jusqu'au 15 octobre pour présenter sa défense</t>
+        </is>
+      </c>
+      <c r="E1168" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNaGtMNXZhNUQ3SjN1WS02dlY0azZvVWh6UWlIZ29MZEJHaWVVU2xfSndMYkNTYUNwRFdnRVNlTGU4cTJrMk9KaEpxazVrVXFFcWIxX21Hck5VZ1Frb18wM1dSRFBfRnZMM2RyQ0c3R1UzQll6SkJsM2tYOXpod08zMlA2Q19UZUhkLXdZQ09OdUNJaU5MNUo0c0FPUWhockEta1FoS3NaSVZZbFE0WUllNDJFYUNrazd4WEVpYXVUUmIxbWlkOUZTSnloZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1168" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1168" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1169" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1169" s="14" t="inlineStr">
+        <is>
+          <t>l'Opinion</t>
+        </is>
+      </c>
+      <c r="D1169" s="15" t="inlineStr">
+        <is>
+          <t>Le compte à rebours judiciaire est relancé pour Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="E1169" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNM0FDU05QOUwwUVpRQktXNFU3dWE5TlROSEZ3RUhJc2VmZDJXRDZKRFZRLWUxU1pGSGdKWVNTOTgtcTJZY3hBVzNzamp3MzBOUmtOZ3NYSk92RGpCZlRnbXdTNUVqVEg1dkxKV1k4V1JZbWFjUUlqRUItdmIyWXppY2JHTWNwZUxwMG5QS1VJbmNVMVNFWGpBTWVkTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1169" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="G1169" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1170" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Europe 1</t>
+        </is>
+      </c>
+      <c r="D1170" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : «Si Marine Le Pen est élue, il y aura une onde de choc jamais vue dans le pays», estime Sébastien Lignier</t>
+        </is>
+      </c>
+      <c r="E1170" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNN2ZaZ01XVWp1VGNRMHZ5NWsxUDkzWUdveUVseGtnbi14S2pDcVlpRUM1YWszVnNLcV9tUWZCRVhDa055NURvRWJYVGtFZEl1N29JNkJEdjYtQXhJUGdYTktJRW9VeVhQODBfT3FTZGFRLW5ZeFRWSHZYcWROeUlIcm4tODZOTVp6UDFtZVVjd2NnUFZqNUMwUkJRa2lNNm1Dbi0tRnJCUDJpSlJyWklpWmlzVW5uVE9NOFNTeDZyOFJsWWVMODJwRldwemRqRWRiSTByOWREYjR6THJZNV9xQTl4bEx5WmxWMTJZUEhKV0FWdFVv0gH6AUFVX3lxTE55QnZ2LVVGZXVoM0NZQmRadVBfQmFveks0S1JyWXBIZHc4cUdwUXFQdUtTemhibXdfYkFDN18yRjktOGF3MzAwWlc0bDAwd3gwemFXaGtybnc1NTVBNG1KaHg3N3dVSklOYzZnTm1mM01JbG1LU2N4dm00ZkRlWEl4bi1McktNdE5pYkpmY1poTzFFNzFvTTdMSDU3WDBZNzExamhPaU5obGZSOFlBSTZCdXNIQzJtM3ZYT290NV9KMUdHOGM5WGtIcGRKNEVPc0QtcE90THk4bjBwRm5nTGU0M0RUeXNyenlicHZCQjR6amtHdlp4Um1sTVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1170" s="8" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G1170" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1171" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1171" s="14" t="inlineStr">
+        <is>
+          <t>lepoint.fr</t>
+        </is>
+      </c>
+      <c r="D1171" s="15" t="inlineStr">
+        <is>
+          <t>Le Pen-Bardella, de l’eau dans le gaz ?</t>
+        </is>
+      </c>
+      <c r="E1171" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQRF9oVFFmWmtveEw5emlqdm1BT3RuYmxSQTBHTzcwVndWQWJBcExLN0Y1Z1BoVlY2Z05DNTVFeWZLTVl0UTZBOWJWdWstQ210dHU0Ynh2dDJfOUVfenZucnJvLWotMUZuU0FVZXNGeVlWclNha2dlb2tkeW9TVngzSm1xSnJmOW0zMDJnUFhncWZHM3hHdzlMR29DdDE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1171" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1171" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1172" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>L'Humanité</t>
+        </is>
+      </c>
+      <c r="D1172" s="10" t="inlineStr">
+        <is>
+          <t>Bardella / Le Pen : l'extrême droite commence-t-elle à se diviser ?</t>
+        </is>
+      </c>
+      <c r="E1172" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOQ1g4QUJ6Rk95SUhlWjNLLWZhNTVGWDltTGxPNVBDZWR0a2tOQWh4MnpoVXNUeFpCVUE3dzMzRzhLOVpaTTZ0aXNnUkZOZUFGWFB3VHRNSDliYm50YjlJVkdzRzZXYU5QTUFVdjZENjEwa1FSV2FNdjNJckNzN19tVmlwV0hXZGI1c2kzWFJHVlEwMWpyUVlkcFhDWVp2eWphTlZKX3ZFUlVKdUJZUXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F1172" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1172" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1173" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1173" s="14" t="inlineStr">
+        <is>
+          <t>L'Indépendant</t>
+        </is>
+      </c>
+      <c r="D1173" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Marine Le Pen a rassemblé 400 parrainages, Jean-Luc Mélenchon à peine 200... Les 500 signatures nécessaires à chaque candidat, "une mauvaise procédure" pour l'élection</t>
+        </is>
+      </c>
+      <c r="E1173" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxQLVlIWmtqQ3cyVE5LM2NPc2dRX0FzV3Jrb3ZuTUJOUXVlOEg5N2M1cEltMDV0U01NOTIxRGJPb21SODNCZ3I2TFM2UVhsOUh3ZHlaRnZRWHdLSWl5a2xickpwdlFHVVVtTFFZSzNTZmRwOUJMbkQzN21DLXhkTmtKc3E5dnM2bUtCMTRrbl81RHZJNTJMeTZvd3htMmpyZEVfX3dfcFpwUWR6UDViNnRnV2ZHNmlBUzJXZzlnR3VNbkpEeUpmdnp5bHlDaU1ReE1qZjBHUDMxUS10ZzZoZGZCVmM2N2hzTXZLOV9VM3ZBcm4xenBTNXdDcTdRTV9QTlUxYndlZGVaZWJrcHFqc3N0SlZ4VmZWZy1fUW9TRGJUVUFnc2s?oc=5</t>
+        </is>
+      </c>
+      <c r="F1173" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1173" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1174" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>parismatch.com</t>
+        </is>
+      </c>
+      <c r="D1174" s="10" t="inlineStr">
+        <is>
+          <t>« Je pensais que c'était la loge du patron du Medef, mais c'était celle de Marine Le Pen ! »</t>
+        </is>
+      </c>
+      <c r="E1174" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPTmxfZWYxYjdWX29qdl91ODhmQkp1Uk9MTDBtU0k1OTN1TnlORE5qa3pDbWtNMUdSU0xGaFNHbG9haDcyNEZOZlUzSDc4QXFTaDRId2FlMUNmMUQtMWhzaUNPcnBGNjIwTWZwajdOMEFpOUlWYmlsNWMxSHYzRDBxRWt6Z0NERXR4X3VpNVVNc2JBUV9FN1Zvamp4TDdWN0pnZ2daUXlYSDBMOUp3X0s0RjF5R1ZWaU51N1lkXzNZQ1ZMajBiTHFudTZzVU4?oc=5</t>
+        </is>
+      </c>
+      <c r="F1174" s="8" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G1174" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1175" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1175" s="14" t="inlineStr">
+        <is>
+          <t>Le Devoir</t>
+        </is>
+      </c>
+      <c r="D1175" s="15" t="inlineStr">
+        <is>
+          <t>Les candidatures à la présidentielle française se multiplient entre Le Pen et Mélenchon</t>
+        </is>
+      </c>
+      <c r="E1175" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVUY0a1p2bm5DNDdRcmlsaV9fRjVZdklFR1pJQTdzdndGNjJHam1CcGY5ZGdnWTl4VFZVYUVWcVY2dXBoYjR3TEdBa0FTM3BQblZJMlZnMVBwdkZRaC1UTS0zb1REMk90cjh2NzF3S01VUk52SlpFdGhnR0piNUtnelFqemtsdkVqcmFkeEJ3MzdoeEZiRlktNXBxUkt2azVvY1Y3d1ByVmVyTjJtUURZbE9TaWZHdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1175" s="12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="G1175" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1176" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Courrier international</t>
+        </is>
+      </c>
+      <c r="D1176" s="10" t="inlineStr">
+        <is>
+          <t>L’interdiction du port du voile, un “air bien connu du répertoire Le Pen”</t>
+        </is>
+      </c>
+      <c r="E1176" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOWk1lMG9sNGFfZW1hN0ZFT0Z1M21kYkp2bzI2TjBuQWFSSnhCMERudkZRbzktaG13SUpvU1pKNTBHaDJRMS1QZXFaNnpwbGRwcDlfYjkyeUNCYnRoNnVnZnpYQVBZLTdTdlBSUXRRRXZHZ1QzS3NjYlhOVXo4RjdTU3ZLQ3llSmttNUxSdU15c2JZWW84YzlVN0lJeHRfU3B5NE9uWk9fcWhxVUJjS0RncDNBVkFBWkNFc2ZWT1ZEOFp6RU03WmJ0TWpGSExtZmhROXhhZy1Bdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1176" s="8" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G1176" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1177" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1177" s="14" t="inlineStr">
+        <is>
+          <t>CNews</t>
+        </is>
+      </c>
+      <c r="D1177" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : si Marine Le Pen l'emporte, Sarah Knafo n'est pas fermée à l'idée de rejoindre un gouvernement de Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="E1177" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUXJPQVBsXzQ1aGxtNkhxTzNKbUpiT2xzNC1oYkdRczM3cThPaEF0bEEydno5ZE8zanhBUkVJWGMtdWV5UTF5ckQ4M1phbU9vdWFmd3dlS1lEUTFmZ0h3a1ByNG1obUh6NmMtQUdoRnFhd2poc3c2TER1ZUNJcVZSTXdJSU5OMGFKUmpHQW5Ld19zMHdPRUdVYUxRNVM1Qk42bXN2em5YMnpwZkdtY3pfQlpwVUtlOWR2YmfSAb8BQVVfeXFMTVZ1MmctWEItQmVHZzRJdjcySHRKVlpZeS1BZy1sVVpOM3dDbzZoZGEwSDIwRk9rWTY1VW1rdlhvaWJfX005ZE9JVFk4VjdQUTNRMVRWT200Wkdfa25uX0o3Y3FPUjZZVVpYazJ6OUhsNnRTUXJyRGVFUlI5UVE3ZHBTQnFXcTk4NWxPNy1GMEdtdE9fS3cyNlV3WHkxcWY3Z0RFTnlMa09jWUkxTzVyVE14RGZfczBEbHlTMTNqOVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F1177" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="G1177" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1178" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>ladepeche.fr</t>
+        </is>
+      </c>
+      <c r="D1178" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : Le Pen en tête, Philippe et Attal décrochent et Glucksmann progresse dans l'opinion</t>
+        </is>
+      </c>
+      <c r="E1178" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPd2hYc0pwZFVpSTdSOHFfTDF3Rm9lc0tzMFEzVXpDM0w1azhYS0Q0Z0FlT21TRkFjM2hEWGF6SEpNMm1qYTBLaGpzd0ZKc3RHRnlZSV8xY184el9XOFMwb2JNRkZxY3JJcnI3OUJkdGpWTXUwM3ZPZ3pRcXlTNXRoLWozQk5FRlczRTJadzVPd0RiTnVJUlZtN3dYVVkxSC1qaUgzdlNDWlNKSFMzdi1iVTJEcWdFUXhaMG9HaTNTQU1YN2o0Zno1WFBIUUIxVWFlMS1YYVhlbTNrMU96ekROZWdnNlQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1178" s="8" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1178" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1179" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1179" s="14" t="inlineStr">
+        <is>
+          <t>Ouest-France</t>
+        </is>
+      </c>
+      <c r="D1179" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : retraites, voile… Les désaccords au RN peuvent-ils fragiliser la campagne de Marine Le Pen ?</t>
+        </is>
+      </c>
+      <c r="E1179" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxQZUViaUh1SDRtcC1uMWFVci0zbmlqS2tVYkl4MXprYUFnSkE0T01uSlZMVWxud0FrN21ldW9CSGZYYTZSQ25ieXIzNHBmTFFGbVU1VUZGU3RuRlpScFdOdXlaNjI5b1cxaWlIUHh3WWptMXBNYnlhcEoxN1lvRG9VQi1uNnJVVFRPbWNIOUFoSzFaMUd5eF95NkN6WnZtMHFBSnRQTFo5dzhncnNnUzI4cEY5djR4bjVESnBjUEpDa0VzRVhFUkNzVFdfWnBGbGNpdWs2Nmp1R05ITWdZT1htX3pyZEZDNE1vYzNtUllXeVZPWU16U3AxQzN5MVdPNERPUVZPdmtoUEVaUE0zb1o5Zm5oSFFabDVDUkFBQjFHRmhwdDJzTG82ZnB5azJ4bVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F1179" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1179" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1180" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Le Figaro</t>
+        </is>
+      </c>
+      <c r="D1180" s="10" t="inlineStr">
+        <is>
+          <t>Le RN souhaite «sanctionner» le port du voile dans l’espace public par «une amende»</t>
+        </is>
+      </c>
+      <c r="E1180" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPN0pYN3NvaVR3Nm11eVFfaE5lcFVqODg0bG1fNzBJd250U0tibVE4X1hXaTlRb2Iza2wtWU1mNlozS000NFVQdVpLX1BlcXJwbEphNmg4ekwtTWowNHRGSndEaWpHM3Q2RER3eUVCX3F3TDhKWlE0T2VqZ2pKRTZmYWw4Q2ZkZEFRRFFuM3BnTVBNa3hkOW13RlI1RkY2UFFYNHRZd2IteGEyUWVxamFvUzFEa0xkcHA2dUNCeDdyWlFQRS1qNTJSLXZvQ05iemRuNUp0cA?oc=5</t>
+        </is>
+      </c>
+      <c r="F1180" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1180" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1181" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1181" s="14" t="inlineStr">
+        <is>
+          <t>Marianne</t>
+        </is>
+      </c>
+      <c r="D1181" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : face à Marine Le Pen et Jean-Luc Mélenchon, la France du double barrage</t>
+        </is>
+      </c>
+      <c r="E1181" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNUWtxUzJBOUUtdHptc3cySERLRF9XLXI5Sk1UbHU2TzVpZkVqbmpGTVd1UndPcHlacVFVLXdRV3FTVGZwU3RwUDQ2c1VzdFI2TEl1WmdmZ3NhNVdpVlprQVJlV05lbTJPb2xWVkdCQ1dueE50RnczOGRuOGtoQVhtX0ZsdDk0a2t0WkwzVE9RaUNRS1l5a3N0bENCV0cxa0NMWUUtOGNRelRUUFkyQld4cVpZZWV4ZFE5Z0JJRVdIOTNpNTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F1181" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1181" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1182" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>lepoint.fr</t>
+        </is>
+      </c>
+      <c r="D1182" s="10" t="inlineStr">
+        <is>
+          <t>« Il a eu le sentiment de ne servir à rien » : au RN, derrière le départ de François Durvye, la reprise en main de Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="E1182" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOeGtPX1lvdUI4YWl2d2tBLUNaWHVpb2xnaWQtd0s3WDlTS252OVMwenhtQkpNTWUyVF9NQlJKcmc5OGJVM0VBRUZ0ZDlvaUlDLXltOGhNYWxnRHZsNHJXNk1WZ0R0YzNTRGxsTThESzhSQVJzdllzUUttcDZYd0ZCQ0RRenFFZVctOVd1bENkOUU5OFhmbHUzREJxcV9KRHhINVlEcTYzR3BTZzJiWDA3NkVmSE1nM1hwazhabHJybkJTVll3bW1mUEJPV1R3b3c4djN6cmJRU3l5VU5hSjZRbHp1SzBiSU81cnVXSFgxOGI?oc=5</t>
+        </is>
+      </c>
+      <c r="F1182" s="8" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G1182" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1183" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1183" s="14" t="inlineStr">
+        <is>
+          <t>BFM</t>
+        </is>
+      </c>
+      <c r="D1183" s="15" t="inlineStr">
+        <is>
+          <t>"Il n'entend pas faire la potiche": quelle place occupera Jordan Bardella dans la campagne présidentielle de Marine Le Pen?</t>
+        </is>
+      </c>
+      <c r="E1183" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQN1FKX0Nfb25ZeTc3TndOdVAxb2VCRkF5RXFLbEJ1QUlndzBwOURzSjh1elltbWlmQUFGNGJWNzBfbDVPdzJfWms2WjhieVI4Q05SWDY1UjYzVUEzOXdXNTJncTJDWTZ3Y1NUcTl6cVhOMnN0TEFCWHBiR3pNbEwtT1Q3QUxGNnRMTTdfMXhjSlptWXpSSnJTaFQ1ekxaNUg4TDE0YVp1TTVOV0ZfekZGT2VER3ZyY0tHMmh5VDBKZEw4UDJmMVpPcFRJWjJQYUZEdTlQUEVvUU1BNlVnZmM4Ri1RVVRtZmpHVk1BU0ZsbDUyQjdKWGw3RnJWTVlxUkRUejVXU2NSbmtxdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F1183" s="12" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G1183" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1184" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Le Club de Mediapart</t>
+        </is>
+      </c>
+      <c r="D1184" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle : la victoire de Marine Le Pen peut tout tourner au cauchemar</t>
+        </is>
+      </c>
+      <c r="E1184" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNQ3JQTTdrZmYtNjBhSWotSmNCUEc3anFGVDQtY2tFUHk0YV9mZVdNYmc5RTNEQlQxYWVWNWZmT2lhUHNkMUtlSnRENWpjY0J2RFNyTmhmdGFoVG9IaDVJX2NOSl9kUW1VenJZVjZacmlXcGdWb19rd0NxckY3bGF2ck1lbzZsLW9qOGFaSXVoOEJzajY1YnZjTWdma29kRWswYm9HbGxnNi1uYnpVQ3NKNUV6cWxWMWc0VWg3UmR3eno0NEFDZkJYZkRsSHIzRURoeUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1184" s="8" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="G1184" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1185" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1185" s="14" t="inlineStr">
+        <is>
+          <t>Le Parisien</t>
+        </is>
+      </c>
+      <c r="D1185" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : le RN reparle de l’interdiction du port du voile… au risque de se rediaboliser</t>
+        </is>
+      </c>
+      <c r="E1185" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxQMGxpTVh0cVkzR2p4S3JlRFBVTmsycHhGV2lTNjY2b0FqOExwOHpJbnl0Ny1DY2s5SHNlSk95bEloMHcxRzR3Nnc5ZWZ2cjlrQzk5bEJHLV9UVktHLWlsMHNpUTJVbVMxNlpVVzFGODVLZDFza0tfU1JDWk02bzVadU1oSEo5X3dnVHNCYlAtLUhLbFhuenVMT00tcE5abFZkN1VyYzgyZUo4S1ZEWnEzN09WWkpzME52X3ZvWV81cDk0RUY4bUtudUtNVGxOeUdDb3d6ZVlNUml4SWZ6SGUwcUF6Wk01ZjZkekFhaHVBTFp5dlFDaWM4X1JEVTJYZEdjUUlEckpyd1FsTTBid2dsRHZSSW51VDBPbmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F1185" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1185" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1186" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Radio France</t>
+        </is>
+      </c>
+      <c r="D1186" s="10" t="inlineStr">
+        <is>
+          <t>Le RN prévoit un référendum sur l’interdiction du port du voile en cas de victoire à la présidentielle</t>
+        </is>
+      </c>
+      <c r="E1186" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNSDZvQmNHVnZ5M05PMFliYngycEdnS05wZy1ySlNZZF9HYVl6cnpncWRLbENxWmFUbHpLMFBQUmY0SFJVUUJ6eFJJQ2RjLUtYVkNCMU9qelY0OWVabkJHYktYQUxNTXZnVnRnbExYaERJaXRxMWVBNzdONVJLUnJjb2dUMC1jaTFuRUxmLWJSYjByeFhGMU1fY3FwaTFVWGFiTDVtVHVKUkNQblhESTdHZDdPazRjb3gz?oc=5</t>
+        </is>
+      </c>
+      <c r="F1186" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1186" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1187" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1187" s="14" t="inlineStr">
+        <is>
+          <t>TF1 Info</t>
+        </is>
+      </c>
+      <c r="D1187" s="15" t="inlineStr">
+        <is>
+          <t>Parrainages pour l'élection présidentielle : Jean-Luc Mélenchon et Marine Le Pen "font semblant d'avoir peur", estime sur LCI Christophe Barbier</t>
+        </is>
+      </c>
+      <c r="E1187" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxQdlowcmptR2l6UWJkaklqRU96TFRyZXQ5U2REOVdFTmxKNXJoUlZJUkZzaEQtdm1uaTRWSno4R1hCTU81a0FNaHppQWM2Vi1VUFNCN1IybS1wWUNsX20zWjFhcHE0Q1dqeHZUcHdLd1lQYjhibm41ckJkTWdPMTctRm1ESDkxUk93NEpHYW1yWW1DVC1TcjJxUVZEUnI3S1ZkOXhHWnQxdVZqdnVkTkxHc2xxWEJudGFvRmt2SHVrYmJGOXVXeThQSDhwWDVkQVlMWHFCYkU0eTlDNEJQSkpreThJbFp6enNtMTA5OFE0akpnU0JxSVQ3MUtEMTYtRzJBbC1pb2xNeWJSTl9WY3RkMQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F1187" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G1187" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1188" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Public Sénat</t>
+        </is>
+      </c>
+      <c r="D1188" s="10" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : que proposent les candidats pour l’école ?</t>
+        </is>
+      </c>
+      <c r="E1188" s="11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPbWNSc056ZllXUE5DVWRyb3BoLVprSkRMNWw0NWYwa3VkcFc1T0hIZ19TbmxoYlhyTFkwNW5EUFYxWUFBMkpWbEV1eE5Xak83NGNWeDl3Y0FlRHUtWV9XaFhvckU1UTQ0bm92OF9UOERFRFBGMnZMczlLNG1PbnB1U2FnT3lrM2phLTNzMElqQ3M2SldDd1doWkpsMW56R0tqYnJvNlZSTG42ZkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F1188" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1188" s="8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B1189" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C1189" s="14" t="inlineStr">
+        <is>
+          <t>Boursorama</t>
+        </is>
+      </c>
+      <c r="D1189" s="15" t="inlineStr">
+        <is>
+          <t>Présidentielle 2027 : face à l'hypothèse d'un duel Mélenchon-Le Pen au second tour, les appels à une primaire</t>
+        </is>
+      </c>
+      <c r="E1189" s="16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wJBVV95cUxOOUlwejRTaHB6UmJWeFpscGtmWTY5QVVqOEdfVl9ESUdUeHQzbldyN0taWXB4elRiMGtJVzBKM3RvUklzNHJnZG1hbERlcGZxSzc1NTZRS3pKS0xWT3dmVkpydTFkazl2YklpWmN4Um9YM1haZFphOWRFazlKamd3OTlCZTEzZktVRUx6b0NQYjFCYzNHMDltWXJrLWRMbTBTV2pRSXE0ekM5RWVtN2RxUkoyUUVWRl9LSzEzUXJxa0R1d01LRGM2NERKUHRpSmQ0TkUycFk4Mnl5LW5BZkFnal9oMF9uZWxubmZidEw0VWNHcERxUG9nVGNYeXZtcUpOZzNka21DZXozaS1DTEU3MHR4QURHNXNBV3I1N0xRZVBIYlE0TXplSkhwUjV6cnd0cHJ0ZnRfem5DRVZZSnQ0bjFjWlpUcGh6Vjc1WXlSb2k2Vl9lNGt0QjdhSdIB4AJBVV95cUxNVGJYNFpRZEpUQjl0UTc0S21WS1FuZjdlZFNPSnIxUm54Nnh3cFVDcF9Pa28ycG5QYVR3b2dubHRwMW5CdktfaG4yM1EtZG9RZkZ3Z1dLSndJRVVzSGZkV2VLUXY0MXFNQ053cDFlYU4tS2IwdFhKeXpWWWpWbGpVZG5tR1cza2F4bkV2UVdOcnljdjlZdzV3TjNKWFA4OEloRzBCSjk1U2JMT3l6VnRGcG0zMkhVN0tUdFlWNTI1cTczeWRMYjg2dzFZZmxSbHBIdFkxQmVzLXYxRjNka1FXb3FSY2NvVnVUYjJYbDRiOHlTUjFXTDhPbGRoR1ZfNXZlZ2tSUVlKWlJveWNTOWZud0RxVDB3dU5tN1JCelpWMTQ2UU0yY2RvZV8zX0ZZV1Q0TGxDSTZaVlpHSnZZbWxHXzhkNFNiMVhNOUpPd2xHMjZiU1FwRzR2bEJiMnVjd0t1?oc=5</t>
+        </is>
+      </c>
+      <c r="F1189" s="12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="G1189" s="12" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1052"/>
+  <autoFilter ref="A1:G1189"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -41223,6 +46292,143 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1050" r:id="rId1049"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1051" r:id="rId1050"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1052" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1053" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1054" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1055" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1056" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1057" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1058" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1059" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1060" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1061" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1062" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1063" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1064" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1065" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1066" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1067" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1068" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1069" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1070" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1071" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1072" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1073" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1074" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1075" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1076" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1077" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1078" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1079" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1080" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1081" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1082" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1083" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1084" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1085" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1086" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1087" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1088" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1089" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1090" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1091" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1092" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1093" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1094" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1095" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1096" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1097" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1098" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1099" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1100" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1101" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1102" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1103" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1104" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1105" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1106" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1107" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1108" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1109" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1110" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1111" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1112" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1113" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1114" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1115" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1116" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1117" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1118" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1119" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1120" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1121" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1122" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1123" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1124" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1125" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1126" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1127" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1128" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1129" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1130" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1131" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1132" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1133" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1134" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1135" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1136" r:id="rId1135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1137" r:id="rId1136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1138" r:id="rId1137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1139" r:id="rId1138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1140" r:id="rId1139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1141" r:id="rId1140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1142" r:id="rId1141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1143" r:id="rId1142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1144" r:id="rId1143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1145" r:id="rId1144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1146" r:id="rId1145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1147" r:id="rId1146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1148" r:id="rId1147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1149" r:id="rId1148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1150" r:id="rId1149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1151" r:id="rId1150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1152" r:id="rId1151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1153" r:id="rId1152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1154" r:id="rId1153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1155" r:id="rId1154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1156" r:id="rId1155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1157" r:id="rId1156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1158" r:id="rId1157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1159" r:id="rId1158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1160" r:id="rId1159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1161" r:id="rId1160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1162" r:id="rId1161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1163" r:id="rId1162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1164" r:id="rId1163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1165" r:id="rId1164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1166" r:id="rId1165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1167" r:id="rId1166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1168" r:id="rId1167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1169" r:id="rId1168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1170" r:id="rId1169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1171" r:id="rId1170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1172" r:id="rId1171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1173" r:id="rId1172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1174" r:id="rId1173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1175" r:id="rId1174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1176" r:id="rId1175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1177" r:id="rId1176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1178" r:id="rId1177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1179" r:id="rId1178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1180" r:id="rId1179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1181" r:id="rId1180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1182" r:id="rId1181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1183" r:id="rId1182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1184" r:id="rId1183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1185" r:id="rId1184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1186" r:id="rId1185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1187" r:id="rId1186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1188" r:id="rId1187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1189" r:id="rId1188"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41258,7 +46464,7 @@
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>Articles detectes par le radar - GDELT + Google News RSS (secours) - 03/09/2026</t>
+          <t>Articles detectes par le radar - GDELT + Google News RSS (secours) - 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -41328,25 +46534,25 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>185.483870967742</v>
+        <v>105.8823529411764</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H8" s="25" t="n">
-        <v>158.8785046728972</v>
+        <v>166.6666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -41356,25 +46562,25 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>483.3333333333333</v>
+        <v>354.8387096774194</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G9" s="28" t="n">
         <v>12</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>1291.666666666667</v>
+        <v>1358.333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -41384,25 +46590,25 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>118.5185185185185</v>
+        <v>100</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>31</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>506.4516129032258</v>
+        <v>622.5806451612902</v>
       </c>
     </row>
     <row r="11">
@@ -41412,25 +46618,25 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>105</v>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>32.91139240506329</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>188</v>
+      </c>
+      <c r="G11" s="28" t="n">
         <v>17</v>
       </c>
-      <c r="C11" s="29" t="n">
-        <v>109</v>
-      </c>
-      <c r="D11" s="28" t="n">
-        <v>43</v>
-      </c>
-      <c r="E11" s="30" t="n">
-        <v>153.4883720930233</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>156</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>16</v>
-      </c>
       <c r="H11" s="30" t="n">
-        <v>875</v>
+        <v>1005.882352941176</v>
       </c>
     </row>
     <row r="12">
@@ -41440,19 +46646,19 @@
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E12" s="25" t="n">
-        <v>855.5555555555555</v>
+        <v>225.8064516129033</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>0</v>
@@ -41475,7 +46681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -43113,6 +48319,626 @@
         <v>4</v>
       </c>
       <c r="F65" s="40" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C66" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="34" t="inlineStr">
+        <is>
+          <t>Voile islamique : référendum et amende proposés par le RN</t>
+        </is>
+      </c>
+      <c r="E66" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" s="36" t="inlineStr">
+        <is>
+          <t>Le Pen conforte son avance dans les sondages mais doit gérer des tensions internes (départ d'un conseiller économique, relation avec Bardella) tout en relançant la polémique du voile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C67" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" s="38" t="inlineStr">
+        <is>
+          <t>Relation Le Pen-Bardella (tandem, duo, rumeurs de tensions)</t>
+        </is>
+      </c>
+      <c r="E67" s="39" t="n">
+        <v>22</v>
+      </c>
+      <c r="F67" s="40" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C68" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" s="34" t="inlineStr">
+        <is>
+          <t>Programme économique du RN et départ du conseiller économique François Durvye</t>
+        </is>
+      </c>
+      <c r="E68" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="F68" s="36" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C69" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" s="38" t="inlineStr">
+        <is>
+          <t>Sondages présidentielle 2027 : Le Pen large en tête dans tous les scénarios</t>
+        </is>
+      </c>
+      <c r="E69" s="39" t="n">
+        <v>14</v>
+      </c>
+      <c r="F69" s="40" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C70" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D70" s="34" t="inlineStr">
+        <is>
+          <t>Polémique "Fuck Marine Le Pen" à Rock en Seine</t>
+        </is>
+      </c>
+      <c r="E70" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="F70" s="36" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C71" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="38" t="inlineStr">
+        <is>
+          <t>Ralliement de Gérald Darmanin et rentrée à Tourcoing ("les frites")</t>
+        </is>
+      </c>
+      <c r="E71" s="39" t="n">
+        <v>28</v>
+      </c>
+      <c r="F71" s="40" t="inlineStr">
+        <is>
+          <t>Philippe élargit son socle avec le soutien de Darmanin et s'impose comme favori du bloc central, tout en affrontant une concurrence frontale de Gabriel Attal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C72" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" s="34" t="inlineStr">
+        <is>
+          <t>Rivalité avec Gabriel Attal pour le leadership du bloc central</t>
+        </is>
+      </c>
+      <c r="E72" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="F72" s="36" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C73" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" s="38" t="inlineStr">
+        <is>
+          <t>Débat avec François Hollande à Sens</t>
+        </is>
+      </c>
+      <c r="E73" s="39" t="n">
+        <v>14</v>
+      </c>
+      <c r="F73" s="40" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C74" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" s="34" t="inlineStr">
+        <is>
+          <t>Propositions de programme (immigration ferme, 35h, retraites, arrêts de travail)</t>
+        </is>
+      </c>
+      <c r="E74" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="F74" s="36" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C75" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" s="38" t="inlineStr">
+        <is>
+          <t>Stratégie de "nouveau parti" en vue des législatives</t>
+        </is>
+      </c>
+      <c r="E75" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="F75" s="40" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C76" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="34" t="inlineStr">
+        <is>
+          <t>Rivalité avec Édouard Philippe pour le bloc central ("pas des photocopies")</t>
+        </is>
+      </c>
+      <c r="E76" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="F76" s="36" t="inlineStr">
+        <is>
+          <t>Attal structure sa campagne (nouvelle équipe) tout en se démarquant explicitement d'Édouard Philippe et en faisant de l'école un marqueur fort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C77" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" s="38" t="inlineStr">
+        <is>
+          <t>Constitution de son équipe de campagne (Céline Géraud, porte-paroles)</t>
+        </is>
+      </c>
+      <c r="E77" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="F77" s="40" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C78" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" s="34" t="inlineStr">
+        <is>
+          <t>Programme école/éducation (salaires enseignants, lecture, drapeau)</t>
+        </is>
+      </c>
+      <c r="E78" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="F78" s="36" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C79" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D79" s="38" t="inlineStr">
+        <is>
+          <t>Débat économique face aux patrons (Medef)</t>
+        </is>
+      </c>
+      <c r="E79" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="F79" s="40" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C80" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D80" s="34" t="inlineStr">
+        <is>
+          <t>Désaccord avec le RN sur l'interdiction du voile</t>
+        </is>
+      </c>
+      <c r="E80" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F80" s="36" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C81" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="38" t="inlineStr">
+        <is>
+          <t>Programme éducation (internats disciplinaires, fin du collège unique, salaires profs)</t>
+        </is>
+      </c>
+      <c r="E81" s="39" t="n">
+        <v>19</v>
+      </c>
+      <c r="F81" s="40" t="inlineStr">
+        <is>
+          <t>Retailleau tente de relancer une campagne poussive avec des propositions radicales sur l'école et la Constitution, alors que ses sondages restent faibles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C82" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" s="34" t="inlineStr">
+        <is>
+          <t>Rentrée à la Foire de Châlons, campagne sous pression des sondages</t>
+        </is>
+      </c>
+      <c r="E82" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="F82" s="36" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C83" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" s="38" t="inlineStr">
+        <is>
+          <t>Réforme constitutionnelle pour "redonner le dernier mot" au peuple</t>
+        </is>
+      </c>
+      <c r="E83" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="F83" s="40" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C84" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D84" s="34" t="inlineStr">
+        <is>
+          <t>Positionnement sur une primaire à droite ("je n'ai peur d'aucune compétition")</t>
+        </is>
+      </c>
+      <c r="E84" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F84" s="36" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C85" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D85" s="38" t="inlineStr">
+        <is>
+          <t>Opposition à la proposition du RN d'interdire le voile</t>
+        </is>
+      </c>
+      <c r="E85" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F85" s="40" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C86" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="34" t="inlineStr">
+        <is>
+          <t>Appel répété à une primaire de la droite et du centre</t>
+        </is>
+      </c>
+      <c r="E86" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="F86" s="36" t="inlineStr">
+        <is>
+          <t>Lisnard cherche à peser via la revendication de ses parrainages et son insistance sur une primaire, tout en restant peu visible médiatiquement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C87" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" s="38" t="inlineStr">
+        <is>
+          <t>Annonce des 500 promesses de parrainages</t>
+        </is>
+      </c>
+      <c r="E87" s="39" t="n">
+        <v>14</v>
+      </c>
+      <c r="F87" s="40" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C88" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" s="34" t="inlineStr">
+        <is>
+          <t>Obsèques de Philippe Bouvard à Cannes</t>
+        </is>
+      </c>
+      <c r="E88" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F88" s="36" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C89" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D89" s="38" t="inlineStr">
+        <is>
+          <t>Programme (fin des taxes sur l'héritage, délit de séjour illégal, retraites)</t>
+        </is>
+      </c>
+      <c r="E89" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="F89" s="40" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C90" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" s="34" t="inlineStr">
+        <is>
+          <t>Rentrée politique et universités d'été à Cannes (Nouvelle Énergie)</t>
+        </is>
+      </c>
+      <c r="E90" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="F90" s="36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -43168,7 +48994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M59"/>
+  <dimension ref="A2:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -43302,16 +49128,16 @@
         </is>
       </c>
       <c r="I4" s="5" t="n">
-        <v>106.8</v>
+        <v>109.1</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>123.8</v>
+        <v>122.9</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>106.7</v>
+        <v>106.4</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>125.5</v>
+        <v>128.2</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>107.7</v>
@@ -43344,19 +49170,19 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>124.7</v>
+        <v>135.1</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>133.3</v>
+        <v>138.2</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>109.1</v>
+        <v>108.8</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>136</v>
+        <v>139.3</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>113.1</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="6">
@@ -43386,19 +49212,19 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>130.1</v>
+        <v>167.5</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>137.3</v>
+        <v>155.7</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>109.1</v>
+        <v>109.4</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>136.6</v>
+        <v>155.2</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>114.3</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
@@ -43422,6 +49248,26 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>157.1</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>116.6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -44423,16 +50269,16 @@
         <v>22</v>
       </c>
       <c r="C53" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F53" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54">
@@ -44442,7 +50288,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C54" t="n">
         <v>6</v>
@@ -44454,7 +50300,7 @@
         <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55">
@@ -44464,16 +50310,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E55" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F55" t="n">
         <v>33</v>
@@ -44486,19 +50332,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C56" t="n">
         <v>18</v>
       </c>
       <c r="D56" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E56" t="n">
         <v>16</v>
       </c>
       <c r="F56" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57">
@@ -44508,7 +50354,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C57" t="n">
         <v>30</v>
@@ -44517,10 +50363,10 @@
         <v>11</v>
       </c>
       <c r="E57" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F57" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58">
@@ -44530,19 +50376,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C58" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D58" t="n">
         <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F58" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
@@ -44552,19 +50398,41 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>26</v>
+      </c>
+      <c r="F59" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="n">
         <v>0</v>
       </c>
-      <c r="E59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" t="n">
-        <v>4</v>
+      <c r="E60" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
